--- a/Results/Group Analysis/GroupCrossing_YoungAdults_Summary.xlsx
+++ b/Results/Group Analysis/GroupCrossing_YoungAdults_Summary.xlsx
@@ -11,6 +11,8 @@
     <sheet name="SegmentROM_deg" sheetId="4" r:id="rId6"/>
     <sheet name="Spatiotemporal" sheetId="5" r:id="rId7"/>
     <sheet name="PeakTiming_pctGC" sheetId="6" r:id="rId8"/>
+    <sheet name="PeakExcursion_deg" sheetId="7" r:id="rId9"/>
+    <sheet name="PeakDelta_deg" sheetId="8" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
@@ -18,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="116" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="190" uniqueCount="79">
   <si>
     <t>Condition</t>
   </si>
@@ -189,6 +191,72 @@
   </si>
   <si>
     <t>Thigh_SD</t>
+  </si>
+  <si>
+    <t>hip_pk_flex_mean</t>
+  </si>
+  <si>
+    <t>hip_pk_flex_SD</t>
+  </si>
+  <si>
+    <t>knee_pk_flex_mean</t>
+  </si>
+  <si>
+    <t>knee_pk_flex_SD</t>
+  </si>
+  <si>
+    <t>ank_dorsi_mean</t>
+  </si>
+  <si>
+    <t>ank_dorsi_SD</t>
+  </si>
+  <si>
+    <t>ank_plant_mean</t>
+  </si>
+  <si>
+    <t>ank_plant_SD</t>
+  </si>
+  <si>
+    <t>hip_pk_ext_mean</t>
+  </si>
+  <si>
+    <t>hip_pk_ext_SD</t>
+  </si>
+  <si>
+    <t>thigh_fwd_mean</t>
+  </si>
+  <si>
+    <t>thigh_fwd_SD</t>
+  </si>
+  <si>
+    <t>shank_back_mean</t>
+  </si>
+  <si>
+    <t>shank_back_SD</t>
+  </si>
+  <si>
+    <t>foot_toedown_mean</t>
+  </si>
+  <si>
+    <t>foot_toedown_SD</t>
+  </si>
+  <si>
+    <t>thigh_back_mean</t>
+  </si>
+  <si>
+    <t>thigh_back_SD</t>
+  </si>
+  <si>
+    <t>shank_fwd_mean</t>
+  </si>
+  <si>
+    <t>shank_fwd_SD</t>
+  </si>
+  <si>
+    <t>foot_toeup_mean</t>
+  </si>
+  <si>
+    <t>foot_toeup_SD</t>
   </si>
 </sst>
 </file>
@@ -294,37 +362,37 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>21.719999999999999</v>
+        <v>21.52</v>
       </c>
       <c r="C2" s="0">
-        <v>4.9199999999999999</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="D2" s="0">
-        <v>20.27</v>
+        <v>19.359999999999999</v>
       </c>
       <c r="E2" s="0">
-        <v>4.1699999999999999</v>
+        <v>4.5099999999999998</v>
       </c>
       <c r="F2" s="0">
-        <v>18.620000000000001</v>
+        <v>17.66</v>
       </c>
       <c r="G2" s="0">
-        <v>4.5199999999999996</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="H2" s="0">
-        <v>83.239999999999995</v>
+        <v>88.219999999999999</v>
       </c>
       <c r="I2" s="0">
-        <v>16.879999999999999</v>
+        <v>20.280000000000001</v>
       </c>
       <c r="J2" s="0">
-        <v>33.600000000000001</v>
+        <v>32.479999999999997</v>
       </c>
       <c r="K2" s="0">
-        <v>9.8399999999999999</v>
+        <v>9.4600000000000009</v>
       </c>
       <c r="L2" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -332,37 +400,37 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>17.109999999999999</v>
+        <v>18.02</v>
       </c>
       <c r="C3" s="0">
-        <v>8.3900000000000006</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="D3" s="0">
-        <v>40.530000000000001</v>
+        <v>39.869999999999997</v>
       </c>
       <c r="E3" s="0">
-        <v>8.1400000000000006</v>
+        <v>7.6299999999999999</v>
       </c>
       <c r="F3" s="0">
-        <v>16.68</v>
+        <v>17.530000000000001</v>
       </c>
       <c r="G3" s="0">
-        <v>8.4800000000000004</v>
+        <v>8.0700000000000003</v>
       </c>
       <c r="H3" s="0">
-        <v>19.079999999999998</v>
+        <v>20.870000000000001</v>
       </c>
       <c r="I3" s="0">
-        <v>5.3700000000000001</v>
+        <v>6.8099999999999996</v>
       </c>
       <c r="J3" s="0">
-        <v>95.900000000000006</v>
+        <v>97.290000000000006</v>
       </c>
       <c r="K3" s="0">
-        <v>14.890000000000001</v>
+        <v>14.08</v>
       </c>
       <c r="L3" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -370,37 +438,37 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>22.690000000000001</v>
+        <v>22.780000000000001</v>
       </c>
       <c r="C4" s="0">
-        <v>5.4400000000000004</v>
+        <v>4.9699999999999998</v>
       </c>
       <c r="D4" s="0">
-        <v>19.809999999999999</v>
+        <v>18.940000000000001</v>
       </c>
       <c r="E4" s="0">
-        <v>4.4800000000000004</v>
+        <v>4.7000000000000002</v>
       </c>
       <c r="F4" s="0">
-        <v>18.640000000000001</v>
+        <v>17.870000000000001</v>
       </c>
       <c r="G4" s="0">
-        <v>4.4800000000000004</v>
+        <v>4.5700000000000003</v>
       </c>
       <c r="H4" s="0">
-        <v>90.200000000000003</v>
+        <v>91.799999999999997</v>
       </c>
       <c r="I4" s="0">
-        <v>16.75</v>
+        <v>15.859999999999999</v>
       </c>
       <c r="J4" s="0">
-        <v>22.98</v>
+        <v>23.949999999999999</v>
       </c>
       <c r="K4" s="0">
-        <v>6.3399999999999999</v>
+        <v>6.3300000000000001</v>
       </c>
       <c r="L4" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -408,37 +476,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>18.25</v>
+        <v>18.550000000000001</v>
       </c>
       <c r="C5" s="0">
-        <v>8.1600000000000001</v>
+        <v>7.4900000000000002</v>
       </c>
       <c r="D5" s="0">
-        <v>41.590000000000003</v>
+        <v>39.539999999999999</v>
       </c>
       <c r="E5" s="0">
-        <v>8.9700000000000006</v>
+        <v>9.8200000000000003</v>
       </c>
       <c r="F5" s="0">
-        <v>17.670000000000002</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="G5" s="0">
-        <v>8.3499999999999996</v>
+        <v>7.9199999999999999</v>
       </c>
       <c r="H5" s="0">
-        <v>26.850000000000001</v>
+        <v>26.300000000000001</v>
       </c>
       <c r="I5" s="0">
-        <v>10.99</v>
+        <v>10.140000000000001</v>
       </c>
       <c r="J5" s="0">
-        <v>91.799999999999997</v>
+        <v>94.280000000000001</v>
       </c>
       <c r="K5" s="0">
-        <v>19.879999999999999</v>
+        <v>19.309999999999999</v>
       </c>
       <c r="L5" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -446,37 +514,37 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>19.600000000000001</v>
+        <v>18.760000000000002</v>
       </c>
       <c r="C6" s="0">
-        <v>9.3800000000000008</v>
+        <v>8.8399999999999999</v>
       </c>
       <c r="D6" s="0">
-        <v>18.890000000000001</v>
+        <v>17.640000000000001</v>
       </c>
       <c r="E6" s="0">
-        <v>6.1299999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="F6" s="0">
-        <v>16.539999999999999</v>
+        <v>15.359999999999999</v>
       </c>
       <c r="G6" s="0">
-        <v>7.7199999999999998</v>
+        <v>7.71</v>
       </c>
       <c r="H6" s="0">
-        <v>83.959999999999994</v>
+        <v>88.299999999999997</v>
       </c>
       <c r="I6" s="0">
-        <v>22.559999999999999</v>
+        <v>23.59</v>
       </c>
       <c r="J6" s="0">
-        <v>24.440000000000001</v>
+        <v>24.140000000000001</v>
       </c>
       <c r="K6" s="0">
-        <v>7.4500000000000002</v>
+        <v>6.8399999999999999</v>
       </c>
       <c r="L6" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -484,37 +552,37 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>15.75</v>
+        <v>15.449999999999999</v>
       </c>
       <c r="C7" s="0">
-        <v>7.4400000000000004</v>
+        <v>6.8300000000000001</v>
       </c>
       <c r="D7" s="0">
-        <v>36.439999999999998</v>
+        <v>34.579999999999998</v>
       </c>
       <c r="E7" s="0">
-        <v>3.7400000000000002</v>
+        <v>5.9800000000000004</v>
       </c>
       <c r="F7" s="0">
-        <v>15.27</v>
+        <v>14.43</v>
       </c>
       <c r="G7" s="0">
-        <v>7.29</v>
+        <v>7.0099999999999998</v>
       </c>
       <c r="H7" s="0">
-        <v>19.059999999999999</v>
+        <v>20.02</v>
       </c>
       <c r="I7" s="0">
-        <v>6.3799999999999999</v>
+        <v>6.3399999999999999</v>
       </c>
       <c r="J7" s="0">
-        <v>90.620000000000005</v>
+        <v>92.439999999999998</v>
       </c>
       <c r="K7" s="0">
-        <v>26.460000000000001</v>
+        <v>24.620000000000001</v>
       </c>
       <c r="L7" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -522,37 +590,37 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>22.690000000000001</v>
+        <v>24</v>
       </c>
       <c r="C8" s="0">
-        <v>6.2400000000000002</v>
+        <v>6.6699999999999999</v>
       </c>
       <c r="D8" s="0">
-        <v>19.440000000000001</v>
+        <v>20.109999999999999</v>
       </c>
       <c r="E8" s="0">
-        <v>5.8399999999999999</v>
+        <v>5.6200000000000001</v>
       </c>
       <c r="F8" s="0">
-        <v>16.710000000000001</v>
+        <v>17.010000000000002</v>
       </c>
       <c r="G8" s="0">
-        <v>5.6100000000000003</v>
+        <v>5.1799999999999997</v>
       </c>
       <c r="H8" s="0">
-        <v>90.200000000000003</v>
+        <v>90.409999999999997</v>
       </c>
       <c r="I8" s="0">
-        <v>21.899999999999999</v>
+        <v>20</v>
       </c>
       <c r="J8" s="0">
-        <v>22.359999999999999</v>
+        <v>26.289999999999999</v>
       </c>
       <c r="K8" s="0">
-        <v>13.17</v>
+        <v>15.890000000000001</v>
       </c>
       <c r="L8" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -560,37 +628,37 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>20.010000000000002</v>
+        <v>21.239999999999998</v>
       </c>
       <c r="C9" s="0">
-        <v>5.2800000000000002</v>
+        <v>5.8099999999999996</v>
       </c>
       <c r="D9" s="0">
-        <v>42.759999999999998</v>
+        <v>40.659999999999997</v>
       </c>
       <c r="E9" s="0">
-        <v>6.0599999999999996</v>
+        <v>7.8499999999999996</v>
       </c>
       <c r="F9" s="0">
-        <v>17.609999999999999</v>
+        <v>17.809999999999999</v>
       </c>
       <c r="G9" s="0">
-        <v>5.9699999999999998</v>
+        <v>5.4800000000000004</v>
       </c>
       <c r="H9" s="0">
-        <v>20.789999999999999</v>
+        <v>19.969999999999999</v>
       </c>
       <c r="I9" s="0">
-        <v>8.6300000000000008</v>
+        <v>8.1699999999999999</v>
       </c>
       <c r="J9" s="0">
-        <v>90.010000000000005</v>
+        <v>92.239999999999995</v>
       </c>
       <c r="K9" s="0">
-        <v>17.41</v>
+        <v>16.949999999999999</v>
       </c>
       <c r="L9" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -598,37 +666,37 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>23.600000000000001</v>
+        <v>23.210000000000001</v>
       </c>
       <c r="C10" s="0">
-        <v>6.4199999999999999</v>
+        <v>5.9500000000000002</v>
       </c>
       <c r="D10" s="0">
-        <v>22.170000000000002</v>
+        <v>22.010000000000002</v>
       </c>
       <c r="E10" s="0">
-        <v>5.0300000000000002</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="F10" s="0">
-        <v>18.129999999999999</v>
+        <v>17.710000000000001</v>
       </c>
       <c r="G10" s="0">
-        <v>5.6200000000000001</v>
+        <v>5.25</v>
       </c>
       <c r="H10" s="0">
-        <v>85.040000000000006</v>
+        <v>87.75</v>
       </c>
       <c r="I10" s="0">
-        <v>19.129999999999999</v>
+        <v>18.879999999999999</v>
       </c>
       <c r="J10" s="0">
-        <v>19.149999999999999</v>
+        <v>19.390000000000001</v>
       </c>
       <c r="K10" s="0">
-        <v>6.5899999999999999</v>
+        <v>6.0499999999999998</v>
       </c>
       <c r="L10" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -636,37 +704,37 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>18.600000000000001</v>
+        <v>20.899999999999999</v>
       </c>
       <c r="C11" s="0">
-        <v>8.4299999999999997</v>
+        <v>9.8200000000000003</v>
       </c>
       <c r="D11" s="0">
-        <v>41.460000000000001</v>
+        <v>41.149999999999999</v>
       </c>
       <c r="E11" s="0">
-        <v>8.0500000000000007</v>
+        <v>7.3899999999999997</v>
       </c>
       <c r="F11" s="0">
-        <v>15.76</v>
+        <v>17.789999999999999</v>
       </c>
       <c r="G11" s="0">
-        <v>9.3000000000000007</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="H11" s="0">
-        <v>17.809999999999999</v>
+        <v>18.620000000000001</v>
       </c>
       <c r="I11" s="0">
-        <v>5.75</v>
+        <v>5.6699999999999999</v>
       </c>
       <c r="J11" s="0">
-        <v>80.299999999999997</v>
+        <v>83.349999999999994</v>
       </c>
       <c r="K11" s="0">
-        <v>25.07</v>
+        <v>24.27</v>
       </c>
       <c r="L11" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -674,37 +742,37 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>21.199999999999999</v>
+        <v>21.82</v>
       </c>
       <c r="C12" s="0">
-        <v>6.3300000000000001</v>
+        <v>6</v>
       </c>
       <c r="D12" s="0">
-        <v>20.399999999999999</v>
+        <v>20.68</v>
       </c>
       <c r="E12" s="0">
-        <v>4.46</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="F12" s="0">
-        <v>16.530000000000001</v>
+        <v>16.82</v>
       </c>
       <c r="G12" s="0">
-        <v>4.7300000000000004</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="H12" s="0">
-        <v>85.859999999999999</v>
+        <v>87.489999999999995</v>
       </c>
       <c r="I12" s="0">
-        <v>21.120000000000001</v>
+        <v>19.75</v>
       </c>
       <c r="J12" s="0">
-        <v>21.73</v>
+        <v>20.75</v>
       </c>
       <c r="K12" s="0">
-        <v>14.859999999999999</v>
+        <v>13.81</v>
       </c>
       <c r="L12" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -712,37 +780,37 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>20.719999999999999</v>
+        <v>22.609999999999999</v>
       </c>
       <c r="C13" s="0">
-        <v>8.6300000000000008</v>
+        <v>9.3200000000000003</v>
       </c>
       <c r="D13" s="0">
-        <v>41.880000000000003</v>
+        <v>43.189999999999998</v>
       </c>
       <c r="E13" s="0">
-        <v>8.8599999999999994</v>
+        <v>8.8100000000000005</v>
       </c>
       <c r="F13" s="0">
-        <v>17.739999999999998</v>
+        <v>19.16</v>
       </c>
       <c r="G13" s="0">
-        <v>7.7800000000000002</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="H13" s="0">
-        <v>18.25</v>
+        <v>18.460000000000001</v>
       </c>
       <c r="I13" s="0">
-        <v>7.1900000000000004</v>
+        <v>6.5899999999999999</v>
       </c>
       <c r="J13" s="0">
-        <v>88.329999999999998</v>
+        <v>89.109999999999999</v>
       </c>
       <c r="K13" s="0">
-        <v>17.760000000000002</v>
+        <v>16.34</v>
       </c>
       <c r="L13" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -795,25 +863,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>72.599999999999994</v>
+        <v>67.700000000000003</v>
       </c>
       <c r="C2" s="0">
-        <v>53.700000000000003</v>
+        <v>23</v>
       </c>
       <c r="D2" s="0">
-        <v>96.5</v>
+        <v>84.799999999999997</v>
       </c>
       <c r="E2" s="0">
-        <v>92.700000000000003</v>
+        <v>32</v>
       </c>
       <c r="F2" s="0">
-        <v>60.799999999999997</v>
+        <v>61.799999999999997</v>
       </c>
       <c r="G2" s="0">
-        <v>38.200000000000003</v>
+        <v>28</v>
       </c>
       <c r="H2" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -821,25 +889,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>45.700000000000003</v>
+        <v>44</v>
       </c>
       <c r="C3" s="0">
-        <v>9.4000000000000004</v>
+        <v>16</v>
       </c>
       <c r="D3" s="0">
-        <v>72.5</v>
+        <v>72.099999999999994</v>
       </c>
       <c r="E3" s="0">
-        <v>31.5</v>
+        <v>28.199999999999999</v>
       </c>
       <c r="F3" s="0">
-        <v>95.299999999999997</v>
+        <v>94.5</v>
       </c>
       <c r="G3" s="0">
-        <v>61.799999999999997</v>
+        <v>31</v>
       </c>
       <c r="H3" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -847,25 +915,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>80.599999999999994</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="C4" s="0">
-        <v>48.5</v>
+        <v>28</v>
       </c>
       <c r="D4" s="0">
-        <v>100</v>
+        <v>90.200000000000003</v>
       </c>
       <c r="E4" s="0">
-        <v>87.200000000000003</v>
+        <v>37</v>
       </c>
       <c r="F4" s="0">
-        <v>54.200000000000003</v>
+        <v>55.100000000000001</v>
       </c>
       <c r="G4" s="0">
-        <v>37</v>
+        <v>33.899999999999999</v>
       </c>
       <c r="H4" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -873,25 +941,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>51.299999999999997</v>
+        <v>50.5</v>
       </c>
       <c r="C5" s="0">
-        <v>14.199999999999999</v>
+        <v>13.1</v>
       </c>
       <c r="D5" s="0">
-        <v>70.200000000000003</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="E5" s="0">
-        <v>32.899999999999999</v>
+        <v>32.5</v>
       </c>
       <c r="F5" s="0">
-        <v>96.900000000000006</v>
+        <v>98.599999999999994</v>
       </c>
       <c r="G5" s="0">
-        <v>64.599999999999994</v>
+        <v>29</v>
       </c>
       <c r="H5" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -899,25 +967,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>85.5</v>
+        <v>83.5</v>
       </c>
       <c r="C6" s="0">
-        <v>50.600000000000001</v>
+        <v>30</v>
       </c>
       <c r="D6" s="0">
-        <v>105.5</v>
+        <v>96.200000000000003</v>
       </c>
       <c r="E6" s="0">
-        <v>82.200000000000003</v>
+        <v>28</v>
       </c>
       <c r="F6" s="0">
-        <v>55.399999999999999</v>
+        <v>56.899999999999999</v>
       </c>
       <c r="G6" s="0">
-        <v>29.600000000000001</v>
+        <v>27.300000000000001</v>
       </c>
       <c r="H6" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -925,25 +993,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>62.299999999999997</v>
+        <v>60.899999999999999</v>
       </c>
       <c r="C7" s="0">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="D7" s="0">
-        <v>85.200000000000003</v>
+        <v>86.400000000000006</v>
       </c>
       <c r="E7" s="0">
-        <v>20.100000000000001</v>
+        <v>18.199999999999999</v>
       </c>
       <c r="F7" s="0">
-        <v>121.40000000000001</v>
+        <v>118.2</v>
       </c>
       <c r="G7" s="0">
-        <v>50.100000000000001</v>
+        <v>28</v>
       </c>
       <c r="H7" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -951,25 +1019,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>68</v>
+        <v>65.400000000000006</v>
       </c>
       <c r="C8" s="0">
-        <v>51.600000000000001</v>
+        <v>21</v>
       </c>
       <c r="D8" s="0">
-        <v>88.700000000000003</v>
+        <v>81.200000000000003</v>
       </c>
       <c r="E8" s="0">
-        <v>83.5</v>
+        <v>27</v>
       </c>
       <c r="F8" s="0">
-        <v>62.799999999999997</v>
+        <v>63.200000000000003</v>
       </c>
       <c r="G8" s="0">
-        <v>39.100000000000001</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="H8" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -977,25 +1045,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>42.700000000000003</v>
+        <v>42.899999999999999</v>
       </c>
       <c r="C9" s="0">
-        <v>9.4000000000000004</v>
+        <v>8.5999999999999996</v>
       </c>
       <c r="D9" s="0">
-        <v>76.400000000000006</v>
+        <v>77.700000000000003</v>
       </c>
       <c r="E9" s="0">
-        <v>25.5</v>
+        <v>23.600000000000001</v>
       </c>
       <c r="F9" s="0">
-        <v>89.599999999999994</v>
+        <v>91.5</v>
       </c>
       <c r="G9" s="0">
-        <v>58.200000000000003</v>
+        <v>27</v>
       </c>
       <c r="H9" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -1003,25 +1071,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>83.299999999999997</v>
+        <v>80.5</v>
       </c>
       <c r="C10" s="0">
-        <v>44.299999999999997</v>
+        <v>14</v>
       </c>
       <c r="D10" s="0">
-        <v>102.59999999999999</v>
+        <v>94.400000000000006</v>
       </c>
       <c r="E10" s="0">
-        <v>69.5</v>
+        <v>26</v>
       </c>
       <c r="F10" s="0">
-        <v>55.600000000000001</v>
+        <v>55.700000000000003</v>
       </c>
       <c r="G10" s="0">
-        <v>34.399999999999999</v>
+        <v>31.399999999999999</v>
       </c>
       <c r="H10" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -1029,25 +1097,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>51.700000000000003</v>
+        <v>52.899999999999999</v>
       </c>
       <c r="C11" s="0">
-        <v>16.100000000000001</v>
+        <v>15</v>
       </c>
       <c r="D11" s="0">
-        <v>68.599999999999994</v>
+        <v>71.200000000000003</v>
       </c>
       <c r="E11" s="0">
-        <v>26.199999999999999</v>
+        <v>24.899999999999999</v>
       </c>
       <c r="F11" s="0">
-        <v>96.700000000000003</v>
+        <v>96.599999999999994</v>
       </c>
       <c r="G11" s="0">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="H11" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -1055,25 +1123,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>86.599999999999994</v>
+        <v>84.900000000000006</v>
       </c>
       <c r="C12" s="0">
-        <v>53.899999999999999</v>
+        <v>23</v>
       </c>
       <c r="D12" s="0">
-        <v>109.59999999999999</v>
+        <v>100.90000000000001</v>
       </c>
       <c r="E12" s="0">
-        <v>84.799999999999997</v>
+        <v>31</v>
       </c>
       <c r="F12" s="0">
-        <v>65.799999999999997</v>
+        <v>65.700000000000003</v>
       </c>
       <c r="G12" s="0">
-        <v>32.299999999999997</v>
+        <v>29.5</v>
       </c>
       <c r="H12" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1081,25 +1149,25 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>68.599999999999994</v>
+        <v>69.700000000000003</v>
       </c>
       <c r="C13" s="0">
-        <v>19.5</v>
+        <v>17.699999999999999</v>
       </c>
       <c r="D13" s="0">
-        <v>92.400000000000006</v>
+        <v>89.900000000000006</v>
       </c>
       <c r="E13" s="0">
-        <v>29.899999999999999</v>
+        <v>27.399999999999999</v>
       </c>
       <c r="F13" s="0">
-        <v>103.2</v>
+        <v>100.90000000000001</v>
       </c>
       <c r="G13" s="0">
-        <v>60.200000000000003</v>
+        <v>29</v>
       </c>
       <c r="H13" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -1107,25 +1175,25 @@
         <v>24</v>
       </c>
       <c r="B14" s="0">
-        <v>24.5</v>
+        <v>24.300000000000001</v>
       </c>
       <c r="C14" s="0">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="D14" s="0">
-        <v>38.200000000000003</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="E14" s="0">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="F14" s="0">
-        <v>51</v>
+        <v>54.100000000000001</v>
       </c>
       <c r="G14" s="0">
-        <v>26</v>
+        <v>25.199999999999999</v>
       </c>
       <c r="H14" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1178,25 +1246,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>93.400000000000006</v>
+        <v>94.799999999999997</v>
       </c>
       <c r="C2" s="0">
-        <v>13.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="D2" s="0">
-        <v>79.299999999999997</v>
+        <v>80.200000000000003</v>
       </c>
       <c r="E2" s="0">
-        <v>7.2999999999999998</v>
+        <v>7</v>
       </c>
       <c r="F2" s="0">
-        <v>84.200000000000003</v>
+        <v>83.700000000000003</v>
       </c>
       <c r="G2" s="0">
-        <v>11</v>
+        <v>9.9000000000000004</v>
       </c>
       <c r="H2" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -1204,25 +1272,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>114.59999999999999</v>
+        <v>112.40000000000001</v>
       </c>
       <c r="C3" s="0">
-        <v>20.399999999999999</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="D3" s="0">
-        <v>106.2</v>
+        <v>104.90000000000001</v>
       </c>
       <c r="E3" s="0">
-        <v>16.100000000000001</v>
+        <v>15.1</v>
       </c>
       <c r="F3" s="0">
-        <v>60.799999999999997</v>
+        <v>60.399999999999999</v>
       </c>
       <c r="G3" s="0">
-        <v>6.4000000000000004</v>
+        <v>5.7999999999999998</v>
       </c>
       <c r="H3" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -1230,25 +1298,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>90.799999999999997</v>
+        <v>91.5</v>
       </c>
       <c r="C4" s="0">
-        <v>19.5</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="D4" s="0">
-        <v>82.299999999999997</v>
+        <v>82.400000000000006</v>
       </c>
       <c r="E4" s="0">
-        <v>8</v>
+        <v>7.2999999999999998</v>
       </c>
       <c r="F4" s="0">
-        <v>96.5</v>
+        <v>96.099999999999994</v>
       </c>
       <c r="G4" s="0">
-        <v>9.0999999999999996</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="H4" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -1256,25 +1324,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>120.40000000000001</v>
+        <v>119</v>
       </c>
       <c r="C5" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="0">
-        <v>117</v>
+        <v>116.59999999999999</v>
       </c>
       <c r="E5" s="0">
-        <v>13.6</v>
+        <v>12.4</v>
       </c>
       <c r="F5" s="0">
-        <v>62</v>
+        <v>61.799999999999997</v>
       </c>
       <c r="G5" s="0">
-        <v>5.7999999999999998</v>
+        <v>5.2999999999999998</v>
       </c>
       <c r="H5" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -1282,25 +1350,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>84.5</v>
+        <v>85.799999999999997</v>
       </c>
       <c r="C6" s="0">
-        <v>17.600000000000001</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="D6" s="0">
-        <v>83</v>
+        <v>83.099999999999994</v>
       </c>
       <c r="E6" s="0">
-        <v>6.0999999999999996</v>
+        <v>5.5999999999999996</v>
       </c>
       <c r="F6" s="0">
-        <v>103.2</v>
+        <v>103.90000000000001</v>
       </c>
       <c r="G6" s="0">
-        <v>11.5</v>
+        <v>10.4</v>
       </c>
       <c r="H6" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -1308,25 +1376,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>124.40000000000001</v>
+        <v>122</v>
       </c>
       <c r="C7" s="0">
-        <v>21.199999999999999</v>
+        <v>20.300000000000001</v>
       </c>
       <c r="D7" s="0">
-        <v>124.7</v>
+        <v>123.3</v>
       </c>
       <c r="E7" s="0">
-        <v>6.7999999999999998</v>
+        <v>7.2999999999999998</v>
       </c>
       <c r="F7" s="0">
         <v>65.599999999999994</v>
       </c>
       <c r="G7" s="0">
-        <v>7.7000000000000002</v>
+        <v>6.7999999999999998</v>
       </c>
       <c r="H7" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1334,25 +1402,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>98.700000000000003</v>
+        <v>99.299999999999997</v>
       </c>
       <c r="C8" s="0">
-        <v>19.399999999999999</v>
+        <v>17.800000000000001</v>
       </c>
       <c r="D8" s="0">
-        <v>82.200000000000003</v>
+        <v>83</v>
       </c>
       <c r="E8" s="0">
-        <v>7.2000000000000002</v>
+        <v>6.9000000000000004</v>
       </c>
       <c r="F8" s="0">
-        <v>84</v>
+        <v>84.400000000000006</v>
       </c>
       <c r="G8" s="0">
-        <v>10.699999999999999</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="H8" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1360,25 +1428,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>119.7</v>
+        <v>117.59999999999999</v>
       </c>
       <c r="C9" s="0">
-        <v>19.399999999999999</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="D9" s="0">
-        <v>106.90000000000001</v>
+        <v>106.7</v>
       </c>
       <c r="E9" s="0">
-        <v>14.6</v>
+        <v>13.300000000000001</v>
       </c>
       <c r="F9" s="0">
-        <v>61.600000000000001</v>
+        <v>61.399999999999999</v>
       </c>
       <c r="G9" s="0">
-        <v>7.4000000000000004</v>
+        <v>6.7999999999999998</v>
       </c>
       <c r="H9" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -1386,25 +1454,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" s="0">
-        <v>21.199999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="D10" s="0">
-        <v>84.700000000000003</v>
+        <v>84.900000000000006</v>
       </c>
       <c r="E10" s="0">
-        <v>7.0999999999999996</v>
+        <v>6.5</v>
       </c>
       <c r="F10" s="0">
-        <v>97.200000000000003</v>
+        <v>97.700000000000003</v>
       </c>
       <c r="G10" s="0">
-        <v>8.4000000000000004</v>
+        <v>7.7999999999999998</v>
       </c>
       <c r="H10" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -1412,25 +1480,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>119.2</v>
+        <v>117.8</v>
       </c>
       <c r="C11" s="0">
-        <v>17.899999999999999</v>
+        <v>16.800000000000001</v>
       </c>
       <c r="D11" s="0">
-        <v>116.3</v>
+        <v>115.8</v>
       </c>
       <c r="E11" s="0">
-        <v>11.5</v>
+        <v>10.6</v>
       </c>
       <c r="F11" s="0">
-        <v>62.600000000000001</v>
+        <v>63.200000000000003</v>
       </c>
       <c r="G11" s="0">
-        <v>7.2000000000000002</v>
+        <v>6.7999999999999998</v>
       </c>
       <c r="H11" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -1438,25 +1506,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>87.599999999999994</v>
+        <v>86.099999999999994</v>
       </c>
       <c r="C12" s="0">
-        <v>17.699999999999999</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="D12" s="0">
-        <v>82.299999999999997</v>
+        <v>82.599999999999994</v>
       </c>
       <c r="E12" s="0">
-        <v>5.2999999999999998</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F12" s="0">
-        <v>107.09999999999999</v>
+        <v>106.90000000000001</v>
       </c>
       <c r="G12" s="0">
-        <v>10.199999999999999</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="H12" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1464,25 +1532,25 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>129.59999999999999</v>
+        <v>126.90000000000001</v>
       </c>
       <c r="C13" s="0">
         <v>17.5</v>
       </c>
       <c r="D13" s="0">
-        <v>133.80000000000001</v>
+        <v>132.40000000000001</v>
       </c>
       <c r="E13" s="0">
-        <v>11.9</v>
+        <v>11.5</v>
       </c>
       <c r="F13" s="0">
-        <v>68.099999999999994</v>
+        <v>67.900000000000006</v>
       </c>
       <c r="G13" s="0">
-        <v>10.800000000000001</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="H13" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -1490,25 +1558,25 @@
         <v>24</v>
       </c>
       <c r="B14" s="0">
-        <v>92.5</v>
+        <v>92.400000000000006</v>
       </c>
       <c r="C14" s="0">
-        <v>8.5</v>
+        <v>7.7999999999999998</v>
       </c>
       <c r="D14" s="0">
-        <v>74.900000000000006</v>
+        <v>75.200000000000003</v>
       </c>
       <c r="E14" s="0">
-        <v>5.9000000000000004</v>
+        <v>5.5</v>
       </c>
       <c r="F14" s="0">
-        <v>45.299999999999997</v>
+        <v>45.200000000000003</v>
       </c>
       <c r="G14" s="0">
-        <v>4.9000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="H14" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1561,25 +1629,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>160.28999999999999</v>
+        <v>163.46000000000001</v>
       </c>
       <c r="C2" s="0">
-        <v>16.52</v>
+        <v>17.25</v>
       </c>
       <c r="D2" s="0">
-        <v>87.150000000000006</v>
+        <v>86.489999999999995</v>
       </c>
       <c r="E2" s="0">
-        <v>9.5</v>
+        <v>8.8499999999999996</v>
       </c>
       <c r="F2" s="0">
-        <v>1.1100000000000001</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="G2" s="0">
         <v>0.17000000000000001</v>
       </c>
       <c r="H2" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -1587,25 +1655,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>156.61000000000001</v>
+        <v>159.18000000000001</v>
       </c>
       <c r="C3" s="0">
-        <v>23.469999999999999</v>
+        <v>22.469999999999999</v>
       </c>
       <c r="D3" s="0">
-        <v>81.650000000000006</v>
+        <v>82.299999999999997</v>
       </c>
       <c r="E3" s="0">
-        <v>5.04</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F3" s="0">
-        <v>1.05</v>
+        <v>1.0800000000000001</v>
       </c>
       <c r="G3" s="0">
         <v>0.17000000000000001</v>
       </c>
       <c r="H3" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -1613,25 +1681,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>162.41999999999999</v>
+        <v>163.49000000000001</v>
       </c>
       <c r="C4" s="0">
-        <v>34.509999999999998</v>
+        <v>31.629999999999999</v>
       </c>
       <c r="D4" s="0">
-        <v>83.75</v>
+        <v>82.989999999999995</v>
       </c>
       <c r="E4" s="0">
-        <v>6.4299999999999997</v>
+        <v>6.2000000000000002</v>
       </c>
       <c r="F4" s="0">
         <v>1.0900000000000001</v>
       </c>
       <c r="G4" s="0">
-        <v>0.17000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="H4" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -1639,25 +1707,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>156.16</v>
+        <v>158.33000000000001</v>
       </c>
       <c r="C5" s="0">
-        <v>28.690000000000001</v>
+        <v>26.809999999999999</v>
       </c>
       <c r="D5" s="0">
-        <v>77.349999999999994</v>
+        <v>77.650000000000006</v>
       </c>
       <c r="E5" s="0">
-        <v>4.5999999999999996</v>
+        <v>4.2800000000000002</v>
       </c>
       <c r="F5" s="0">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="G5" s="0">
-        <v>0.22</v>
+        <v>0.20999999999999999</v>
       </c>
       <c r="H5" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -1665,25 +1733,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>151.97999999999999</v>
+        <v>155.71000000000001</v>
       </c>
       <c r="C6" s="0">
-        <v>30</v>
+        <v>29.120000000000001</v>
       </c>
       <c r="D6" s="0">
-        <v>79.060000000000002</v>
+        <v>78.219999999999999</v>
       </c>
       <c r="E6" s="0">
-        <v>6.5700000000000003</v>
+        <v>6.4000000000000004</v>
       </c>
       <c r="F6" s="0">
-        <v>0.97999999999999998</v>
+        <v>1</v>
       </c>
       <c r="G6" s="0">
-        <v>0.22</v>
+        <v>0.20999999999999999</v>
       </c>
       <c r="H6" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -1691,25 +1759,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>155.87</v>
+        <v>157.71000000000001</v>
       </c>
       <c r="C7" s="0">
-        <v>39.369999999999997</v>
+        <v>36.270000000000003</v>
       </c>
       <c r="D7" s="0">
-        <v>73.310000000000002</v>
+        <v>73.739999999999995</v>
       </c>
       <c r="E7" s="0">
-        <v>5</v>
+        <v>4.71</v>
       </c>
       <c r="F7" s="0">
-        <v>0.93999999999999995</v>
+        <v>0.95999999999999996</v>
       </c>
       <c r="G7" s="0">
-        <v>0.25</v>
+        <v>0.23000000000000001</v>
       </c>
       <c r="H7" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1717,25 +1785,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>161.22</v>
+        <v>164.16999999999999</v>
       </c>
       <c r="C8" s="0">
-        <v>23.739999999999998</v>
+        <v>23.030000000000001</v>
       </c>
       <c r="D8" s="0">
-        <v>87.370000000000005</v>
+        <v>86.450000000000003</v>
       </c>
       <c r="E8" s="0">
-        <v>9.0299999999999994</v>
+        <v>8.5999999999999996</v>
       </c>
       <c r="F8" s="0">
-        <v>1.1399999999999999</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="G8" s="0">
-        <v>0.20999999999999999</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="H8" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1743,25 +1811,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>158.37</v>
+        <v>160.66999999999999</v>
       </c>
       <c r="C9" s="0">
-        <v>24.460000000000001</v>
+        <v>23.140000000000001</v>
       </c>
       <c r="D9" s="0">
-        <v>83.540000000000006</v>
+        <v>83.799999999999997</v>
       </c>
       <c r="E9" s="0">
-        <v>5.9100000000000001</v>
+        <v>5.4400000000000004</v>
       </c>
       <c r="F9" s="0">
-        <v>1.1100000000000001</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="G9" s="0">
-        <v>0.20999999999999999</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="H9" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -1769,25 +1837,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>150.00999999999999</v>
+        <v>153.50999999999999</v>
       </c>
       <c r="C10" s="0">
-        <v>26.219999999999999</v>
+        <v>25.649999999999999</v>
       </c>
       <c r="D10" s="0">
-        <v>81.480000000000004</v>
+        <v>80.709999999999994</v>
       </c>
       <c r="E10" s="0">
-        <v>4.3099999999999996</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="F10" s="0">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G10" s="0">
-        <v>0.22</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="H10" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -1795,25 +1863,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>144.18000000000001</v>
+        <v>148.66999999999999</v>
       </c>
       <c r="C11" s="0">
-        <v>32.770000000000003</v>
+        <v>32.18</v>
       </c>
       <c r="D11" s="0">
-        <v>80.900000000000006</v>
+        <v>80.439999999999998</v>
       </c>
       <c r="E11" s="0">
-        <v>10.16</v>
+        <v>9.3499999999999996</v>
       </c>
       <c r="F11" s="0">
-        <v>0.93999999999999995</v>
+        <v>0.96999999999999997</v>
       </c>
       <c r="G11" s="0">
-        <v>0.22</v>
+        <v>0.20999999999999999</v>
       </c>
       <c r="H11" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -1821,25 +1889,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>147.05000000000001</v>
+        <v>149.49000000000001</v>
       </c>
       <c r="C12" s="0">
-        <v>38.859999999999999</v>
+        <v>36.049999999999997</v>
       </c>
       <c r="D12" s="0">
-        <v>86.200000000000003</v>
+        <v>84.099999999999994</v>
       </c>
       <c r="E12" s="0">
-        <v>17.670000000000002</v>
+        <v>17.059999999999999</v>
       </c>
       <c r="F12" s="0">
         <v>0.95999999999999996</v>
       </c>
       <c r="G12" s="0">
-        <v>0.20999999999999999</v>
+        <v>0.19</v>
       </c>
       <c r="H12" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1847,25 +1915,25 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>156.94999999999999</v>
+        <v>157.96000000000001</v>
       </c>
       <c r="C13" s="0">
-        <v>28</v>
+        <v>25.699999999999999</v>
       </c>
       <c r="D13" s="0">
-        <v>71.030000000000001</v>
+        <v>70.700000000000003</v>
       </c>
       <c r="E13" s="0">
-        <v>7.2800000000000002</v>
+        <v>6.7000000000000002</v>
       </c>
       <c r="F13" s="0">
-        <v>0.91000000000000003</v>
+        <v>0.92000000000000004</v>
       </c>
       <c r="G13" s="0">
-        <v>0.19</v>
+        <v>0.17000000000000001</v>
       </c>
       <c r="H13" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -1873,25 +1941,25 @@
         <v>24</v>
       </c>
       <c r="B14" s="0">
-        <v>127.84999999999999</v>
+        <v>131.63</v>
       </c>
       <c r="C14" s="0">
-        <v>16.469999999999999</v>
+        <v>18.050000000000001</v>
       </c>
       <c r="D14" s="0">
-        <v>96.549999999999997</v>
+        <v>96.290000000000006</v>
       </c>
       <c r="E14" s="0">
-        <v>4.0899999999999999</v>
+        <v>3.7999999999999998</v>
       </c>
       <c r="F14" s="0">
-        <v>1.03</v>
+        <v>1.0600000000000001</v>
       </c>
       <c r="G14" s="0">
         <v>0.17000000000000001</v>
       </c>
       <c r="H14" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1976,49 +2044,49 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>38.420000000000002</v>
+        <v>40.640000000000001</v>
       </c>
       <c r="C2" s="0">
-        <v>23.640000000000001</v>
+        <v>21.829999999999998</v>
       </c>
       <c r="D2" s="0">
-        <v>52.609999999999999</v>
+        <v>51.079999999999998</v>
       </c>
       <c r="E2" s="0">
-        <v>12.460000000000001</v>
+        <v>11.76</v>
       </c>
       <c r="F2" s="0">
-        <v>44.689999999999998</v>
+        <v>48.049999999999997</v>
       </c>
       <c r="G2" s="0">
-        <v>9.0700000000000003</v>
+        <v>12.16</v>
       </c>
       <c r="H2" s="0">
-        <v>49.299999999999997</v>
+        <v>49.280000000000001</v>
       </c>
       <c r="I2" s="0">
-        <v>4.2999999999999998</v>
+        <v>3.9199999999999999</v>
       </c>
       <c r="J2" s="0">
-        <v>35.409999999999997</v>
+        <v>34.75</v>
       </c>
       <c r="K2" s="0">
-        <v>4.6799999999999997</v>
+        <v>4.6200000000000001</v>
       </c>
       <c r="L2" s="0">
-        <v>36.32</v>
+        <v>35.859999999999999</v>
       </c>
       <c r="M2" s="0">
-        <v>3.5099999999999998</v>
+        <v>3.4300000000000002</v>
       </c>
       <c r="N2" s="0">
-        <v>51.100000000000001</v>
+        <v>51.479999999999997</v>
       </c>
       <c r="O2" s="0">
-        <v>5.4900000000000002</v>
+        <v>5</v>
       </c>
       <c r="P2" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -2026,49 +2094,49 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>34.039999999999999</v>
+        <v>37.329999999999998</v>
       </c>
       <c r="C3" s="0">
-        <v>36.240000000000002</v>
+        <v>33.399999999999999</v>
       </c>
       <c r="D3" s="0">
-        <v>58.420000000000002</v>
+        <v>56.82</v>
       </c>
       <c r="E3" s="0">
-        <v>3.8500000000000001</v>
+        <v>5.21</v>
       </c>
       <c r="F3" s="0">
-        <v>60.439999999999998</v>
+        <v>58.490000000000002</v>
       </c>
       <c r="G3" s="0">
-        <v>16.800000000000001</v>
+        <v>16.18</v>
       </c>
       <c r="H3" s="0">
-        <v>52.350000000000001</v>
+        <v>51.859999999999999</v>
       </c>
       <c r="I3" s="0">
-        <v>6.2800000000000002</v>
+        <v>5.8799999999999999</v>
       </c>
       <c r="J3" s="0">
-        <v>47.840000000000003</v>
+        <v>46.729999999999997</v>
       </c>
       <c r="K3" s="0">
-        <v>5.8300000000000001</v>
+        <v>6.0700000000000003</v>
       </c>
       <c r="L3" s="0">
-        <v>48.909999999999997</v>
+        <v>48.43</v>
       </c>
       <c r="M3" s="0">
-        <v>5.4100000000000001</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="N3" s="0">
-        <v>61.600000000000001</v>
+        <v>60.979999999999997</v>
       </c>
       <c r="O3" s="0">
-        <v>6.6799999999999997</v>
+        <v>6.1600000000000001</v>
       </c>
       <c r="P3" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2076,49 +2144,49 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>40.799999999999997</v>
+        <v>41.909999999999997</v>
       </c>
       <c r="C4" s="0">
-        <v>20.050000000000001</v>
+        <v>18.539999999999999</v>
       </c>
       <c r="D4" s="0">
-        <v>52.060000000000002</v>
+        <v>50.280000000000001</v>
       </c>
       <c r="E4" s="0">
-        <v>24.579999999999998</v>
+        <v>22.920000000000002</v>
       </c>
       <c r="F4" s="0">
-        <v>46.850000000000001</v>
+        <v>49.630000000000003</v>
       </c>
       <c r="G4" s="0">
-        <v>17.030000000000001</v>
+        <v>17.199999999999999</v>
       </c>
       <c r="H4" s="0">
-        <v>50.600000000000001</v>
+        <v>50.060000000000002</v>
       </c>
       <c r="I4" s="0">
-        <v>7.3200000000000003</v>
+        <v>6.8399999999999999</v>
       </c>
       <c r="J4" s="0">
-        <v>33.32</v>
+        <v>32.509999999999998</v>
       </c>
       <c r="K4" s="0">
-        <v>6.1200000000000001</v>
+        <v>5.9900000000000002</v>
       </c>
       <c r="L4" s="0">
-        <v>36.229999999999997</v>
+        <v>35.530000000000001</v>
       </c>
       <c r="M4" s="0">
-        <v>6.7000000000000002</v>
+        <v>6.3899999999999997</v>
       </c>
       <c r="N4" s="0">
-        <v>51.189999999999998</v>
+        <v>50.979999999999997</v>
       </c>
       <c r="O4" s="0">
-        <v>7.4900000000000002</v>
+        <v>6.8600000000000003</v>
       </c>
       <c r="P4" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -2126,49 +2194,49 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>33.18</v>
+        <v>36.310000000000002</v>
       </c>
       <c r="C5" s="0">
-        <v>29.170000000000002</v>
+        <v>27.879999999999999</v>
       </c>
       <c r="D5" s="0">
-        <v>59.359999999999999</v>
+        <v>58.049999999999997</v>
       </c>
       <c r="E5" s="0">
-        <v>7</v>
+        <v>7.2599999999999998</v>
       </c>
       <c r="F5" s="0">
-        <v>52.310000000000002</v>
+        <v>51.990000000000002</v>
       </c>
       <c r="G5" s="0">
-        <v>23.449999999999999</v>
+        <v>21.43</v>
       </c>
       <c r="H5" s="0">
-        <v>55.780000000000001</v>
+        <v>55.020000000000003</v>
       </c>
       <c r="I5" s="0">
-        <v>0.98999999999999999</v>
+        <v>2.21</v>
       </c>
       <c r="J5" s="0">
-        <v>51.390000000000001</v>
+        <v>50.619999999999997</v>
       </c>
       <c r="K5" s="0">
-        <v>1.02</v>
+        <v>2.23</v>
       </c>
       <c r="L5" s="0">
-        <v>52.659999999999997</v>
+        <v>52.020000000000003</v>
       </c>
       <c r="M5" s="0">
-        <v>1.53</v>
+        <v>2.21</v>
       </c>
       <c r="N5" s="0">
-        <v>64.659999999999997</v>
+        <v>63.909999999999997</v>
       </c>
       <c r="O5" s="0">
-        <v>2</v>
+        <v>2.7000000000000002</v>
       </c>
       <c r="P5" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -2176,49 +2244,49 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>31.600000000000001</v>
+        <v>34.509999999999998</v>
       </c>
       <c r="C6" s="0">
-        <v>26.010000000000002</v>
+        <v>24.329999999999998</v>
       </c>
       <c r="D6" s="0">
-        <v>49.530000000000001</v>
+        <v>48.020000000000003</v>
       </c>
       <c r="E6" s="0">
-        <v>13.92</v>
+        <v>12.98</v>
       </c>
       <c r="F6" s="0">
-        <v>36.68</v>
+        <v>40.259999999999998</v>
       </c>
       <c r="G6" s="0">
-        <v>19.559999999999999</v>
+        <v>20.210000000000001</v>
       </c>
       <c r="H6" s="0">
-        <v>47.390000000000001</v>
+        <v>47.68</v>
       </c>
       <c r="I6" s="0">
-        <v>5.5300000000000002</v>
+        <v>5.1100000000000003</v>
       </c>
       <c r="J6" s="0">
-        <v>28.809999999999999</v>
+        <v>28.640000000000001</v>
       </c>
       <c r="K6" s="0">
-        <v>4.8399999999999999</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="L6" s="0">
-        <v>32.799999999999997</v>
+        <v>32.219999999999999</v>
       </c>
       <c r="M6" s="0">
-        <v>6.4000000000000004</v>
+        <v>6.04</v>
       </c>
       <c r="N6" s="0">
-        <v>47.020000000000003</v>
+        <v>47.710000000000001</v>
       </c>
       <c r="O6" s="0">
-        <v>6.6900000000000004</v>
+        <v>6.2199999999999998</v>
       </c>
       <c r="P6" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -2226,49 +2294,49 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>30.75</v>
+        <v>36.109999999999999</v>
       </c>
       <c r="C7" s="0">
-        <v>29.460000000000001</v>
+        <v>29.440000000000001</v>
       </c>
       <c r="D7" s="0">
-        <v>60.780000000000001</v>
+        <v>59.359999999999999</v>
       </c>
       <c r="E7" s="0">
-        <v>8.0500000000000007</v>
+        <v>7.9900000000000002</v>
       </c>
       <c r="F7" s="0">
-        <v>60.939999999999998</v>
+        <v>60.390000000000001</v>
       </c>
       <c r="G7" s="0">
-        <v>16.949999999999999</v>
+        <v>15.539999999999999</v>
       </c>
       <c r="H7" s="0">
-        <v>54.340000000000003</v>
+        <v>54.130000000000003</v>
       </c>
       <c r="I7" s="0">
-        <v>3.1099999999999999</v>
+        <v>2.8900000000000001</v>
       </c>
       <c r="J7" s="0">
-        <v>51.420000000000002</v>
+        <v>51.07</v>
       </c>
       <c r="K7" s="0">
-        <v>2.8799999999999999</v>
+        <v>2.79</v>
       </c>
       <c r="L7" s="0">
-        <v>51.609999999999999</v>
+        <v>51.469999999999999</v>
       </c>
       <c r="M7" s="0">
-        <v>2.8799999999999999</v>
+        <v>2.6600000000000001</v>
       </c>
       <c r="N7" s="0">
-        <v>64.719999999999999</v>
+        <v>64.090000000000003</v>
       </c>
       <c r="O7" s="0">
-        <v>2.96</v>
+        <v>3.0800000000000001</v>
       </c>
       <c r="P7" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -2276,49 +2344,49 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>35.700000000000003</v>
+        <v>37.829999999999998</v>
       </c>
       <c r="C8" s="0">
-        <v>16.890000000000001</v>
+        <v>16.420000000000002</v>
       </c>
       <c r="D8" s="0">
-        <v>42.659999999999997</v>
+        <v>42.18</v>
       </c>
       <c r="E8" s="0">
-        <v>19.100000000000001</v>
+        <v>17.48</v>
       </c>
       <c r="F8" s="0">
-        <v>50.57</v>
+        <v>52.810000000000002</v>
       </c>
       <c r="G8" s="0">
-        <v>15.52</v>
+        <v>15.359999999999999</v>
       </c>
       <c r="H8" s="0">
-        <v>47.920000000000002</v>
+        <v>47.75</v>
       </c>
       <c r="I8" s="0">
-        <v>6.3099999999999996</v>
+        <v>5.7800000000000002</v>
       </c>
       <c r="J8" s="0">
-        <v>34.560000000000002</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="K8" s="0">
-        <v>3.8700000000000001</v>
+        <v>4.2000000000000002</v>
       </c>
       <c r="L8" s="0">
-        <v>36.920000000000002</v>
+        <v>36.119999999999997</v>
       </c>
       <c r="M8" s="0">
-        <v>4.4299999999999997</v>
+        <v>4.5499999999999998</v>
       </c>
       <c r="N8" s="0">
-        <v>52.520000000000003</v>
+        <v>52.310000000000002</v>
       </c>
       <c r="O8" s="0">
-        <v>5.7400000000000002</v>
+        <v>5.2699999999999996</v>
       </c>
       <c r="P8" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -2326,49 +2394,49 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>28.390000000000001</v>
+        <v>33.090000000000003</v>
       </c>
       <c r="C9" s="0">
-        <v>15.58</v>
+        <v>18.890000000000001</v>
       </c>
       <c r="D9" s="0">
-        <v>59.170000000000002</v>
+        <v>57.719999999999999</v>
       </c>
       <c r="E9" s="0">
-        <v>9.7799999999999994</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="F9" s="0">
-        <v>57.090000000000003</v>
+        <v>55.810000000000002</v>
       </c>
       <c r="G9" s="0">
-        <v>14.73</v>
+        <v>13.869999999999999</v>
       </c>
       <c r="H9" s="0">
-        <v>54.560000000000002</v>
+        <v>53.840000000000003</v>
       </c>
       <c r="I9" s="0">
-        <v>1.55</v>
+        <v>2.3599999999999999</v>
       </c>
       <c r="J9" s="0">
-        <v>49.18</v>
+        <v>48.460000000000001</v>
       </c>
       <c r="K9" s="0">
-        <v>3.1200000000000001</v>
+        <v>3.4300000000000002</v>
       </c>
       <c r="L9" s="0">
-        <v>51.210000000000001</v>
+        <v>50.579999999999998</v>
       </c>
       <c r="M9" s="0">
-        <v>2.48</v>
+        <v>2.7999999999999998</v>
       </c>
       <c r="N9" s="0">
-        <v>63.990000000000002</v>
+        <v>63.18</v>
       </c>
       <c r="O9" s="0">
-        <v>2.8399999999999999</v>
+        <v>3.3700000000000001</v>
       </c>
       <c r="P9" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -2376,49 +2444,49 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>34.200000000000003</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="C10" s="0">
-        <v>21.030000000000001</v>
+        <v>20.390000000000001</v>
       </c>
       <c r="D10" s="0">
-        <v>52.969999999999999</v>
+        <v>50.880000000000003</v>
       </c>
       <c r="E10" s="0">
-        <v>23.07</v>
+        <v>21.780000000000001</v>
       </c>
       <c r="F10" s="0">
-        <v>39.5</v>
+        <v>42.579999999999998</v>
       </c>
       <c r="G10" s="0">
-        <v>15.68</v>
+        <v>16.48</v>
       </c>
       <c r="H10" s="0">
-        <v>50.670000000000002</v>
+        <v>50.219999999999999</v>
       </c>
       <c r="I10" s="0">
-        <v>3.6600000000000001</v>
+        <v>3.5499999999999998</v>
       </c>
       <c r="J10" s="0">
-        <v>29.649999999999999</v>
+        <v>29.260000000000002</v>
       </c>
       <c r="K10" s="0">
-        <v>3.9900000000000002</v>
+        <v>3.7799999999999998</v>
       </c>
       <c r="L10" s="0">
-        <v>33.18</v>
+        <v>32.880000000000003</v>
       </c>
       <c r="M10" s="0">
-        <v>4.3700000000000001</v>
+        <v>4.0700000000000003</v>
       </c>
       <c r="N10" s="0">
-        <v>51.609999999999999</v>
+        <v>51.399999999999999</v>
       </c>
       <c r="O10" s="0">
-        <v>4.0999999999999996</v>
+        <v>3.7799999999999998</v>
       </c>
       <c r="P10" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -2426,49 +2494,49 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>29.449999999999999</v>
+        <v>33.640000000000001</v>
       </c>
       <c r="C11" s="0">
-        <v>23.59</v>
+        <v>24.23</v>
       </c>
       <c r="D11" s="0">
-        <v>51.259999999999998</v>
+        <v>51.159999999999997</v>
       </c>
       <c r="E11" s="0">
-        <v>9.3399999999999999</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="F11" s="0">
-        <v>58.189999999999998</v>
+        <v>57.799999999999997</v>
       </c>
       <c r="G11" s="0">
-        <v>17.190000000000001</v>
+        <v>15.73</v>
       </c>
       <c r="H11" s="0">
-        <v>55.630000000000003</v>
+        <v>54.990000000000002</v>
       </c>
       <c r="I11" s="0">
-        <v>1.1699999999999999</v>
+        <v>2</v>
       </c>
       <c r="J11" s="0">
-        <v>53.700000000000003</v>
+        <v>52.659999999999997</v>
       </c>
       <c r="K11" s="0">
-        <v>5.5999999999999996</v>
+        <v>5.8099999999999996</v>
       </c>
       <c r="L11" s="0">
-        <v>54.859999999999999</v>
+        <v>53.899999999999999</v>
       </c>
       <c r="M11" s="0">
-        <v>5.7599999999999998</v>
+        <v>5.8399999999999999</v>
       </c>
       <c r="N11" s="0">
-        <v>66.549999999999997</v>
+        <v>65.560000000000002</v>
       </c>
       <c r="O11" s="0">
-        <v>5.6100000000000003</v>
+        <v>5.75</v>
       </c>
       <c r="P11" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -2476,49 +2544,49 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>49.670000000000002</v>
+        <v>49.899999999999999</v>
       </c>
       <c r="C12" s="0">
-        <v>17.620000000000001</v>
+        <v>15.77</v>
       </c>
       <c r="D12" s="0">
-        <v>48.159999999999997</v>
+        <v>46.869999999999997</v>
       </c>
       <c r="E12" s="0">
-        <v>21.07</v>
+        <v>19.109999999999999</v>
       </c>
       <c r="F12" s="0">
-        <v>44.560000000000002</v>
+        <v>43.799999999999997</v>
       </c>
       <c r="G12" s="0">
-        <v>10.43</v>
+        <v>9.7400000000000002</v>
       </c>
       <c r="H12" s="0">
-        <v>52.039999999999999</v>
+        <v>51.490000000000002</v>
       </c>
       <c r="I12" s="0">
-        <v>8.4499999999999993</v>
+        <v>7.8499999999999996</v>
       </c>
       <c r="J12" s="0">
-        <v>34.509999999999998</v>
+        <v>33.43</v>
       </c>
       <c r="K12" s="0">
-        <v>5.6299999999999999</v>
+        <v>5.8799999999999999</v>
       </c>
       <c r="L12" s="0">
-        <v>38.280000000000001</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="M12" s="0">
-        <v>5.6699999999999999</v>
+        <v>5.7800000000000002</v>
       </c>
       <c r="N12" s="0">
-        <v>56.109999999999999</v>
+        <v>55.100000000000001</v>
       </c>
       <c r="O12" s="0">
-        <v>11.67</v>
+        <v>10.720000000000001</v>
       </c>
       <c r="P12" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -2526,49 +2594,49 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>31.960000000000001</v>
+        <v>38.390000000000001</v>
       </c>
       <c r="C13" s="0">
-        <v>28.920000000000002</v>
+        <v>30.289999999999999</v>
       </c>
       <c r="D13" s="0">
-        <v>62.960000000000001</v>
+        <v>61.280000000000001</v>
       </c>
       <c r="E13" s="0">
-        <v>9.5500000000000007</v>
+        <v>9.4800000000000004</v>
       </c>
       <c r="F13" s="0">
-        <v>56.299999999999997</v>
+        <v>57.189999999999998</v>
       </c>
       <c r="G13" s="0">
-        <v>21.800000000000001</v>
+        <v>20.039999999999999</v>
       </c>
       <c r="H13" s="0">
-        <v>54.990000000000002</v>
+        <v>54.700000000000003</v>
       </c>
       <c r="I13" s="0">
-        <v>3.5899999999999999</v>
+        <v>3.3700000000000001</v>
       </c>
       <c r="J13" s="0">
-        <v>51.659999999999997</v>
+        <v>51.479999999999997</v>
       </c>
       <c r="K13" s="0">
-        <v>2.98</v>
+        <v>2.77</v>
       </c>
       <c r="L13" s="0">
-        <v>52.380000000000003</v>
+        <v>52.130000000000003</v>
       </c>
       <c r="M13" s="0">
-        <v>3</v>
+        <v>2.8199999999999998</v>
       </c>
       <c r="N13" s="0">
-        <v>65.719999999999999</v>
+        <v>65.109999999999999</v>
       </c>
       <c r="O13" s="0">
-        <v>3.8700000000000001</v>
+        <v>3.7599999999999998</v>
       </c>
       <c r="P13" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -2576,49 +2644,2191 @@
         <v>24</v>
       </c>
       <c r="B14" s="0">
-        <v>43.140000000000001</v>
+        <v>45.119999999999997</v>
       </c>
       <c r="C14" s="0">
-        <v>19.98</v>
+        <v>18.98</v>
       </c>
       <c r="D14" s="0">
-        <v>53.810000000000002</v>
+        <v>52.990000000000002</v>
       </c>
       <c r="E14" s="0">
-        <v>10.27</v>
+        <v>9.6199999999999992</v>
       </c>
       <c r="F14" s="0">
-        <v>46.380000000000003</v>
+        <v>47.109999999999999</v>
       </c>
       <c r="G14" s="0">
-        <v>5.79</v>
+        <v>5.6299999999999999</v>
       </c>
       <c r="H14" s="0">
-        <v>56.579999999999998</v>
+        <v>55.859999999999999</v>
       </c>
       <c r="I14" s="0">
-        <v>10.279999999999999</v>
+        <v>9.5800000000000001</v>
       </c>
       <c r="J14" s="0">
-        <v>39.259999999999998</v>
+        <v>38.710000000000001</v>
       </c>
       <c r="K14" s="0">
-        <v>1.28</v>
+        <v>1.8600000000000001</v>
       </c>
       <c r="L14" s="0">
-        <v>40.18</v>
+        <v>39.619999999999997</v>
       </c>
       <c r="M14" s="0">
-        <v>2.2799999999999998</v>
+        <v>2.5600000000000001</v>
       </c>
       <c r="N14" s="0">
-        <v>67.530000000000001</v>
+        <v>67.939999999999998</v>
       </c>
       <c r="O14" s="0">
-        <v>7.9199999999999999</v>
+        <v>7.3099999999999996</v>
       </c>
       <c r="P14" s="0">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:X14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" customWidth="true"/>
+    <col min="2" max="2" width="17.5703125" customWidth="true"/>
+    <col min="3" max="3" width="14.85546875" customWidth="true"/>
+    <col min="4" max="4" width="19.140625" customWidth="true"/>
+    <col min="5" max="5" width="16.42578125" customWidth="true"/>
+    <col min="6" max="6" width="15.7109375" customWidth="true"/>
+    <col min="7" max="7" width="13" customWidth="true"/>
+    <col min="8" max="8" width="15.85546875" customWidth="true"/>
+    <col min="9" max="9" width="13.140625" customWidth="true"/>
+    <col min="10" max="10" width="17" customWidth="true"/>
+    <col min="11" max="11" width="14.28515625" customWidth="true"/>
+    <col min="12" max="12" width="16.140625" customWidth="true"/>
+    <col min="13" max="13" width="13.42578125" customWidth="true"/>
+    <col min="14" max="14" width="17.28515625" customWidth="true"/>
+    <col min="15" max="15" width="14.5703125" customWidth="true"/>
+    <col min="16" max="16" width="19.85546875" customWidth="true"/>
+    <col min="17" max="17" width="17.140625" customWidth="true"/>
+    <col min="18" max="18" width="16.7109375" customWidth="true"/>
+    <col min="19" max="19" width="14" customWidth="true"/>
+    <col min="20" max="20" width="16.7109375" customWidth="true"/>
+    <col min="21" max="21" width="14" customWidth="true"/>
+    <col min="22" max="22" width="17.140625" customWidth="true"/>
+    <col min="23" max="23" width="14.42578125" customWidth="true"/>
+    <col min="24" max="24" width="13.7109375" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M1" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="O1" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="P1" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q1" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="R1" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="S1" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="T1" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="U1" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="V1" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="W1" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="X1" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0">
+        <v>45.530000000000001</v>
+      </c>
+      <c r="C2" s="0">
+        <v>51.189999999999998</v>
+      </c>
+      <c r="D2" s="0">
+        <v>52.960000000000001</v>
+      </c>
+      <c r="E2" s="0">
+        <v>84.890000000000001</v>
+      </c>
+      <c r="F2" s="0">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="G2" s="0">
+        <v>25.870000000000001</v>
+      </c>
+      <c r="H2" s="0">
+        <v>28.140000000000001</v>
+      </c>
+      <c r="I2" s="0">
+        <v>16.809999999999999</v>
+      </c>
+      <c r="J2" s="0">
+        <v>22.16</v>
+      </c>
+      <c r="K2" s="0">
+        <v>8.25</v>
+      </c>
+      <c r="L2" s="0">
+        <v>62.880000000000003</v>
+      </c>
+      <c r="M2" s="0">
+        <v>12.16</v>
+      </c>
+      <c r="N2" s="0">
+        <v>52.009999999999998</v>
+      </c>
+      <c r="O2" s="0">
+        <v>6.5800000000000001</v>
+      </c>
+      <c r="P2" s="0">
+        <v>68.680000000000007</v>
+      </c>
+      <c r="Q2" s="0">
+        <v>7.5199999999999996</v>
+      </c>
+      <c r="R2" s="0">
+        <v>20.850000000000001</v>
+      </c>
+      <c r="S2" s="0">
+        <v>3.3500000000000001</v>
+      </c>
+      <c r="T2" s="0">
+        <v>28.149999999999999</v>
+      </c>
+      <c r="U2" s="0">
+        <v>3.23</v>
+      </c>
+      <c r="V2" s="0">
+        <v>26.140000000000001</v>
+      </c>
+      <c r="W2" s="0">
+        <v>9.6899999999999995</v>
+      </c>
+      <c r="X2" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0">
+        <v>10.08</v>
+      </c>
+      <c r="C3" s="0">
+        <v>7.1799999999999997</v>
+      </c>
+      <c r="D3" s="0">
+        <v>39.649999999999999</v>
+      </c>
+      <c r="E3" s="0">
+        <v>43.479999999999997</v>
+      </c>
+      <c r="F3" s="0">
+        <v>35.810000000000002</v>
+      </c>
+      <c r="G3" s="0">
+        <v>23.859999999999999</v>
+      </c>
+      <c r="H3" s="0">
+        <v>58.700000000000003</v>
+      </c>
+      <c r="I3" s="0">
+        <v>62.829999999999998</v>
+      </c>
+      <c r="J3" s="0">
+        <v>33.939999999999998</v>
+      </c>
+      <c r="K3" s="0">
+        <v>14.17</v>
+      </c>
+      <c r="L3" s="0">
+        <v>35.039999999999999</v>
+      </c>
+      <c r="M3" s="0">
+        <v>6.1299999999999999</v>
+      </c>
+      <c r="N3" s="0">
+        <v>80.659999999999997</v>
+      </c>
+      <c r="O3" s="0">
+        <v>15.5</v>
+      </c>
+      <c r="P3" s="0">
+        <v>86.950000000000003</v>
+      </c>
+      <c r="Q3" s="0">
+        <v>15.35</v>
+      </c>
+      <c r="R3" s="0">
+        <v>25.379999999999999</v>
+      </c>
+      <c r="S3" s="0">
+        <v>5.6100000000000003</v>
+      </c>
+      <c r="T3" s="0">
+        <v>24.260000000000002</v>
+      </c>
+      <c r="U3" s="0">
+        <v>4</v>
+      </c>
+      <c r="V3" s="0">
+        <v>25.489999999999998</v>
+      </c>
+      <c r="W3" s="0">
+        <v>4.9500000000000002</v>
+      </c>
+      <c r="X3" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0">
+        <v>45.18</v>
+      </c>
+      <c r="C4" s="0">
+        <v>48.07</v>
+      </c>
+      <c r="D4" s="0">
+        <v>48.890000000000001</v>
+      </c>
+      <c r="E4" s="0">
+        <v>83.019999999999996</v>
+      </c>
+      <c r="F4" s="0">
+        <v>30.829999999999998</v>
+      </c>
+      <c r="G4" s="0">
+        <v>26.829999999999998</v>
+      </c>
+      <c r="H4" s="0">
+        <v>24.309999999999999</v>
+      </c>
+      <c r="I4" s="0">
+        <v>14.15</v>
+      </c>
+      <c r="J4" s="0">
+        <v>31.699999999999999</v>
+      </c>
+      <c r="K4" s="0">
+        <v>23.260000000000002</v>
+      </c>
+      <c r="L4" s="0">
+        <v>78.170000000000002</v>
+      </c>
+      <c r="M4" s="0">
+        <v>10.18</v>
+      </c>
+      <c r="N4" s="0">
+        <v>53.350000000000001</v>
+      </c>
+      <c r="O4" s="0">
+        <v>6.1500000000000004</v>
+      </c>
+      <c r="P4" s="0">
+        <v>69.170000000000002</v>
+      </c>
+      <c r="Q4" s="0">
+        <v>6.2199999999999998</v>
+      </c>
+      <c r="R4" s="0">
+        <v>18.16</v>
+      </c>
+      <c r="S4" s="0">
+        <v>4.9100000000000001</v>
+      </c>
+      <c r="T4" s="0">
+        <v>29.07</v>
+      </c>
+      <c r="U4" s="0">
+        <v>4.0499999999999998</v>
+      </c>
+      <c r="V4" s="0">
+        <v>22.350000000000001</v>
+      </c>
+      <c r="W4" s="0">
+        <v>15.539999999999999</v>
+      </c>
+      <c r="X4" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0">
+        <v>12.550000000000001</v>
+      </c>
+      <c r="C5" s="0">
+        <v>10.140000000000001</v>
+      </c>
+      <c r="D5" s="0">
+        <v>40.460000000000001</v>
+      </c>
+      <c r="E5" s="0">
+        <v>46.740000000000002</v>
+      </c>
+      <c r="F5" s="0">
+        <v>38.409999999999997</v>
+      </c>
+      <c r="G5" s="0">
+        <v>36.990000000000002</v>
+      </c>
+      <c r="H5" s="0">
+        <v>60.18</v>
+      </c>
+      <c r="I5" s="0">
+        <v>68.090000000000003</v>
+      </c>
+      <c r="J5" s="0">
+        <v>37.829999999999998</v>
+      </c>
+      <c r="K5" s="0">
+        <v>21.620000000000001</v>
+      </c>
+      <c r="L5" s="0">
+        <v>37.740000000000002</v>
+      </c>
+      <c r="M5" s="0">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="N5" s="0">
+        <v>93.290000000000006</v>
+      </c>
+      <c r="O5" s="0">
+        <v>13.69</v>
+      </c>
+      <c r="P5" s="0">
+        <v>93.260000000000005</v>
+      </c>
+      <c r="Q5" s="0">
+        <v>10.970000000000001</v>
+      </c>
+      <c r="R5" s="0">
+        <v>24.289999999999999</v>
+      </c>
+      <c r="S5" s="0">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="T5" s="0">
+        <v>23.350000000000001</v>
+      </c>
+      <c r="U5" s="0">
+        <v>5.2800000000000002</v>
+      </c>
+      <c r="V5" s="0">
+        <v>25.710000000000001</v>
+      </c>
+      <c r="W5" s="0">
+        <v>7.2800000000000002</v>
+      </c>
+      <c r="X5" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0">
+        <v>47.090000000000003</v>
+      </c>
+      <c r="C6" s="0">
+        <v>43</v>
+      </c>
+      <c r="D6" s="0">
+        <v>51.43</v>
+      </c>
+      <c r="E6" s="0">
+        <v>65.609999999999999</v>
+      </c>
+      <c r="F6" s="0">
+        <v>28.920000000000002</v>
+      </c>
+      <c r="G6" s="0">
+        <v>21.780000000000001</v>
+      </c>
+      <c r="H6" s="0">
+        <v>27.969999999999999</v>
+      </c>
+      <c r="I6" s="0">
+        <v>12.35</v>
+      </c>
+      <c r="J6" s="0">
+        <v>36.460000000000001</v>
+      </c>
+      <c r="K6" s="0">
+        <v>17.850000000000001</v>
+      </c>
+      <c r="L6" s="0">
+        <v>82.890000000000001</v>
+      </c>
+      <c r="M6" s="0">
+        <v>9.6400000000000006</v>
+      </c>
+      <c r="N6" s="0">
+        <v>52.950000000000003</v>
+      </c>
+      <c r="O6" s="0">
+        <v>5.9900000000000002</v>
+      </c>
+      <c r="P6" s="0">
+        <v>65.109999999999999</v>
+      </c>
+      <c r="Q6" s="0">
+        <v>9.0700000000000003</v>
+      </c>
+      <c r="R6" s="0">
+        <v>20.960000000000001</v>
+      </c>
+      <c r="S6" s="0">
+        <v>3.02</v>
+      </c>
+      <c r="T6" s="0">
+        <v>30.140000000000001</v>
+      </c>
+      <c r="U6" s="0">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="V6" s="0">
+        <v>20.699999999999999</v>
+      </c>
+      <c r="W6" s="0">
+        <v>12.26</v>
+      </c>
+      <c r="X6" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
         <v>6</v>
+      </c>
+      <c r="B7" s="0">
+        <v>10.24</v>
+      </c>
+      <c r="C7" s="0">
+        <v>7.1200000000000001</v>
+      </c>
+      <c r="D7" s="0">
+        <v>44.969999999999999</v>
+      </c>
+      <c r="E7" s="0">
+        <v>40.159999999999997</v>
+      </c>
+      <c r="F7" s="0">
+        <v>56.43</v>
+      </c>
+      <c r="G7" s="0">
+        <v>51.18</v>
+      </c>
+      <c r="H7" s="0">
+        <v>61.799999999999997</v>
+      </c>
+      <c r="I7" s="0">
+        <v>52.189999999999998</v>
+      </c>
+      <c r="J7" s="0">
+        <v>50.619999999999997</v>
+      </c>
+      <c r="K7" s="0">
+        <v>19.550000000000001</v>
+      </c>
+      <c r="L7" s="0">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="M7" s="0">
+        <v>8.0800000000000001</v>
+      </c>
+      <c r="N7" s="0">
+        <v>101.45999999999999</v>
+      </c>
+      <c r="O7" s="0">
+        <v>11.26</v>
+      </c>
+      <c r="P7" s="0">
+        <v>97.459999999999994</v>
+      </c>
+      <c r="Q7" s="0">
+        <v>13.619999999999999</v>
+      </c>
+      <c r="R7" s="0">
+        <v>25.41</v>
+      </c>
+      <c r="S7" s="0">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="T7" s="0">
+        <v>21.789999999999999</v>
+      </c>
+      <c r="U7" s="0">
+        <v>6.5700000000000003</v>
+      </c>
+      <c r="V7" s="0">
+        <v>24.579999999999998</v>
+      </c>
+      <c r="W7" s="0">
+        <v>9.5</v>
+      </c>
+      <c r="X7" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0">
+        <v>40.829999999999998</v>
+      </c>
+      <c r="C8" s="0">
+        <v>52.659999999999997</v>
+      </c>
+      <c r="D8" s="0">
+        <v>47.310000000000002</v>
+      </c>
+      <c r="E8" s="0">
+        <v>78.200000000000003</v>
+      </c>
+      <c r="F8" s="0">
+        <v>31.140000000000001</v>
+      </c>
+      <c r="G8" s="0">
+        <v>30.329999999999998</v>
+      </c>
+      <c r="H8" s="0">
+        <v>32.100000000000001</v>
+      </c>
+      <c r="I8" s="0">
+        <v>16.300000000000001</v>
+      </c>
+      <c r="J8" s="0">
+        <v>23.640000000000001</v>
+      </c>
+      <c r="K8" s="0">
+        <v>13.35</v>
+      </c>
+      <c r="L8" s="0">
+        <v>66.510000000000005</v>
+      </c>
+      <c r="M8" s="0">
+        <v>9.8399999999999999</v>
+      </c>
+      <c r="N8" s="0">
+        <v>51.700000000000003</v>
+      </c>
+      <c r="O8" s="0">
+        <v>5.6100000000000003</v>
+      </c>
+      <c r="P8" s="0">
+        <v>70.969999999999999</v>
+      </c>
+      <c r="Q8" s="0">
+        <v>6.7400000000000002</v>
+      </c>
+      <c r="R8" s="0">
+        <v>18.02</v>
+      </c>
+      <c r="S8" s="0">
+        <v>2.8300000000000001</v>
+      </c>
+      <c r="T8" s="0">
+        <v>31.300000000000001</v>
+      </c>
+      <c r="U8" s="0">
+        <v>3.8100000000000001</v>
+      </c>
+      <c r="V8" s="0">
+        <v>28.289999999999999</v>
+      </c>
+      <c r="W8" s="0">
+        <v>12.98</v>
+      </c>
+      <c r="X8" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0">
+        <v>13.4</v>
+      </c>
+      <c r="C9" s="0">
+        <v>10.710000000000001</v>
+      </c>
+      <c r="D9" s="0">
+        <v>36.460000000000001</v>
+      </c>
+      <c r="E9" s="0">
+        <v>41.710000000000001</v>
+      </c>
+      <c r="F9" s="0">
+        <v>41.030000000000001</v>
+      </c>
+      <c r="G9" s="0">
+        <v>29.690000000000001</v>
+      </c>
+      <c r="H9" s="0">
+        <v>50.479999999999997</v>
+      </c>
+      <c r="I9" s="0">
+        <v>59.219999999999999</v>
+      </c>
+      <c r="J9" s="0">
+        <v>29.530000000000001</v>
+      </c>
+      <c r="K9" s="0">
+        <v>12.529999999999999</v>
+      </c>
+      <c r="L9" s="0">
+        <v>36.539999999999999</v>
+      </c>
+      <c r="M9" s="0">
+        <v>5.54</v>
+      </c>
+      <c r="N9" s="0">
+        <v>82.299999999999997</v>
+      </c>
+      <c r="O9" s="0">
+        <v>12.83</v>
+      </c>
+      <c r="P9" s="0">
+        <v>91.560000000000002</v>
+      </c>
+      <c r="Q9" s="0">
+        <v>14.81</v>
+      </c>
+      <c r="R9" s="0">
+        <v>24.84</v>
+      </c>
+      <c r="S9" s="0">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="T9" s="0">
+        <v>24.379999999999999</v>
+      </c>
+      <c r="U9" s="0">
+        <v>3.1499999999999999</v>
+      </c>
+      <c r="V9" s="0">
+        <v>26.030000000000001</v>
+      </c>
+      <c r="W9" s="0">
+        <v>7.1600000000000001</v>
+      </c>
+      <c r="X9" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0">
+        <v>49.369999999999997</v>
+      </c>
+      <c r="C10" s="0">
+        <v>49.380000000000003</v>
+      </c>
+      <c r="D10" s="0">
+        <v>52.049999999999997</v>
+      </c>
+      <c r="E10" s="0">
+        <v>73.609999999999999</v>
+      </c>
+      <c r="F10" s="0">
+        <v>31.969999999999999</v>
+      </c>
+      <c r="G10" s="0">
+        <v>25.329999999999998</v>
+      </c>
+      <c r="H10" s="0">
+        <v>23.719999999999999</v>
+      </c>
+      <c r="I10" s="0">
+        <v>10.890000000000001</v>
+      </c>
+      <c r="J10" s="0">
+        <v>30.629999999999999</v>
+      </c>
+      <c r="K10" s="0">
+        <v>15.99</v>
+      </c>
+      <c r="L10" s="0">
+        <v>80.540000000000006</v>
+      </c>
+      <c r="M10" s="0">
+        <v>9.3499999999999996</v>
+      </c>
+      <c r="N10" s="0">
+        <v>53.719999999999999</v>
+      </c>
+      <c r="O10" s="0">
+        <v>5.4800000000000004</v>
+      </c>
+      <c r="P10" s="0">
+        <v>68.349999999999994</v>
+      </c>
+      <c r="Q10" s="0">
+        <v>5.4199999999999999</v>
+      </c>
+      <c r="R10" s="0">
+        <v>17.199999999999999</v>
+      </c>
+      <c r="S10" s="0">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="T10" s="0">
+        <v>31.140000000000001</v>
+      </c>
+      <c r="U10" s="0">
+        <v>3.6000000000000001</v>
+      </c>
+      <c r="V10" s="0">
+        <v>21.690000000000001</v>
+      </c>
+      <c r="W10" s="0">
+        <v>15.52</v>
+      </c>
+      <c r="X10" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0">
+        <v>10.92</v>
+      </c>
+      <c r="C11" s="0">
+        <v>5.9900000000000002</v>
+      </c>
+      <c r="D11" s="0">
+        <v>38.25</v>
+      </c>
+      <c r="E11" s="0">
+        <v>40.950000000000003</v>
+      </c>
+      <c r="F11" s="0">
+        <v>36.560000000000002</v>
+      </c>
+      <c r="G11" s="0">
+        <v>31.629999999999999</v>
+      </c>
+      <c r="H11" s="0">
+        <v>60.009999999999998</v>
+      </c>
+      <c r="I11" s="0">
+        <v>58.759999999999998</v>
+      </c>
+      <c r="J11" s="0">
+        <v>41.799999999999997</v>
+      </c>
+      <c r="K11" s="0">
+        <v>18.199999999999999</v>
+      </c>
+      <c r="L11" s="0">
+        <v>38.439999999999998</v>
+      </c>
+      <c r="M11" s="0">
+        <v>7.0199999999999996</v>
+      </c>
+      <c r="N11" s="0">
+        <v>95.650000000000006</v>
+      </c>
+      <c r="O11" s="0">
+        <v>12.390000000000001</v>
+      </c>
+      <c r="P11" s="0">
+        <v>95.280000000000001</v>
+      </c>
+      <c r="Q11" s="0">
+        <v>13.130000000000001</v>
+      </c>
+      <c r="R11" s="0">
+        <v>24.760000000000002</v>
+      </c>
+      <c r="S11" s="0">
+        <v>5.8099999999999996</v>
+      </c>
+      <c r="T11" s="0">
+        <v>20.18</v>
+      </c>
+      <c r="U11" s="0">
+        <v>5.5800000000000001</v>
+      </c>
+      <c r="V11" s="0">
+        <v>22.510000000000002</v>
+      </c>
+      <c r="W11" s="0">
+        <v>6.0700000000000003</v>
+      </c>
+      <c r="X11" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0">
+        <v>56.890000000000001</v>
+      </c>
+      <c r="C12" s="0">
+        <v>52.420000000000002</v>
+      </c>
+      <c r="D12" s="0">
+        <v>64.719999999999999</v>
+      </c>
+      <c r="E12" s="0">
+        <v>79.579999999999998</v>
+      </c>
+      <c r="F12" s="0">
+        <v>33.890000000000001</v>
+      </c>
+      <c r="G12" s="0">
+        <v>26.98</v>
+      </c>
+      <c r="H12" s="0">
+        <v>31.829999999999998</v>
+      </c>
+      <c r="I12" s="0">
+        <v>11.75</v>
+      </c>
+      <c r="J12" s="0">
+        <v>27.98</v>
+      </c>
+      <c r="K12" s="0">
+        <v>12.35</v>
+      </c>
+      <c r="L12" s="0">
+        <v>88.109999999999999</v>
+      </c>
+      <c r="M12" s="0">
+        <v>8.2100000000000009</v>
+      </c>
+      <c r="N12" s="0">
+        <v>53.340000000000003</v>
+      </c>
+      <c r="O12" s="0">
+        <v>6.5</v>
+      </c>
+      <c r="P12" s="0">
+        <v>68.359999999999999</v>
+      </c>
+      <c r="Q12" s="0">
+        <v>7.8200000000000003</v>
+      </c>
+      <c r="R12" s="0">
+        <v>18.760000000000002</v>
+      </c>
+      <c r="S12" s="0">
+        <v>4.3300000000000001</v>
+      </c>
+      <c r="T12" s="0">
+        <v>29.239999999999998</v>
+      </c>
+      <c r="U12" s="0">
+        <v>4.3799999999999999</v>
+      </c>
+      <c r="V12" s="0">
+        <v>17.77</v>
+      </c>
+      <c r="W12" s="0">
+        <v>12.91</v>
+      </c>
+      <c r="X12" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="C13" s="0">
+        <v>6.8700000000000001</v>
+      </c>
+      <c r="D13" s="0">
+        <v>45.670000000000002</v>
+      </c>
+      <c r="E13" s="0">
+        <v>42.630000000000003</v>
+      </c>
+      <c r="F13" s="0">
+        <v>45.100000000000001</v>
+      </c>
+      <c r="G13" s="0">
+        <v>33.719999999999999</v>
+      </c>
+      <c r="H13" s="0">
+        <v>55.82</v>
+      </c>
+      <c r="I13" s="0">
+        <v>57.799999999999997</v>
+      </c>
+      <c r="J13" s="0">
+        <v>59.759999999999998</v>
+      </c>
+      <c r="K13" s="0">
+        <v>22.280000000000001</v>
+      </c>
+      <c r="L13" s="0">
+        <v>42.329999999999998</v>
+      </c>
+      <c r="M13" s="0">
+        <v>9.3399999999999999</v>
+      </c>
+      <c r="N13" s="0">
+        <v>108.52</v>
+      </c>
+      <c r="O13" s="0">
+        <v>13.279999999999999</v>
+      </c>
+      <c r="P13" s="0">
+        <v>101.37</v>
+      </c>
+      <c r="Q13" s="0">
+        <v>11.24</v>
+      </c>
+      <c r="R13" s="0">
+        <v>25.559999999999999</v>
+      </c>
+      <c r="S13" s="0">
+        <v>2.6800000000000002</v>
+      </c>
+      <c r="T13" s="0">
+        <v>23.890000000000001</v>
+      </c>
+      <c r="U13" s="0">
+        <v>3.8900000000000001</v>
+      </c>
+      <c r="V13" s="0">
+        <v>25.539999999999999</v>
+      </c>
+      <c r="W13" s="0">
+        <v>8.6099999999999994</v>
+      </c>
+      <c r="X13" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="0">
+        <v>12.029999999999999</v>
+      </c>
+      <c r="C14" s="0">
+        <v>3.96</v>
+      </c>
+      <c r="D14" s="0">
+        <v>10.84</v>
+      </c>
+      <c r="E14" s="0">
+        <v>5.9100000000000001</v>
+      </c>
+      <c r="F14" s="0">
+        <v>29.620000000000001</v>
+      </c>
+      <c r="G14" s="0">
+        <v>17.5</v>
+      </c>
+      <c r="H14" s="0">
+        <v>24.52</v>
+      </c>
+      <c r="I14" s="0">
+        <v>13.68</v>
+      </c>
+      <c r="J14" s="0">
+        <v>12.130000000000001</v>
+      </c>
+      <c r="K14" s="0">
+        <v>2.3100000000000001</v>
+      </c>
+      <c r="L14" s="0">
+        <v>26.300000000000001</v>
+      </c>
+      <c r="M14" s="0">
+        <v>3.1299999999999999</v>
+      </c>
+      <c r="N14" s="0">
+        <v>48.450000000000003</v>
+      </c>
+      <c r="O14" s="0">
+        <v>5.21</v>
+      </c>
+      <c r="P14" s="0">
+        <v>68.290000000000006</v>
+      </c>
+      <c r="Q14" s="0">
+        <v>5.8300000000000001</v>
+      </c>
+      <c r="R14" s="0">
+        <v>18.789999999999999</v>
+      </c>
+      <c r="S14" s="0">
+        <v>3.5499999999999998</v>
+      </c>
+      <c r="T14" s="0">
+        <v>26.699999999999999</v>
+      </c>
+      <c r="U14" s="0">
+        <v>2.04</v>
+      </c>
+      <c r="V14" s="0">
+        <v>24.07</v>
+      </c>
+      <c r="W14" s="0">
+        <v>3.3900000000000001</v>
+      </c>
+      <c r="X14" s="0">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:X14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" customWidth="true"/>
+    <col min="2" max="2" width="17.5703125" customWidth="true"/>
+    <col min="3" max="3" width="14.85546875" customWidth="true"/>
+    <col min="4" max="4" width="19.140625" customWidth="true"/>
+    <col min="5" max="5" width="16.42578125" customWidth="true"/>
+    <col min="6" max="6" width="15.7109375" customWidth="true"/>
+    <col min="7" max="7" width="13" customWidth="true"/>
+    <col min="8" max="8" width="15.85546875" customWidth="true"/>
+    <col min="9" max="9" width="13.140625" customWidth="true"/>
+    <col min="10" max="10" width="17" customWidth="true"/>
+    <col min="11" max="11" width="14.28515625" customWidth="true"/>
+    <col min="12" max="12" width="16.140625" customWidth="true"/>
+    <col min="13" max="13" width="13.42578125" customWidth="true"/>
+    <col min="14" max="14" width="17.28515625" customWidth="true"/>
+    <col min="15" max="15" width="14.5703125" customWidth="true"/>
+    <col min="16" max="16" width="19.85546875" customWidth="true"/>
+    <col min="17" max="17" width="17.140625" customWidth="true"/>
+    <col min="18" max="18" width="16.7109375" customWidth="true"/>
+    <col min="19" max="19" width="14" customWidth="true"/>
+    <col min="20" max="20" width="16.7109375" customWidth="true"/>
+    <col min="21" max="21" width="14" customWidth="true"/>
+    <col min="22" max="22" width="17.140625" customWidth="true"/>
+    <col min="23" max="23" width="14.42578125" customWidth="true"/>
+    <col min="24" max="24" width="13.7109375" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M1" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="O1" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="P1" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q1" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="R1" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="S1" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="T1" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="U1" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="V1" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="W1" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="X1" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0">
+        <v>33.020000000000003</v>
+      </c>
+      <c r="C2" s="0">
+        <v>53.109999999999999</v>
+      </c>
+      <c r="D2" s="0">
+        <v>41.130000000000003</v>
+      </c>
+      <c r="E2" s="0">
+        <v>83.709999999999994</v>
+      </c>
+      <c r="F2" s="0">
+        <v>4.0800000000000001</v>
+      </c>
+      <c r="G2" s="0">
+        <v>18.920000000000002</v>
+      </c>
+      <c r="H2" s="0">
+        <v>3.6299999999999999</v>
+      </c>
+      <c r="I2" s="0">
+        <v>13.08</v>
+      </c>
+      <c r="J2" s="0">
+        <v>10.23</v>
+      </c>
+      <c r="K2" s="0">
+        <v>6.75</v>
+      </c>
+      <c r="L2" s="0">
+        <v>36.079999999999998</v>
+      </c>
+      <c r="M2" s="0">
+        <v>9.5800000000000001</v>
+      </c>
+      <c r="N2" s="0">
+        <v>3.5600000000000001</v>
+      </c>
+      <c r="O2" s="0">
+        <v>3.1499999999999999</v>
+      </c>
+      <c r="P2" s="0">
+        <v>0.38</v>
+      </c>
+      <c r="Q2" s="0">
+        <v>4.8300000000000001</v>
+      </c>
+      <c r="R2" s="0">
+        <v>1.49</v>
+      </c>
+      <c r="S2" s="0">
+        <v>2.52</v>
+      </c>
+      <c r="T2" s="0">
+        <v>1.45</v>
+      </c>
+      <c r="U2" s="0">
+        <v>3.4300000000000002</v>
+      </c>
+      <c r="V2" s="0">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="W2" s="0">
+        <v>8.9700000000000006</v>
+      </c>
+      <c r="X2" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0">
+        <v>-2.4399999999999999</v>
+      </c>
+      <c r="C3" s="0">
+        <v>8.1500000000000004</v>
+      </c>
+      <c r="D3" s="0">
+        <v>27.829999999999998</v>
+      </c>
+      <c r="E3" s="0">
+        <v>40.469999999999999</v>
+      </c>
+      <c r="F3" s="0">
+        <v>6.1900000000000004</v>
+      </c>
+      <c r="G3" s="0">
+        <v>21.43</v>
+      </c>
+      <c r="H3" s="0">
+        <v>34.18</v>
+      </c>
+      <c r="I3" s="0">
+        <v>52.140000000000001</v>
+      </c>
+      <c r="J3" s="0">
+        <v>22.010000000000002</v>
+      </c>
+      <c r="K3" s="0">
+        <v>13.300000000000001</v>
+      </c>
+      <c r="L3" s="0">
+        <v>8.2400000000000002</v>
+      </c>
+      <c r="M3" s="0">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="N3" s="0">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="O3" s="0">
+        <v>14.449999999999999</v>
+      </c>
+      <c r="P3" s="0">
+        <v>18.66</v>
+      </c>
+      <c r="Q3" s="0">
+        <v>11.800000000000001</v>
+      </c>
+      <c r="R3" s="0">
+        <v>6.0199999999999996</v>
+      </c>
+      <c r="S3" s="0">
+        <v>4.7400000000000002</v>
+      </c>
+      <c r="T3" s="0">
+        <v>-2.4399999999999999</v>
+      </c>
+      <c r="U3" s="0">
+        <v>3.4100000000000001</v>
+      </c>
+      <c r="V3" s="0">
+        <v>1.4099999999999999</v>
+      </c>
+      <c r="W3" s="0">
+        <v>3.2999999999999998</v>
+      </c>
+      <c r="X3" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0">
+        <v>33.149999999999999</v>
+      </c>
+      <c r="C4" s="0">
+        <v>49.390000000000001</v>
+      </c>
+      <c r="D4" s="0">
+        <v>38.039999999999999</v>
+      </c>
+      <c r="E4" s="0">
+        <v>81.319999999999993</v>
+      </c>
+      <c r="F4" s="0">
+        <v>1.21</v>
+      </c>
+      <c r="G4" s="0">
+        <v>20.420000000000002</v>
+      </c>
+      <c r="H4" s="0">
+        <v>-0.20000000000000001</v>
+      </c>
+      <c r="I4" s="0">
+        <v>14.460000000000001</v>
+      </c>
+      <c r="J4" s="0">
+        <v>19.57</v>
+      </c>
+      <c r="K4" s="0">
+        <v>21.829999999999998</v>
+      </c>
+      <c r="L4" s="0">
+        <v>51.869999999999997</v>
+      </c>
+      <c r="M4" s="0">
+        <v>9.1300000000000008</v>
+      </c>
+      <c r="N4" s="0">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="O4" s="0">
+        <v>3.6699999999999999</v>
+      </c>
+      <c r="P4" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="Q4" s="0">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="R4" s="0">
+        <v>-0.63</v>
+      </c>
+      <c r="S4" s="0">
+        <v>2.5</v>
+      </c>
+      <c r="T4" s="0">
+        <v>2.3700000000000001</v>
+      </c>
+      <c r="U4" s="0">
+        <v>4.9900000000000002</v>
+      </c>
+      <c r="V4" s="0">
+        <v>-1.73</v>
+      </c>
+      <c r="W4" s="0">
+        <v>14.48</v>
+      </c>
+      <c r="X4" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0">
+        <v>0.53000000000000003</v>
+      </c>
+      <c r="C5" s="0">
+        <v>7.8200000000000003</v>
+      </c>
+      <c r="D5" s="0">
+        <v>29.620000000000001</v>
+      </c>
+      <c r="E5" s="0">
+        <v>42.560000000000002</v>
+      </c>
+      <c r="F5" s="0">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="G5" s="0">
+        <v>30.030000000000001</v>
+      </c>
+      <c r="H5" s="0">
+        <v>35.659999999999997</v>
+      </c>
+      <c r="I5" s="0">
+        <v>56.939999999999998</v>
+      </c>
+      <c r="J5" s="0">
+        <v>25.699999999999999</v>
+      </c>
+      <c r="K5" s="0">
+        <v>20.960000000000001</v>
+      </c>
+      <c r="L5" s="0">
+        <v>11.43</v>
+      </c>
+      <c r="M5" s="0">
+        <v>5.0899999999999999</v>
+      </c>
+      <c r="N5" s="0">
+        <v>44.829999999999998</v>
+      </c>
+      <c r="O5" s="0">
+        <v>13.56</v>
+      </c>
+      <c r="P5" s="0">
+        <v>24.960000000000001</v>
+      </c>
+      <c r="Q5" s="0">
+        <v>7.9100000000000001</v>
+      </c>
+      <c r="R5" s="0">
+        <v>5.5</v>
+      </c>
+      <c r="S5" s="0">
+        <v>3.46</v>
+      </c>
+      <c r="T5" s="0">
+        <v>-3.3500000000000001</v>
+      </c>
+      <c r="U5" s="0">
+        <v>4.2599999999999998</v>
+      </c>
+      <c r="V5" s="0">
+        <v>1.6399999999999999</v>
+      </c>
+      <c r="W5" s="0">
+        <v>5.3799999999999999</v>
+      </c>
+      <c r="X5" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0">
+        <v>34.579999999999998</v>
+      </c>
+      <c r="C6" s="0">
+        <v>45.420000000000002</v>
+      </c>
+      <c r="D6" s="0">
+        <v>39.609999999999999</v>
+      </c>
+      <c r="E6" s="0">
+        <v>63.490000000000002</v>
+      </c>
+      <c r="F6" s="0">
+        <v>-0.69999999999999996</v>
+      </c>
+      <c r="G6" s="0">
+        <v>12.31</v>
+      </c>
+      <c r="H6" s="0">
+        <v>3.4500000000000002</v>
+      </c>
+      <c r="I6" s="0">
+        <v>14.859999999999999</v>
+      </c>
+      <c r="J6" s="0">
+        <v>24.530000000000001</v>
+      </c>
+      <c r="K6" s="0">
+        <v>15.67</v>
+      </c>
+      <c r="L6" s="0">
+        <v>56.090000000000003</v>
+      </c>
+      <c r="M6" s="0">
+        <v>7.4900000000000002</v>
+      </c>
+      <c r="N6" s="0">
+        <v>4.4900000000000002</v>
+      </c>
+      <c r="O6" s="0">
+        <v>3.1499999999999999</v>
+      </c>
+      <c r="P6" s="0">
+        <v>-3.1800000000000002</v>
+      </c>
+      <c r="Q6" s="0">
+        <v>11.050000000000001</v>
+      </c>
+      <c r="R6" s="0">
+        <v>1.6000000000000001</v>
+      </c>
+      <c r="S6" s="0">
+        <v>5.5499999999999998</v>
+      </c>
+      <c r="T6" s="0">
+        <v>3.4399999999999999</v>
+      </c>
+      <c r="U6" s="0">
+        <v>5.3799999999999999</v>
+      </c>
+      <c r="V6" s="0">
+        <v>-3.3799999999999999</v>
+      </c>
+      <c r="W6" s="0">
+        <v>12.029999999999999</v>
+      </c>
+      <c r="X6" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0">
+        <v>-2.2799999999999998</v>
+      </c>
+      <c r="C7" s="0">
+        <v>7.8399999999999999</v>
+      </c>
+      <c r="D7" s="0">
+        <v>33.149999999999999</v>
+      </c>
+      <c r="E7" s="0">
+        <v>34.969999999999999</v>
+      </c>
+      <c r="F7" s="0">
+        <v>26.809999999999999</v>
+      </c>
+      <c r="G7" s="0">
+        <v>50.18</v>
+      </c>
+      <c r="H7" s="0">
+        <v>37.280000000000001</v>
+      </c>
+      <c r="I7" s="0">
+        <v>42.219999999999999</v>
+      </c>
+      <c r="J7" s="0">
+        <v>38.689999999999998</v>
+      </c>
+      <c r="K7" s="0">
+        <v>19.609999999999999</v>
+      </c>
+      <c r="L7" s="0">
+        <v>13.4</v>
+      </c>
+      <c r="M7" s="0">
+        <v>6.2000000000000002</v>
+      </c>
+      <c r="N7" s="0">
+        <v>53</v>
+      </c>
+      <c r="O7" s="0">
+        <v>10.460000000000001</v>
+      </c>
+      <c r="P7" s="0">
+        <v>29.170000000000002</v>
+      </c>
+      <c r="Q7" s="0">
+        <v>12.65</v>
+      </c>
+      <c r="R7" s="0">
+        <v>6.0499999999999998</v>
+      </c>
+      <c r="S7" s="0">
+        <v>2.6499999999999999</v>
+      </c>
+      <c r="T7" s="0">
+        <v>-4.9100000000000001</v>
+      </c>
+      <c r="U7" s="0">
+        <v>6.5199999999999996</v>
+      </c>
+      <c r="V7" s="0">
+        <v>0.51000000000000001</v>
+      </c>
+      <c r="W7" s="0">
+        <v>8.2400000000000002</v>
+      </c>
+      <c r="X7" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0">
+        <v>28.809999999999999</v>
+      </c>
+      <c r="C8" s="0">
+        <v>53.130000000000003</v>
+      </c>
+      <c r="D8" s="0">
+        <v>36.460000000000001</v>
+      </c>
+      <c r="E8" s="0">
+        <v>76.219999999999999</v>
+      </c>
+      <c r="F8" s="0">
+        <v>1.52</v>
+      </c>
+      <c r="G8" s="0">
+        <v>20.530000000000001</v>
+      </c>
+      <c r="H8" s="0">
+        <v>7.5899999999999999</v>
+      </c>
+      <c r="I8" s="0">
+        <v>8.6899999999999995</v>
+      </c>
+      <c r="J8" s="0">
+        <v>11.51</v>
+      </c>
+      <c r="K8" s="0">
+        <v>11.609999999999999</v>
+      </c>
+      <c r="L8" s="0">
+        <v>40.210000000000001</v>
+      </c>
+      <c r="M8" s="0">
+        <v>7.0300000000000002</v>
+      </c>
+      <c r="N8" s="0">
+        <v>3.25</v>
+      </c>
+      <c r="O8" s="0">
+        <v>2.6499999999999999</v>
+      </c>
+      <c r="P8" s="0">
+        <v>2.6699999999999999</v>
+      </c>
+      <c r="Q8" s="0">
+        <v>3.0099999999999998</v>
+      </c>
+      <c r="R8" s="0">
+        <v>-0.77000000000000002</v>
+      </c>
+      <c r="S8" s="0">
+        <v>2.8799999999999999</v>
+      </c>
+      <c r="T8" s="0">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="U8" s="0">
+        <v>4.8200000000000003</v>
+      </c>
+      <c r="V8" s="0">
+        <v>4.2199999999999998</v>
+      </c>
+      <c r="W8" s="0">
+        <v>12.85</v>
+      </c>
+      <c r="X8" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0">
+        <v>1.3700000000000001</v>
+      </c>
+      <c r="C9" s="0">
+        <v>9.4299999999999997</v>
+      </c>
+      <c r="D9" s="0">
+        <v>25.620000000000001</v>
+      </c>
+      <c r="E9" s="0">
+        <v>37.609999999999999</v>
+      </c>
+      <c r="F9" s="0">
+        <v>11.41</v>
+      </c>
+      <c r="G9" s="0">
+        <v>27.370000000000001</v>
+      </c>
+      <c r="H9" s="0">
+        <v>25.969999999999999</v>
+      </c>
+      <c r="I9" s="0">
+        <v>49.18</v>
+      </c>
+      <c r="J9" s="0">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="K9" s="0">
+        <v>11.66</v>
+      </c>
+      <c r="L9" s="0">
+        <v>10.24</v>
+      </c>
+      <c r="M9" s="0">
+        <v>4.29</v>
+      </c>
+      <c r="N9" s="0">
+        <v>33.840000000000003</v>
+      </c>
+      <c r="O9" s="0">
+        <v>12.140000000000001</v>
+      </c>
+      <c r="P9" s="0">
+        <v>23.27</v>
+      </c>
+      <c r="Q9" s="0">
+        <v>12.15</v>
+      </c>
+      <c r="R9" s="0">
+        <v>6.04</v>
+      </c>
+      <c r="S9" s="0">
+        <v>3.7400000000000002</v>
+      </c>
+      <c r="T9" s="0">
+        <v>-2.3300000000000001</v>
+      </c>
+      <c r="U9" s="0">
+        <v>3.48</v>
+      </c>
+      <c r="V9" s="0">
+        <v>1.96</v>
+      </c>
+      <c r="W9" s="0">
+        <v>6.2300000000000004</v>
+      </c>
+      <c r="X9" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0">
+        <v>37.340000000000003</v>
+      </c>
+      <c r="C10" s="0">
+        <v>50.979999999999997</v>
+      </c>
+      <c r="D10" s="0">
+        <v>41.210000000000001</v>
+      </c>
+      <c r="E10" s="0">
+        <v>71.140000000000001</v>
+      </c>
+      <c r="F10" s="0">
+        <v>2.3500000000000001</v>
+      </c>
+      <c r="G10" s="0">
+        <v>15.19</v>
+      </c>
+      <c r="H10" s="0">
+        <v>-0.80000000000000004</v>
+      </c>
+      <c r="I10" s="0">
+        <v>13.01</v>
+      </c>
+      <c r="J10" s="0">
+        <v>18.5</v>
+      </c>
+      <c r="K10" s="0">
+        <v>14.029999999999999</v>
+      </c>
+      <c r="L10" s="0">
+        <v>54.229999999999997</v>
+      </c>
+      <c r="M10" s="0">
+        <v>7.5999999999999996</v>
+      </c>
+      <c r="N10" s="0">
+        <v>5.2599999999999998</v>
+      </c>
+      <c r="O10" s="0">
+        <v>1.6200000000000001</v>
+      </c>
+      <c r="P10" s="0">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="Q10" s="0">
+        <v>5.7000000000000002</v>
+      </c>
+      <c r="R10" s="0">
+        <v>-1.5900000000000001</v>
+      </c>
+      <c r="S10" s="0">
+        <v>2.29</v>
+      </c>
+      <c r="T10" s="0">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="U10" s="0">
+        <v>4.4100000000000001</v>
+      </c>
+      <c r="V10" s="0">
+        <v>-2.3799999999999999</v>
+      </c>
+      <c r="W10" s="0">
+        <v>14.31</v>
+      </c>
+      <c r="X10" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="C11" s="0">
+        <v>5.5199999999999996</v>
+      </c>
+      <c r="D11" s="0">
+        <v>27.41</v>
+      </c>
+      <c r="E11" s="0">
+        <v>36.409999999999997</v>
+      </c>
+      <c r="F11" s="0">
+        <v>6.9400000000000004</v>
+      </c>
+      <c r="G11" s="0">
+        <v>29.359999999999999</v>
+      </c>
+      <c r="H11" s="0">
+        <v>35.5</v>
+      </c>
+      <c r="I11" s="0">
+        <v>47.990000000000002</v>
+      </c>
+      <c r="J11" s="0">
+        <v>29.670000000000002</v>
+      </c>
+      <c r="K11" s="0">
+        <v>18.640000000000001</v>
+      </c>
+      <c r="L11" s="0">
+        <v>12.140000000000001</v>
+      </c>
+      <c r="M11" s="0">
+        <v>6.9800000000000004</v>
+      </c>
+      <c r="N11" s="0">
+        <v>47.189999999999998</v>
+      </c>
+      <c r="O11" s="0">
+        <v>11.199999999999999</v>
+      </c>
+      <c r="P11" s="0">
+        <v>26.98</v>
+      </c>
+      <c r="Q11" s="0">
+        <v>10.98</v>
+      </c>
+      <c r="R11" s="0">
+        <v>5.96</v>
+      </c>
+      <c r="S11" s="0">
+        <v>4.5700000000000003</v>
+      </c>
+      <c r="T11" s="0">
+        <v>-6.5199999999999996</v>
+      </c>
+      <c r="U11" s="0">
+        <v>5.7300000000000004</v>
+      </c>
+      <c r="V11" s="0">
+        <v>-1.5600000000000001</v>
+      </c>
+      <c r="W11" s="0">
+        <v>5.6100000000000003</v>
+      </c>
+      <c r="X11" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0">
+        <v>44.380000000000003</v>
+      </c>
+      <c r="C12" s="0">
+        <v>54.880000000000003</v>
+      </c>
+      <c r="D12" s="0">
+        <v>52.890000000000001</v>
+      </c>
+      <c r="E12" s="0">
+        <v>77.819999999999993</v>
+      </c>
+      <c r="F12" s="0">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="G12" s="0">
+        <v>16.629999999999999</v>
+      </c>
+      <c r="H12" s="0">
+        <v>7.3200000000000003</v>
+      </c>
+      <c r="I12" s="0">
+        <v>6.5999999999999996</v>
+      </c>
+      <c r="J12" s="0">
+        <v>16.050000000000001</v>
+      </c>
+      <c r="K12" s="0">
+        <v>10.48</v>
+      </c>
+      <c r="L12" s="0">
+        <v>61.310000000000002</v>
+      </c>
+      <c r="M12" s="0">
+        <v>6.3600000000000003</v>
+      </c>
+      <c r="N12" s="0">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="O12" s="0">
+        <v>3.0899999999999999</v>
+      </c>
+      <c r="P12" s="0">
+        <v>0.059999999999999998</v>
+      </c>
+      <c r="Q12" s="0">
+        <v>5.0099999999999998</v>
+      </c>
+      <c r="R12" s="0">
+        <v>-0.59999999999999998</v>
+      </c>
+      <c r="S12" s="0">
+        <v>3.5800000000000001</v>
+      </c>
+      <c r="T12" s="0">
+        <v>2.54</v>
+      </c>
+      <c r="U12" s="0">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="V12" s="0">
+        <v>-6.2999999999999998</v>
+      </c>
+      <c r="W12" s="0">
+        <v>11.35</v>
+      </c>
+      <c r="X12" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0">
+        <v>-2.5499999999999998</v>
+      </c>
+      <c r="C13" s="0">
+        <v>7.9000000000000004</v>
+      </c>
+      <c r="D13" s="0">
+        <v>33.850000000000001</v>
+      </c>
+      <c r="E13" s="0">
+        <v>39.130000000000003</v>
+      </c>
+      <c r="F13" s="0">
+        <v>15.48</v>
+      </c>
+      <c r="G13" s="0">
+        <v>31.460000000000001</v>
+      </c>
+      <c r="H13" s="0">
+        <v>31.309999999999999</v>
+      </c>
+      <c r="I13" s="0">
+        <v>48.030000000000001</v>
+      </c>
+      <c r="J13" s="0">
+        <v>47.829999999999998</v>
+      </c>
+      <c r="K13" s="0">
+        <v>22.449999999999999</v>
+      </c>
+      <c r="L13" s="0">
+        <v>15.529999999999999</v>
+      </c>
+      <c r="M13" s="0">
+        <v>8.6400000000000006</v>
+      </c>
+      <c r="N13" s="0">
+        <v>60.060000000000002</v>
+      </c>
+      <c r="O13" s="0">
+        <v>13.65</v>
+      </c>
+      <c r="P13" s="0">
+        <v>33.079999999999998</v>
+      </c>
+      <c r="Q13" s="0">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="R13" s="0">
+        <v>6.2000000000000002</v>
+      </c>
+      <c r="S13" s="0">
+        <v>4.3799999999999999</v>
+      </c>
+      <c r="T13" s="0">
+        <v>-2.8199999999999998</v>
+      </c>
+      <c r="U13" s="0">
+        <v>3.5600000000000001</v>
+      </c>
+      <c r="V13" s="0">
+        <v>1.47</v>
+      </c>
+      <c r="W13" s="0">
+        <v>7.0300000000000002</v>
+      </c>
+      <c r="X13" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="0">
+        <v>0</v>
+      </c>
+      <c r="C14" s="0">
+        <v>0</v>
+      </c>
+      <c r="D14" s="0">
+        <v>0</v>
+      </c>
+      <c r="E14" s="0">
+        <v>0</v>
+      </c>
+      <c r="F14" s="0">
+        <v>0</v>
+      </c>
+      <c r="G14" s="0">
+        <v>0</v>
+      </c>
+      <c r="H14" s="0">
+        <v>0</v>
+      </c>
+      <c r="I14" s="0">
+        <v>0</v>
+      </c>
+      <c r="J14" s="0">
+        <v>0</v>
+      </c>
+      <c r="K14" s="0">
+        <v>0</v>
+      </c>
+      <c r="L14" s="0">
+        <v>0</v>
+      </c>
+      <c r="M14" s="0">
+        <v>0</v>
+      </c>
+      <c r="N14" s="0">
+        <v>0</v>
+      </c>
+      <c r="O14" s="0">
+        <v>0</v>
+      </c>
+      <c r="P14" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="0">
+        <v>0</v>
+      </c>
+      <c r="R14" s="0">
+        <v>0</v>
+      </c>
+      <c r="S14" s="0">
+        <v>0</v>
+      </c>
+      <c r="T14" s="0">
+        <v>0</v>
+      </c>
+      <c r="U14" s="0">
+        <v>0</v>
+      </c>
+      <c r="V14" s="0">
+        <v>0</v>
+      </c>
+      <c r="W14" s="0">
+        <v>0</v>
+      </c>
+      <c r="X14" s="0">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Group Analysis/GroupCrossing_YoungAdults_Summary.xlsx
+++ b/Results/Group Analysis/GroupCrossing_YoungAdults_Summary.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="190" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="178" uniqueCount="73">
   <si>
     <t>Condition</t>
   </si>
@@ -197,24 +197,6 @@
   </si>
   <si>
     <t>hip_pk_flex_SD</t>
-  </si>
-  <si>
-    <t>knee_pk_flex_mean</t>
-  </si>
-  <si>
-    <t>knee_pk_flex_SD</t>
-  </si>
-  <si>
-    <t>ank_dorsi_mean</t>
-  </si>
-  <si>
-    <t>ank_dorsi_SD</t>
-  </si>
-  <si>
-    <t>ank_plant_mean</t>
-  </si>
-  <si>
-    <t>ank_plant_SD</t>
   </si>
   <si>
     <t>hip_pk_ext_mean</t>
@@ -2044,10 +2026,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>40.640000000000001</v>
+        <v>45.100000000000001</v>
       </c>
       <c r="C2" s="0">
-        <v>21.829999999999998</v>
+        <v>11.960000000000001</v>
       </c>
       <c r="D2" s="0">
         <v>51.079999999999998</v>
@@ -2094,10 +2076,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>37.329999999999998</v>
+        <v>50.950000000000003</v>
       </c>
       <c r="C3" s="0">
-        <v>33.399999999999999</v>
+        <v>13.01</v>
       </c>
       <c r="D3" s="0">
         <v>56.82</v>
@@ -2144,10 +2126,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>41.909999999999997</v>
+        <v>53.090000000000003</v>
       </c>
       <c r="C4" s="0">
-        <v>18.539999999999999</v>
+        <v>10.33</v>
       </c>
       <c r="D4" s="0">
         <v>50.280000000000001</v>
@@ -2194,10 +2176,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>36.310000000000002</v>
+        <v>56.619999999999997</v>
       </c>
       <c r="C5" s="0">
-        <v>27.879999999999999</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="D5" s="0">
         <v>58.049999999999997</v>
@@ -2244,10 +2226,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>34.509999999999998</v>
+        <v>44.890000000000001</v>
       </c>
       <c r="C6" s="0">
-        <v>24.329999999999998</v>
+        <v>10.52</v>
       </c>
       <c r="D6" s="0">
         <v>48.020000000000003</v>
@@ -2294,10 +2276,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>36.109999999999999</v>
+        <v>58.759999999999998</v>
       </c>
       <c r="C7" s="0">
-        <v>29.440000000000001</v>
+        <v>14.529999999999999</v>
       </c>
       <c r="D7" s="0">
         <v>59.359999999999999</v>
@@ -2344,10 +2326,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>37.829999999999998</v>
+        <v>52</v>
       </c>
       <c r="C8" s="0">
-        <v>16.420000000000002</v>
+        <v>9.6099999999999994</v>
       </c>
       <c r="D8" s="0">
         <v>42.18</v>
@@ -2394,10 +2376,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>33.090000000000003</v>
+        <v>56.729999999999997</v>
       </c>
       <c r="C9" s="0">
-        <v>18.890000000000001</v>
+        <v>5.75</v>
       </c>
       <c r="D9" s="0">
         <v>57.719999999999999</v>
@@ -2444,10 +2426,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>36.799999999999997</v>
+        <v>47.210000000000001</v>
       </c>
       <c r="C10" s="0">
-        <v>20.390000000000001</v>
+        <v>14.039999999999999</v>
       </c>
       <c r="D10" s="0">
         <v>50.880000000000003</v>
@@ -2494,10 +2476,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>33.640000000000001</v>
+        <v>56.299999999999997</v>
       </c>
       <c r="C11" s="0">
-        <v>24.23</v>
+        <v>14.59</v>
       </c>
       <c r="D11" s="0">
         <v>51.159999999999997</v>
@@ -2544,10 +2526,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>49.899999999999999</v>
+        <v>55.68</v>
       </c>
       <c r="C12" s="0">
-        <v>15.77</v>
+        <v>11.300000000000001</v>
       </c>
       <c r="D12" s="0">
         <v>46.869999999999997</v>
@@ -2594,10 +2576,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>38.390000000000001</v>
+        <v>52.530000000000001</v>
       </c>
       <c r="C13" s="0">
-        <v>30.289999999999999</v>
+        <v>10.52</v>
       </c>
       <c r="D13" s="0">
         <v>61.280000000000001</v>
@@ -2644,10 +2626,10 @@
         <v>24</v>
       </c>
       <c r="B14" s="0">
-        <v>45.119999999999997</v>
+        <v>60.030000000000001</v>
       </c>
       <c r="C14" s="0">
-        <v>18.98</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="D14" s="0">
         <v>52.990000000000002</v>
@@ -2695,33 +2677,27 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.140625" customWidth="true"/>
     <col min="2" max="2" width="17.5703125" customWidth="true"/>
     <col min="3" max="3" width="14.85546875" customWidth="true"/>
-    <col min="4" max="4" width="19.140625" customWidth="true"/>
-    <col min="5" max="5" width="16.42578125" customWidth="true"/>
-    <col min="6" max="6" width="15.7109375" customWidth="true"/>
-    <col min="7" max="7" width="13" customWidth="true"/>
-    <col min="8" max="8" width="15.85546875" customWidth="true"/>
-    <col min="9" max="9" width="13.140625" customWidth="true"/>
-    <col min="10" max="10" width="17" customWidth="true"/>
-    <col min="11" max="11" width="14.28515625" customWidth="true"/>
-    <col min="12" max="12" width="16.140625" customWidth="true"/>
-    <col min="13" max="13" width="13.42578125" customWidth="true"/>
-    <col min="14" max="14" width="17.28515625" customWidth="true"/>
-    <col min="15" max="15" width="14.5703125" customWidth="true"/>
-    <col min="16" max="16" width="19.85546875" customWidth="true"/>
-    <col min="17" max="17" width="17.140625" customWidth="true"/>
-    <col min="18" max="18" width="16.7109375" customWidth="true"/>
-    <col min="19" max="19" width="14" customWidth="true"/>
-    <col min="20" max="20" width="16.7109375" customWidth="true"/>
-    <col min="21" max="21" width="14" customWidth="true"/>
-    <col min="22" max="22" width="17.140625" customWidth="true"/>
-    <col min="23" max="23" width="14.42578125" customWidth="true"/>
-    <col min="24" max="24" width="13.7109375" customWidth="true"/>
+    <col min="4" max="4" width="17" customWidth="true"/>
+    <col min="5" max="5" width="14.28515625" customWidth="true"/>
+    <col min="6" max="6" width="16.140625" customWidth="true"/>
+    <col min="7" max="7" width="13.42578125" customWidth="true"/>
+    <col min="8" max="8" width="17.28515625" customWidth="true"/>
+    <col min="9" max="9" width="14.5703125" customWidth="true"/>
+    <col min="10" max="10" width="19.85546875" customWidth="true"/>
+    <col min="11" max="11" width="17.140625" customWidth="true"/>
+    <col min="12" max="12" width="16.7109375" customWidth="true"/>
+    <col min="13" max="13" width="14" customWidth="true"/>
+    <col min="14" max="14" width="16.7109375" customWidth="true"/>
+    <col min="15" max="15" width="14" customWidth="true"/>
+    <col min="16" max="16" width="17.140625" customWidth="true"/>
+    <col min="17" max="17" width="14.42578125" customWidth="true"/>
+    <col min="18" max="18" width="13.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2777,24 +2753,6 @@
         <v>72</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="S1" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="T1" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="U1" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="V1" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="W1" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="X1" s="0" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2803,72 +2761,54 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>45.530000000000001</v>
+        <v>51.68</v>
       </c>
       <c r="C2" s="0">
-        <v>51.189999999999998</v>
+        <v>46.219999999999999</v>
       </c>
       <c r="D2" s="0">
-        <v>52.960000000000001</v>
+        <v>16.010000000000002</v>
       </c>
       <c r="E2" s="0">
-        <v>84.890000000000001</v>
+        <v>10.81</v>
       </c>
       <c r="F2" s="0">
-        <v>33.700000000000003</v>
+        <v>62.880000000000003</v>
       </c>
       <c r="G2" s="0">
-        <v>25.870000000000001</v>
+        <v>12.16</v>
       </c>
       <c r="H2" s="0">
-        <v>28.140000000000001</v>
+        <v>52.009999999999998</v>
       </c>
       <c r="I2" s="0">
-        <v>16.809999999999999</v>
+        <v>6.5800000000000001</v>
       </c>
       <c r="J2" s="0">
-        <v>22.16</v>
+        <v>68.680000000000007</v>
       </c>
       <c r="K2" s="0">
-        <v>8.25</v>
+        <v>7.5199999999999996</v>
       </c>
       <c r="L2" s="0">
-        <v>62.880000000000003</v>
+        <v>20.850000000000001</v>
       </c>
       <c r="M2" s="0">
-        <v>12.16</v>
+        <v>3.3500000000000001</v>
       </c>
       <c r="N2" s="0">
-        <v>52.009999999999998</v>
+        <v>28.149999999999999</v>
       </c>
       <c r="O2" s="0">
-        <v>6.5800000000000001</v>
+        <v>3.23</v>
       </c>
       <c r="P2" s="0">
-        <v>68.680000000000007</v>
+        <v>26.140000000000001</v>
       </c>
       <c r="Q2" s="0">
-        <v>7.5199999999999996</v>
+        <v>9.6899999999999995</v>
       </c>
       <c r="R2" s="0">
-        <v>20.850000000000001</v>
-      </c>
-      <c r="S2" s="0">
-        <v>3.3500000000000001</v>
-      </c>
-      <c r="T2" s="0">
-        <v>28.149999999999999</v>
-      </c>
-      <c r="U2" s="0">
-        <v>3.23</v>
-      </c>
-      <c r="V2" s="0">
-        <v>26.140000000000001</v>
-      </c>
-      <c r="W2" s="0">
-        <v>9.6899999999999995</v>
-      </c>
-      <c r="X2" s="0">
         <v>7</v>
       </c>
     </row>
@@ -2877,72 +2817,54 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>10.08</v>
+        <v>34.530000000000001</v>
       </c>
       <c r="C3" s="0">
-        <v>7.1799999999999997</v>
+        <v>13.34</v>
       </c>
       <c r="D3" s="0">
-        <v>39.649999999999999</v>
+        <v>9.4900000000000002</v>
       </c>
       <c r="E3" s="0">
-        <v>43.479999999999997</v>
+        <v>6.3099999999999996</v>
       </c>
       <c r="F3" s="0">
-        <v>35.810000000000002</v>
+        <v>35.039999999999999</v>
       </c>
       <c r="G3" s="0">
-        <v>23.859999999999999</v>
+        <v>6.1299999999999999</v>
       </c>
       <c r="H3" s="0">
-        <v>58.700000000000003</v>
+        <v>80.659999999999997</v>
       </c>
       <c r="I3" s="0">
-        <v>62.829999999999998</v>
+        <v>15.5</v>
       </c>
       <c r="J3" s="0">
-        <v>33.939999999999998</v>
+        <v>86.950000000000003</v>
       </c>
       <c r="K3" s="0">
-        <v>14.17</v>
+        <v>15.35</v>
       </c>
       <c r="L3" s="0">
-        <v>35.039999999999999</v>
+        <v>25.379999999999999</v>
       </c>
       <c r="M3" s="0">
-        <v>6.1299999999999999</v>
+        <v>5.6100000000000003</v>
       </c>
       <c r="N3" s="0">
-        <v>80.659999999999997</v>
+        <v>24.260000000000002</v>
       </c>
       <c r="O3" s="0">
-        <v>15.5</v>
+        <v>4</v>
       </c>
       <c r="P3" s="0">
-        <v>86.950000000000003</v>
+        <v>25.489999999999998</v>
       </c>
       <c r="Q3" s="0">
-        <v>15.35</v>
+        <v>4.9500000000000002</v>
       </c>
       <c r="R3" s="0">
-        <v>25.379999999999999</v>
-      </c>
-      <c r="S3" s="0">
-        <v>5.6100000000000003</v>
-      </c>
-      <c r="T3" s="0">
-        <v>24.260000000000002</v>
-      </c>
-      <c r="U3" s="0">
-        <v>4</v>
-      </c>
-      <c r="V3" s="0">
-        <v>25.489999999999998</v>
-      </c>
-      <c r="W3" s="0">
-        <v>4.9500000000000002</v>
-      </c>
-      <c r="X3" s="0">
         <v>7</v>
       </c>
     </row>
@@ -2951,72 +2873,54 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>45.18</v>
+        <v>57.960000000000001</v>
       </c>
       <c r="C4" s="0">
-        <v>48.07</v>
+        <v>45.07</v>
       </c>
       <c r="D4" s="0">
-        <v>48.890000000000001</v>
+        <v>18.920000000000002</v>
       </c>
       <c r="E4" s="0">
-        <v>83.019999999999996</v>
+        <v>6.0999999999999996</v>
       </c>
       <c r="F4" s="0">
-        <v>30.829999999999998</v>
+        <v>78.170000000000002</v>
       </c>
       <c r="G4" s="0">
-        <v>26.829999999999998</v>
+        <v>10.18</v>
       </c>
       <c r="H4" s="0">
-        <v>24.309999999999999</v>
+        <v>53.350000000000001</v>
       </c>
       <c r="I4" s="0">
-        <v>14.15</v>
+        <v>6.1500000000000004</v>
       </c>
       <c r="J4" s="0">
-        <v>31.699999999999999</v>
+        <v>69.170000000000002</v>
       </c>
       <c r="K4" s="0">
-        <v>23.260000000000002</v>
+        <v>6.2199999999999998</v>
       </c>
       <c r="L4" s="0">
-        <v>78.170000000000002</v>
+        <v>18.16</v>
       </c>
       <c r="M4" s="0">
-        <v>10.18</v>
+        <v>4.9100000000000001</v>
       </c>
       <c r="N4" s="0">
-        <v>53.350000000000001</v>
+        <v>29.07</v>
       </c>
       <c r="O4" s="0">
-        <v>6.1500000000000004</v>
+        <v>4.0499999999999998</v>
       </c>
       <c r="P4" s="0">
-        <v>69.170000000000002</v>
+        <v>22.350000000000001</v>
       </c>
       <c r="Q4" s="0">
-        <v>6.2199999999999998</v>
+        <v>15.539999999999999</v>
       </c>
       <c r="R4" s="0">
-        <v>18.16</v>
-      </c>
-      <c r="S4" s="0">
-        <v>4.9100000000000001</v>
-      </c>
-      <c r="T4" s="0">
-        <v>29.07</v>
-      </c>
-      <c r="U4" s="0">
-        <v>4.0499999999999998</v>
-      </c>
-      <c r="V4" s="0">
-        <v>22.350000000000001</v>
-      </c>
-      <c r="W4" s="0">
-        <v>15.539999999999999</v>
-      </c>
-      <c r="X4" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3025,72 +2929,54 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>12.550000000000001</v>
+        <v>41.700000000000003</v>
       </c>
       <c r="C5" s="0">
-        <v>10.140000000000001</v>
+        <v>16.289999999999999</v>
       </c>
       <c r="D5" s="0">
-        <v>40.460000000000001</v>
+        <v>8.6799999999999997</v>
       </c>
       <c r="E5" s="0">
-        <v>46.740000000000002</v>
+        <v>6.46</v>
       </c>
       <c r="F5" s="0">
-        <v>38.409999999999997</v>
+        <v>37.740000000000002</v>
       </c>
       <c r="G5" s="0">
-        <v>36.990000000000002</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="H5" s="0">
-        <v>60.18</v>
+        <v>93.290000000000006</v>
       </c>
       <c r="I5" s="0">
-        <v>68.090000000000003</v>
+        <v>13.69</v>
       </c>
       <c r="J5" s="0">
-        <v>37.829999999999998</v>
+        <v>93.260000000000005</v>
       </c>
       <c r="K5" s="0">
-        <v>21.620000000000001</v>
+        <v>10.970000000000001</v>
       </c>
       <c r="L5" s="0">
-        <v>37.740000000000002</v>
+        <v>24.289999999999999</v>
       </c>
       <c r="M5" s="0">
-        <v>4.7699999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N5" s="0">
-        <v>93.290000000000006</v>
+        <v>23.350000000000001</v>
       </c>
       <c r="O5" s="0">
-        <v>13.69</v>
+        <v>5.2800000000000002</v>
       </c>
       <c r="P5" s="0">
-        <v>93.260000000000005</v>
+        <v>25.710000000000001</v>
       </c>
       <c r="Q5" s="0">
-        <v>10.970000000000001</v>
+        <v>7.2800000000000002</v>
       </c>
       <c r="R5" s="0">
-        <v>24.289999999999999</v>
-      </c>
-      <c r="S5" s="0">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="T5" s="0">
-        <v>23.350000000000001</v>
-      </c>
-      <c r="U5" s="0">
-        <v>5.2800000000000002</v>
-      </c>
-      <c r="V5" s="0">
-        <v>25.710000000000001</v>
-      </c>
-      <c r="W5" s="0">
-        <v>7.2800000000000002</v>
-      </c>
-      <c r="X5" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3099,72 +2985,54 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>47.090000000000003</v>
+        <v>58.670000000000002</v>
       </c>
       <c r="C6" s="0">
-        <v>43</v>
+        <v>33.840000000000003</v>
       </c>
       <c r="D6" s="0">
-        <v>51.43</v>
+        <v>24.879999999999999</v>
       </c>
       <c r="E6" s="0">
-        <v>65.609999999999999</v>
+        <v>20.129999999999999</v>
       </c>
       <c r="F6" s="0">
-        <v>28.920000000000002</v>
+        <v>82.890000000000001</v>
       </c>
       <c r="G6" s="0">
-        <v>21.780000000000001</v>
+        <v>9.6400000000000006</v>
       </c>
       <c r="H6" s="0">
-        <v>27.969999999999999</v>
+        <v>52.950000000000003</v>
       </c>
       <c r="I6" s="0">
-        <v>12.35</v>
+        <v>5.9900000000000002</v>
       </c>
       <c r="J6" s="0">
-        <v>36.460000000000001</v>
+        <v>65.109999999999999</v>
       </c>
       <c r="K6" s="0">
-        <v>17.850000000000001</v>
+        <v>9.0700000000000003</v>
       </c>
       <c r="L6" s="0">
-        <v>82.890000000000001</v>
+        <v>20.960000000000001</v>
       </c>
       <c r="M6" s="0">
-        <v>9.6400000000000006</v>
+        <v>3.02</v>
       </c>
       <c r="N6" s="0">
-        <v>52.950000000000003</v>
+        <v>30.140000000000001</v>
       </c>
       <c r="O6" s="0">
-        <v>5.9900000000000002</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="P6" s="0">
-        <v>65.109999999999999</v>
+        <v>20.699999999999999</v>
       </c>
       <c r="Q6" s="0">
-        <v>9.0700000000000003</v>
+        <v>12.26</v>
       </c>
       <c r="R6" s="0">
-        <v>20.960000000000001</v>
-      </c>
-      <c r="S6" s="0">
-        <v>3.02</v>
-      </c>
-      <c r="T6" s="0">
-        <v>30.140000000000001</v>
-      </c>
-      <c r="U6" s="0">
-        <v>4.6500000000000004</v>
-      </c>
-      <c r="V6" s="0">
-        <v>20.699999999999999</v>
-      </c>
-      <c r="W6" s="0">
-        <v>12.26</v>
-      </c>
-      <c r="X6" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3173,72 +3041,54 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>10.24</v>
+        <v>44.329999999999998</v>
       </c>
       <c r="C7" s="0">
-        <v>7.1200000000000001</v>
+        <v>26.75</v>
       </c>
       <c r="D7" s="0">
-        <v>44.969999999999999</v>
+        <v>16.530000000000001</v>
       </c>
       <c r="E7" s="0">
-        <v>40.159999999999997</v>
+        <v>15.25</v>
       </c>
       <c r="F7" s="0">
-        <v>56.43</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="G7" s="0">
-        <v>51.18</v>
+        <v>8.0800000000000001</v>
       </c>
       <c r="H7" s="0">
-        <v>61.799999999999997</v>
+        <v>101.45999999999999</v>
       </c>
       <c r="I7" s="0">
-        <v>52.189999999999998</v>
+        <v>11.26</v>
       </c>
       <c r="J7" s="0">
-        <v>50.619999999999997</v>
+        <v>97.459999999999994</v>
       </c>
       <c r="K7" s="0">
-        <v>19.550000000000001</v>
+        <v>13.619999999999999</v>
       </c>
       <c r="L7" s="0">
-        <v>40.200000000000003</v>
+        <v>25.41</v>
       </c>
       <c r="M7" s="0">
-        <v>8.0800000000000001</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="N7" s="0">
-        <v>101.45999999999999</v>
+        <v>21.789999999999999</v>
       </c>
       <c r="O7" s="0">
-        <v>11.26</v>
+        <v>6.5700000000000003</v>
       </c>
       <c r="P7" s="0">
-        <v>97.459999999999994</v>
+        <v>24.579999999999998</v>
       </c>
       <c r="Q7" s="0">
-        <v>13.619999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="R7" s="0">
-        <v>25.41</v>
-      </c>
-      <c r="S7" s="0">
-        <v>4.3099999999999996</v>
-      </c>
-      <c r="T7" s="0">
-        <v>21.789999999999999</v>
-      </c>
-      <c r="U7" s="0">
-        <v>6.5700000000000003</v>
-      </c>
-      <c r="V7" s="0">
-        <v>24.579999999999998</v>
-      </c>
-      <c r="W7" s="0">
-        <v>9.5</v>
-      </c>
-      <c r="X7" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3247,72 +3097,54 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>40.829999999999998</v>
+        <v>54.350000000000001</v>
       </c>
       <c r="C8" s="0">
-        <v>52.659999999999997</v>
+        <v>43.920000000000002</v>
       </c>
       <c r="D8" s="0">
-        <v>47.310000000000002</v>
+        <v>10.119999999999999</v>
       </c>
       <c r="E8" s="0">
-        <v>78.200000000000003</v>
+        <v>7.3499999999999996</v>
       </c>
       <c r="F8" s="0">
-        <v>31.140000000000001</v>
+        <v>66.510000000000005</v>
       </c>
       <c r="G8" s="0">
-        <v>30.329999999999998</v>
+        <v>9.8399999999999999</v>
       </c>
       <c r="H8" s="0">
-        <v>32.100000000000001</v>
+        <v>51.700000000000003</v>
       </c>
       <c r="I8" s="0">
-        <v>16.300000000000001</v>
+        <v>5.6100000000000003</v>
       </c>
       <c r="J8" s="0">
-        <v>23.640000000000001</v>
+        <v>70.969999999999999</v>
       </c>
       <c r="K8" s="0">
-        <v>13.35</v>
+        <v>6.7400000000000002</v>
       </c>
       <c r="L8" s="0">
-        <v>66.510000000000005</v>
+        <v>18.02</v>
       </c>
       <c r="M8" s="0">
-        <v>9.8399999999999999</v>
+        <v>2.8300000000000001</v>
       </c>
       <c r="N8" s="0">
-        <v>51.700000000000003</v>
+        <v>31.300000000000001</v>
       </c>
       <c r="O8" s="0">
-        <v>5.6100000000000003</v>
+        <v>3.8100000000000001</v>
       </c>
       <c r="P8" s="0">
-        <v>70.969999999999999</v>
+        <v>28.289999999999999</v>
       </c>
       <c r="Q8" s="0">
-        <v>6.7400000000000002</v>
+        <v>12.98</v>
       </c>
       <c r="R8" s="0">
-        <v>18.02</v>
-      </c>
-      <c r="S8" s="0">
-        <v>2.8300000000000001</v>
-      </c>
-      <c r="T8" s="0">
-        <v>31.300000000000001</v>
-      </c>
-      <c r="U8" s="0">
-        <v>3.8100000000000001</v>
-      </c>
-      <c r="V8" s="0">
-        <v>28.289999999999999</v>
-      </c>
-      <c r="W8" s="0">
-        <v>12.98</v>
-      </c>
-      <c r="X8" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3321,72 +3153,54 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>13.4</v>
+        <v>31.719999999999999</v>
       </c>
       <c r="C9" s="0">
-        <v>10.710000000000001</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="D9" s="0">
-        <v>36.460000000000001</v>
+        <v>11.210000000000001</v>
       </c>
       <c r="E9" s="0">
-        <v>41.710000000000001</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="F9" s="0">
-        <v>41.030000000000001</v>
+        <v>36.539999999999999</v>
       </c>
       <c r="G9" s="0">
-        <v>29.690000000000001</v>
+        <v>5.54</v>
       </c>
       <c r="H9" s="0">
-        <v>50.479999999999997</v>
+        <v>82.299999999999997</v>
       </c>
       <c r="I9" s="0">
-        <v>59.219999999999999</v>
+        <v>12.83</v>
       </c>
       <c r="J9" s="0">
-        <v>29.530000000000001</v>
+        <v>91.560000000000002</v>
       </c>
       <c r="K9" s="0">
-        <v>12.529999999999999</v>
+        <v>14.81</v>
       </c>
       <c r="L9" s="0">
-        <v>36.539999999999999</v>
+        <v>24.84</v>
       </c>
       <c r="M9" s="0">
-        <v>5.54</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="N9" s="0">
-        <v>82.299999999999997</v>
+        <v>24.379999999999999</v>
       </c>
       <c r="O9" s="0">
-        <v>12.83</v>
+        <v>3.1499999999999999</v>
       </c>
       <c r="P9" s="0">
-        <v>91.560000000000002</v>
+        <v>26.030000000000001</v>
       </c>
       <c r="Q9" s="0">
-        <v>14.81</v>
+        <v>7.1600000000000001</v>
       </c>
       <c r="R9" s="0">
-        <v>24.84</v>
-      </c>
-      <c r="S9" s="0">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="T9" s="0">
-        <v>24.379999999999999</v>
-      </c>
-      <c r="U9" s="0">
-        <v>3.1499999999999999</v>
-      </c>
-      <c r="V9" s="0">
-        <v>26.030000000000001</v>
-      </c>
-      <c r="W9" s="0">
-        <v>7.1600000000000001</v>
-      </c>
-      <c r="X9" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3395,72 +3209,54 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>49.369999999999997</v>
+        <v>60.200000000000003</v>
       </c>
       <c r="C10" s="0">
-        <v>49.380000000000003</v>
+        <v>41.829999999999998</v>
       </c>
       <c r="D10" s="0">
-        <v>52.049999999999997</v>
+        <v>19.809999999999999</v>
       </c>
       <c r="E10" s="0">
-        <v>73.609999999999999</v>
+        <v>14.06</v>
       </c>
       <c r="F10" s="0">
-        <v>31.969999999999999</v>
+        <v>80.540000000000006</v>
       </c>
       <c r="G10" s="0">
-        <v>25.329999999999998</v>
+        <v>9.3499999999999996</v>
       </c>
       <c r="H10" s="0">
-        <v>23.719999999999999</v>
+        <v>53.719999999999999</v>
       </c>
       <c r="I10" s="0">
-        <v>10.890000000000001</v>
+        <v>5.4800000000000004</v>
       </c>
       <c r="J10" s="0">
-        <v>30.629999999999999</v>
+        <v>68.349999999999994</v>
       </c>
       <c r="K10" s="0">
-        <v>15.99</v>
+        <v>5.4199999999999999</v>
       </c>
       <c r="L10" s="0">
-        <v>80.540000000000006</v>
+        <v>17.199999999999999</v>
       </c>
       <c r="M10" s="0">
-        <v>9.3499999999999996</v>
+        <v>5.1100000000000003</v>
       </c>
       <c r="N10" s="0">
-        <v>53.719999999999999</v>
+        <v>31.140000000000001</v>
       </c>
       <c r="O10" s="0">
-        <v>5.4800000000000004</v>
+        <v>3.6000000000000001</v>
       </c>
       <c r="P10" s="0">
-        <v>68.349999999999994</v>
+        <v>21.690000000000001</v>
       </c>
       <c r="Q10" s="0">
-        <v>5.4199999999999999</v>
+        <v>15.52</v>
       </c>
       <c r="R10" s="0">
-        <v>17.199999999999999</v>
-      </c>
-      <c r="S10" s="0">
-        <v>5.1100000000000003</v>
-      </c>
-      <c r="T10" s="0">
-        <v>31.140000000000001</v>
-      </c>
-      <c r="U10" s="0">
-        <v>3.6000000000000001</v>
-      </c>
-      <c r="V10" s="0">
-        <v>21.690000000000001</v>
-      </c>
-      <c r="W10" s="0">
-        <v>15.52</v>
-      </c>
-      <c r="X10" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3469,72 +3265,54 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>10.92</v>
+        <v>38.170000000000002</v>
       </c>
       <c r="C11" s="0">
-        <v>5.9900000000000002</v>
+        <v>20.07</v>
       </c>
       <c r="D11" s="0">
-        <v>38.25</v>
+        <v>14.550000000000001</v>
       </c>
       <c r="E11" s="0">
-        <v>40.950000000000003</v>
+        <v>13.960000000000001</v>
       </c>
       <c r="F11" s="0">
-        <v>36.560000000000002</v>
+        <v>38.439999999999998</v>
       </c>
       <c r="G11" s="0">
-        <v>31.629999999999999</v>
+        <v>7.0199999999999996</v>
       </c>
       <c r="H11" s="0">
-        <v>60.009999999999998</v>
+        <v>95.650000000000006</v>
       </c>
       <c r="I11" s="0">
-        <v>58.759999999999998</v>
+        <v>12.390000000000001</v>
       </c>
       <c r="J11" s="0">
-        <v>41.799999999999997</v>
+        <v>95.280000000000001</v>
       </c>
       <c r="K11" s="0">
-        <v>18.199999999999999</v>
+        <v>13.130000000000001</v>
       </c>
       <c r="L11" s="0">
-        <v>38.439999999999998</v>
+        <v>24.760000000000002</v>
       </c>
       <c r="M11" s="0">
-        <v>7.0199999999999996</v>
+        <v>5.8099999999999996</v>
       </c>
       <c r="N11" s="0">
-        <v>95.650000000000006</v>
+        <v>20.18</v>
       </c>
       <c r="O11" s="0">
-        <v>12.390000000000001</v>
+        <v>5.5800000000000001</v>
       </c>
       <c r="P11" s="0">
-        <v>95.280000000000001</v>
+        <v>22.510000000000002</v>
       </c>
       <c r="Q11" s="0">
-        <v>13.130000000000001</v>
+        <v>6.0700000000000003</v>
       </c>
       <c r="R11" s="0">
-        <v>24.760000000000002</v>
-      </c>
-      <c r="S11" s="0">
-        <v>5.8099999999999996</v>
-      </c>
-      <c r="T11" s="0">
-        <v>20.18</v>
-      </c>
-      <c r="U11" s="0">
-        <v>5.5800000000000001</v>
-      </c>
-      <c r="V11" s="0">
-        <v>22.510000000000002</v>
-      </c>
-      <c r="W11" s="0">
-        <v>6.0700000000000003</v>
-      </c>
-      <c r="X11" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3543,72 +3321,54 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>56.890000000000001</v>
+        <v>60.090000000000003</v>
       </c>
       <c r="C12" s="0">
-        <v>52.420000000000002</v>
+        <v>48.899999999999999</v>
       </c>
       <c r="D12" s="0">
-        <v>64.719999999999999</v>
+        <v>24.780000000000001</v>
       </c>
       <c r="E12" s="0">
-        <v>79.579999999999998</v>
+        <v>16.210000000000001</v>
       </c>
       <c r="F12" s="0">
-        <v>33.890000000000001</v>
+        <v>88.109999999999999</v>
       </c>
       <c r="G12" s="0">
-        <v>26.98</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="H12" s="0">
-        <v>31.829999999999998</v>
+        <v>53.340000000000003</v>
       </c>
       <c r="I12" s="0">
-        <v>11.75</v>
+        <v>6.5</v>
       </c>
       <c r="J12" s="0">
-        <v>27.98</v>
+        <v>68.359999999999999</v>
       </c>
       <c r="K12" s="0">
-        <v>12.35</v>
+        <v>7.8200000000000003</v>
       </c>
       <c r="L12" s="0">
-        <v>88.109999999999999</v>
+        <v>18.760000000000002</v>
       </c>
       <c r="M12" s="0">
-        <v>8.2100000000000009</v>
+        <v>4.3300000000000001</v>
       </c>
       <c r="N12" s="0">
-        <v>53.340000000000003</v>
+        <v>29.239999999999998</v>
       </c>
       <c r="O12" s="0">
-        <v>6.5</v>
+        <v>4.3799999999999999</v>
       </c>
       <c r="P12" s="0">
-        <v>68.359999999999999</v>
+        <v>17.77</v>
       </c>
       <c r="Q12" s="0">
-        <v>7.8200000000000003</v>
+        <v>12.91</v>
       </c>
       <c r="R12" s="0">
-        <v>18.760000000000002</v>
-      </c>
-      <c r="S12" s="0">
-        <v>4.3300000000000001</v>
-      </c>
-      <c r="T12" s="0">
-        <v>29.239999999999998</v>
-      </c>
-      <c r="U12" s="0">
-        <v>4.3799999999999999</v>
-      </c>
-      <c r="V12" s="0">
-        <v>17.77</v>
-      </c>
-      <c r="W12" s="0">
-        <v>12.91</v>
-      </c>
-      <c r="X12" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3617,72 +3377,54 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>9.9600000000000009</v>
+        <v>48.869999999999997</v>
       </c>
       <c r="C13" s="0">
-        <v>6.8700000000000001</v>
+        <v>31.629999999999999</v>
       </c>
       <c r="D13" s="0">
-        <v>45.670000000000002</v>
+        <v>20.850000000000001</v>
       </c>
       <c r="E13" s="0">
-        <v>42.630000000000003</v>
+        <v>23.670000000000002</v>
       </c>
       <c r="F13" s="0">
-        <v>45.100000000000001</v>
+        <v>42.329999999999998</v>
       </c>
       <c r="G13" s="0">
-        <v>33.719999999999999</v>
+        <v>9.3399999999999999</v>
       </c>
       <c r="H13" s="0">
-        <v>55.82</v>
+        <v>108.52</v>
       </c>
       <c r="I13" s="0">
-        <v>57.799999999999997</v>
+        <v>13.279999999999999</v>
       </c>
       <c r="J13" s="0">
-        <v>59.759999999999998</v>
+        <v>101.37</v>
       </c>
       <c r="K13" s="0">
-        <v>22.280000000000001</v>
+        <v>11.24</v>
       </c>
       <c r="L13" s="0">
-        <v>42.329999999999998</v>
+        <v>25.559999999999999</v>
       </c>
       <c r="M13" s="0">
-        <v>9.3399999999999999</v>
+        <v>2.6800000000000002</v>
       </c>
       <c r="N13" s="0">
-        <v>108.52</v>
+        <v>23.890000000000001</v>
       </c>
       <c r="O13" s="0">
-        <v>13.279999999999999</v>
+        <v>3.8900000000000001</v>
       </c>
       <c r="P13" s="0">
-        <v>101.37</v>
+        <v>25.539999999999999</v>
       </c>
       <c r="Q13" s="0">
-        <v>11.24</v>
+        <v>8.6099999999999994</v>
       </c>
       <c r="R13" s="0">
-        <v>25.559999999999999</v>
-      </c>
-      <c r="S13" s="0">
-        <v>2.6800000000000002</v>
-      </c>
-      <c r="T13" s="0">
-        <v>23.890000000000001</v>
-      </c>
-      <c r="U13" s="0">
-        <v>3.8900000000000001</v>
-      </c>
-      <c r="V13" s="0">
-        <v>25.539999999999999</v>
-      </c>
-      <c r="W13" s="0">
-        <v>8.6099999999999994</v>
-      </c>
-      <c r="X13" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3691,72 +3433,54 @@
         <v>24</v>
       </c>
       <c r="B14" s="0">
-        <v>12.029999999999999</v>
+        <v>14.58</v>
       </c>
       <c r="C14" s="0">
-        <v>3.96</v>
+        <v>3.0699999999999998</v>
       </c>
       <c r="D14" s="0">
-        <v>10.84</v>
+        <v>9.5700000000000003</v>
       </c>
       <c r="E14" s="0">
-        <v>5.9100000000000001</v>
+        <v>4.6699999999999999</v>
       </c>
       <c r="F14" s="0">
-        <v>29.620000000000001</v>
+        <v>26.300000000000001</v>
       </c>
       <c r="G14" s="0">
-        <v>17.5</v>
+        <v>3.1299999999999999</v>
       </c>
       <c r="H14" s="0">
-        <v>24.52</v>
+        <v>48.450000000000003</v>
       </c>
       <c r="I14" s="0">
-        <v>13.68</v>
+        <v>5.21</v>
       </c>
       <c r="J14" s="0">
-        <v>12.130000000000001</v>
+        <v>68.290000000000006</v>
       </c>
       <c r="K14" s="0">
-        <v>2.3100000000000001</v>
+        <v>5.8300000000000001</v>
       </c>
       <c r="L14" s="0">
-        <v>26.300000000000001</v>
+        <v>18.789999999999999</v>
       </c>
       <c r="M14" s="0">
-        <v>3.1299999999999999</v>
+        <v>3.5499999999999998</v>
       </c>
       <c r="N14" s="0">
-        <v>48.450000000000003</v>
+        <v>26.699999999999999</v>
       </c>
       <c r="O14" s="0">
-        <v>5.21</v>
+        <v>2.04</v>
       </c>
       <c r="P14" s="0">
-        <v>68.290000000000006</v>
+        <v>24.07</v>
       </c>
       <c r="Q14" s="0">
-        <v>5.8300000000000001</v>
+        <v>3.3900000000000001</v>
       </c>
       <c r="R14" s="0">
-        <v>18.789999999999999</v>
-      </c>
-      <c r="S14" s="0">
-        <v>3.5499999999999998</v>
-      </c>
-      <c r="T14" s="0">
-        <v>26.699999999999999</v>
-      </c>
-      <c r="U14" s="0">
-        <v>2.04</v>
-      </c>
-      <c r="V14" s="0">
-        <v>24.07</v>
-      </c>
-      <c r="W14" s="0">
-        <v>3.3900000000000001</v>
-      </c>
-      <c r="X14" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3766,33 +3490,27 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.140625" customWidth="true"/>
     <col min="2" max="2" width="17.5703125" customWidth="true"/>
     <col min="3" max="3" width="14.85546875" customWidth="true"/>
-    <col min="4" max="4" width="19.140625" customWidth="true"/>
-    <col min="5" max="5" width="16.42578125" customWidth="true"/>
-    <col min="6" max="6" width="15.7109375" customWidth="true"/>
-    <col min="7" max="7" width="13" customWidth="true"/>
-    <col min="8" max="8" width="15.85546875" customWidth="true"/>
-    <col min="9" max="9" width="13.140625" customWidth="true"/>
-    <col min="10" max="10" width="17" customWidth="true"/>
-    <col min="11" max="11" width="14.28515625" customWidth="true"/>
-    <col min="12" max="12" width="16.140625" customWidth="true"/>
-    <col min="13" max="13" width="13.42578125" customWidth="true"/>
-    <col min="14" max="14" width="17.28515625" customWidth="true"/>
-    <col min="15" max="15" width="14.5703125" customWidth="true"/>
-    <col min="16" max="16" width="19.85546875" customWidth="true"/>
-    <col min="17" max="17" width="17.140625" customWidth="true"/>
-    <col min="18" max="18" width="16.7109375" customWidth="true"/>
-    <col min="19" max="19" width="14" customWidth="true"/>
-    <col min="20" max="20" width="16.7109375" customWidth="true"/>
-    <col min="21" max="21" width="14" customWidth="true"/>
-    <col min="22" max="22" width="17.140625" customWidth="true"/>
-    <col min="23" max="23" width="14.42578125" customWidth="true"/>
-    <col min="24" max="24" width="13.7109375" customWidth="true"/>
+    <col min="4" max="4" width="17" customWidth="true"/>
+    <col min="5" max="5" width="14.28515625" customWidth="true"/>
+    <col min="6" max="6" width="16.140625" customWidth="true"/>
+    <col min="7" max="7" width="13.42578125" customWidth="true"/>
+    <col min="8" max="8" width="17.28515625" customWidth="true"/>
+    <col min="9" max="9" width="14.5703125" customWidth="true"/>
+    <col min="10" max="10" width="19.85546875" customWidth="true"/>
+    <col min="11" max="11" width="17.140625" customWidth="true"/>
+    <col min="12" max="12" width="16.7109375" customWidth="true"/>
+    <col min="13" max="13" width="14" customWidth="true"/>
+    <col min="14" max="14" width="16.7109375" customWidth="true"/>
+    <col min="15" max="15" width="14" customWidth="true"/>
+    <col min="16" max="16" width="17.140625" customWidth="true"/>
+    <col min="17" max="17" width="14.42578125" customWidth="true"/>
+    <col min="18" max="18" width="13.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3848,24 +3566,6 @@
         <v>72</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="S1" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="T1" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="U1" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="V1" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="W1" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="X1" s="0" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3874,72 +3574,54 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>33.020000000000003</v>
+        <v>36.880000000000003</v>
       </c>
       <c r="C2" s="0">
-        <v>53.109999999999999</v>
+        <v>43.759999999999998</v>
       </c>
       <c r="D2" s="0">
-        <v>41.130000000000003</v>
+        <v>6.3700000000000001</v>
       </c>
       <c r="E2" s="0">
-        <v>83.709999999999994</v>
+        <v>14.949999999999999</v>
       </c>
       <c r="F2" s="0">
-        <v>4.0800000000000001</v>
+        <v>36.079999999999998</v>
       </c>
       <c r="G2" s="0">
-        <v>18.920000000000002</v>
+        <v>9.5800000000000001</v>
       </c>
       <c r="H2" s="0">
-        <v>3.6299999999999999</v>
+        <v>3.5600000000000001</v>
       </c>
       <c r="I2" s="0">
-        <v>13.08</v>
+        <v>3.1499999999999999</v>
       </c>
       <c r="J2" s="0">
-        <v>10.23</v>
+        <v>0.38</v>
       </c>
       <c r="K2" s="0">
-        <v>6.75</v>
+        <v>4.8300000000000001</v>
       </c>
       <c r="L2" s="0">
-        <v>36.079999999999998</v>
+        <v>1.49</v>
       </c>
       <c r="M2" s="0">
-        <v>9.5800000000000001</v>
+        <v>2.52</v>
       </c>
       <c r="N2" s="0">
-        <v>3.5600000000000001</v>
+        <v>1.45</v>
       </c>
       <c r="O2" s="0">
-        <v>3.1499999999999999</v>
+        <v>3.4300000000000002</v>
       </c>
       <c r="P2" s="0">
-        <v>0.38</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="Q2" s="0">
-        <v>4.8300000000000001</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="R2" s="0">
-        <v>1.49</v>
-      </c>
-      <c r="S2" s="0">
-        <v>2.52</v>
-      </c>
-      <c r="T2" s="0">
-        <v>1.45</v>
-      </c>
-      <c r="U2" s="0">
-        <v>3.4300000000000002</v>
-      </c>
-      <c r="V2" s="0">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="W2" s="0">
-        <v>8.9700000000000006</v>
-      </c>
-      <c r="X2" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3948,72 +3630,54 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
+        <v>19.739999999999998</v>
+      </c>
+      <c r="C3" s="0">
+        <v>14.24</v>
+      </c>
+      <c r="D3" s="0">
+        <v>-0.16</v>
+      </c>
+      <c r="E3" s="0">
+        <v>8.7400000000000002</v>
+      </c>
+      <c r="F3" s="0">
+        <v>8.2400000000000002</v>
+      </c>
+      <c r="G3" s="0">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="H3" s="0">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="I3" s="0">
+        <v>14.449999999999999</v>
+      </c>
+      <c r="J3" s="0">
+        <v>18.66</v>
+      </c>
+      <c r="K3" s="0">
+        <v>11.800000000000001</v>
+      </c>
+      <c r="L3" s="0">
+        <v>6.0199999999999996</v>
+      </c>
+      <c r="M3" s="0">
+        <v>4.7400000000000002</v>
+      </c>
+      <c r="N3" s="0">
         <v>-2.4399999999999999</v>
       </c>
-      <c r="C3" s="0">
-        <v>8.1500000000000004</v>
-      </c>
-      <c r="D3" s="0">
-        <v>27.829999999999998</v>
-      </c>
-      <c r="E3" s="0">
-        <v>40.469999999999999</v>
-      </c>
-      <c r="F3" s="0">
-        <v>6.1900000000000004</v>
-      </c>
-      <c r="G3" s="0">
-        <v>21.43</v>
-      </c>
-      <c r="H3" s="0">
-        <v>34.18</v>
-      </c>
-      <c r="I3" s="0">
-        <v>52.140000000000001</v>
-      </c>
-      <c r="J3" s="0">
-        <v>22.010000000000002</v>
-      </c>
-      <c r="K3" s="0">
-        <v>13.300000000000001</v>
-      </c>
-      <c r="L3" s="0">
-        <v>8.2400000000000002</v>
-      </c>
-      <c r="M3" s="0">
-        <v>4.0599999999999996</v>
-      </c>
-      <c r="N3" s="0">
-        <v>32.200000000000003</v>
-      </c>
       <c r="O3" s="0">
-        <v>14.449999999999999</v>
+        <v>3.4100000000000001</v>
       </c>
       <c r="P3" s="0">
-        <v>18.66</v>
+        <v>1.4099999999999999</v>
       </c>
       <c r="Q3" s="0">
-        <v>11.800000000000001</v>
+        <v>3.2999999999999998</v>
       </c>
       <c r="R3" s="0">
-        <v>6.0199999999999996</v>
-      </c>
-      <c r="S3" s="0">
-        <v>4.7400000000000002</v>
-      </c>
-      <c r="T3" s="0">
-        <v>-2.4399999999999999</v>
-      </c>
-      <c r="U3" s="0">
-        <v>3.4100000000000001</v>
-      </c>
-      <c r="V3" s="0">
-        <v>1.4099999999999999</v>
-      </c>
-      <c r="W3" s="0">
-        <v>3.2999999999999998</v>
-      </c>
-      <c r="X3" s="0">
         <v>7</v>
       </c>
     </row>
@@ -4022,72 +3686,54 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>33.149999999999999</v>
+        <v>43.380000000000003</v>
       </c>
       <c r="C4" s="0">
-        <v>49.390000000000001</v>
+        <v>42.979999999999997</v>
       </c>
       <c r="D4" s="0">
-        <v>38.039999999999999</v>
+        <v>9.3499999999999996</v>
       </c>
       <c r="E4" s="0">
-        <v>81.319999999999993</v>
+        <v>8.3499999999999996</v>
       </c>
       <c r="F4" s="0">
-        <v>1.21</v>
+        <v>51.869999999999997</v>
       </c>
       <c r="G4" s="0">
-        <v>20.420000000000002</v>
+        <v>9.1300000000000008</v>
       </c>
       <c r="H4" s="0">
-        <v>-0.20000000000000001</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="I4" s="0">
-        <v>14.460000000000001</v>
+        <v>3.6699999999999999</v>
       </c>
       <c r="J4" s="0">
-        <v>19.57</v>
+        <v>0.88</v>
       </c>
       <c r="K4" s="0">
-        <v>21.829999999999998</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="L4" s="0">
-        <v>51.869999999999997</v>
+        <v>-0.63</v>
       </c>
       <c r="M4" s="0">
-        <v>9.1300000000000008</v>
+        <v>2.5</v>
       </c>
       <c r="N4" s="0">
-        <v>4.8899999999999997</v>
+        <v>2.3700000000000001</v>
       </c>
       <c r="O4" s="0">
-        <v>3.6699999999999999</v>
+        <v>4.9900000000000002</v>
       </c>
       <c r="P4" s="0">
-        <v>0.88</v>
+        <v>-1.73</v>
       </c>
       <c r="Q4" s="0">
-        <v>4.1500000000000004</v>
+        <v>14.48</v>
       </c>
       <c r="R4" s="0">
-        <v>-0.63</v>
-      </c>
-      <c r="S4" s="0">
-        <v>2.5</v>
-      </c>
-      <c r="T4" s="0">
-        <v>2.3700000000000001</v>
-      </c>
-      <c r="U4" s="0">
-        <v>4.9900000000000002</v>
-      </c>
-      <c r="V4" s="0">
-        <v>-1.73</v>
-      </c>
-      <c r="W4" s="0">
-        <v>14.48</v>
-      </c>
-      <c r="X4" s="0">
         <v>7</v>
       </c>
     </row>
@@ -4096,72 +3742,54 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>0.53000000000000003</v>
+        <v>27.120000000000001</v>
       </c>
       <c r="C5" s="0">
-        <v>7.8200000000000003</v>
+        <v>15</v>
       </c>
       <c r="D5" s="0">
-        <v>29.620000000000001</v>
+        <v>-0.89000000000000001</v>
       </c>
       <c r="E5" s="0">
-        <v>42.560000000000002</v>
+        <v>6.1500000000000004</v>
       </c>
       <c r="F5" s="0">
-        <v>8.7899999999999991</v>
+        <v>11.43</v>
       </c>
       <c r="G5" s="0">
-        <v>30.030000000000001</v>
+        <v>5.0899999999999999</v>
       </c>
       <c r="H5" s="0">
-        <v>35.659999999999997</v>
+        <v>44.829999999999998</v>
       </c>
       <c r="I5" s="0">
-        <v>56.939999999999998</v>
+        <v>13.56</v>
       </c>
       <c r="J5" s="0">
-        <v>25.699999999999999</v>
+        <v>24.960000000000001</v>
       </c>
       <c r="K5" s="0">
-        <v>20.960000000000001</v>
+        <v>7.9100000000000001</v>
       </c>
       <c r="L5" s="0">
-        <v>11.43</v>
+        <v>5.5</v>
       </c>
       <c r="M5" s="0">
-        <v>5.0899999999999999</v>
+        <v>3.46</v>
       </c>
       <c r="N5" s="0">
-        <v>44.829999999999998</v>
+        <v>-3.3500000000000001</v>
       </c>
       <c r="O5" s="0">
-        <v>13.56</v>
+        <v>4.2599999999999998</v>
       </c>
       <c r="P5" s="0">
-        <v>24.960000000000001</v>
+        <v>1.6399999999999999</v>
       </c>
       <c r="Q5" s="0">
-        <v>7.9100000000000001</v>
+        <v>5.3799999999999999</v>
       </c>
       <c r="R5" s="0">
-        <v>5.5</v>
-      </c>
-      <c r="S5" s="0">
-        <v>3.46</v>
-      </c>
-      <c r="T5" s="0">
-        <v>-3.3500000000000001</v>
-      </c>
-      <c r="U5" s="0">
-        <v>4.2599999999999998</v>
-      </c>
-      <c r="V5" s="0">
-        <v>1.6399999999999999</v>
-      </c>
-      <c r="W5" s="0">
-        <v>5.3799999999999999</v>
-      </c>
-      <c r="X5" s="0">
         <v>7</v>
       </c>
     </row>
@@ -4170,72 +3798,54 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>34.579999999999998</v>
+        <v>43.869999999999997</v>
       </c>
       <c r="C6" s="0">
-        <v>45.420000000000002</v>
+        <v>31.289999999999999</v>
       </c>
       <c r="D6" s="0">
-        <v>39.609999999999999</v>
+        <v>15.23</v>
       </c>
       <c r="E6" s="0">
-        <v>63.490000000000002</v>
+        <v>25</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.69999999999999996</v>
+        <v>56.090000000000003</v>
       </c>
       <c r="G6" s="0">
-        <v>12.31</v>
+        <v>7.4900000000000002</v>
       </c>
       <c r="H6" s="0">
-        <v>3.4500000000000002</v>
+        <v>4.4900000000000002</v>
       </c>
       <c r="I6" s="0">
-        <v>14.859999999999999</v>
+        <v>3.1499999999999999</v>
       </c>
       <c r="J6" s="0">
-        <v>24.530000000000001</v>
+        <v>-3.1800000000000002</v>
       </c>
       <c r="K6" s="0">
-        <v>15.67</v>
+        <v>11.050000000000001</v>
       </c>
       <c r="L6" s="0">
-        <v>56.090000000000003</v>
+        <v>1.6000000000000001</v>
       </c>
       <c r="M6" s="0">
-        <v>7.4900000000000002</v>
+        <v>5.5499999999999998</v>
       </c>
       <c r="N6" s="0">
-        <v>4.4900000000000002</v>
+        <v>3.4399999999999999</v>
       </c>
       <c r="O6" s="0">
-        <v>3.1499999999999999</v>
+        <v>5.3799999999999999</v>
       </c>
       <c r="P6" s="0">
-        <v>-3.1800000000000002</v>
+        <v>-3.3799999999999999</v>
       </c>
       <c r="Q6" s="0">
-        <v>11.050000000000001</v>
+        <v>12.029999999999999</v>
       </c>
       <c r="R6" s="0">
-        <v>1.6000000000000001</v>
-      </c>
-      <c r="S6" s="0">
-        <v>5.5499999999999998</v>
-      </c>
-      <c r="T6" s="0">
-        <v>3.4399999999999999</v>
-      </c>
-      <c r="U6" s="0">
-        <v>5.3799999999999999</v>
-      </c>
-      <c r="V6" s="0">
-        <v>-3.3799999999999999</v>
-      </c>
-      <c r="W6" s="0">
-        <v>12.029999999999999</v>
-      </c>
-      <c r="X6" s="0">
         <v>7</v>
       </c>
     </row>
@@ -4244,72 +3854,54 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>-2.2799999999999998</v>
+        <v>29.530000000000001</v>
       </c>
       <c r="C7" s="0">
-        <v>7.8399999999999999</v>
+        <v>26.32</v>
       </c>
       <c r="D7" s="0">
-        <v>33.149999999999999</v>
+        <v>6.8799999999999999</v>
       </c>
       <c r="E7" s="0">
-        <v>34.969999999999999</v>
+        <v>15.6</v>
       </c>
       <c r="F7" s="0">
-        <v>26.809999999999999</v>
+        <v>13.4</v>
       </c>
       <c r="G7" s="0">
-        <v>50.18</v>
+        <v>6.2000000000000002</v>
       </c>
       <c r="H7" s="0">
-        <v>37.280000000000001</v>
+        <v>53</v>
       </c>
       <c r="I7" s="0">
-        <v>42.219999999999999</v>
+        <v>10.460000000000001</v>
       </c>
       <c r="J7" s="0">
-        <v>38.689999999999998</v>
+        <v>29.170000000000002</v>
       </c>
       <c r="K7" s="0">
-        <v>19.609999999999999</v>
+        <v>12.65</v>
       </c>
       <c r="L7" s="0">
-        <v>13.4</v>
+        <v>6.0499999999999998</v>
       </c>
       <c r="M7" s="0">
-        <v>6.2000000000000002</v>
+        <v>2.6499999999999999</v>
       </c>
       <c r="N7" s="0">
-        <v>53</v>
+        <v>-4.9100000000000001</v>
       </c>
       <c r="O7" s="0">
-        <v>10.460000000000001</v>
+        <v>6.5199999999999996</v>
       </c>
       <c r="P7" s="0">
-        <v>29.170000000000002</v>
+        <v>0.51000000000000001</v>
       </c>
       <c r="Q7" s="0">
-        <v>12.65</v>
+        <v>8.2400000000000002</v>
       </c>
       <c r="R7" s="0">
-        <v>6.0499999999999998</v>
-      </c>
-      <c r="S7" s="0">
-        <v>2.6499999999999999</v>
-      </c>
-      <c r="T7" s="0">
-        <v>-4.9100000000000001</v>
-      </c>
-      <c r="U7" s="0">
-        <v>6.5199999999999996</v>
-      </c>
-      <c r="V7" s="0">
-        <v>0.51000000000000001</v>
-      </c>
-      <c r="W7" s="0">
-        <v>8.2400000000000002</v>
-      </c>
-      <c r="X7" s="0">
         <v>7</v>
       </c>
     </row>
@@ -4318,72 +3910,54 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>28.809999999999999</v>
+        <v>39.759999999999998</v>
       </c>
       <c r="C8" s="0">
-        <v>53.130000000000003</v>
+        <v>41.32</v>
       </c>
       <c r="D8" s="0">
-        <v>36.460000000000001</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="E8" s="0">
-        <v>76.219999999999999</v>
+        <v>10.57</v>
       </c>
       <c r="F8" s="0">
-        <v>1.52</v>
+        <v>40.210000000000001</v>
       </c>
       <c r="G8" s="0">
-        <v>20.530000000000001</v>
+        <v>7.0300000000000002</v>
       </c>
       <c r="H8" s="0">
-        <v>7.5899999999999999</v>
+        <v>3.25</v>
       </c>
       <c r="I8" s="0">
-        <v>8.6899999999999995</v>
+        <v>2.6499999999999999</v>
       </c>
       <c r="J8" s="0">
-        <v>11.51</v>
+        <v>2.6699999999999999</v>
       </c>
       <c r="K8" s="0">
-        <v>11.609999999999999</v>
+        <v>3.0099999999999998</v>
       </c>
       <c r="L8" s="0">
-        <v>40.210000000000001</v>
+        <v>-0.77000000000000002</v>
       </c>
       <c r="M8" s="0">
-        <v>7.0300000000000002</v>
+        <v>2.8799999999999999</v>
       </c>
       <c r="N8" s="0">
-        <v>3.25</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="O8" s="0">
-        <v>2.6499999999999999</v>
+        <v>4.8200000000000003</v>
       </c>
       <c r="P8" s="0">
-        <v>2.6699999999999999</v>
+        <v>4.2199999999999998</v>
       </c>
       <c r="Q8" s="0">
-        <v>3.0099999999999998</v>
+        <v>12.85</v>
       </c>
       <c r="R8" s="0">
-        <v>-0.77000000000000002</v>
-      </c>
-      <c r="S8" s="0">
-        <v>2.8799999999999999</v>
-      </c>
-      <c r="T8" s="0">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="U8" s="0">
-        <v>4.8200000000000003</v>
-      </c>
-      <c r="V8" s="0">
-        <v>4.2199999999999998</v>
-      </c>
-      <c r="W8" s="0">
-        <v>12.85</v>
-      </c>
-      <c r="X8" s="0">
         <v>7</v>
       </c>
     </row>
@@ -4392,72 +3966,54 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>1.3700000000000001</v>
+        <v>17.129999999999999</v>
       </c>
       <c r="C9" s="0">
-        <v>9.4299999999999997</v>
+        <v>7.3399999999999999</v>
       </c>
       <c r="D9" s="0">
-        <v>25.620000000000001</v>
+        <v>1.6399999999999999</v>
       </c>
       <c r="E9" s="0">
-        <v>37.609999999999999</v>
+        <v>10.220000000000001</v>
       </c>
       <c r="F9" s="0">
-        <v>11.41</v>
+        <v>10.24</v>
       </c>
       <c r="G9" s="0">
-        <v>27.370000000000001</v>
+        <v>4.29</v>
       </c>
       <c r="H9" s="0">
-        <v>25.969999999999999</v>
+        <v>33.840000000000003</v>
       </c>
       <c r="I9" s="0">
-        <v>49.18</v>
+        <v>12.140000000000001</v>
       </c>
       <c r="J9" s="0">
-        <v>17.399999999999999</v>
+        <v>23.27</v>
       </c>
       <c r="K9" s="0">
-        <v>11.66</v>
+        <v>12.15</v>
       </c>
       <c r="L9" s="0">
-        <v>10.24</v>
+        <v>6.04</v>
       </c>
       <c r="M9" s="0">
-        <v>4.29</v>
+        <v>3.7400000000000002</v>
       </c>
       <c r="N9" s="0">
-        <v>33.840000000000003</v>
+        <v>-2.3300000000000001</v>
       </c>
       <c r="O9" s="0">
-        <v>12.140000000000001</v>
+        <v>3.48</v>
       </c>
       <c r="P9" s="0">
-        <v>23.27</v>
+        <v>1.96</v>
       </c>
       <c r="Q9" s="0">
-        <v>12.15</v>
+        <v>6.2300000000000004</v>
       </c>
       <c r="R9" s="0">
-        <v>6.04</v>
-      </c>
-      <c r="S9" s="0">
-        <v>3.7400000000000002</v>
-      </c>
-      <c r="T9" s="0">
-        <v>-2.3300000000000001</v>
-      </c>
-      <c r="U9" s="0">
-        <v>3.48</v>
-      </c>
-      <c r="V9" s="0">
-        <v>1.96</v>
-      </c>
-      <c r="W9" s="0">
-        <v>6.2300000000000004</v>
-      </c>
-      <c r="X9" s="0">
         <v>7</v>
       </c>
     </row>
@@ -4466,72 +4022,54 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>37.340000000000003</v>
+        <v>45.619999999999997</v>
       </c>
       <c r="C10" s="0">
-        <v>50.979999999999997</v>
+        <v>39.289999999999999</v>
       </c>
       <c r="D10" s="0">
-        <v>41.210000000000001</v>
+        <v>10.23</v>
       </c>
       <c r="E10" s="0">
-        <v>71.140000000000001</v>
+        <v>17.16</v>
       </c>
       <c r="F10" s="0">
-        <v>2.3500000000000001</v>
+        <v>54.229999999999997</v>
       </c>
       <c r="G10" s="0">
-        <v>15.19</v>
+        <v>7.5999999999999996</v>
       </c>
       <c r="H10" s="0">
-        <v>-0.80000000000000004</v>
+        <v>5.2599999999999998</v>
       </c>
       <c r="I10" s="0">
-        <v>13.01</v>
+        <v>1.6200000000000001</v>
       </c>
       <c r="J10" s="0">
-        <v>18.5</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="K10" s="0">
-        <v>14.029999999999999</v>
+        <v>5.7000000000000002</v>
       </c>
       <c r="L10" s="0">
-        <v>54.229999999999997</v>
+        <v>-1.5900000000000001</v>
       </c>
       <c r="M10" s="0">
-        <v>7.5999999999999996</v>
+        <v>2.29</v>
       </c>
       <c r="N10" s="0">
-        <v>5.2599999999999998</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="O10" s="0">
-        <v>1.6200000000000001</v>
+        <v>4.4100000000000001</v>
       </c>
       <c r="P10" s="0">
-        <v>0.050000000000000003</v>
+        <v>-2.3799999999999999</v>
       </c>
       <c r="Q10" s="0">
-        <v>5.7000000000000002</v>
+        <v>14.31</v>
       </c>
       <c r="R10" s="0">
-        <v>-1.5900000000000001</v>
-      </c>
-      <c r="S10" s="0">
-        <v>2.29</v>
-      </c>
-      <c r="T10" s="0">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="U10" s="0">
-        <v>4.4100000000000001</v>
-      </c>
-      <c r="V10" s="0">
-        <v>-2.3799999999999999</v>
-      </c>
-      <c r="W10" s="0">
-        <v>14.31</v>
-      </c>
-      <c r="X10" s="0">
         <v>7</v>
       </c>
     </row>
@@ -4540,72 +4078,54 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>-1.1000000000000001</v>
+        <v>23.59</v>
       </c>
       <c r="C11" s="0">
-        <v>5.5199999999999996</v>
+        <v>19.66</v>
       </c>
       <c r="D11" s="0">
-        <v>27.41</v>
+        <v>4.9800000000000004</v>
       </c>
       <c r="E11" s="0">
-        <v>36.409999999999997</v>
+        <v>14.01</v>
       </c>
       <c r="F11" s="0">
-        <v>6.9400000000000004</v>
+        <v>12.140000000000001</v>
       </c>
       <c r="G11" s="0">
-        <v>29.359999999999999</v>
+        <v>6.9800000000000004</v>
       </c>
       <c r="H11" s="0">
-        <v>35.5</v>
+        <v>47.189999999999998</v>
       </c>
       <c r="I11" s="0">
-        <v>47.990000000000002</v>
+        <v>11.199999999999999</v>
       </c>
       <c r="J11" s="0">
-        <v>29.670000000000002</v>
+        <v>26.98</v>
       </c>
       <c r="K11" s="0">
-        <v>18.640000000000001</v>
+        <v>10.98</v>
       </c>
       <c r="L11" s="0">
-        <v>12.140000000000001</v>
+        <v>5.96</v>
       </c>
       <c r="M11" s="0">
-        <v>6.9800000000000004</v>
+        <v>4.5700000000000003</v>
       </c>
       <c r="N11" s="0">
-        <v>47.189999999999998</v>
+        <v>-6.5199999999999996</v>
       </c>
       <c r="O11" s="0">
-        <v>11.199999999999999</v>
+        <v>5.7300000000000004</v>
       </c>
       <c r="P11" s="0">
-        <v>26.98</v>
+        <v>-1.5600000000000001</v>
       </c>
       <c r="Q11" s="0">
-        <v>10.98</v>
+        <v>5.6100000000000003</v>
       </c>
       <c r="R11" s="0">
-        <v>5.96</v>
-      </c>
-      <c r="S11" s="0">
-        <v>4.5700000000000003</v>
-      </c>
-      <c r="T11" s="0">
-        <v>-6.5199999999999996</v>
-      </c>
-      <c r="U11" s="0">
-        <v>5.7300000000000004</v>
-      </c>
-      <c r="V11" s="0">
-        <v>-1.5600000000000001</v>
-      </c>
-      <c r="W11" s="0">
-        <v>5.6100000000000003</v>
-      </c>
-      <c r="X11" s="0">
         <v>7</v>
       </c>
     </row>
@@ -4614,72 +4134,54 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>44.380000000000003</v>
+        <v>45.299999999999997</v>
       </c>
       <c r="C12" s="0">
-        <v>54.880000000000003</v>
+        <v>46.469999999999999</v>
       </c>
       <c r="D12" s="0">
-        <v>52.890000000000001</v>
+        <v>15.130000000000001</v>
       </c>
       <c r="E12" s="0">
-        <v>77.819999999999993</v>
+        <v>18.760000000000002</v>
       </c>
       <c r="F12" s="0">
-        <v>4.2699999999999996</v>
+        <v>61.310000000000002</v>
       </c>
       <c r="G12" s="0">
-        <v>16.629999999999999</v>
+        <v>6.3600000000000003</v>
       </c>
       <c r="H12" s="0">
-        <v>7.3200000000000003</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="I12" s="0">
-        <v>6.5999999999999996</v>
+        <v>3.0899999999999999</v>
       </c>
       <c r="J12" s="0">
-        <v>16.050000000000001</v>
+        <v>0.059999999999999998</v>
       </c>
       <c r="K12" s="0">
-        <v>10.48</v>
+        <v>5.0099999999999998</v>
       </c>
       <c r="L12" s="0">
-        <v>61.310000000000002</v>
+        <v>-0.59999999999999998</v>
       </c>
       <c r="M12" s="0">
-        <v>6.3600000000000003</v>
+        <v>3.5800000000000001</v>
       </c>
       <c r="N12" s="0">
-        <v>4.8899999999999997</v>
+        <v>2.54</v>
       </c>
       <c r="O12" s="0">
-        <v>3.0899999999999999</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="P12" s="0">
-        <v>0.059999999999999998</v>
+        <v>-6.2999999999999998</v>
       </c>
       <c r="Q12" s="0">
-        <v>5.0099999999999998</v>
+        <v>11.35</v>
       </c>
       <c r="R12" s="0">
-        <v>-0.59999999999999998</v>
-      </c>
-      <c r="S12" s="0">
-        <v>3.5800000000000001</v>
-      </c>
-      <c r="T12" s="0">
-        <v>2.54</v>
-      </c>
-      <c r="U12" s="0">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="V12" s="0">
-        <v>-6.2999999999999998</v>
-      </c>
-      <c r="W12" s="0">
-        <v>11.35</v>
-      </c>
-      <c r="X12" s="0">
         <v>7</v>
       </c>
     </row>
@@ -4688,72 +4190,54 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>-2.5499999999999998</v>
+        <v>34.079999999999998</v>
       </c>
       <c r="C13" s="0">
-        <v>7.9000000000000004</v>
+        <v>30.949999999999999</v>
       </c>
       <c r="D13" s="0">
-        <v>33.850000000000001</v>
+        <v>11.199999999999999</v>
       </c>
       <c r="E13" s="0">
-        <v>39.130000000000003</v>
+        <v>24.100000000000001</v>
       </c>
       <c r="F13" s="0">
-        <v>15.48</v>
+        <v>15.529999999999999</v>
       </c>
       <c r="G13" s="0">
-        <v>31.460000000000001</v>
+        <v>8.6400000000000006</v>
       </c>
       <c r="H13" s="0">
-        <v>31.309999999999999</v>
+        <v>60.060000000000002</v>
       </c>
       <c r="I13" s="0">
-        <v>48.030000000000001</v>
+        <v>13.65</v>
       </c>
       <c r="J13" s="0">
-        <v>47.829999999999998</v>
+        <v>33.079999999999998</v>
       </c>
       <c r="K13" s="0">
-        <v>22.449999999999999</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="L13" s="0">
-        <v>15.529999999999999</v>
+        <v>6.2000000000000002</v>
       </c>
       <c r="M13" s="0">
-        <v>8.6400000000000006</v>
+        <v>4.3799999999999999</v>
       </c>
       <c r="N13" s="0">
-        <v>60.060000000000002</v>
+        <v>-2.8199999999999998</v>
       </c>
       <c r="O13" s="0">
-        <v>13.65</v>
+        <v>3.5600000000000001</v>
       </c>
       <c r="P13" s="0">
-        <v>33.079999999999998</v>
+        <v>1.47</v>
       </c>
       <c r="Q13" s="0">
-        <v>9.1999999999999993</v>
+        <v>7.0300000000000002</v>
       </c>
       <c r="R13" s="0">
-        <v>6.2000000000000002</v>
-      </c>
-      <c r="S13" s="0">
-        <v>4.3799999999999999</v>
-      </c>
-      <c r="T13" s="0">
-        <v>-2.8199999999999998</v>
-      </c>
-      <c r="U13" s="0">
-        <v>3.5600000000000001</v>
-      </c>
-      <c r="V13" s="0">
-        <v>1.47</v>
-      </c>
-      <c r="W13" s="0">
-        <v>7.0300000000000002</v>
-      </c>
-      <c r="X13" s="0">
         <v>7</v>
       </c>
     </row>
@@ -4810,24 +4294,6 @@
         <v>0</v>
       </c>
       <c r="R14" s="0">
-        <v>0</v>
-      </c>
-      <c r="S14" s="0">
-        <v>0</v>
-      </c>
-      <c r="T14" s="0">
-        <v>0</v>
-      </c>
-      <c r="U14" s="0">
-        <v>0</v>
-      </c>
-      <c r="V14" s="0">
-        <v>0</v>
-      </c>
-      <c r="W14" s="0">
-        <v>0</v>
-      </c>
-      <c r="X14" s="0">
         <v>7</v>
       </c>
     </row>

--- a/Results/Group Analysis/GroupCrossing_YoungAdults_Summary.xlsx
+++ b/Results/Group Analysis/GroupCrossing_YoungAdults_Summary.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="178" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="190" uniqueCount="79">
   <si>
     <t>Condition</t>
   </si>
@@ -203,6 +203,24 @@
   </si>
   <si>
     <t>hip_pk_ext_SD</t>
+  </si>
+  <si>
+    <t>knee_pk_flex_mean</t>
+  </si>
+  <si>
+    <t>knee_pk_flex_SD</t>
+  </si>
+  <si>
+    <t>ank_plant_mean</t>
+  </si>
+  <si>
+    <t>ank_plant_SD</t>
+  </si>
+  <si>
+    <t>ank_dorsi_mean</t>
+  </si>
+  <si>
+    <t>ank_dorsi_SD</t>
   </si>
   <si>
     <t>thigh_fwd_mean</t>
@@ -2038,10 +2056,10 @@
         <v>11.76</v>
       </c>
       <c r="F2" s="0">
-        <v>48.049999999999997</v>
+        <v>63.119999999999997</v>
       </c>
       <c r="G2" s="0">
-        <v>12.16</v>
+        <v>15.06</v>
       </c>
       <c r="H2" s="0">
         <v>49.280000000000001</v>
@@ -2088,10 +2106,10 @@
         <v>5.21</v>
       </c>
       <c r="F3" s="0">
-        <v>58.490000000000002</v>
+        <v>66.099999999999994</v>
       </c>
       <c r="G3" s="0">
-        <v>16.18</v>
+        <v>12.82</v>
       </c>
       <c r="H3" s="0">
         <v>51.859999999999999</v>
@@ -2138,10 +2156,10 @@
         <v>22.920000000000002</v>
       </c>
       <c r="F4" s="0">
-        <v>49.630000000000003</v>
+        <v>67.799999999999997</v>
       </c>
       <c r="G4" s="0">
-        <v>17.199999999999999</v>
+        <v>12.130000000000001</v>
       </c>
       <c r="H4" s="0">
         <v>50.060000000000002</v>
@@ -2188,10 +2206,10 @@
         <v>7.2599999999999998</v>
       </c>
       <c r="F5" s="0">
-        <v>51.990000000000002</v>
+        <v>64.379999999999995</v>
       </c>
       <c r="G5" s="0">
-        <v>21.43</v>
+        <v>22.030000000000001</v>
       </c>
       <c r="H5" s="0">
         <v>55.020000000000003</v>
@@ -2238,10 +2256,10 @@
         <v>12.98</v>
       </c>
       <c r="F6" s="0">
-        <v>40.259999999999998</v>
+        <v>53.210000000000001</v>
       </c>
       <c r="G6" s="0">
-        <v>20.210000000000001</v>
+        <v>21.670000000000002</v>
       </c>
       <c r="H6" s="0">
         <v>47.68</v>
@@ -2288,10 +2306,10 @@
         <v>7.9900000000000002</v>
       </c>
       <c r="F7" s="0">
-        <v>60.390000000000001</v>
+        <v>66.560000000000002</v>
       </c>
       <c r="G7" s="0">
-        <v>15.539999999999999</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="H7" s="0">
         <v>54.130000000000003</v>
@@ -2338,10 +2356,10 @@
         <v>17.48</v>
       </c>
       <c r="F8" s="0">
-        <v>52.810000000000002</v>
+        <v>60.369999999999997</v>
       </c>
       <c r="G8" s="0">
-        <v>15.359999999999999</v>
+        <v>18.940000000000001</v>
       </c>
       <c r="H8" s="0">
         <v>47.75</v>
@@ -2388,10 +2406,10 @@
         <v>9.7200000000000006</v>
       </c>
       <c r="F9" s="0">
-        <v>55.810000000000002</v>
+        <v>64.849999999999994</v>
       </c>
       <c r="G9" s="0">
-        <v>13.869999999999999</v>
+        <v>14.44</v>
       </c>
       <c r="H9" s="0">
         <v>53.840000000000003</v>
@@ -2438,10 +2456,10 @@
         <v>21.780000000000001</v>
       </c>
       <c r="F10" s="0">
-        <v>42.579999999999998</v>
+        <v>64.349999999999994</v>
       </c>
       <c r="G10" s="0">
-        <v>16.48</v>
+        <v>14.550000000000001</v>
       </c>
       <c r="H10" s="0">
         <v>50.219999999999999</v>
@@ -2488,10 +2506,10 @@
         <v>8.5299999999999994</v>
       </c>
       <c r="F11" s="0">
-        <v>57.799999999999997</v>
+        <v>66.989999999999995</v>
       </c>
       <c r="G11" s="0">
-        <v>15.73</v>
+        <v>13.75</v>
       </c>
       <c r="H11" s="0">
         <v>54.990000000000002</v>
@@ -2538,10 +2556,10 @@
         <v>19.109999999999999</v>
       </c>
       <c r="F12" s="0">
-        <v>43.799999999999997</v>
+        <v>53.25</v>
       </c>
       <c r="G12" s="0">
-        <v>9.7400000000000002</v>
+        <v>12.109999999999999</v>
       </c>
       <c r="H12" s="0">
         <v>51.490000000000002</v>
@@ -2588,10 +2606,10 @@
         <v>9.4800000000000004</v>
       </c>
       <c r="F13" s="0">
-        <v>57.189999999999998</v>
+        <v>69.730000000000004</v>
       </c>
       <c r="G13" s="0">
-        <v>20.039999999999999</v>
+        <v>19.449999999999999</v>
       </c>
       <c r="H13" s="0">
         <v>54.700000000000003</v>
@@ -2638,10 +2656,10 @@
         <v>9.6199999999999992</v>
       </c>
       <c r="F14" s="0">
-        <v>47.109999999999999</v>
+        <v>59.670000000000002</v>
       </c>
       <c r="G14" s="0">
-        <v>5.6299999999999999</v>
+        <v>9.0399999999999991</v>
       </c>
       <c r="H14" s="0">
         <v>55.859999999999999</v>
@@ -2677,7 +2695,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.140625" customWidth="true"/>
@@ -2685,19 +2703,25 @@
     <col min="3" max="3" width="14.85546875" customWidth="true"/>
     <col min="4" max="4" width="17" customWidth="true"/>
     <col min="5" max="5" width="14.28515625" customWidth="true"/>
-    <col min="6" max="6" width="16.140625" customWidth="true"/>
-    <col min="7" max="7" width="13.42578125" customWidth="true"/>
-    <col min="8" max="8" width="17.28515625" customWidth="true"/>
-    <col min="9" max="9" width="14.5703125" customWidth="true"/>
-    <col min="10" max="10" width="19.85546875" customWidth="true"/>
-    <col min="11" max="11" width="17.140625" customWidth="true"/>
-    <col min="12" max="12" width="16.7109375" customWidth="true"/>
-    <col min="13" max="13" width="14" customWidth="true"/>
-    <col min="14" max="14" width="16.7109375" customWidth="true"/>
-    <col min="15" max="15" width="14" customWidth="true"/>
-    <col min="16" max="16" width="17.140625" customWidth="true"/>
-    <col min="17" max="17" width="14.42578125" customWidth="true"/>
-    <col min="18" max="18" width="13.7109375" customWidth="true"/>
+    <col min="6" max="6" width="19.140625" customWidth="true"/>
+    <col min="7" max="7" width="16.42578125" customWidth="true"/>
+    <col min="8" max="8" width="15.85546875" customWidth="true"/>
+    <col min="9" max="9" width="13.140625" customWidth="true"/>
+    <col min="10" max="10" width="15.7109375" customWidth="true"/>
+    <col min="11" max="11" width="13" customWidth="true"/>
+    <col min="12" max="12" width="16.140625" customWidth="true"/>
+    <col min="13" max="13" width="13.42578125" customWidth="true"/>
+    <col min="14" max="14" width="17.28515625" customWidth="true"/>
+    <col min="15" max="15" width="14.5703125" customWidth="true"/>
+    <col min="16" max="16" width="19.85546875" customWidth="true"/>
+    <col min="17" max="17" width="17.140625" customWidth="true"/>
+    <col min="18" max="18" width="16.7109375" customWidth="true"/>
+    <col min="19" max="19" width="14" customWidth="true"/>
+    <col min="20" max="20" width="16.7109375" customWidth="true"/>
+    <col min="21" max="21" width="14" customWidth="true"/>
+    <col min="22" max="22" width="17.140625" customWidth="true"/>
+    <col min="23" max="23" width="14.42578125" customWidth="true"/>
+    <col min="24" max="24" width="13.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2753,6 +2777,24 @@
         <v>72</v>
       </c>
       <c r="R1" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="S1" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="T1" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="U1" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="V1" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="W1" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="X1" s="0" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2773,42 +2815,60 @@
         <v>10.81</v>
       </c>
       <c r="F2" s="0">
+        <v>72.829999999999998</v>
+      </c>
+      <c r="G2" s="0">
+        <v>75.170000000000002</v>
+      </c>
+      <c r="H2" s="0">
+        <v>44.600000000000001</v>
+      </c>
+      <c r="I2" s="0">
+        <v>21.710000000000001</v>
+      </c>
+      <c r="J2" s="0">
+        <v>17.25</v>
+      </c>
+      <c r="K2" s="0">
+        <v>15</v>
+      </c>
+      <c r="L2" s="0">
         <v>62.880000000000003</v>
       </c>
-      <c r="G2" s="0">
+      <c r="M2" s="0">
         <v>12.16</v>
       </c>
-      <c r="H2" s="0">
+      <c r="N2" s="0">
         <v>52.009999999999998</v>
       </c>
-      <c r="I2" s="0">
+      <c r="O2" s="0">
         <v>6.5800000000000001</v>
       </c>
-      <c r="J2" s="0">
+      <c r="P2" s="0">
         <v>68.680000000000007</v>
       </c>
-      <c r="K2" s="0">
+      <c r="Q2" s="0">
         <v>7.5199999999999996</v>
       </c>
-      <c r="L2" s="0">
+      <c r="R2" s="0">
         <v>20.850000000000001</v>
       </c>
-      <c r="M2" s="0">
+      <c r="S2" s="0">
         <v>3.3500000000000001</v>
       </c>
-      <c r="N2" s="0">
+      <c r="T2" s="0">
         <v>28.149999999999999</v>
       </c>
-      <c r="O2" s="0">
+      <c r="U2" s="0">
         <v>3.23</v>
       </c>
-      <c r="P2" s="0">
+      <c r="V2" s="0">
         <v>26.140000000000001</v>
       </c>
-      <c r="Q2" s="0">
+      <c r="W2" s="0">
         <v>9.6899999999999995</v>
       </c>
-      <c r="R2" s="0">
+      <c r="X2" s="0">
         <v>7</v>
       </c>
     </row>
@@ -2829,42 +2889,60 @@
         <v>6.3099999999999996</v>
       </c>
       <c r="F3" s="0">
+        <v>64.640000000000001</v>
+      </c>
+      <c r="G3" s="0">
+        <v>26.949999999999999</v>
+      </c>
+      <c r="H3" s="0">
+        <v>80.120000000000005</v>
+      </c>
+      <c r="I3" s="0">
+        <v>54.57</v>
+      </c>
+      <c r="J3" s="0">
+        <v>14.390000000000001</v>
+      </c>
+      <c r="K3" s="0">
+        <v>7.79</v>
+      </c>
+      <c r="L3" s="0">
         <v>35.039999999999999</v>
       </c>
-      <c r="G3" s="0">
+      <c r="M3" s="0">
         <v>6.1299999999999999</v>
       </c>
-      <c r="H3" s="0">
+      <c r="N3" s="0">
         <v>80.659999999999997</v>
       </c>
-      <c r="I3" s="0">
+      <c r="O3" s="0">
         <v>15.5</v>
       </c>
-      <c r="J3" s="0">
+      <c r="P3" s="0">
         <v>86.950000000000003</v>
       </c>
-      <c r="K3" s="0">
+      <c r="Q3" s="0">
         <v>15.35</v>
       </c>
-      <c r="L3" s="0">
+      <c r="R3" s="0">
         <v>25.379999999999999</v>
       </c>
-      <c r="M3" s="0">
+      <c r="S3" s="0">
         <v>5.6100000000000003</v>
       </c>
-      <c r="N3" s="0">
+      <c r="T3" s="0">
         <v>24.260000000000002</v>
       </c>
-      <c r="O3" s="0">
+      <c r="U3" s="0">
         <v>4</v>
       </c>
-      <c r="P3" s="0">
+      <c r="V3" s="0">
         <v>25.489999999999998</v>
       </c>
-      <c r="Q3" s="0">
+      <c r="W3" s="0">
         <v>4.9500000000000002</v>
       </c>
-      <c r="R3" s="0">
+      <c r="X3" s="0">
         <v>7</v>
       </c>
     </row>
@@ -2885,42 +2963,60 @@
         <v>6.0999999999999996</v>
       </c>
       <c r="F4" s="0">
+        <v>79.140000000000001</v>
+      </c>
+      <c r="G4" s="0">
+        <v>70.719999999999999</v>
+      </c>
+      <c r="H4" s="0">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="I4" s="0">
+        <v>23.449999999999999</v>
+      </c>
+      <c r="J4" s="0">
+        <v>15.85</v>
+      </c>
+      <c r="K4" s="0">
+        <v>11.77</v>
+      </c>
+      <c r="L4" s="0">
         <v>78.170000000000002</v>
       </c>
-      <c r="G4" s="0">
+      <c r="M4" s="0">
         <v>10.18</v>
       </c>
-      <c r="H4" s="0">
+      <c r="N4" s="0">
         <v>53.350000000000001</v>
       </c>
-      <c r="I4" s="0">
+      <c r="O4" s="0">
         <v>6.1500000000000004</v>
       </c>
-      <c r="J4" s="0">
+      <c r="P4" s="0">
         <v>69.170000000000002</v>
       </c>
-      <c r="K4" s="0">
+      <c r="Q4" s="0">
         <v>6.2199999999999998</v>
       </c>
-      <c r="L4" s="0">
+      <c r="R4" s="0">
         <v>18.16</v>
       </c>
-      <c r="M4" s="0">
+      <c r="S4" s="0">
         <v>4.9100000000000001</v>
       </c>
-      <c r="N4" s="0">
+      <c r="T4" s="0">
         <v>29.07</v>
       </c>
-      <c r="O4" s="0">
+      <c r="U4" s="0">
         <v>4.0499999999999998</v>
       </c>
-      <c r="P4" s="0">
+      <c r="V4" s="0">
         <v>22.350000000000001</v>
       </c>
-      <c r="Q4" s="0">
+      <c r="W4" s="0">
         <v>15.539999999999999</v>
       </c>
-      <c r="R4" s="0">
+      <c r="X4" s="0">
         <v>7</v>
       </c>
     </row>
@@ -2941,42 +3037,60 @@
         <v>6.46</v>
       </c>
       <c r="F5" s="0">
+        <v>65.609999999999999</v>
+      </c>
+      <c r="G5" s="0">
+        <v>32.109999999999999</v>
+      </c>
+      <c r="H5" s="0">
+        <v>89.120000000000005</v>
+      </c>
+      <c r="I5" s="0">
+        <v>58.18</v>
+      </c>
+      <c r="J5" s="0">
+        <v>9.4600000000000009</v>
+      </c>
+      <c r="K5" s="0">
+        <v>3.7000000000000002</v>
+      </c>
+      <c r="L5" s="0">
         <v>37.740000000000002</v>
       </c>
-      <c r="G5" s="0">
+      <c r="M5" s="0">
         <v>4.7699999999999996</v>
       </c>
-      <c r="H5" s="0">
+      <c r="N5" s="0">
         <v>93.290000000000006</v>
       </c>
-      <c r="I5" s="0">
+      <c r="O5" s="0">
         <v>13.69</v>
       </c>
-      <c r="J5" s="0">
+      <c r="P5" s="0">
         <v>93.260000000000005</v>
       </c>
-      <c r="K5" s="0">
+      <c r="Q5" s="0">
         <v>10.970000000000001</v>
       </c>
-      <c r="L5" s="0">
+      <c r="R5" s="0">
         <v>24.289999999999999</v>
       </c>
-      <c r="M5" s="0">
+      <c r="S5" s="0">
         <v>4.4000000000000004</v>
       </c>
-      <c r="N5" s="0">
+      <c r="T5" s="0">
         <v>23.350000000000001</v>
       </c>
-      <c r="O5" s="0">
+      <c r="U5" s="0">
         <v>5.2800000000000002</v>
       </c>
-      <c r="P5" s="0">
+      <c r="V5" s="0">
         <v>25.710000000000001</v>
       </c>
-      <c r="Q5" s="0">
+      <c r="W5" s="0">
         <v>7.2800000000000002</v>
       </c>
-      <c r="R5" s="0">
+      <c r="X5" s="0">
         <v>7</v>
       </c>
     </row>
@@ -2997,42 +3111,60 @@
         <v>20.129999999999999</v>
       </c>
       <c r="F6" s="0">
+        <v>86.079999999999998</v>
+      </c>
+      <c r="G6" s="0">
+        <v>68.299999999999997</v>
+      </c>
+      <c r="H6" s="0">
+        <v>40.829999999999998</v>
+      </c>
+      <c r="I6" s="0">
+        <v>17.719999999999999</v>
+      </c>
+      <c r="J6" s="0">
+        <v>16.059999999999999</v>
+      </c>
+      <c r="K6" s="0">
+        <v>10.630000000000001</v>
+      </c>
+      <c r="L6" s="0">
         <v>82.890000000000001</v>
       </c>
-      <c r="G6" s="0">
+      <c r="M6" s="0">
         <v>9.6400000000000006</v>
       </c>
-      <c r="H6" s="0">
+      <c r="N6" s="0">
         <v>52.950000000000003</v>
       </c>
-      <c r="I6" s="0">
+      <c r="O6" s="0">
         <v>5.9900000000000002</v>
       </c>
-      <c r="J6" s="0">
+      <c r="P6" s="0">
         <v>65.109999999999999</v>
       </c>
-      <c r="K6" s="0">
+      <c r="Q6" s="0">
         <v>9.0700000000000003</v>
       </c>
-      <c r="L6" s="0">
+      <c r="R6" s="0">
         <v>20.960000000000001</v>
       </c>
-      <c r="M6" s="0">
+      <c r="S6" s="0">
         <v>3.02</v>
       </c>
-      <c r="N6" s="0">
+      <c r="T6" s="0">
         <v>30.140000000000001</v>
       </c>
-      <c r="O6" s="0">
+      <c r="U6" s="0">
         <v>4.6500000000000004</v>
       </c>
-      <c r="P6" s="0">
+      <c r="V6" s="0">
         <v>20.699999999999999</v>
       </c>
-      <c r="Q6" s="0">
+      <c r="W6" s="0">
         <v>12.26</v>
       </c>
-      <c r="R6" s="0">
+      <c r="X6" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3053,42 +3185,60 @@
         <v>15.25</v>
       </c>
       <c r="F7" s="0">
+        <v>76.569999999999993</v>
+      </c>
+      <c r="G7" s="0">
+        <v>17.27</v>
+      </c>
+      <c r="H7" s="0">
+        <v>102.93000000000001</v>
+      </c>
+      <c r="I7" s="0">
+        <v>52.899999999999999</v>
+      </c>
+      <c r="J7" s="0">
+        <v>15.300000000000001</v>
+      </c>
+      <c r="K7" s="0">
+        <v>13.69</v>
+      </c>
+      <c r="L7" s="0">
         <v>40.200000000000003</v>
       </c>
-      <c r="G7" s="0">
+      <c r="M7" s="0">
         <v>8.0800000000000001</v>
       </c>
-      <c r="H7" s="0">
+      <c r="N7" s="0">
         <v>101.45999999999999</v>
       </c>
-      <c r="I7" s="0">
+      <c r="O7" s="0">
         <v>11.26</v>
       </c>
-      <c r="J7" s="0">
+      <c r="P7" s="0">
         <v>97.459999999999994</v>
       </c>
-      <c r="K7" s="0">
+      <c r="Q7" s="0">
         <v>13.619999999999999</v>
       </c>
-      <c r="L7" s="0">
+      <c r="R7" s="0">
         <v>25.41</v>
       </c>
-      <c r="M7" s="0">
+      <c r="S7" s="0">
         <v>4.3099999999999996</v>
       </c>
-      <c r="N7" s="0">
+      <c r="T7" s="0">
         <v>21.789999999999999</v>
       </c>
-      <c r="O7" s="0">
+      <c r="U7" s="0">
         <v>6.5700000000000003</v>
       </c>
-      <c r="P7" s="0">
+      <c r="V7" s="0">
         <v>24.579999999999998</v>
       </c>
-      <c r="Q7" s="0">
+      <c r="W7" s="0">
         <v>9.5</v>
       </c>
-      <c r="R7" s="0">
+      <c r="X7" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3109,42 +3259,60 @@
         <v>7.3499999999999996</v>
       </c>
       <c r="F8" s="0">
+        <v>70.859999999999999</v>
+      </c>
+      <c r="G8" s="0">
+        <v>66.519999999999996</v>
+      </c>
+      <c r="H8" s="0">
+        <v>49.039999999999999</v>
+      </c>
+      <c r="I8" s="0">
+        <v>21.190000000000001</v>
+      </c>
+      <c r="J8" s="0">
+        <v>14.199999999999999</v>
+      </c>
+      <c r="K8" s="0">
+        <v>15.68</v>
+      </c>
+      <c r="L8" s="0">
         <v>66.510000000000005</v>
       </c>
-      <c r="G8" s="0">
+      <c r="M8" s="0">
         <v>9.8399999999999999</v>
       </c>
-      <c r="H8" s="0">
+      <c r="N8" s="0">
         <v>51.700000000000003</v>
       </c>
-      <c r="I8" s="0">
+      <c r="O8" s="0">
         <v>5.6100000000000003</v>
       </c>
-      <c r="J8" s="0">
+      <c r="P8" s="0">
         <v>70.969999999999999</v>
       </c>
-      <c r="K8" s="0">
+      <c r="Q8" s="0">
         <v>6.7400000000000002</v>
       </c>
-      <c r="L8" s="0">
+      <c r="R8" s="0">
         <v>18.02</v>
       </c>
-      <c r="M8" s="0">
+      <c r="S8" s="0">
         <v>2.8300000000000001</v>
       </c>
-      <c r="N8" s="0">
+      <c r="T8" s="0">
         <v>31.300000000000001</v>
       </c>
-      <c r="O8" s="0">
+      <c r="U8" s="0">
         <v>3.8100000000000001</v>
       </c>
-      <c r="P8" s="0">
+      <c r="V8" s="0">
         <v>28.289999999999999</v>
       </c>
-      <c r="Q8" s="0">
+      <c r="W8" s="0">
         <v>12.98</v>
       </c>
-      <c r="R8" s="0">
+      <c r="X8" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3165,42 +3333,60 @@
         <v>9.8800000000000008</v>
       </c>
       <c r="F9" s="0">
+        <v>70.370000000000005</v>
+      </c>
+      <c r="G9" s="0">
+        <v>24.57</v>
+      </c>
+      <c r="H9" s="0">
+        <v>76.620000000000005</v>
+      </c>
+      <c r="I9" s="0">
+        <v>54.32</v>
+      </c>
+      <c r="J9" s="0">
+        <v>14.9</v>
+      </c>
+      <c r="K9" s="0">
+        <v>10.16</v>
+      </c>
+      <c r="L9" s="0">
         <v>36.539999999999999</v>
       </c>
-      <c r="G9" s="0">
+      <c r="M9" s="0">
         <v>5.54</v>
       </c>
-      <c r="H9" s="0">
+      <c r="N9" s="0">
         <v>82.299999999999997</v>
       </c>
-      <c r="I9" s="0">
+      <c r="O9" s="0">
         <v>12.83</v>
       </c>
-      <c r="J9" s="0">
+      <c r="P9" s="0">
         <v>91.560000000000002</v>
       </c>
-      <c r="K9" s="0">
+      <c r="Q9" s="0">
         <v>14.81</v>
       </c>
-      <c r="L9" s="0">
+      <c r="R9" s="0">
         <v>24.84</v>
       </c>
-      <c r="M9" s="0">
+      <c r="S9" s="0">
         <v>4.2699999999999996</v>
       </c>
-      <c r="N9" s="0">
+      <c r="T9" s="0">
         <v>24.379999999999999</v>
       </c>
-      <c r="O9" s="0">
+      <c r="U9" s="0">
         <v>3.1499999999999999</v>
       </c>
-      <c r="P9" s="0">
+      <c r="V9" s="0">
         <v>26.030000000000001</v>
       </c>
-      <c r="Q9" s="0">
+      <c r="W9" s="0">
         <v>7.1600000000000001</v>
       </c>
-      <c r="R9" s="0">
+      <c r="X9" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3221,42 +3407,60 @@
         <v>14.06</v>
       </c>
       <c r="F10" s="0">
+        <v>83.310000000000002</v>
+      </c>
+      <c r="G10" s="0">
+        <v>57.990000000000002</v>
+      </c>
+      <c r="H10" s="0">
+        <v>40.509999999999998</v>
+      </c>
+      <c r="I10" s="0">
+        <v>20.690000000000001</v>
+      </c>
+      <c r="J10" s="0">
+        <v>15.17</v>
+      </c>
+      <c r="K10" s="0">
+        <v>11.74</v>
+      </c>
+      <c r="L10" s="0">
         <v>80.540000000000006</v>
       </c>
-      <c r="G10" s="0">
+      <c r="M10" s="0">
         <v>9.3499999999999996</v>
       </c>
-      <c r="H10" s="0">
+      <c r="N10" s="0">
         <v>53.719999999999999</v>
       </c>
-      <c r="I10" s="0">
+      <c r="O10" s="0">
         <v>5.4800000000000004</v>
       </c>
-      <c r="J10" s="0">
+      <c r="P10" s="0">
         <v>68.349999999999994</v>
       </c>
-      <c r="K10" s="0">
+      <c r="Q10" s="0">
         <v>5.4199999999999999</v>
       </c>
-      <c r="L10" s="0">
+      <c r="R10" s="0">
         <v>17.199999999999999</v>
       </c>
-      <c r="M10" s="0">
+      <c r="S10" s="0">
         <v>5.1100000000000003</v>
       </c>
-      <c r="N10" s="0">
+      <c r="T10" s="0">
         <v>31.140000000000001</v>
       </c>
-      <c r="O10" s="0">
+      <c r="U10" s="0">
         <v>3.6000000000000001</v>
       </c>
-      <c r="P10" s="0">
+      <c r="V10" s="0">
         <v>21.690000000000001</v>
       </c>
-      <c r="Q10" s="0">
+      <c r="W10" s="0">
         <v>15.52</v>
       </c>
-      <c r="R10" s="0">
+      <c r="X10" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3277,42 +3481,60 @@
         <v>13.960000000000001</v>
       </c>
       <c r="F11" s="0">
+        <v>64.560000000000002</v>
+      </c>
+      <c r="G11" s="0">
+        <v>24.699999999999999</v>
+      </c>
+      <c r="H11" s="0">
+        <v>85.590000000000003</v>
+      </c>
+      <c r="I11" s="0">
+        <v>53.140000000000001</v>
+      </c>
+      <c r="J11" s="0">
+        <v>10.99</v>
+      </c>
+      <c r="K11" s="0">
+        <v>5.6600000000000001</v>
+      </c>
+      <c r="L11" s="0">
         <v>38.439999999999998</v>
       </c>
-      <c r="G11" s="0">
+      <c r="M11" s="0">
         <v>7.0199999999999996</v>
       </c>
-      <c r="H11" s="0">
+      <c r="N11" s="0">
         <v>95.650000000000006</v>
       </c>
-      <c r="I11" s="0">
+      <c r="O11" s="0">
         <v>12.390000000000001</v>
       </c>
-      <c r="J11" s="0">
+      <c r="P11" s="0">
         <v>95.280000000000001</v>
       </c>
-      <c r="K11" s="0">
+      <c r="Q11" s="0">
         <v>13.130000000000001</v>
       </c>
-      <c r="L11" s="0">
+      <c r="R11" s="0">
         <v>24.760000000000002</v>
       </c>
-      <c r="M11" s="0">
+      <c r="S11" s="0">
         <v>5.8099999999999996</v>
       </c>
-      <c r="N11" s="0">
+      <c r="T11" s="0">
         <v>20.18</v>
       </c>
-      <c r="O11" s="0">
+      <c r="U11" s="0">
         <v>5.5800000000000001</v>
       </c>
-      <c r="P11" s="0">
+      <c r="V11" s="0">
         <v>22.510000000000002</v>
       </c>
-      <c r="Q11" s="0">
+      <c r="W11" s="0">
         <v>6.0700000000000003</v>
       </c>
-      <c r="R11" s="0">
+      <c r="X11" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3333,42 +3555,60 @@
         <v>16.210000000000001</v>
       </c>
       <c r="F12" s="0">
+        <v>87.430000000000007</v>
+      </c>
+      <c r="G12" s="0">
+        <v>67.709999999999994</v>
+      </c>
+      <c r="H12" s="0">
+        <v>48.359999999999999</v>
+      </c>
+      <c r="I12" s="0">
+        <v>20.16</v>
+      </c>
+      <c r="J12" s="0">
+        <v>17.359999999999999</v>
+      </c>
+      <c r="K12" s="0">
+        <v>14.119999999999999</v>
+      </c>
+      <c r="L12" s="0">
         <v>88.109999999999999</v>
       </c>
-      <c r="G12" s="0">
+      <c r="M12" s="0">
         <v>8.2100000000000009</v>
       </c>
-      <c r="H12" s="0">
+      <c r="N12" s="0">
         <v>53.340000000000003</v>
       </c>
-      <c r="I12" s="0">
+      <c r="O12" s="0">
         <v>6.5</v>
       </c>
-      <c r="J12" s="0">
+      <c r="P12" s="0">
         <v>68.359999999999999</v>
       </c>
-      <c r="K12" s="0">
+      <c r="Q12" s="0">
         <v>7.8200000000000003</v>
       </c>
-      <c r="L12" s="0">
+      <c r="R12" s="0">
         <v>18.760000000000002</v>
       </c>
-      <c r="M12" s="0">
+      <c r="S12" s="0">
         <v>4.3300000000000001</v>
       </c>
-      <c r="N12" s="0">
+      <c r="T12" s="0">
         <v>29.239999999999998</v>
       </c>
-      <c r="O12" s="0">
+      <c r="U12" s="0">
         <v>4.3799999999999999</v>
       </c>
-      <c r="P12" s="0">
+      <c r="V12" s="0">
         <v>17.77</v>
       </c>
-      <c r="Q12" s="0">
+      <c r="W12" s="0">
         <v>12.91</v>
       </c>
-      <c r="R12" s="0">
+      <c r="X12" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3389,42 +3629,60 @@
         <v>23.670000000000002</v>
       </c>
       <c r="F13" s="0">
+        <v>76.739999999999995</v>
+      </c>
+      <c r="G13" s="0">
+        <v>24.120000000000001</v>
+      </c>
+      <c r="H13" s="0">
+        <v>87.950000000000003</v>
+      </c>
+      <c r="I13" s="0">
+        <v>53.789999999999999</v>
+      </c>
+      <c r="J13" s="0">
+        <v>12.970000000000001</v>
+      </c>
+      <c r="K13" s="0">
+        <v>6.1900000000000004</v>
+      </c>
+      <c r="L13" s="0">
         <v>42.329999999999998</v>
       </c>
-      <c r="G13" s="0">
+      <c r="M13" s="0">
         <v>9.3399999999999999</v>
       </c>
-      <c r="H13" s="0">
+      <c r="N13" s="0">
         <v>108.52</v>
       </c>
-      <c r="I13" s="0">
+      <c r="O13" s="0">
         <v>13.279999999999999</v>
       </c>
-      <c r="J13" s="0">
+      <c r="P13" s="0">
         <v>101.37</v>
       </c>
-      <c r="K13" s="0">
+      <c r="Q13" s="0">
         <v>11.24</v>
       </c>
-      <c r="L13" s="0">
+      <c r="R13" s="0">
         <v>25.559999999999999</v>
       </c>
-      <c r="M13" s="0">
+      <c r="S13" s="0">
         <v>2.6800000000000002</v>
       </c>
-      <c r="N13" s="0">
+      <c r="T13" s="0">
         <v>23.890000000000001</v>
       </c>
-      <c r="O13" s="0">
+      <c r="U13" s="0">
         <v>3.8900000000000001</v>
       </c>
-      <c r="P13" s="0">
+      <c r="V13" s="0">
         <v>25.539999999999999</v>
       </c>
-      <c r="Q13" s="0">
+      <c r="W13" s="0">
         <v>8.6099999999999994</v>
       </c>
-      <c r="R13" s="0">
+      <c r="X13" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3445,42 +3703,60 @@
         <v>4.6699999999999999</v>
       </c>
       <c r="F14" s="0">
+        <v>30.140000000000001</v>
+      </c>
+      <c r="G14" s="0">
+        <v>12.83</v>
+      </c>
+      <c r="H14" s="0">
+        <v>46.310000000000002</v>
+      </c>
+      <c r="I14" s="0">
+        <v>24.609999999999999</v>
+      </c>
+      <c r="J14" s="0">
+        <v>7.8300000000000001</v>
+      </c>
+      <c r="K14" s="0">
+        <v>3.21</v>
+      </c>
+      <c r="L14" s="0">
         <v>26.300000000000001</v>
       </c>
-      <c r="G14" s="0">
+      <c r="M14" s="0">
         <v>3.1299999999999999</v>
       </c>
-      <c r="H14" s="0">
+      <c r="N14" s="0">
         <v>48.450000000000003</v>
       </c>
-      <c r="I14" s="0">
+      <c r="O14" s="0">
         <v>5.21</v>
       </c>
-      <c r="J14" s="0">
+      <c r="P14" s="0">
         <v>68.290000000000006</v>
       </c>
-      <c r="K14" s="0">
+      <c r="Q14" s="0">
         <v>5.8300000000000001</v>
       </c>
-      <c r="L14" s="0">
+      <c r="R14" s="0">
         <v>18.789999999999999</v>
       </c>
-      <c r="M14" s="0">
+      <c r="S14" s="0">
         <v>3.5499999999999998</v>
       </c>
-      <c r="N14" s="0">
+      <c r="T14" s="0">
         <v>26.699999999999999</v>
       </c>
-      <c r="O14" s="0">
+      <c r="U14" s="0">
         <v>2.04</v>
       </c>
-      <c r="P14" s="0">
+      <c r="V14" s="0">
         <v>24.07</v>
       </c>
-      <c r="Q14" s="0">
+      <c r="W14" s="0">
         <v>3.3900000000000001</v>
       </c>
-      <c r="R14" s="0">
+      <c r="X14" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3490,7 +3766,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.140625" customWidth="true"/>
@@ -3498,19 +3774,25 @@
     <col min="3" max="3" width="14.85546875" customWidth="true"/>
     <col min="4" max="4" width="17" customWidth="true"/>
     <col min="5" max="5" width="14.28515625" customWidth="true"/>
-    <col min="6" max="6" width="16.140625" customWidth="true"/>
-    <col min="7" max="7" width="13.42578125" customWidth="true"/>
-    <col min="8" max="8" width="17.28515625" customWidth="true"/>
-    <col min="9" max="9" width="14.5703125" customWidth="true"/>
-    <col min="10" max="10" width="19.85546875" customWidth="true"/>
-    <col min="11" max="11" width="17.140625" customWidth="true"/>
-    <col min="12" max="12" width="16.7109375" customWidth="true"/>
-    <col min="13" max="13" width="14" customWidth="true"/>
-    <col min="14" max="14" width="16.7109375" customWidth="true"/>
-    <col min="15" max="15" width="14" customWidth="true"/>
-    <col min="16" max="16" width="17.140625" customWidth="true"/>
-    <col min="17" max="17" width="14.42578125" customWidth="true"/>
-    <col min="18" max="18" width="13.7109375" customWidth="true"/>
+    <col min="6" max="6" width="19.140625" customWidth="true"/>
+    <col min="7" max="7" width="16.42578125" customWidth="true"/>
+    <col min="8" max="8" width="15.85546875" customWidth="true"/>
+    <col min="9" max="9" width="13.140625" customWidth="true"/>
+    <col min="10" max="10" width="15.7109375" customWidth="true"/>
+    <col min="11" max="11" width="13" customWidth="true"/>
+    <col min="12" max="12" width="16.140625" customWidth="true"/>
+    <col min="13" max="13" width="13.42578125" customWidth="true"/>
+    <col min="14" max="14" width="17.28515625" customWidth="true"/>
+    <col min="15" max="15" width="14.5703125" customWidth="true"/>
+    <col min="16" max="16" width="19.85546875" customWidth="true"/>
+    <col min="17" max="17" width="17.140625" customWidth="true"/>
+    <col min="18" max="18" width="16.7109375" customWidth="true"/>
+    <col min="19" max="19" width="14" customWidth="true"/>
+    <col min="20" max="20" width="16.7109375" customWidth="true"/>
+    <col min="21" max="21" width="14" customWidth="true"/>
+    <col min="22" max="22" width="17.140625" customWidth="true"/>
+    <col min="23" max="23" width="14.42578125" customWidth="true"/>
+    <col min="24" max="24" width="13.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3566,6 +3848,24 @@
         <v>72</v>
       </c>
       <c r="R1" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="S1" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="T1" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="U1" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="V1" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="W1" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="X1" s="0" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3586,42 +3886,60 @@
         <v>14.949999999999999</v>
       </c>
       <c r="F2" s="0">
+        <v>47.229999999999997</v>
+      </c>
+      <c r="G2" s="0">
+        <v>74.469999999999999</v>
+      </c>
+      <c r="H2" s="0">
+        <v>-1.71</v>
+      </c>
+      <c r="I2" s="0">
+        <v>10.26</v>
+      </c>
+      <c r="J2" s="0">
+        <v>9.4199999999999999</v>
+      </c>
+      <c r="K2" s="0">
+        <v>13.279999999999999</v>
+      </c>
+      <c r="L2" s="0">
         <v>36.079999999999998</v>
       </c>
-      <c r="G2" s="0">
+      <c r="M2" s="0">
         <v>9.5800000000000001</v>
       </c>
-      <c r="H2" s="0">
+      <c r="N2" s="0">
         <v>3.5600000000000001</v>
       </c>
-      <c r="I2" s="0">
+      <c r="O2" s="0">
         <v>3.1499999999999999</v>
       </c>
-      <c r="J2" s="0">
+      <c r="P2" s="0">
         <v>0.38</v>
       </c>
-      <c r="K2" s="0">
+      <c r="Q2" s="0">
         <v>4.8300000000000001</v>
       </c>
-      <c r="L2" s="0">
+      <c r="R2" s="0">
         <v>1.49</v>
       </c>
-      <c r="M2" s="0">
+      <c r="S2" s="0">
         <v>2.52</v>
       </c>
-      <c r="N2" s="0">
+      <c r="T2" s="0">
         <v>1.45</v>
       </c>
-      <c r="O2" s="0">
+      <c r="U2" s="0">
         <v>3.4300000000000002</v>
       </c>
-      <c r="P2" s="0">
+      <c r="V2" s="0">
         <v>2.0699999999999998</v>
       </c>
-      <c r="Q2" s="0">
+      <c r="W2" s="0">
         <v>8.9700000000000006</v>
       </c>
-      <c r="R2" s="0">
+      <c r="X2" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3642,42 +3960,60 @@
         <v>8.7400000000000002</v>
       </c>
       <c r="F3" s="0">
+        <v>39.030000000000001</v>
+      </c>
+      <c r="G3" s="0">
+        <v>27.48</v>
+      </c>
+      <c r="H3" s="0">
+        <v>33.810000000000002</v>
+      </c>
+      <c r="I3" s="0">
+        <v>33.420000000000002</v>
+      </c>
+      <c r="J3" s="0">
+        <v>6.5599999999999996</v>
+      </c>
+      <c r="K3" s="0">
+        <v>5.75</v>
+      </c>
+      <c r="L3" s="0">
         <v>8.2400000000000002</v>
       </c>
-      <c r="G3" s="0">
+      <c r="M3" s="0">
         <v>4.0599999999999996</v>
       </c>
-      <c r="H3" s="0">
+      <c r="N3" s="0">
         <v>32.200000000000003</v>
       </c>
-      <c r="I3" s="0">
+      <c r="O3" s="0">
         <v>14.449999999999999</v>
       </c>
-      <c r="J3" s="0">
+      <c r="P3" s="0">
         <v>18.66</v>
       </c>
-      <c r="K3" s="0">
+      <c r="Q3" s="0">
         <v>11.800000000000001</v>
       </c>
-      <c r="L3" s="0">
+      <c r="R3" s="0">
         <v>6.0199999999999996</v>
       </c>
-      <c r="M3" s="0">
+      <c r="S3" s="0">
         <v>4.7400000000000002</v>
       </c>
-      <c r="N3" s="0">
+      <c r="T3" s="0">
         <v>-2.4399999999999999</v>
       </c>
-      <c r="O3" s="0">
+      <c r="U3" s="0">
         <v>3.4100000000000001</v>
       </c>
-      <c r="P3" s="0">
+      <c r="V3" s="0">
         <v>1.4099999999999999</v>
       </c>
-      <c r="Q3" s="0">
+      <c r="W3" s="0">
         <v>3.2999999999999998</v>
       </c>
-      <c r="R3" s="0">
+      <c r="X3" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3698,42 +4034,60 @@
         <v>8.3499999999999996</v>
       </c>
       <c r="F4" s="0">
+        <v>49</v>
+      </c>
+      <c r="G4" s="0">
+        <v>70.689999999999998</v>
+      </c>
+      <c r="H4" s="0">
+        <v>-7.0099999999999998</v>
+      </c>
+      <c r="I4" s="0">
+        <v>11.779999999999999</v>
+      </c>
+      <c r="J4" s="0">
+        <v>8.0199999999999996</v>
+      </c>
+      <c r="K4" s="0">
+        <v>11.609999999999999</v>
+      </c>
+      <c r="L4" s="0">
         <v>51.869999999999997</v>
       </c>
-      <c r="G4" s="0">
+      <c r="M4" s="0">
         <v>9.1300000000000008</v>
       </c>
-      <c r="H4" s="0">
+      <c r="N4" s="0">
         <v>4.8899999999999997</v>
       </c>
-      <c r="I4" s="0">
+      <c r="O4" s="0">
         <v>3.6699999999999999</v>
       </c>
-      <c r="J4" s="0">
+      <c r="P4" s="0">
         <v>0.88</v>
       </c>
-      <c r="K4" s="0">
+      <c r="Q4" s="0">
         <v>4.1500000000000004</v>
       </c>
-      <c r="L4" s="0">
+      <c r="R4" s="0">
         <v>-0.63</v>
       </c>
-      <c r="M4" s="0">
+      <c r="S4" s="0">
         <v>2.5</v>
       </c>
-      <c r="N4" s="0">
+      <c r="T4" s="0">
         <v>2.3700000000000001</v>
       </c>
-      <c r="O4" s="0">
+      <c r="U4" s="0">
         <v>4.9900000000000002</v>
       </c>
-      <c r="P4" s="0">
+      <c r="V4" s="0">
         <v>-1.73</v>
       </c>
-      <c r="Q4" s="0">
+      <c r="W4" s="0">
         <v>14.48</v>
       </c>
-      <c r="R4" s="0">
+      <c r="X4" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3754,42 +4108,60 @@
         <v>6.1500000000000004</v>
       </c>
       <c r="F5" s="0">
+        <v>35.469999999999999</v>
+      </c>
+      <c r="G5" s="0">
+        <v>41.259999999999998</v>
+      </c>
+      <c r="H5" s="0">
+        <v>42.810000000000002</v>
+      </c>
+      <c r="I5" s="0">
+        <v>35.060000000000002</v>
+      </c>
+      <c r="J5" s="0">
+        <v>1.6299999999999999</v>
+      </c>
+      <c r="K5" s="0">
+        <v>3.6000000000000001</v>
+      </c>
+      <c r="L5" s="0">
         <v>11.43</v>
       </c>
-      <c r="G5" s="0">
+      <c r="M5" s="0">
         <v>5.0899999999999999</v>
       </c>
-      <c r="H5" s="0">
+      <c r="N5" s="0">
         <v>44.829999999999998</v>
       </c>
-      <c r="I5" s="0">
+      <c r="O5" s="0">
         <v>13.56</v>
       </c>
-      <c r="J5" s="0">
+      <c r="P5" s="0">
         <v>24.960000000000001</v>
       </c>
-      <c r="K5" s="0">
+      <c r="Q5" s="0">
         <v>7.9100000000000001</v>
       </c>
-      <c r="L5" s="0">
+      <c r="R5" s="0">
         <v>5.5</v>
       </c>
-      <c r="M5" s="0">
+      <c r="S5" s="0">
         <v>3.46</v>
       </c>
-      <c r="N5" s="0">
+      <c r="T5" s="0">
         <v>-3.3500000000000001</v>
       </c>
-      <c r="O5" s="0">
+      <c r="U5" s="0">
         <v>4.2599999999999998</v>
       </c>
-      <c r="P5" s="0">
+      <c r="V5" s="0">
         <v>1.6399999999999999</v>
       </c>
-      <c r="Q5" s="0">
+      <c r="W5" s="0">
         <v>5.3799999999999999</v>
       </c>
-      <c r="R5" s="0">
+      <c r="X5" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3810,42 +4182,60 @@
         <v>25</v>
       </c>
       <c r="F6" s="0">
+        <v>60.469999999999999</v>
+      </c>
+      <c r="G6" s="0">
+        <v>67.180000000000007</v>
+      </c>
+      <c r="H6" s="0">
+        <v>-5.4800000000000004</v>
+      </c>
+      <c r="I6" s="0">
+        <v>13.25</v>
+      </c>
+      <c r="J6" s="0">
+        <v>8.2300000000000004</v>
+      </c>
+      <c r="K6" s="0">
+        <v>10.07</v>
+      </c>
+      <c r="L6" s="0">
         <v>56.090000000000003</v>
       </c>
-      <c r="G6" s="0">
+      <c r="M6" s="0">
         <v>7.4900000000000002</v>
       </c>
-      <c r="H6" s="0">
+      <c r="N6" s="0">
         <v>4.4900000000000002</v>
       </c>
-      <c r="I6" s="0">
+      <c r="O6" s="0">
         <v>3.1499999999999999</v>
       </c>
-      <c r="J6" s="0">
+      <c r="P6" s="0">
         <v>-3.1800000000000002</v>
       </c>
-      <c r="K6" s="0">
+      <c r="Q6" s="0">
         <v>11.050000000000001</v>
       </c>
-      <c r="L6" s="0">
+      <c r="R6" s="0">
         <v>1.6000000000000001</v>
       </c>
-      <c r="M6" s="0">
+      <c r="S6" s="0">
         <v>5.5499999999999998</v>
       </c>
-      <c r="N6" s="0">
+      <c r="T6" s="0">
         <v>3.4399999999999999</v>
       </c>
-      <c r="O6" s="0">
+      <c r="U6" s="0">
         <v>5.3799999999999999</v>
       </c>
-      <c r="P6" s="0">
+      <c r="V6" s="0">
         <v>-3.3799999999999999</v>
       </c>
-      <c r="Q6" s="0">
+      <c r="W6" s="0">
         <v>12.029999999999999</v>
       </c>
-      <c r="R6" s="0">
+      <c r="X6" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3866,42 +4256,60 @@
         <v>15.6</v>
       </c>
       <c r="F7" s="0">
+        <v>50.969999999999999</v>
+      </c>
+      <c r="G7" s="0">
+        <v>18.48</v>
+      </c>
+      <c r="H7" s="0">
+        <v>56.619999999999997</v>
+      </c>
+      <c r="I7" s="0">
+        <v>40.469999999999999</v>
+      </c>
+      <c r="J7" s="0">
+        <v>7.4800000000000004</v>
+      </c>
+      <c r="K7" s="0">
+        <v>11.710000000000001</v>
+      </c>
+      <c r="L7" s="0">
         <v>13.4</v>
       </c>
-      <c r="G7" s="0">
+      <c r="M7" s="0">
         <v>6.2000000000000002</v>
       </c>
-      <c r="H7" s="0">
+      <c r="N7" s="0">
         <v>53</v>
       </c>
-      <c r="I7" s="0">
+      <c r="O7" s="0">
         <v>10.460000000000001</v>
       </c>
-      <c r="J7" s="0">
+      <c r="P7" s="0">
         <v>29.170000000000002</v>
       </c>
-      <c r="K7" s="0">
+      <c r="Q7" s="0">
         <v>12.65</v>
       </c>
-      <c r="L7" s="0">
+      <c r="R7" s="0">
         <v>6.0499999999999998</v>
       </c>
-      <c r="M7" s="0">
+      <c r="S7" s="0">
         <v>2.6499999999999999</v>
       </c>
-      <c r="N7" s="0">
+      <c r="T7" s="0">
         <v>-4.9100000000000001</v>
       </c>
-      <c r="O7" s="0">
+      <c r="U7" s="0">
         <v>6.5199999999999996</v>
       </c>
-      <c r="P7" s="0">
+      <c r="V7" s="0">
         <v>0.51000000000000001</v>
       </c>
-      <c r="Q7" s="0">
+      <c r="W7" s="0">
         <v>8.2400000000000002</v>
       </c>
-      <c r="R7" s="0">
+      <c r="X7" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3922,42 +4330,60 @@
         <v>10.57</v>
       </c>
       <c r="F8" s="0">
+        <v>40.719999999999999</v>
+      </c>
+      <c r="G8" s="0">
+        <v>69.439999999999998</v>
+      </c>
+      <c r="H8" s="0">
+        <v>2.73</v>
+      </c>
+      <c r="I8" s="0">
+        <v>9.0500000000000007</v>
+      </c>
+      <c r="J8" s="0">
+        <v>6.3700000000000001</v>
+      </c>
+      <c r="K8" s="0">
+        <v>14.890000000000001</v>
+      </c>
+      <c r="L8" s="0">
         <v>40.210000000000001</v>
       </c>
-      <c r="G8" s="0">
+      <c r="M8" s="0">
         <v>7.0300000000000002</v>
       </c>
-      <c r="H8" s="0">
+      <c r="N8" s="0">
         <v>3.25</v>
       </c>
-      <c r="I8" s="0">
+      <c r="O8" s="0">
         <v>2.6499999999999999</v>
       </c>
-      <c r="J8" s="0">
+      <c r="P8" s="0">
         <v>2.6699999999999999</v>
       </c>
-      <c r="K8" s="0">
+      <c r="Q8" s="0">
         <v>3.0099999999999998</v>
       </c>
-      <c r="L8" s="0">
+      <c r="R8" s="0">
         <v>-0.77000000000000002</v>
       </c>
-      <c r="M8" s="0">
+      <c r="S8" s="0">
         <v>2.8799999999999999</v>
       </c>
-      <c r="N8" s="0">
+      <c r="T8" s="0">
         <v>4.5999999999999996</v>
       </c>
-      <c r="O8" s="0">
+      <c r="U8" s="0">
         <v>4.8200000000000003</v>
       </c>
-      <c r="P8" s="0">
+      <c r="V8" s="0">
         <v>4.2199999999999998</v>
       </c>
-      <c r="Q8" s="0">
+      <c r="W8" s="0">
         <v>12.85</v>
       </c>
-      <c r="R8" s="0">
+      <c r="X8" s="0">
         <v>7</v>
       </c>
     </row>
@@ -3978,42 +4404,60 @@
         <v>10.220000000000001</v>
       </c>
       <c r="F9" s="0">
+        <v>40.229999999999997</v>
+      </c>
+      <c r="G9" s="0">
+        <v>23.239999999999998</v>
+      </c>
+      <c r="H9" s="0">
+        <v>30.309999999999999</v>
+      </c>
+      <c r="I9" s="0">
+        <v>32.020000000000003</v>
+      </c>
+      <c r="J9" s="0">
+        <v>7.0700000000000003</v>
+      </c>
+      <c r="K9" s="0">
+        <v>7.8600000000000003</v>
+      </c>
+      <c r="L9" s="0">
         <v>10.24</v>
       </c>
-      <c r="G9" s="0">
+      <c r="M9" s="0">
         <v>4.29</v>
       </c>
-      <c r="H9" s="0">
+      <c r="N9" s="0">
         <v>33.840000000000003</v>
       </c>
-      <c r="I9" s="0">
+      <c r="O9" s="0">
         <v>12.140000000000001</v>
       </c>
-      <c r="J9" s="0">
+      <c r="P9" s="0">
         <v>23.27</v>
       </c>
-      <c r="K9" s="0">
+      <c r="Q9" s="0">
         <v>12.15</v>
       </c>
-      <c r="L9" s="0">
+      <c r="R9" s="0">
         <v>6.04</v>
       </c>
-      <c r="M9" s="0">
+      <c r="S9" s="0">
         <v>3.7400000000000002</v>
       </c>
-      <c r="N9" s="0">
+      <c r="T9" s="0">
         <v>-2.3300000000000001</v>
       </c>
-      <c r="O9" s="0">
+      <c r="U9" s="0">
         <v>3.48</v>
       </c>
-      <c r="P9" s="0">
+      <c r="V9" s="0">
         <v>1.96</v>
       </c>
-      <c r="Q9" s="0">
+      <c r="W9" s="0">
         <v>6.2300000000000004</v>
       </c>
-      <c r="R9" s="0">
+      <c r="X9" s="0">
         <v>7</v>
       </c>
     </row>
@@ -4034,42 +4478,60 @@
         <v>17.16</v>
       </c>
       <c r="F10" s="0">
+        <v>53.170000000000002</v>
+      </c>
+      <c r="G10" s="0">
+        <v>58.579999999999998</v>
+      </c>
+      <c r="H10" s="0">
+        <v>-5.79</v>
+      </c>
+      <c r="I10" s="0">
+        <v>12.109999999999999</v>
+      </c>
+      <c r="J10" s="0">
+        <v>7.3399999999999999</v>
+      </c>
+      <c r="K10" s="0">
+        <v>11.359999999999999</v>
+      </c>
+      <c r="L10" s="0">
         <v>54.229999999999997</v>
       </c>
-      <c r="G10" s="0">
+      <c r="M10" s="0">
         <v>7.5999999999999996</v>
       </c>
-      <c r="H10" s="0">
+      <c r="N10" s="0">
         <v>5.2599999999999998</v>
       </c>
-      <c r="I10" s="0">
+      <c r="O10" s="0">
         <v>1.6200000000000001</v>
       </c>
-      <c r="J10" s="0">
+      <c r="P10" s="0">
         <v>0.050000000000000003</v>
       </c>
-      <c r="K10" s="0">
+      <c r="Q10" s="0">
         <v>5.7000000000000002</v>
       </c>
-      <c r="L10" s="0">
+      <c r="R10" s="0">
         <v>-1.5900000000000001</v>
       </c>
-      <c r="M10" s="0">
+      <c r="S10" s="0">
         <v>2.29</v>
       </c>
-      <c r="N10" s="0">
+      <c r="T10" s="0">
         <v>4.4400000000000004</v>
       </c>
-      <c r="O10" s="0">
+      <c r="U10" s="0">
         <v>4.4100000000000001</v>
       </c>
-      <c r="P10" s="0">
+      <c r="V10" s="0">
         <v>-2.3799999999999999</v>
       </c>
-      <c r="Q10" s="0">
+      <c r="W10" s="0">
         <v>14.31</v>
       </c>
-      <c r="R10" s="0">
+      <c r="X10" s="0">
         <v>7</v>
       </c>
     </row>
@@ -4090,42 +4552,60 @@
         <v>14.01</v>
       </c>
       <c r="F11" s="0">
+        <v>34.420000000000002</v>
+      </c>
+      <c r="G11" s="0">
+        <v>34.710000000000001</v>
+      </c>
+      <c r="H11" s="0">
+        <v>39.280000000000001</v>
+      </c>
+      <c r="I11" s="0">
+        <v>32.590000000000003</v>
+      </c>
+      <c r="J11" s="0">
+        <v>3.1600000000000001</v>
+      </c>
+      <c r="K11" s="0">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="L11" s="0">
         <v>12.140000000000001</v>
       </c>
-      <c r="G11" s="0">
+      <c r="M11" s="0">
         <v>6.9800000000000004</v>
       </c>
-      <c r="H11" s="0">
+      <c r="N11" s="0">
         <v>47.189999999999998</v>
       </c>
-      <c r="I11" s="0">
+      <c r="O11" s="0">
         <v>11.199999999999999</v>
       </c>
-      <c r="J11" s="0">
+      <c r="P11" s="0">
         <v>26.98</v>
       </c>
-      <c r="K11" s="0">
+      <c r="Q11" s="0">
         <v>10.98</v>
       </c>
-      <c r="L11" s="0">
+      <c r="R11" s="0">
         <v>5.96</v>
       </c>
-      <c r="M11" s="0">
+      <c r="S11" s="0">
         <v>4.5700000000000003</v>
       </c>
-      <c r="N11" s="0">
+      <c r="T11" s="0">
         <v>-6.5199999999999996</v>
       </c>
-      <c r="O11" s="0">
+      <c r="U11" s="0">
         <v>5.7300000000000004</v>
       </c>
-      <c r="P11" s="0">
+      <c r="V11" s="0">
         <v>-1.5600000000000001</v>
       </c>
-      <c r="Q11" s="0">
+      <c r="W11" s="0">
         <v>5.6100000000000003</v>
       </c>
-      <c r="R11" s="0">
+      <c r="X11" s="0">
         <v>7</v>
       </c>
     </row>
@@ -4146,42 +4626,60 @@
         <v>18.760000000000002</v>
       </c>
       <c r="F12" s="0">
+        <v>61.829999999999998</v>
+      </c>
+      <c r="G12" s="0">
+        <v>66.719999999999999</v>
+      </c>
+      <c r="H12" s="0">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="I12" s="0">
+        <v>8.4199999999999999</v>
+      </c>
+      <c r="J12" s="0">
+        <v>9.5399999999999991</v>
+      </c>
+      <c r="K12" s="0">
+        <v>12.23</v>
+      </c>
+      <c r="L12" s="0">
         <v>61.310000000000002</v>
       </c>
-      <c r="G12" s="0">
+      <c r="M12" s="0">
         <v>6.3600000000000003</v>
       </c>
-      <c r="H12" s="0">
+      <c r="N12" s="0">
         <v>4.8899999999999997</v>
       </c>
-      <c r="I12" s="0">
+      <c r="O12" s="0">
         <v>3.0899999999999999</v>
       </c>
-      <c r="J12" s="0">
+      <c r="P12" s="0">
         <v>0.059999999999999998</v>
       </c>
-      <c r="K12" s="0">
+      <c r="Q12" s="0">
         <v>5.0099999999999998</v>
       </c>
-      <c r="L12" s="0">
+      <c r="R12" s="0">
         <v>-0.59999999999999998</v>
       </c>
-      <c r="M12" s="0">
+      <c r="S12" s="0">
         <v>3.5800000000000001</v>
       </c>
-      <c r="N12" s="0">
+      <c r="T12" s="0">
         <v>2.54</v>
       </c>
-      <c r="O12" s="0">
+      <c r="U12" s="0">
         <v>4.4000000000000004</v>
       </c>
-      <c r="P12" s="0">
+      <c r="V12" s="0">
         <v>-6.2999999999999998</v>
       </c>
-      <c r="Q12" s="0">
+      <c r="W12" s="0">
         <v>11.35</v>
       </c>
-      <c r="R12" s="0">
+      <c r="X12" s="0">
         <v>7</v>
       </c>
     </row>
@@ -4202,42 +4700,60 @@
         <v>24.100000000000001</v>
       </c>
       <c r="F13" s="0">
+        <v>51.130000000000003</v>
+      </c>
+      <c r="G13" s="0">
+        <v>23.98</v>
+      </c>
+      <c r="H13" s="0">
+        <v>41.640000000000001</v>
+      </c>
+      <c r="I13" s="0">
+        <v>36.560000000000002</v>
+      </c>
+      <c r="J13" s="0">
+        <v>5.1399999999999997</v>
+      </c>
+      <c r="K13" s="0">
+        <v>4.4900000000000002</v>
+      </c>
+      <c r="L13" s="0">
         <v>15.529999999999999</v>
       </c>
-      <c r="G13" s="0">
+      <c r="M13" s="0">
         <v>8.6400000000000006</v>
       </c>
-      <c r="H13" s="0">
+      <c r="N13" s="0">
         <v>60.060000000000002</v>
       </c>
-      <c r="I13" s="0">
+      <c r="O13" s="0">
         <v>13.65</v>
       </c>
-      <c r="J13" s="0">
+      <c r="P13" s="0">
         <v>33.079999999999998</v>
       </c>
-      <c r="K13" s="0">
+      <c r="Q13" s="0">
         <v>9.1999999999999993</v>
       </c>
-      <c r="L13" s="0">
+      <c r="R13" s="0">
         <v>6.2000000000000002</v>
       </c>
-      <c r="M13" s="0">
+      <c r="S13" s="0">
         <v>4.3799999999999999</v>
       </c>
-      <c r="N13" s="0">
+      <c r="T13" s="0">
         <v>-2.8199999999999998</v>
       </c>
-      <c r="O13" s="0">
+      <c r="U13" s="0">
         <v>3.5600000000000001</v>
       </c>
-      <c r="P13" s="0">
+      <c r="V13" s="0">
         <v>1.47</v>
       </c>
-      <c r="Q13" s="0">
+      <c r="W13" s="0">
         <v>7.0300000000000002</v>
       </c>
-      <c r="R13" s="0">
+      <c r="X13" s="0">
         <v>7</v>
       </c>
     </row>
@@ -4294,6 +4810,24 @@
         <v>0</v>
       </c>
       <c r="R14" s="0">
+        <v>0</v>
+      </c>
+      <c r="S14" s="0">
+        <v>0</v>
+      </c>
+      <c r="T14" s="0">
+        <v>0</v>
+      </c>
+      <c r="U14" s="0">
+        <v>0</v>
+      </c>
+      <c r="V14" s="0">
+        <v>0</v>
+      </c>
+      <c r="W14" s="0">
+        <v>0</v>
+      </c>
+      <c r="X14" s="0">
         <v>7</v>
       </c>
     </row>

--- a/Results/Group Analysis/GroupCrossing_YoungAdults_Summary.xlsx
+++ b/Results/Group Analysis/GroupCrossing_YoungAdults_Summary.xlsx
@@ -10,7 +10,7 @@
     <sheet name="ROM_deg" sheetId="3" r:id="rId5"/>
     <sheet name="SegmentROM_deg" sheetId="4" r:id="rId6"/>
     <sheet name="Spatiotemporal" sheetId="5" r:id="rId7"/>
-    <sheet name="PeakTiming_pctGC" sheetId="6" r:id="rId8"/>
+    <sheet name="PeakTiming_vsClearance" sheetId="6" r:id="rId8"/>
     <sheet name="PeakExcursion_deg" sheetId="7" r:id="rId9"/>
     <sheet name="PeakDelta_deg" sheetId="8" r:id="rId10"/>
   </sheets>
@@ -2044,22 +2044,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>45.100000000000001</v>
+        <v>-4.0199999999999996</v>
       </c>
       <c r="C2" s="0">
-        <v>11.960000000000001</v>
+        <v>12.130000000000001</v>
       </c>
       <c r="D2" s="0">
-        <v>51.079999999999998</v>
+        <v>1.96</v>
       </c>
       <c r="E2" s="0">
-        <v>11.76</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="F2" s="0">
-        <v>63.119999999999997</v>
+        <v>13.84</v>
       </c>
       <c r="G2" s="0">
-        <v>15.06</v>
+        <v>15.859999999999999</v>
       </c>
       <c r="H2" s="0">
         <v>49.280000000000001</v>
@@ -2068,22 +2068,22 @@
         <v>3.9199999999999999</v>
       </c>
       <c r="J2" s="0">
-        <v>34.75</v>
+        <v>-14.539999999999999</v>
       </c>
       <c r="K2" s="0">
-        <v>4.6200000000000001</v>
+        <v>8.0099999999999998</v>
       </c>
       <c r="L2" s="0">
-        <v>35.859999999999999</v>
+        <v>-13.43</v>
       </c>
       <c r="M2" s="0">
-        <v>3.4300000000000002</v>
+        <v>5.7599999999999998</v>
       </c>
       <c r="N2" s="0">
-        <v>51.479999999999997</v>
+        <v>2.3599999999999999</v>
       </c>
       <c r="O2" s="0">
-        <v>5</v>
+        <v>1.78</v>
       </c>
       <c r="P2" s="0">
         <v>7</v>
@@ -2094,22 +2094,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>50.950000000000003</v>
+        <v>-0.83999999999999997</v>
       </c>
       <c r="C3" s="0">
-        <v>13.01</v>
+        <v>11.99</v>
       </c>
       <c r="D3" s="0">
-        <v>56.82</v>
+        <v>5.0300000000000002</v>
       </c>
       <c r="E3" s="0">
-        <v>5.21</v>
+        <v>5.4800000000000004</v>
       </c>
       <c r="F3" s="0">
-        <v>66.099999999999994</v>
+        <v>14.24</v>
       </c>
       <c r="G3" s="0">
-        <v>12.82</v>
+        <v>15.57</v>
       </c>
       <c r="H3" s="0">
         <v>51.859999999999999</v>
@@ -2118,22 +2118,22 @@
         <v>5.8799999999999999</v>
       </c>
       <c r="J3" s="0">
-        <v>46.729999999999997</v>
+        <v>-5.1299999999999999</v>
       </c>
       <c r="K3" s="0">
-        <v>6.0700000000000003</v>
+        <v>1.8200000000000001</v>
       </c>
       <c r="L3" s="0">
-        <v>48.43</v>
+        <v>-3.4399999999999999</v>
       </c>
       <c r="M3" s="0">
-        <v>5.0999999999999996</v>
+        <v>0.88</v>
       </c>
       <c r="N3" s="0">
-        <v>60.979999999999997</v>
+        <v>9.1799999999999997</v>
       </c>
       <c r="O3" s="0">
-        <v>6.1600000000000001</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P3" s="0">
         <v>7</v>
@@ -2144,22 +2144,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>53.090000000000003</v>
+        <v>3.2200000000000002</v>
       </c>
       <c r="C4" s="0">
-        <v>10.33</v>
+        <v>10.56</v>
       </c>
       <c r="D4" s="0">
-        <v>50.280000000000001</v>
+        <v>0.46999999999999997</v>
       </c>
       <c r="E4" s="0">
-        <v>22.920000000000002</v>
+        <v>25.219999999999999</v>
       </c>
       <c r="F4" s="0">
-        <v>67.799999999999997</v>
+        <v>17.73</v>
       </c>
       <c r="G4" s="0">
-        <v>12.130000000000001</v>
+        <v>15.02</v>
       </c>
       <c r="H4" s="0">
         <v>50.060000000000002</v>
@@ -2168,22 +2168,22 @@
         <v>6.8399999999999999</v>
       </c>
       <c r="J4" s="0">
-        <v>32.509999999999998</v>
+        <v>-17.559999999999999</v>
       </c>
       <c r="K4" s="0">
-        <v>5.9900000000000002</v>
+        <v>9.1500000000000004</v>
       </c>
       <c r="L4" s="0">
-        <v>35.530000000000001</v>
+        <v>-14.529999999999999</v>
       </c>
       <c r="M4" s="0">
-        <v>6.3899999999999997</v>
+        <v>9.6600000000000001</v>
       </c>
       <c r="N4" s="0">
-        <v>50.979999999999997</v>
+        <v>1.25</v>
       </c>
       <c r="O4" s="0">
-        <v>6.8600000000000003</v>
+        <v>1.01</v>
       </c>
       <c r="P4" s="0">
         <v>7</v>
@@ -2194,22 +2194,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>56.619999999999997</v>
+        <v>1.8300000000000001</v>
       </c>
       <c r="C5" s="0">
-        <v>9.7899999999999991</v>
+        <v>9.2400000000000002</v>
       </c>
       <c r="D5" s="0">
-        <v>58.049999999999997</v>
+        <v>3.02</v>
       </c>
       <c r="E5" s="0">
-        <v>7.2599999999999998</v>
+        <v>6.5199999999999996</v>
       </c>
       <c r="F5" s="0">
-        <v>64.379999999999995</v>
+        <v>9.3599999999999994</v>
       </c>
       <c r="G5" s="0">
-        <v>22.030000000000001</v>
+        <v>22.530000000000001</v>
       </c>
       <c r="H5" s="0">
         <v>55.020000000000003</v>
@@ -2218,22 +2218,22 @@
         <v>2.21</v>
       </c>
       <c r="J5" s="0">
-        <v>50.619999999999997</v>
+        <v>-4.3899999999999997</v>
       </c>
       <c r="K5" s="0">
-        <v>2.23</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="L5" s="0">
-        <v>52.020000000000003</v>
+        <v>-3</v>
       </c>
       <c r="M5" s="0">
-        <v>2.21</v>
+        <v>0.77000000000000002</v>
       </c>
       <c r="N5" s="0">
-        <v>63.909999999999997</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="O5" s="0">
-        <v>2.7000000000000002</v>
+        <v>1.52</v>
       </c>
       <c r="P5" s="0">
         <v>7</v>
@@ -2244,22 +2244,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>44.890000000000001</v>
+        <v>-2.21</v>
       </c>
       <c r="C6" s="0">
-        <v>10.52</v>
+        <v>9.8699999999999992</v>
       </c>
       <c r="D6" s="0">
-        <v>48.020000000000003</v>
+        <v>0.92000000000000004</v>
       </c>
       <c r="E6" s="0">
-        <v>12.98</v>
+        <v>13.42</v>
       </c>
       <c r="F6" s="0">
-        <v>53.210000000000001</v>
+        <v>5.5300000000000002</v>
       </c>
       <c r="G6" s="0">
-        <v>21.670000000000002</v>
+        <v>18.629999999999999</v>
       </c>
       <c r="H6" s="0">
         <v>47.68</v>
@@ -2268,22 +2268,22 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="J6" s="0">
-        <v>28.640000000000001</v>
+        <v>-19.039999999999999</v>
       </c>
       <c r="K6" s="0">
-        <v>4.4400000000000004</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="L6" s="0">
-        <v>32.219999999999999</v>
+        <v>-15.460000000000001</v>
       </c>
       <c r="M6" s="0">
-        <v>6.04</v>
+        <v>7.0099999999999998</v>
       </c>
       <c r="N6" s="0">
-        <v>47.710000000000001</v>
+        <v>0.59999999999999998</v>
       </c>
       <c r="O6" s="0">
-        <v>6.2199999999999998</v>
+        <v>1.5800000000000001</v>
       </c>
       <c r="P6" s="0">
         <v>7</v>
@@ -2294,22 +2294,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>58.759999999999998</v>
+        <v>4.7199999999999998</v>
       </c>
       <c r="C7" s="0">
-        <v>14.529999999999999</v>
+        <v>16.73</v>
       </c>
       <c r="D7" s="0">
-        <v>59.359999999999999</v>
+        <v>5.3300000000000001</v>
       </c>
       <c r="E7" s="0">
-        <v>7.9900000000000002</v>
+        <v>6.9699999999999998</v>
       </c>
       <c r="F7" s="0">
-        <v>66.560000000000002</v>
+        <v>12.43</v>
       </c>
       <c r="G7" s="0">
-        <v>16.059999999999999</v>
+        <v>17.649999999999999</v>
       </c>
       <c r="H7" s="0">
         <v>54.130000000000003</v>
@@ -2318,22 +2318,22 @@
         <v>2.8900000000000001</v>
       </c>
       <c r="J7" s="0">
-        <v>51.07</v>
+        <v>-3.0600000000000001</v>
       </c>
       <c r="K7" s="0">
-        <v>2.79</v>
+        <v>0.59999999999999998</v>
       </c>
       <c r="L7" s="0">
-        <v>51.469999999999999</v>
+        <v>-2.6600000000000001</v>
       </c>
       <c r="M7" s="0">
-        <v>2.6600000000000001</v>
+        <v>0.77000000000000002</v>
       </c>
       <c r="N7" s="0">
-        <v>64.090000000000003</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="O7" s="0">
-        <v>3.0800000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="P7" s="0">
         <v>7</v>
@@ -2344,22 +2344,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>52</v>
+        <v>2.4399999999999999</v>
       </c>
       <c r="C8" s="0">
-        <v>9.6099999999999994</v>
+        <v>10.029999999999999</v>
       </c>
       <c r="D8" s="0">
-        <v>42.18</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="E8" s="0">
-        <v>17.48</v>
+        <v>11.619999999999999</v>
       </c>
       <c r="F8" s="0">
-        <v>60.369999999999997</v>
+        <v>12.619999999999999</v>
       </c>
       <c r="G8" s="0">
-        <v>18.940000000000001</v>
+        <v>15.869999999999999</v>
       </c>
       <c r="H8" s="0">
         <v>47.75</v>
@@ -2368,22 +2368,22 @@
         <v>5.7800000000000002</v>
       </c>
       <c r="J8" s="0">
-        <v>33.700000000000003</v>
+        <v>-14.06</v>
       </c>
       <c r="K8" s="0">
-        <v>4.2000000000000002</v>
+        <v>8.6600000000000001</v>
       </c>
       <c r="L8" s="0">
-        <v>36.119999999999997</v>
+        <v>-11.630000000000001</v>
       </c>
       <c r="M8" s="0">
-        <v>4.5499999999999998</v>
+        <v>8.9399999999999995</v>
       </c>
       <c r="N8" s="0">
-        <v>52.310000000000002</v>
+        <v>2.3500000000000001</v>
       </c>
       <c r="O8" s="0">
-        <v>5.2699999999999996</v>
+        <v>7.4000000000000004</v>
       </c>
       <c r="P8" s="0">
         <v>7</v>
@@ -2394,22 +2394,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>56.729999999999997</v>
+        <v>2.8999999999999999</v>
       </c>
       <c r="C9" s="0">
-        <v>5.75</v>
+        <v>7.2199999999999998</v>
       </c>
       <c r="D9" s="0">
-        <v>57.719999999999999</v>
+        <v>3.9300000000000002</v>
       </c>
       <c r="E9" s="0">
-        <v>9.7200000000000006</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="F9" s="0">
-        <v>64.849999999999994</v>
+        <v>11.01</v>
       </c>
       <c r="G9" s="0">
-        <v>14.44</v>
+        <v>15.98</v>
       </c>
       <c r="H9" s="0">
         <v>53.840000000000003</v>
@@ -2418,22 +2418,22 @@
         <v>2.3599999999999999</v>
       </c>
       <c r="J9" s="0">
-        <v>48.460000000000001</v>
+        <v>-5.3799999999999999</v>
       </c>
       <c r="K9" s="0">
-        <v>3.4300000000000002</v>
+        <v>1.6799999999999999</v>
       </c>
       <c r="L9" s="0">
-        <v>50.579999999999998</v>
+        <v>-3.2599999999999998</v>
       </c>
       <c r="M9" s="0">
-        <v>2.7999999999999998</v>
+        <v>1.22</v>
       </c>
       <c r="N9" s="0">
-        <v>63.18</v>
+        <v>9.4600000000000009</v>
       </c>
       <c r="O9" s="0">
-        <v>3.3700000000000001</v>
+        <v>1.4199999999999999</v>
       </c>
       <c r="P9" s="0">
         <v>7</v>
@@ -2444,22 +2444,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>47.210000000000001</v>
+        <v>-2.9900000000000002</v>
       </c>
       <c r="C10" s="0">
-        <v>14.039999999999999</v>
+        <v>13.85</v>
       </c>
       <c r="D10" s="0">
-        <v>50.880000000000003</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="E10" s="0">
-        <v>21.780000000000001</v>
+        <v>22.170000000000002</v>
       </c>
       <c r="F10" s="0">
-        <v>64.349999999999994</v>
+        <v>14.130000000000001</v>
       </c>
       <c r="G10" s="0">
-        <v>14.550000000000001</v>
+        <v>14.630000000000001</v>
       </c>
       <c r="H10" s="0">
         <v>50.219999999999999</v>
@@ -2468,22 +2468,22 @@
         <v>3.5499999999999998</v>
       </c>
       <c r="J10" s="0">
-        <v>29.260000000000002</v>
+        <v>-20.960000000000001</v>
       </c>
       <c r="K10" s="0">
-        <v>3.7799999999999998</v>
+        <v>1.6899999999999999</v>
       </c>
       <c r="L10" s="0">
-        <v>32.880000000000003</v>
+        <v>-17.34</v>
       </c>
       <c r="M10" s="0">
-        <v>4.0700000000000003</v>
+        <v>1.8500000000000001</v>
       </c>
       <c r="N10" s="0">
-        <v>51.399999999999999</v>
+        <v>1.21</v>
       </c>
       <c r="O10" s="0">
-        <v>3.7799999999999998</v>
+        <v>0.88</v>
       </c>
       <c r="P10" s="0">
         <v>7</v>
@@ -2494,22 +2494,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>56.299999999999997</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="C11" s="0">
-        <v>14.59</v>
+        <v>15.619999999999999</v>
       </c>
       <c r="D11" s="0">
-        <v>51.159999999999997</v>
+        <v>-3.8599999999999999</v>
       </c>
       <c r="E11" s="0">
-        <v>8.5299999999999994</v>
+        <v>7.7300000000000004</v>
       </c>
       <c r="F11" s="0">
-        <v>66.989999999999995</v>
+        <v>12</v>
       </c>
       <c r="G11" s="0">
-        <v>13.75</v>
+        <v>14.91</v>
       </c>
       <c r="H11" s="0">
         <v>54.990000000000002</v>
@@ -2518,22 +2518,22 @@
         <v>2</v>
       </c>
       <c r="J11" s="0">
-        <v>52.659999999999997</v>
+        <v>-2.3300000000000001</v>
       </c>
       <c r="K11" s="0">
-        <v>5.8099999999999996</v>
+        <v>5.29</v>
       </c>
       <c r="L11" s="0">
-        <v>53.899999999999999</v>
+        <v>-1.0900000000000001</v>
       </c>
       <c r="M11" s="0">
-        <v>5.8399999999999999</v>
+        <v>5.5800000000000001</v>
       </c>
       <c r="N11" s="0">
-        <v>65.560000000000002</v>
+        <v>10.640000000000001</v>
       </c>
       <c r="O11" s="0">
-        <v>5.75</v>
+        <v>5.4500000000000002</v>
       </c>
       <c r="P11" s="0">
         <v>7</v>
@@ -2544,22 +2544,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>55.68</v>
+        <v>4.3300000000000001</v>
       </c>
       <c r="C12" s="0">
-        <v>11.300000000000001</v>
+        <v>12.33</v>
       </c>
       <c r="D12" s="0">
-        <v>46.869999999999997</v>
+        <v>-4.4800000000000004</v>
       </c>
       <c r="E12" s="0">
-        <v>19.109999999999999</v>
+        <v>27.260000000000002</v>
       </c>
       <c r="F12" s="0">
-        <v>53.25</v>
+        <v>1.76</v>
       </c>
       <c r="G12" s="0">
-        <v>12.109999999999999</v>
+        <v>12.699999999999999</v>
       </c>
       <c r="H12" s="0">
         <v>51.490000000000002</v>
@@ -2568,22 +2568,22 @@
         <v>7.8499999999999996</v>
       </c>
       <c r="J12" s="0">
-        <v>33.43</v>
+        <v>-18.07</v>
       </c>
       <c r="K12" s="0">
-        <v>5.8799999999999999</v>
+        <v>9.3900000000000006</v>
       </c>
       <c r="L12" s="0">
-        <v>37.299999999999997</v>
+        <v>-14.19</v>
       </c>
       <c r="M12" s="0">
-        <v>5.7800000000000002</v>
+        <v>9.0199999999999996</v>
       </c>
       <c r="N12" s="0">
-        <v>55.100000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="O12" s="0">
-        <v>10.720000000000001</v>
+        <v>7.6699999999999999</v>
       </c>
       <c r="P12" s="0">
         <v>7</v>
@@ -2594,22 +2594,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>52.530000000000001</v>
+        <v>-2.04</v>
       </c>
       <c r="C13" s="0">
-        <v>10.52</v>
+        <v>12.789999999999999</v>
       </c>
       <c r="D13" s="0">
-        <v>61.280000000000001</v>
+        <v>6.71</v>
       </c>
       <c r="E13" s="0">
-        <v>9.4800000000000004</v>
+        <v>8.2400000000000002</v>
       </c>
       <c r="F13" s="0">
-        <v>69.730000000000004</v>
+        <v>15.029999999999999</v>
       </c>
       <c r="G13" s="0">
-        <v>19.449999999999999</v>
+        <v>21.75</v>
       </c>
       <c r="H13" s="0">
         <v>54.700000000000003</v>
@@ -2618,22 +2618,22 @@
         <v>3.3700000000000001</v>
       </c>
       <c r="J13" s="0">
-        <v>51.479999999999997</v>
+        <v>-3.2200000000000002</v>
       </c>
       <c r="K13" s="0">
-        <v>2.77</v>
+        <v>1.23</v>
       </c>
       <c r="L13" s="0">
-        <v>52.130000000000003</v>
+        <v>-2.5699999999999998</v>
       </c>
       <c r="M13" s="0">
-        <v>2.8199999999999998</v>
+        <v>0.59999999999999998</v>
       </c>
       <c r="N13" s="0">
-        <v>65.109999999999999</v>
+        <v>10.550000000000001</v>
       </c>
       <c r="O13" s="0">
-        <v>3.7599999999999998</v>
+        <v>2.73</v>
       </c>
       <c r="P13" s="0">
         <v>7</v>
@@ -2644,22 +2644,22 @@
         <v>24</v>
       </c>
       <c r="B14" s="0">
-        <v>60.030000000000001</v>
+        <v>4.4100000000000001</v>
       </c>
       <c r="C14" s="0">
-        <v>8.9499999999999993</v>
+        <v>7.2199999999999998</v>
       </c>
       <c r="D14" s="0">
-        <v>52.990000000000002</v>
+        <v>-2.52</v>
       </c>
       <c r="E14" s="0">
-        <v>9.6199999999999992</v>
+        <v>16.84</v>
       </c>
       <c r="F14" s="0">
-        <v>59.670000000000002</v>
+        <v>3.8199999999999998</v>
       </c>
       <c r="G14" s="0">
-        <v>9.0399999999999991</v>
+        <v>14.949999999999999</v>
       </c>
       <c r="H14" s="0">
         <v>55.859999999999999</v>
@@ -2668,22 +2668,22 @@
         <v>9.5800000000000001</v>
       </c>
       <c r="J14" s="0">
-        <v>38.710000000000001</v>
+        <v>-17.149999999999999</v>
       </c>
       <c r="K14" s="0">
-        <v>1.8600000000000001</v>
+        <v>8.9900000000000002</v>
       </c>
       <c r="L14" s="0">
-        <v>39.619999999999997</v>
+        <v>-16.239999999999998</v>
       </c>
       <c r="M14" s="0">
-        <v>2.5600000000000001</v>
+        <v>8.7799999999999994</v>
       </c>
       <c r="N14" s="0">
-        <v>67.939999999999998</v>
+        <v>12.470000000000001</v>
       </c>
       <c r="O14" s="0">
-        <v>7.3099999999999996</v>
+        <v>11.859999999999999</v>
       </c>
       <c r="P14" s="0">
         <v>7</v>

--- a/Results/Group Analysis/GroupCrossing_YoungAdults_Summary.xlsx
+++ b/Results/Group Analysis/GroupCrossing_YoungAdults_Summary.xlsx
@@ -412,22 +412,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>37.990000000000002</v>
+        <v>35.640000000000001</v>
       </c>
       <c r="C2" s="0">
-        <v>37.520000000000003</v>
+        <v>35.799999999999997</v>
       </c>
       <c r="D2" s="0">
-        <v>5.1699999999999999</v>
+        <v>5.46</v>
       </c>
       <c r="E2" s="0">
-        <v>12.84</v>
+        <v>12.039999999999999</v>
       </c>
       <c r="F2" s="0">
-        <v>39.420000000000002</v>
+        <v>35.469999999999999</v>
       </c>
       <c r="G2" s="0">
-        <v>64.609999999999999</v>
+        <v>61.579999999999998</v>
       </c>
       <c r="H2" s="0">
         <v>1.3400000000000001</v>
@@ -442,10 +442,10 @@
         <v>17.09</v>
       </c>
       <c r="L2" s="0">
-        <v>34.340000000000003</v>
+        <v>32.719999999999999</v>
       </c>
       <c r="M2" s="0">
-        <v>8.7100000000000009</v>
+        <v>9.5</v>
       </c>
       <c r="N2" s="0">
         <v>4.3200000000000003</v>
@@ -460,10 +460,10 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="R2" s="0">
-        <v>2.1699999999999999</v>
+        <v>2.0600000000000001</v>
       </c>
       <c r="S2" s="0">
-        <v>2.6699999999999999</v>
+        <v>2.52</v>
       </c>
       <c r="T2" s="0">
         <v>2.8900000000000001</v>
@@ -486,22 +486,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>18.59</v>
+        <v>17.34</v>
       </c>
       <c r="C3" s="0">
-        <v>16.039999999999999</v>
+        <v>15.470000000000001</v>
       </c>
       <c r="D3" s="0">
-        <v>7.2699999999999996</v>
+        <v>5.96</v>
       </c>
       <c r="E3" s="0">
-        <v>18.579999999999998</v>
+        <v>17.82</v>
       </c>
       <c r="F3" s="0">
-        <v>34.030000000000001</v>
+        <v>25.43</v>
       </c>
       <c r="G3" s="0">
-        <v>28.609999999999999</v>
+        <v>37.159999999999997</v>
       </c>
       <c r="H3" s="0">
         <v>31.469999999999999</v>
@@ -516,10 +516,10 @@
         <v>11.140000000000001</v>
       </c>
       <c r="L3" s="0">
-        <v>8.9100000000000001</v>
+        <v>8.3200000000000003</v>
       </c>
       <c r="M3" s="0">
-        <v>3.6699999999999999</v>
+        <v>3.8599999999999999</v>
       </c>
       <c r="N3" s="0">
         <v>33.899999999999999</v>
@@ -534,10 +534,10 @@
         <v>10.529999999999999</v>
       </c>
       <c r="R3" s="0">
-        <v>6.6399999999999997</v>
+        <v>6.7599999999999998</v>
       </c>
       <c r="S3" s="0">
-        <v>4.3600000000000003</v>
+        <v>4.0899999999999999</v>
       </c>
       <c r="T3" s="0">
         <v>-1.98</v>
@@ -708,22 +708,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>47.780000000000001</v>
+        <v>45.109999999999999</v>
       </c>
       <c r="C6" s="0">
-        <v>32.189999999999998</v>
+        <v>31.16</v>
       </c>
       <c r="D6" s="0">
-        <v>17.670000000000002</v>
+        <v>16.23</v>
       </c>
       <c r="E6" s="0">
-        <v>22.739999999999998</v>
+        <v>21.699999999999999</v>
       </c>
       <c r="F6" s="0">
-        <v>54.130000000000003</v>
+        <v>51.939999999999998</v>
       </c>
       <c r="G6" s="0">
-        <v>58.079999999999998</v>
+        <v>54.719999999999999</v>
       </c>
       <c r="H6" s="0">
         <v>-1.55</v>
@@ -738,10 +738,10 @@
         <v>8.9800000000000004</v>
       </c>
       <c r="L6" s="0">
-        <v>54.170000000000002</v>
+        <v>55.780000000000001</v>
       </c>
       <c r="M6" s="0">
-        <v>7.3600000000000003</v>
+        <v>8.4100000000000001</v>
       </c>
       <c r="N6" s="0">
         <v>5.3799999999999999</v>
@@ -756,10 +756,10 @@
         <v>9.6899999999999995</v>
       </c>
       <c r="R6" s="0">
-        <v>1.0800000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="S6" s="0">
-        <v>4.79</v>
+        <v>4.75</v>
       </c>
       <c r="T6" s="0">
         <v>4.0499999999999998</v>
@@ -782,22 +782,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>28.559999999999999</v>
+        <v>29.02</v>
       </c>
       <c r="C7" s="0">
-        <v>22.32</v>
+        <v>20.920000000000002</v>
       </c>
       <c r="D7" s="0">
-        <v>9.6099999999999994</v>
+        <v>8.0600000000000005</v>
       </c>
       <c r="E7" s="0">
-        <v>15.369999999999999</v>
+        <v>15.119999999999999</v>
       </c>
       <c r="F7" s="0">
-        <v>52.490000000000002</v>
+        <v>43.619999999999997</v>
       </c>
       <c r="G7" s="0">
-        <v>17.920000000000002</v>
+        <v>31.449999999999999</v>
       </c>
       <c r="H7" s="0">
         <v>57</v>
@@ -812,10 +812,10 @@
         <v>10.66</v>
       </c>
       <c r="L7" s="0">
-        <v>12.779999999999999</v>
+        <v>14.289999999999999</v>
       </c>
       <c r="M7" s="0">
-        <v>5.3799999999999999</v>
+        <v>6.79</v>
       </c>
       <c r="N7" s="0">
         <v>54.5</v>
@@ -830,10 +830,10 @@
         <v>12.02</v>
       </c>
       <c r="R7" s="0">
-        <v>6.79</v>
+        <v>5.9400000000000004</v>
       </c>
       <c r="S7" s="0">
-        <v>2.7000000000000002</v>
+        <v>3.5899999999999999</v>
       </c>
       <c r="T7" s="0">
         <v>-3.6899999999999999</v>
@@ -1152,22 +1152,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>39.619999999999997</v>
+        <v>40.979999999999997</v>
       </c>
       <c r="C12" s="0">
-        <v>45</v>
+        <v>41.840000000000003</v>
       </c>
       <c r="D12" s="0">
-        <v>15.34</v>
+        <v>12.859999999999999</v>
       </c>
       <c r="E12" s="0">
-        <v>17.129999999999999</v>
+        <v>17.34</v>
       </c>
       <c r="F12" s="0">
-        <v>57.899999999999999</v>
+        <v>51.140000000000001</v>
       </c>
       <c r="G12" s="0">
-        <v>61.789999999999999</v>
+        <v>60.329999999999998</v>
       </c>
       <c r="H12" s="0">
         <v>1.1799999999999999</v>
@@ -1182,10 +1182,10 @@
         <v>11.390000000000001</v>
       </c>
       <c r="L12" s="0">
-        <v>59.390000000000001</v>
+        <v>59.18</v>
       </c>
       <c r="M12" s="0">
-        <v>6.8099999999999996</v>
+        <v>6.4100000000000001</v>
       </c>
       <c r="N12" s="0">
         <v>6.0899999999999999</v>
@@ -1200,10 +1200,10 @@
         <v>4.5499999999999998</v>
       </c>
       <c r="R12" s="0">
-        <v>-0.20999999999999999</v>
+        <v>0.14999999999999999</v>
       </c>
       <c r="S12" s="0">
-        <v>3.1299999999999999</v>
+        <v>3.1200000000000001</v>
       </c>
       <c r="T12" s="0">
         <v>4.5499999999999998</v>
@@ -1226,22 +1226,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>30.260000000000002</v>
+        <v>28.949999999999999</v>
       </c>
       <c r="C13" s="0">
-        <v>30</v>
+        <v>28.030000000000001</v>
       </c>
       <c r="D13" s="0">
-        <v>12.539999999999999</v>
+        <v>11.41</v>
       </c>
       <c r="E13" s="0">
-        <v>22.289999999999999</v>
+        <v>20.879999999999999</v>
       </c>
       <c r="F13" s="0">
-        <v>49.969999999999999</v>
+        <v>49.68</v>
       </c>
       <c r="G13" s="0">
-        <v>22.109999999999999</v>
+        <v>20.48</v>
       </c>
       <c r="H13" s="0">
         <v>45.270000000000003</v>
@@ -1256,10 +1256,10 @@
         <v>4.4900000000000002</v>
       </c>
       <c r="L13" s="0">
-        <v>14.66</v>
+        <v>13.94</v>
       </c>
       <c r="M13" s="0">
-        <v>7.4900000000000002</v>
+        <v>7.3399999999999999</v>
       </c>
       <c r="N13" s="0">
         <v>60.009999999999998</v>
@@ -1274,10 +1274,10 @@
         <v>9.2799999999999994</v>
       </c>
       <c r="R13" s="0">
-        <v>8.1400000000000006</v>
+        <v>7.9299999999999997</v>
       </c>
       <c r="S13" s="0">
-        <v>5.1699999999999999</v>
+        <v>4.8799999999999999</v>
       </c>
       <c r="T13" s="0">
         <v>-2.2200000000000002</v>
@@ -1936,13 +1936,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>60.100000000000001</v>
+        <v>58.299999999999997</v>
       </c>
       <c r="C2" s="0">
         <v>23</v>
       </c>
       <c r="D2" s="0">
-        <v>78.299999999999997</v>
+        <v>76.299999999999997</v>
       </c>
       <c r="E2" s="0">
         <v>32</v>
@@ -1962,16 +1962,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>45.700000000000003</v>
+        <v>43.5</v>
       </c>
       <c r="C3" s="0">
         <v>16</v>
       </c>
       <c r="D3" s="0">
-        <v>62.899999999999999</v>
+        <v>57.700000000000003</v>
       </c>
       <c r="E3" s="0">
-        <v>29.199999999999999</v>
+        <v>31.399999999999999</v>
       </c>
       <c r="F3" s="0">
         <v>93.700000000000003</v>
@@ -2040,13 +2040,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>86.599999999999994</v>
+        <v>82.799999999999997</v>
       </c>
       <c r="C6" s="0">
         <v>30</v>
       </c>
       <c r="D6" s="0">
-        <v>90.799999999999997</v>
+        <v>91.5</v>
       </c>
       <c r="E6" s="0">
         <v>28</v>
@@ -2066,16 +2066,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>62.600000000000001</v>
+        <v>61.299999999999997</v>
       </c>
       <c r="C7" s="0">
-        <v>16.100000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="D7" s="0">
-        <v>89.299999999999997</v>
+        <v>83.200000000000003</v>
       </c>
       <c r="E7" s="0">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F7" s="0">
         <v>120.2</v>
@@ -2196,13 +2196,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>80.5</v>
+        <v>78.900000000000006</v>
       </c>
       <c r="C12" s="0">
         <v>23</v>
       </c>
       <c r="D12" s="0">
-        <v>97.099999999999994</v>
+        <v>93.099999999999994</v>
       </c>
       <c r="E12" s="0">
         <v>31</v>
@@ -2222,16 +2222,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>68.299999999999997</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="C13" s="0">
-        <v>16.5</v>
+        <v>17.199999999999999</v>
       </c>
       <c r="D13" s="0">
-        <v>90.200000000000003</v>
+        <v>92.400000000000006</v>
       </c>
       <c r="E13" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F13" s="0">
         <v>103.40000000000001</v>
@@ -2331,10 +2331,10 @@
         <v>6.9000000000000004</v>
       </c>
       <c r="F2" s="0">
-        <v>81.900000000000006</v>
+        <v>79.299999999999997</v>
       </c>
       <c r="G2" s="0">
-        <v>9.0999999999999996</v>
+        <v>11.5</v>
       </c>
       <c r="H2" s="0">
         <v>9</v>
@@ -2357,10 +2357,10 @@
         <v>14</v>
       </c>
       <c r="F3" s="0">
-        <v>60.899999999999999</v>
+        <v>59.700000000000003</v>
       </c>
       <c r="G3" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H3" s="0">
         <v>9</v>
@@ -2435,10 +2435,10 @@
         <v>5.7000000000000002</v>
       </c>
       <c r="F6" s="0">
-        <v>100.59999999999999</v>
+        <v>101</v>
       </c>
       <c r="G6" s="0">
-        <v>10.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="H6" s="0">
         <v>9</v>
@@ -2464,7 +2464,7 @@
         <v>64.900000000000006</v>
       </c>
       <c r="G7" s="0">
-        <v>6.0999999999999996</v>
+        <v>5.7000000000000002</v>
       </c>
       <c r="H7" s="0">
         <v>9</v>
@@ -2591,10 +2591,10 @@
         <v>6.7999999999999998</v>
       </c>
       <c r="F12" s="0">
-        <v>104.59999999999999</v>
+        <v>103.8</v>
       </c>
       <c r="G12" s="0">
-        <v>9.1999999999999993</v>
+        <v>8.9000000000000004</v>
       </c>
       <c r="H12" s="0">
         <v>9</v>
@@ -2617,10 +2617,10 @@
         <v>10.199999999999999</v>
       </c>
       <c r="F13" s="0">
-        <v>68.200000000000003</v>
+        <v>66.5</v>
       </c>
       <c r="G13" s="0">
-        <v>8.1999999999999993</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="H13" s="0">
         <v>9</v>
@@ -3085,16 +3085,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>14.49</v>
+        <v>16.210000000000001</v>
       </c>
       <c r="C2" s="0">
-        <v>13.44</v>
+        <v>13.59</v>
       </c>
       <c r="D2" s="0">
-        <v>34.93</v>
+        <v>37.399999999999999</v>
       </c>
       <c r="E2" s="0">
-        <v>24.010000000000002</v>
+        <v>23.649999999999999</v>
       </c>
       <c r="F2" s="0">
         <v>38.729999999999997</v>
@@ -3111,16 +3111,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>24.600000000000001</v>
+        <v>24.43</v>
       </c>
       <c r="C3" s="0">
-        <v>15.69</v>
+        <v>14.69</v>
       </c>
       <c r="D3" s="0">
-        <v>27.879999999999999</v>
+        <v>26.780000000000001</v>
       </c>
       <c r="E3" s="0">
-        <v>26.539999999999999</v>
+        <v>25.039999999999999</v>
       </c>
       <c r="F3" s="0">
         <v>36.159999999999997</v>
@@ -3189,16 +3189,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>28.800000000000001</v>
+        <v>29.699999999999999</v>
       </c>
       <c r="C6" s="0">
-        <v>17.329999999999998</v>
+        <v>16.43</v>
       </c>
       <c r="D6" s="0">
-        <v>41.439999999999998</v>
+        <v>47.280000000000001</v>
       </c>
       <c r="E6" s="0">
-        <v>35</v>
+        <v>37.119999999999997</v>
       </c>
       <c r="F6" s="0">
         <v>31.920000000000002</v>
@@ -3215,16 +3215,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>37.469999999999999</v>
+        <v>38.009999999999998</v>
       </c>
       <c r="C7" s="0">
-        <v>18.899999999999999</v>
+        <v>17.75</v>
       </c>
       <c r="D7" s="0">
-        <v>39.630000000000003</v>
+        <v>38.920000000000002</v>
       </c>
       <c r="E7" s="0">
-        <v>28.609999999999999</v>
+        <v>26.84</v>
       </c>
       <c r="F7" s="0">
         <v>54.259999999999998</v>
@@ -3345,16 +3345,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>24.57</v>
+        <v>29.059999999999999</v>
       </c>
       <c r="C12" s="0">
-        <v>13.699999999999999</v>
+        <v>17.949999999999999</v>
       </c>
       <c r="D12" s="0">
-        <v>34.579999999999998</v>
+        <v>38.57</v>
       </c>
       <c r="E12" s="0">
-        <v>32.75</v>
+        <v>32.350000000000001</v>
       </c>
       <c r="F12" s="0">
         <v>34.399999999999999</v>
@@ -3371,16 +3371,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>42.82</v>
+        <v>41.079999999999998</v>
       </c>
       <c r="C13" s="0">
-        <v>20.899999999999999</v>
+        <v>19.969999999999999</v>
       </c>
       <c r="D13" s="0">
-        <v>47.619999999999997</v>
+        <v>54.920000000000002</v>
       </c>
       <c r="E13" s="0">
-        <v>32.090000000000003</v>
+        <v>36.18</v>
       </c>
       <c r="F13" s="0">
         <v>53.460000000000001</v>
@@ -3468,16 +3468,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>-45.579999999999998</v>
+        <v>-42.049999999999997</v>
       </c>
       <c r="C2" s="0">
-        <v>45.189999999999998</v>
+        <v>43.579999999999998</v>
       </c>
       <c r="D2" s="0">
-        <v>-43.359999999999999</v>
+        <v>-38.890000000000001</v>
       </c>
       <c r="E2" s="0">
-        <v>74.359999999999999</v>
+        <v>70.840000000000003</v>
       </c>
       <c r="F2" s="0">
         <v>-29.329999999999998</v>
@@ -3494,16 +3494,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>-21.100000000000001</v>
+        <v>-19.050000000000001</v>
       </c>
       <c r="C3" s="0">
-        <v>12.01</v>
+        <v>12.81</v>
       </c>
       <c r="D3" s="0">
-        <v>-35</v>
+        <v>-30.940000000000001</v>
       </c>
       <c r="E3" s="0">
-        <v>40.159999999999997</v>
+        <v>39.490000000000002</v>
       </c>
       <c r="F3" s="0">
         <v>-57.590000000000003</v>
@@ -3572,16 +3572,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>-57.789999999999999</v>
+        <v>-53.079999999999998</v>
       </c>
       <c r="C6" s="0">
-        <v>46.100000000000001</v>
+        <v>45.380000000000003</v>
       </c>
       <c r="D6" s="0">
-        <v>-49.359999999999999</v>
+        <v>-44.25</v>
       </c>
       <c r="E6" s="0">
-        <v>73.519999999999996</v>
+        <v>70.459999999999994</v>
       </c>
       <c r="F6" s="0">
         <v>-28.219999999999999</v>
@@ -3598,16 +3598,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>-25.149999999999999</v>
+        <v>-23.300000000000001</v>
       </c>
       <c r="C7" s="0">
-        <v>15.56</v>
+        <v>15.58</v>
       </c>
       <c r="D7" s="0">
-        <v>-49.710000000000001</v>
+        <v>-44.280000000000001</v>
       </c>
       <c r="E7" s="0">
-        <v>40.409999999999997</v>
+        <v>41.170000000000002</v>
       </c>
       <c r="F7" s="0">
         <v>-65.950000000000003</v>
@@ -3728,16 +3728,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>-55.909999999999997</v>
+        <v>-49.869999999999997</v>
       </c>
       <c r="C12" s="0">
-        <v>50.609999999999999</v>
+        <v>49.869999999999997</v>
       </c>
       <c r="D12" s="0">
-        <v>-62.520000000000003</v>
+        <v>-54.5</v>
       </c>
       <c r="E12" s="0">
-        <v>73.969999999999999</v>
+        <v>72.140000000000001</v>
       </c>
       <c r="F12" s="0">
         <v>-29.390000000000001</v>
@@ -3754,16 +3754,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>-25.5</v>
+        <v>-24.48</v>
       </c>
       <c r="C13" s="0">
-        <v>10.91</v>
+        <v>10.5</v>
       </c>
       <c r="D13" s="0">
-        <v>-42.590000000000003</v>
+        <v>-37.490000000000002</v>
       </c>
       <c r="E13" s="0">
-        <v>42</v>
+        <v>41.469999999999999</v>
       </c>
       <c r="F13" s="0">
         <v>-49.890000000000001</v>
@@ -3883,16 +3883,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>-4.4699999999999998</v>
+        <v>-3.1899999999999999</v>
       </c>
       <c r="C2" s="0">
-        <v>10.33</v>
+        <v>10.4</v>
       </c>
       <c r="D2" s="0">
-        <v>4.5</v>
+        <v>7.79</v>
       </c>
       <c r="E2" s="0">
-        <v>16.120000000000001</v>
+        <v>18.030000000000001</v>
       </c>
       <c r="F2" s="0">
         <v>12.57</v>
@@ -3919,10 +3919,10 @@
         <v>6.1600000000000001</v>
       </c>
       <c r="N2" s="0">
-        <v>1.8</v>
+        <v>2.3300000000000001</v>
       </c>
       <c r="O2" s="0">
-        <v>4.0599999999999996</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="P2" s="0">
         <v>9</v>
@@ -3933,13 +3933,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>-5.4900000000000002</v>
+        <v>-2.2000000000000002</v>
       </c>
       <c r="C3" s="0">
-        <v>17.050000000000001</v>
+        <v>18.75</v>
       </c>
       <c r="D3" s="0">
-        <v>2.7000000000000002</v>
+        <v>1.96</v>
       </c>
       <c r="E3" s="0">
         <v>6.3399999999999999</v>
@@ -3969,10 +3969,10 @@
         <v>0.76000000000000001</v>
       </c>
       <c r="N3" s="0">
-        <v>9.4399999999999995</v>
+        <v>10.93</v>
       </c>
       <c r="O3" s="0">
-        <v>1.0600000000000001</v>
+        <v>4.5800000000000001</v>
       </c>
       <c r="P3" s="0">
         <v>9</v>
@@ -4083,16 +4083,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>-2.0899999999999999</v>
+        <v>-2.6099999999999999</v>
       </c>
       <c r="C6" s="0">
-        <v>8.3699999999999992</v>
+        <v>7.9900000000000002</v>
       </c>
       <c r="D6" s="0">
-        <v>1.3100000000000001</v>
+        <v>6.8300000000000001</v>
       </c>
       <c r="E6" s="0">
-        <v>11.710000000000001</v>
+        <v>19.859999999999999</v>
       </c>
       <c r="F6" s="0">
         <v>3.4199999999999999</v>
@@ -4119,10 +4119,10 @@
         <v>6.1100000000000003</v>
       </c>
       <c r="N6" s="0">
-        <v>1.05</v>
+        <v>1.1899999999999999</v>
       </c>
       <c r="O6" s="0">
-        <v>1.7</v>
+        <v>1.6399999999999999</v>
       </c>
       <c r="P6" s="0">
         <v>9</v>
@@ -4133,16 +4133,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>1.1499999999999999</v>
+        <v>1.53</v>
       </c>
       <c r="C7" s="0">
-        <v>17.489999999999998</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="D7" s="0">
-        <v>5.71</v>
+        <v>4.46</v>
       </c>
       <c r="E7" s="0">
-        <v>6.0700000000000003</v>
+        <v>6.8099999999999996</v>
       </c>
       <c r="F7" s="0">
         <v>11.84</v>
@@ -4169,10 +4169,10 @@
         <v>0.69999999999999996</v>
       </c>
       <c r="N7" s="0">
-        <v>10.17</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="O7" s="0">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="P7" s="0">
         <v>9</v>
@@ -4383,16 +4383,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>5.3899999999999997</v>
+        <v>4.5899999999999999</v>
       </c>
       <c r="C12" s="0">
-        <v>11.6</v>
+        <v>10.98</v>
       </c>
       <c r="D12" s="0">
-        <v>-4.8300000000000001</v>
+        <v>-9.6300000000000008</v>
       </c>
       <c r="E12" s="0">
-        <v>24.899999999999999</v>
+        <v>26.75</v>
       </c>
       <c r="F12" s="0">
         <v>-0.23999999999999999</v>
@@ -4419,10 +4419,10 @@
         <v>7.9100000000000001</v>
       </c>
       <c r="N12" s="0">
-        <v>2.8999999999999999</v>
+        <v>2.6899999999999999</v>
       </c>
       <c r="O12" s="0">
-        <v>6.75</v>
+        <v>6.3499999999999996</v>
       </c>
       <c r="P12" s="0">
         <v>9</v>
@@ -4433,16 +4433,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>-3.2400000000000002</v>
+        <v>-1.26</v>
       </c>
       <c r="C13" s="0">
-        <v>12.1</v>
+        <v>12.52</v>
       </c>
       <c r="D13" s="0">
-        <v>7.3300000000000001</v>
+        <v>9.6199999999999992</v>
       </c>
       <c r="E13" s="0">
-        <v>7.7000000000000002</v>
+        <v>9.6300000000000008</v>
       </c>
       <c r="F13" s="0">
         <v>15.08</v>
@@ -4469,10 +4469,10 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="N13" s="0">
-        <v>10.57</v>
+        <v>10.52</v>
       </c>
       <c r="O13" s="0">
-        <v>2.3700000000000001</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="P13" s="0">
         <v>9</v>
@@ -4642,22 +4642,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>54.060000000000002</v>
+        <v>51.399999999999999</v>
       </c>
       <c r="C2" s="0">
-        <v>39.909999999999997</v>
+        <v>38.18</v>
       </c>
       <c r="D2" s="0">
-        <v>14.24</v>
+        <v>14.529999999999999</v>
       </c>
       <c r="E2" s="0">
-        <v>9.9600000000000009</v>
+        <v>9.3599999999999994</v>
       </c>
       <c r="F2" s="0">
-        <v>65.569999999999993</v>
+        <v>65.090000000000003</v>
       </c>
       <c r="G2" s="0">
-        <v>64.950000000000003</v>
+        <v>60.770000000000003</v>
       </c>
       <c r="H2" s="0">
         <v>47.450000000000003</v>
@@ -4672,10 +4672,10 @@
         <v>19.149999999999999</v>
       </c>
       <c r="L2" s="0">
-        <v>61.359999999999999</v>
+        <v>59.32</v>
       </c>
       <c r="M2" s="0">
-        <v>10.699999999999999</v>
+        <v>11.73</v>
       </c>
       <c r="N2" s="0">
         <v>52.450000000000003</v>
@@ -4690,10 +4690,10 @@
         <v>6.79</v>
       </c>
       <c r="R2" s="0">
-        <v>20.530000000000001</v>
+        <v>20.09</v>
       </c>
       <c r="S2" s="0">
-        <v>2.9199999999999999</v>
+        <v>3.04</v>
       </c>
       <c r="T2" s="0">
         <v>29.350000000000001</v>
@@ -4716,22 +4716,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>34.659999999999997</v>
+        <v>33.109999999999999</v>
       </c>
       <c r="C3" s="0">
-        <v>14.74</v>
+        <v>14.550000000000001</v>
       </c>
       <c r="D3" s="0">
-        <v>16.34</v>
+        <v>15.029999999999999</v>
       </c>
       <c r="E3" s="0">
-        <v>18.050000000000001</v>
+        <v>17.34</v>
       </c>
       <c r="F3" s="0">
-        <v>60.18</v>
+        <v>55.049999999999997</v>
       </c>
       <c r="G3" s="0">
-        <v>28.300000000000001</v>
+        <v>30.609999999999999</v>
       </c>
       <c r="H3" s="0">
         <v>77.590000000000003</v>
@@ -4746,10 +4746,10 @@
         <v>12.18</v>
       </c>
       <c r="L3" s="0">
-        <v>35.920000000000002</v>
+        <v>34.920000000000002</v>
       </c>
       <c r="M3" s="0">
-        <v>5.46</v>
+        <v>5.9199999999999999</v>
       </c>
       <c r="N3" s="0">
         <v>82.030000000000001</v>
@@ -4764,10 +4764,10 @@
         <v>13.31</v>
       </c>
       <c r="R3" s="0">
-        <v>25</v>
+        <v>24.780000000000001</v>
       </c>
       <c r="S3" s="0">
-        <v>4.7999999999999998</v>
+        <v>4.5300000000000002</v>
       </c>
       <c r="T3" s="0">
         <v>24.48</v>
@@ -4938,22 +4938,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>63.850000000000001</v>
+        <v>60.869999999999997</v>
       </c>
       <c r="C6" s="0">
-        <v>34.130000000000003</v>
+        <v>33.149999999999999</v>
       </c>
       <c r="D6" s="0">
-        <v>26.739999999999998</v>
+        <v>25.309999999999999</v>
       </c>
       <c r="E6" s="0">
-        <v>19.41</v>
+        <v>18.66</v>
       </c>
       <c r="F6" s="0">
-        <v>80.280000000000001</v>
+        <v>81.560000000000002</v>
       </c>
       <c r="G6" s="0">
-        <v>58.780000000000001</v>
+        <v>55.119999999999997</v>
       </c>
       <c r="H6" s="0">
         <v>44.57</v>
@@ -4968,10 +4968,10 @@
         <v>9.7799999999999994</v>
       </c>
       <c r="L6" s="0">
-        <v>81.189999999999998</v>
+        <v>82.379999999999995</v>
       </c>
       <c r="M6" s="0">
-        <v>8.7400000000000002</v>
+        <v>8.9299999999999997</v>
       </c>
       <c r="N6" s="0">
         <v>53.509999999999998</v>
@@ -4986,10 +4986,10 @@
         <v>8.1699999999999999</v>
       </c>
       <c r="R6" s="0">
-        <v>19.440000000000001</v>
+        <v>18.59</v>
       </c>
       <c r="S6" s="0">
-        <v>4.0499999999999998</v>
+        <v>4.5700000000000003</v>
       </c>
       <c r="T6" s="0">
         <v>30.510000000000002</v>
@@ -5012,22 +5012,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>44.630000000000003</v>
+        <v>44.780000000000001</v>
       </c>
       <c r="C7" s="0">
-        <v>22.649999999999999</v>
+        <v>21.190000000000001</v>
       </c>
       <c r="D7" s="0">
-        <v>18.68</v>
+        <v>17.129999999999999</v>
       </c>
       <c r="E7" s="0">
-        <v>15.529999999999999</v>
+        <v>15.25</v>
       </c>
       <c r="F7" s="0">
-        <v>78.640000000000001</v>
+        <v>73.230000000000004</v>
       </c>
       <c r="G7" s="0">
-        <v>16.890000000000001</v>
+        <v>22.640000000000001</v>
       </c>
       <c r="H7" s="0">
         <v>103.11</v>
@@ -5042,10 +5042,10 @@
         <v>12.550000000000001</v>
       </c>
       <c r="L7" s="0">
-        <v>39.789999999999999</v>
+        <v>40.899999999999999</v>
       </c>
       <c r="M7" s="0">
-        <v>6.9000000000000004</v>
+        <v>7.25</v>
       </c>
       <c r="N7" s="0">
         <v>102.63</v>
@@ -5060,10 +5060,10 @@
         <v>12.18</v>
       </c>
       <c r="R7" s="0">
-        <v>25.149999999999999</v>
+        <v>23.969999999999999</v>
       </c>
       <c r="S7" s="0">
-        <v>4.1799999999999997</v>
+        <v>5.2699999999999996</v>
       </c>
       <c r="T7" s="0">
         <v>22.780000000000001</v>
@@ -5382,22 +5382,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>55.390000000000001</v>
+        <v>56.439999999999998</v>
       </c>
       <c r="C12" s="0">
-        <v>46.340000000000003</v>
+        <v>43.009999999999998</v>
       </c>
       <c r="D12" s="0">
-        <v>25.079999999999998</v>
+        <v>22.530000000000001</v>
       </c>
       <c r="E12" s="0">
-        <v>14.82</v>
+        <v>15.5</v>
       </c>
       <c r="F12" s="0">
-        <v>84.010000000000005</v>
+        <v>81.150000000000006</v>
       </c>
       <c r="G12" s="0">
-        <v>62.469999999999999</v>
+        <v>58.399999999999999</v>
       </c>
       <c r="H12" s="0">
         <v>47.149999999999999</v>
@@ -5412,10 +5412,10 @@
         <v>13.24</v>
       </c>
       <c r="L12" s="0">
-        <v>86.409999999999997</v>
+        <v>85.780000000000001</v>
       </c>
       <c r="M12" s="0">
-        <v>7.7300000000000004</v>
+        <v>7.4699999999999998</v>
       </c>
       <c r="N12" s="0">
         <v>54.219999999999999</v>
@@ -5430,10 +5430,10 @@
         <v>7.3300000000000001</v>
       </c>
       <c r="R12" s="0">
-        <v>18.140000000000001</v>
+        <v>18.18</v>
       </c>
       <c r="S12" s="0">
-        <v>3.9700000000000002</v>
+        <v>3.71</v>
       </c>
       <c r="T12" s="0">
         <v>31.010000000000002</v>
@@ -5456,22 +5456,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>46.030000000000001</v>
+        <v>44.409999999999997</v>
       </c>
       <c r="C13" s="0">
-        <v>29.829999999999998</v>
+        <v>28</v>
       </c>
       <c r="D13" s="0">
-        <v>22.289999999999999</v>
+        <v>21.079999999999998</v>
       </c>
       <c r="E13" s="0">
-        <v>21.940000000000001</v>
+        <v>20.600000000000001</v>
       </c>
       <c r="F13" s="0">
-        <v>76.069999999999993</v>
+        <v>79.700000000000003</v>
       </c>
       <c r="G13" s="0">
-        <v>22.09</v>
+        <v>22.870000000000001</v>
       </c>
       <c r="H13" s="0">
         <v>91.239999999999995</v>
@@ -5486,10 +5486,10 @@
         <v>6.2300000000000004</v>
       </c>
       <c r="L13" s="0">
-        <v>41.68</v>
+        <v>40.539999999999999</v>
       </c>
       <c r="M13" s="0">
-        <v>8</v>
+        <v>8.2300000000000004</v>
       </c>
       <c r="N13" s="0">
         <v>108.14</v>
@@ -5504,10 +5504,10 @@
         <v>10.1</v>
       </c>
       <c r="R13" s="0">
-        <v>26.5</v>
+        <v>25.960000000000001</v>
       </c>
       <c r="S13" s="0">
-        <v>3.0099999999999998</v>
+        <v>3.2400000000000002</v>
       </c>
       <c r="T13" s="0">
         <v>24.239999999999998</v>

--- a/Results/Group Analysis/GroupCrossing_YoungAdults_Summary.xlsx
+++ b/Results/Group Analysis/GroupCrossing_YoungAdults_Summary.xlsx
@@ -412,73 +412,73 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>35.640000000000001</v>
+        <v>37.689999999999998</v>
       </c>
       <c r="C2" s="0">
-        <v>35.799999999999997</v>
+        <v>34.369999999999997</v>
       </c>
       <c r="D2" s="0">
-        <v>5.46</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="E2" s="0">
-        <v>12.039999999999999</v>
+        <v>11.869999999999999</v>
       </c>
       <c r="F2" s="0">
-        <v>35.469999999999999</v>
+        <v>32.060000000000002</v>
       </c>
       <c r="G2" s="0">
-        <v>61.579999999999998</v>
+        <v>59.049999999999997</v>
       </c>
       <c r="H2" s="0">
-        <v>1.3400000000000001</v>
+        <v>2.9300000000000002</v>
       </c>
       <c r="I2" s="0">
-        <v>14.43</v>
+        <v>14.5</v>
       </c>
       <c r="J2" s="0">
-        <v>12.609999999999999</v>
+        <v>12.93</v>
       </c>
       <c r="K2" s="0">
-        <v>17.09</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="L2" s="0">
-        <v>32.719999999999999</v>
+        <v>32.450000000000003</v>
       </c>
       <c r="M2" s="0">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="N2" s="0">
-        <v>4.3200000000000003</v>
+        <v>4.2800000000000002</v>
       </c>
       <c r="O2" s="0">
-        <v>3.1299999999999999</v>
+        <v>2.9500000000000002</v>
       </c>
       <c r="P2" s="0">
-        <v>1</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="Q2" s="0">
-        <v>4.4000000000000004</v>
+        <v>4.3700000000000001</v>
       </c>
       <c r="R2" s="0">
-        <v>2.0600000000000001</v>
+        <v>2.04</v>
       </c>
       <c r="S2" s="0">
-        <v>2.52</v>
+        <v>2.3700000000000001</v>
       </c>
       <c r="T2" s="0">
-        <v>2.8900000000000001</v>
+        <v>2.5800000000000001</v>
       </c>
       <c r="U2" s="0">
-        <v>5.4699999999999998</v>
+        <v>5.2400000000000002</v>
       </c>
       <c r="V2" s="0">
-        <v>4.1200000000000001</v>
+        <v>3.8999999999999999</v>
       </c>
       <c r="W2" s="0">
-        <v>9.3000000000000007</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="X2" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -486,73 +486,73 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>17.34</v>
+        <v>15.380000000000001</v>
       </c>
       <c r="C3" s="0">
-        <v>15.470000000000001</v>
+        <v>15.84</v>
       </c>
       <c r="D3" s="0">
-        <v>5.96</v>
+        <v>6.1299999999999999</v>
       </c>
       <c r="E3" s="0">
-        <v>17.82</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="F3" s="0">
-        <v>25.43</v>
+        <v>26.829999999999998</v>
       </c>
       <c r="G3" s="0">
-        <v>37.159999999999997</v>
+        <v>35.310000000000002</v>
       </c>
       <c r="H3" s="0">
-        <v>31.469999999999999</v>
+        <v>26.609999999999999</v>
       </c>
       <c r="I3" s="0">
-        <v>31.890000000000001</v>
+        <v>33.770000000000003</v>
       </c>
       <c r="J3" s="0">
-        <v>11.49</v>
+        <v>21.84</v>
       </c>
       <c r="K3" s="0">
-        <v>11.140000000000001</v>
+        <v>34.359999999999999</v>
       </c>
       <c r="L3" s="0">
-        <v>8.3200000000000003</v>
+        <v>8.1799999999999997</v>
       </c>
       <c r="M3" s="0">
-        <v>3.8599999999999999</v>
+        <v>3.6699999999999999</v>
       </c>
       <c r="N3" s="0">
-        <v>33.899999999999999</v>
+        <v>31.390000000000001</v>
       </c>
       <c r="O3" s="0">
-        <v>14.44</v>
+        <v>15.75</v>
       </c>
       <c r="P3" s="0">
-        <v>19.5</v>
+        <v>17.469999999999999</v>
       </c>
       <c r="Q3" s="0">
-        <v>10.529999999999999</v>
+        <v>11.82</v>
       </c>
       <c r="R3" s="0">
-        <v>6.7599999999999998</v>
+        <v>6.1200000000000001</v>
       </c>
       <c r="S3" s="0">
-        <v>4.0899999999999999</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="T3" s="0">
-        <v>-1.98</v>
+        <v>-0.90000000000000002</v>
       </c>
       <c r="U3" s="0">
-        <v>3.1400000000000001</v>
+        <v>4.5300000000000002</v>
       </c>
       <c r="V3" s="0">
-        <v>1.73</v>
+        <v>2.4100000000000001</v>
       </c>
       <c r="W3" s="0">
-        <v>2.9500000000000002</v>
+        <v>3.52</v>
       </c>
       <c r="X3" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -560,73 +560,73 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>44.609999999999999</v>
+        <v>42.75</v>
       </c>
       <c r="C4" s="0">
-        <v>39.009999999999998</v>
+        <v>37.240000000000002</v>
       </c>
       <c r="D4" s="0">
-        <v>9.4499999999999993</v>
+        <v>8.7699999999999996</v>
       </c>
       <c r="E4" s="0">
-        <v>7.5199999999999996</v>
+        <v>7.4100000000000001</v>
       </c>
       <c r="F4" s="0">
-        <v>45.710000000000001</v>
+        <v>43.560000000000002</v>
       </c>
       <c r="G4" s="0">
-        <v>61.579999999999998</v>
+        <v>58.450000000000003</v>
       </c>
       <c r="H4" s="0">
-        <v>-4.7400000000000002</v>
+        <v>-4.8099999999999996</v>
       </c>
       <c r="I4" s="0">
-        <v>11.32</v>
+        <v>10.67</v>
       </c>
       <c r="J4" s="0">
-        <v>6.8099999999999996</v>
+        <v>12.56</v>
       </c>
       <c r="K4" s="0">
-        <v>10.34</v>
+        <v>20.620000000000001</v>
       </c>
       <c r="L4" s="0">
-        <v>50.009999999999998</v>
+        <v>48.560000000000002</v>
       </c>
       <c r="M4" s="0">
-        <v>8.75</v>
+        <v>9.4399999999999995</v>
       </c>
       <c r="N4" s="0">
-        <v>5.2599999999999998</v>
+        <v>5.0700000000000003</v>
       </c>
       <c r="O4" s="0">
-        <v>3.6099999999999999</v>
+        <v>3.46</v>
       </c>
       <c r="P4" s="0">
-        <v>0.20000000000000001</v>
+        <v>0.89000000000000001</v>
       </c>
       <c r="Q4" s="0">
-        <v>4.7800000000000002</v>
+        <v>5.0099999999999998</v>
       </c>
       <c r="R4" s="0">
-        <v>-0.44</v>
+        <v>-0.11</v>
       </c>
       <c r="S4" s="0">
-        <v>2.5</v>
+        <v>2.5800000000000001</v>
       </c>
       <c r="T4" s="0">
-        <v>3.21</v>
+        <v>3.1899999999999999</v>
       </c>
       <c r="U4" s="0">
-        <v>4.9900000000000002</v>
+        <v>4.71</v>
       </c>
       <c r="V4" s="0">
-        <v>-0.040000000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="W4" s="0">
-        <v>12.99</v>
+        <v>12.43</v>
       </c>
       <c r="X4" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -634,73 +634,73 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>21.539999999999999</v>
+        <v>21.030000000000001</v>
       </c>
       <c r="C5" s="0">
-        <v>18.780000000000001</v>
+        <v>17.780000000000001</v>
       </c>
       <c r="D5" s="0">
-        <v>3.8300000000000001</v>
+        <v>3.4399999999999999</v>
       </c>
       <c r="E5" s="0">
-        <v>11.859999999999999</v>
+        <v>11.25</v>
       </c>
       <c r="F5" s="0">
-        <v>36.770000000000003</v>
+        <v>34.960000000000001</v>
       </c>
       <c r="G5" s="0">
-        <v>35.939999999999998</v>
+        <v>34.369999999999997</v>
       </c>
       <c r="H5" s="0">
-        <v>44.829999999999998</v>
+        <v>42.57</v>
       </c>
       <c r="I5" s="0">
-        <v>30.649999999999999</v>
+        <v>29.760000000000002</v>
       </c>
       <c r="J5" s="0">
-        <v>2.8199999999999998</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="K5" s="0">
-        <v>4.0300000000000002</v>
+        <v>21.59</v>
       </c>
       <c r="L5" s="0">
-        <v>11.109999999999999</v>
+        <v>11.19</v>
       </c>
       <c r="M5" s="0">
-        <v>4.6299999999999999</v>
+        <v>4.3700000000000001</v>
       </c>
       <c r="N5" s="0">
-        <v>47.609999999999999</v>
+        <v>45.75</v>
       </c>
       <c r="O5" s="0">
-        <v>14.029999999999999</v>
+        <v>14.470000000000001</v>
       </c>
       <c r="P5" s="0">
-        <v>27.949999999999999</v>
+        <v>27.239999999999998</v>
       </c>
       <c r="Q5" s="0">
-        <v>10.369999999999999</v>
+        <v>10.029999999999999</v>
       </c>
       <c r="R5" s="0">
-        <v>6.6900000000000004</v>
+        <v>6.4000000000000004</v>
       </c>
       <c r="S5" s="0">
-        <v>3.9700000000000002</v>
+        <v>3.8599999999999999</v>
       </c>
       <c r="T5" s="0">
-        <v>-2.2999999999999998</v>
+        <v>-2.0800000000000001</v>
       </c>
       <c r="U5" s="0">
-        <v>4.8300000000000001</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="V5" s="0">
-        <v>2.3999999999999999</v>
+        <v>2.6000000000000001</v>
       </c>
       <c r="W5" s="0">
-        <v>5.0499999999999998</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="X5" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -708,73 +708,73 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>45.109999999999999</v>
+        <v>41.630000000000003</v>
       </c>
       <c r="C6" s="0">
-        <v>31.16</v>
+        <v>31.370000000000001</v>
       </c>
       <c r="D6" s="0">
-        <v>16.23</v>
+        <v>18.920000000000002</v>
       </c>
       <c r="E6" s="0">
-        <v>21.699999999999999</v>
+        <v>22.149999999999999</v>
       </c>
       <c r="F6" s="0">
-        <v>51.939999999999998</v>
+        <v>51.530000000000001</v>
       </c>
       <c r="G6" s="0">
-        <v>54.719999999999999</v>
+        <v>51.609999999999999</v>
       </c>
       <c r="H6" s="0">
-        <v>-1.55</v>
+        <v>-0.82999999999999996</v>
       </c>
       <c r="I6" s="0">
-        <v>14.07</v>
+        <v>13.460000000000001</v>
       </c>
       <c r="J6" s="0">
-        <v>7.5700000000000003</v>
+        <v>10.73</v>
       </c>
       <c r="K6" s="0">
-        <v>8.9800000000000004</v>
+        <v>13.1</v>
       </c>
       <c r="L6" s="0">
-        <v>55.780000000000001</v>
+        <v>54.689999999999998</v>
       </c>
       <c r="M6" s="0">
-        <v>8.4100000000000001</v>
+        <v>8.6400000000000006</v>
       </c>
       <c r="N6" s="0">
-        <v>5.3799999999999999</v>
+        <v>5.4800000000000004</v>
       </c>
       <c r="O6" s="0">
-        <v>3.6400000000000001</v>
+        <v>3.4399999999999999</v>
       </c>
       <c r="P6" s="0">
-        <v>-2.5800000000000001</v>
+        <v>-1.6299999999999999</v>
       </c>
       <c r="Q6" s="0">
-        <v>9.6899999999999995</v>
+        <v>9.6099999999999994</v>
       </c>
       <c r="R6" s="0">
-        <v>0.56000000000000005</v>
+        <v>1.03</v>
       </c>
       <c r="S6" s="0">
-        <v>4.75</v>
+        <v>4.7199999999999998</v>
       </c>
       <c r="T6" s="0">
-        <v>4.0499999999999998</v>
+        <v>3.79</v>
       </c>
       <c r="U6" s="0">
-        <v>5.3099999999999996</v>
+        <v>5.0700000000000003</v>
       </c>
       <c r="V6" s="0">
-        <v>-1.78</v>
+        <v>-0.89000000000000001</v>
       </c>
       <c r="W6" s="0">
-        <v>10.94</v>
+        <v>10.69</v>
       </c>
       <c r="X6" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -782,73 +782,73 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>29.02</v>
+        <v>28.489999999999998</v>
       </c>
       <c r="C7" s="0">
-        <v>20.920000000000002</v>
+        <v>19.800000000000001</v>
       </c>
       <c r="D7" s="0">
-        <v>8.0600000000000005</v>
+        <v>7.5499999999999998</v>
       </c>
       <c r="E7" s="0">
-        <v>15.119999999999999</v>
+        <v>14.34</v>
       </c>
       <c r="F7" s="0">
-        <v>43.619999999999997</v>
+        <v>42.479999999999997</v>
       </c>
       <c r="G7" s="0">
-        <v>31.449999999999999</v>
+        <v>29.870000000000001</v>
       </c>
       <c r="H7" s="0">
-        <v>57</v>
+        <v>54.030000000000001</v>
       </c>
       <c r="I7" s="0">
-        <v>39.789999999999999</v>
+        <v>38.670000000000002</v>
       </c>
       <c r="J7" s="0">
-        <v>9.0999999999999996</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="K7" s="0">
-        <v>10.66</v>
+        <v>10.25</v>
       </c>
       <c r="L7" s="0">
-        <v>14.289999999999999</v>
+        <v>13.43</v>
       </c>
       <c r="M7" s="0">
-        <v>6.79</v>
+        <v>6.9699999999999998</v>
       </c>
       <c r="N7" s="0">
-        <v>54.5</v>
+        <v>53.75</v>
       </c>
       <c r="O7" s="0">
-        <v>9.5899999999999999</v>
+        <v>9.3499999999999996</v>
       </c>
       <c r="P7" s="0">
-        <v>31.59</v>
+        <v>32.210000000000001</v>
       </c>
       <c r="Q7" s="0">
-        <v>12.02</v>
+        <v>11.5</v>
       </c>
       <c r="R7" s="0">
-        <v>5.9400000000000004</v>
+        <v>6.7000000000000002</v>
       </c>
       <c r="S7" s="0">
-        <v>3.5899999999999999</v>
+        <v>4.1600000000000001</v>
       </c>
       <c r="T7" s="0">
-        <v>-3.6899999999999999</v>
+        <v>-4.46</v>
       </c>
       <c r="U7" s="0">
-        <v>6.6200000000000001</v>
+        <v>6.7000000000000002</v>
       </c>
       <c r="V7" s="0">
-        <v>1.1799999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="W7" s="0">
-        <v>7.2699999999999996</v>
+        <v>6.9199999999999999</v>
       </c>
       <c r="X7" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -856,73 +856,73 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>38.399999999999999</v>
+        <v>36.880000000000003</v>
       </c>
       <c r="C8" s="0">
-        <v>38.450000000000003</v>
+        <v>36.259999999999998</v>
       </c>
       <c r="D8" s="0">
-        <v>0.71999999999999997</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="E8" s="0">
-        <v>9.8000000000000007</v>
+        <v>9.2599999999999998</v>
       </c>
       <c r="F8" s="0">
-        <v>38.340000000000003</v>
+        <v>35.859999999999999</v>
       </c>
       <c r="G8" s="0">
-        <v>64.640000000000001</v>
+        <v>60.920000000000002</v>
       </c>
       <c r="H8" s="0">
-        <v>1.3200000000000001</v>
+        <v>1.0700000000000001</v>
       </c>
       <c r="I8" s="0">
-        <v>9.2799999999999994</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="J8" s="0">
-        <v>5.8899999999999997</v>
+        <v>12.16</v>
       </c>
       <c r="K8" s="0">
-        <v>13.859999999999999</v>
+        <v>22.850000000000001</v>
       </c>
       <c r="L8" s="0">
-        <v>38.939999999999998</v>
+        <v>38.280000000000001</v>
       </c>
       <c r="M8" s="0">
-        <v>6.5899999999999999</v>
+        <v>6.5599999999999996</v>
       </c>
       <c r="N8" s="0">
-        <v>4.1900000000000004</v>
+        <v>4.1699999999999999</v>
       </c>
       <c r="O8" s="0">
-        <v>3.0099999999999998</v>
+        <v>2.8399999999999999</v>
       </c>
       <c r="P8" s="0">
-        <v>2.2200000000000002</v>
+        <v>2.9500000000000002</v>
       </c>
       <c r="Q8" s="0">
-        <v>3.9199999999999999</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="R8" s="0">
-        <v>-0.56000000000000005</v>
+        <v>-0.31</v>
       </c>
       <c r="S8" s="0">
-        <v>2.5600000000000001</v>
+        <v>2.54</v>
       </c>
       <c r="T8" s="0">
-        <v>4.8700000000000001</v>
+        <v>5.3799999999999999</v>
       </c>
       <c r="U8" s="0">
-        <v>4.3499999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="V8" s="0">
-        <v>5.0899999999999999</v>
+        <v>5.9199999999999999</v>
       </c>
       <c r="W8" s="0">
-        <v>11.27</v>
+        <v>10.949999999999999</v>
       </c>
       <c r="X8" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -930,73 +930,73 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>14.84</v>
+        <v>15.23</v>
       </c>
       <c r="C9" s="0">
-        <v>9.4000000000000004</v>
+        <v>8.8699999999999992</v>
       </c>
       <c r="D9" s="0">
-        <v>4.2599999999999998</v>
+        <v>4.0700000000000003</v>
       </c>
       <c r="E9" s="0">
-        <v>12.02</v>
+        <v>11.26</v>
       </c>
       <c r="F9" s="0">
-        <v>39.710000000000001</v>
+        <v>37.229999999999997</v>
       </c>
       <c r="G9" s="0">
-        <v>21.57</v>
+        <v>21.510000000000002</v>
       </c>
       <c r="H9" s="0">
-        <v>31.600000000000001</v>
+        <v>30.27</v>
       </c>
       <c r="I9" s="0">
-        <v>29.870000000000001</v>
+        <v>28.219999999999999</v>
       </c>
       <c r="J9" s="0">
-        <v>7.21</v>
+        <v>12.09</v>
       </c>
       <c r="K9" s="0">
-        <v>7.2800000000000002</v>
+        <v>16.140000000000001</v>
       </c>
       <c r="L9" s="0">
-        <v>10.720000000000001</v>
+        <v>10.359999999999999</v>
       </c>
       <c r="M9" s="0">
-        <v>3.8900000000000001</v>
+        <v>3.8300000000000001</v>
       </c>
       <c r="N9" s="0">
-        <v>35.57</v>
+        <v>34.659999999999997</v>
       </c>
       <c r="O9" s="0">
-        <v>12.16</v>
+        <v>11.82</v>
       </c>
       <c r="P9" s="0">
-        <v>24.75</v>
+        <v>24.469999999999999</v>
       </c>
       <c r="Q9" s="0">
-        <v>11.74</v>
+        <v>11.1</v>
       </c>
       <c r="R9" s="0">
-        <v>6.7999999999999998</v>
+        <v>6.8499999999999996</v>
       </c>
       <c r="S9" s="0">
-        <v>3.6899999999999999</v>
+        <v>3.48</v>
       </c>
       <c r="T9" s="0">
-        <v>-1.3</v>
+        <v>-1.28</v>
       </c>
       <c r="U9" s="0">
-        <v>4.2699999999999996</v>
+        <v>4.0300000000000002</v>
       </c>
       <c r="V9" s="0">
-        <v>2.73</v>
+        <v>2.8799999999999999</v>
       </c>
       <c r="W9" s="0">
-        <v>5.6600000000000001</v>
+        <v>5.3600000000000003</v>
       </c>
       <c r="X9" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -1004,73 +1004,73 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>47.049999999999997</v>
+        <v>46.039999999999999</v>
       </c>
       <c r="C10" s="0">
-        <v>35.810000000000002</v>
+        <v>33.909999999999997</v>
       </c>
       <c r="D10" s="0">
-        <v>9.8300000000000001</v>
+        <v>9.2100000000000009</v>
       </c>
       <c r="E10" s="0">
-        <v>14.94</v>
+        <v>14.220000000000001</v>
       </c>
       <c r="F10" s="0">
-        <v>49.710000000000001</v>
+        <v>45.990000000000002</v>
       </c>
       <c r="G10" s="0">
-        <v>51.350000000000001</v>
+        <v>49.810000000000002</v>
       </c>
       <c r="H10" s="0">
-        <v>-5.46</v>
+        <v>-4.4699999999999998</v>
       </c>
       <c r="I10" s="0">
-        <v>15.35</v>
+        <v>14.800000000000001</v>
       </c>
       <c r="J10" s="0">
-        <v>7.8799999999999999</v>
+        <v>7.4100000000000001</v>
       </c>
       <c r="K10" s="0">
-        <v>9.9900000000000002</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="L10" s="0">
-        <v>52.399999999999999</v>
+        <v>51.340000000000003</v>
       </c>
       <c r="M10" s="0">
-        <v>7.5499999999999998</v>
+        <v>7.8700000000000001</v>
       </c>
       <c r="N10" s="0">
-        <v>5.9299999999999997</v>
+        <v>5.7699999999999996</v>
       </c>
       <c r="O10" s="0">
-        <v>2.9300000000000002</v>
+        <v>2.8100000000000001</v>
       </c>
       <c r="P10" s="0">
-        <v>0.17999999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="Q10" s="0">
-        <v>6.1900000000000004</v>
+        <v>5.9000000000000004</v>
       </c>
       <c r="R10" s="0">
-        <v>-1.1399999999999999</v>
+        <v>-0.91000000000000003</v>
       </c>
       <c r="S10" s="0">
-        <v>2.6000000000000001</v>
+        <v>2.5600000000000001</v>
       </c>
       <c r="T10" s="0">
-        <v>5.4699999999999998</v>
+        <v>5.25</v>
       </c>
       <c r="U10" s="0">
-        <v>5.4699999999999998</v>
+        <v>5.2000000000000002</v>
       </c>
       <c r="V10" s="0">
-        <v>0.40000000000000002</v>
+        <v>0.96999999999999997</v>
       </c>
       <c r="W10" s="0">
-        <v>13.720000000000001</v>
+        <v>13.06</v>
       </c>
       <c r="X10" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -1078,73 +1078,73 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>20.199999999999999</v>
+        <v>19.02</v>
       </c>
       <c r="C11" s="0">
-        <v>19.890000000000001</v>
+        <v>19.120000000000001</v>
       </c>
       <c r="D11" s="0">
-        <v>8.3000000000000007</v>
+        <v>7.5</v>
       </c>
       <c r="E11" s="0">
-        <v>14.779999999999999</v>
+        <v>14.16</v>
       </c>
       <c r="F11" s="0">
-        <v>40.390000000000001</v>
+        <v>38.350000000000001</v>
       </c>
       <c r="G11" s="0">
-        <v>34.219999999999999</v>
+        <v>32.899999999999999</v>
       </c>
       <c r="H11" s="0">
-        <v>49.759999999999998</v>
+        <v>46.229999999999997</v>
       </c>
       <c r="I11" s="0">
-        <v>35.060000000000002</v>
+        <v>34.890000000000001</v>
       </c>
       <c r="J11" s="0">
-        <v>4.7199999999999998</v>
+        <v>5.2300000000000004</v>
       </c>
       <c r="K11" s="0">
-        <v>6.5300000000000002</v>
+        <v>6.3600000000000003</v>
       </c>
       <c r="L11" s="0">
-        <v>11.68</v>
+        <v>11.369999999999999</v>
       </c>
       <c r="M11" s="0">
-        <v>6.2400000000000002</v>
+        <v>5.96</v>
       </c>
       <c r="N11" s="0">
-        <v>48.200000000000003</v>
+        <v>46.329999999999998</v>
       </c>
       <c r="O11" s="0">
-        <v>9.9399999999999995</v>
+        <v>11.08</v>
       </c>
       <c r="P11" s="0">
-        <v>30.239999999999998</v>
+        <v>30.710000000000001</v>
       </c>
       <c r="Q11" s="0">
-        <v>11.789999999999999</v>
+        <v>11.220000000000001</v>
       </c>
       <c r="R11" s="0">
-        <v>7.5</v>
+        <v>7.1100000000000003</v>
       </c>
       <c r="S11" s="0">
-        <v>5.1799999999999997</v>
+        <v>5.04</v>
       </c>
       <c r="T11" s="0">
-        <v>-4.4100000000000001</v>
+        <v>-3.1899999999999999</v>
       </c>
       <c r="U11" s="0">
-        <v>7.2999999999999998</v>
+        <v>7.9000000000000004</v>
       </c>
       <c r="V11" s="0">
-        <v>0.33000000000000002</v>
+        <v>1.1699999999999999</v>
       </c>
       <c r="W11" s="0">
-        <v>6.25</v>
+        <v>6.46</v>
       </c>
       <c r="X11" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -1152,73 +1152,73 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>40.979999999999997</v>
+        <v>39.5</v>
       </c>
       <c r="C12" s="0">
-        <v>41.840000000000003</v>
+        <v>39.390000000000001</v>
       </c>
       <c r="D12" s="0">
-        <v>12.859999999999999</v>
+        <v>15.380000000000001</v>
       </c>
       <c r="E12" s="0">
-        <v>17.34</v>
+        <v>17.890000000000001</v>
       </c>
       <c r="F12" s="0">
-        <v>51.140000000000001</v>
+        <v>50.57</v>
       </c>
       <c r="G12" s="0">
-        <v>60.329999999999998</v>
+        <v>56.450000000000003</v>
       </c>
       <c r="H12" s="0">
-        <v>1.1799999999999999</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="I12" s="0">
-        <v>8.1799999999999997</v>
+        <v>7.6900000000000004</v>
       </c>
       <c r="J12" s="0">
-        <v>9.0700000000000003</v>
+        <v>11.15</v>
       </c>
       <c r="K12" s="0">
-        <v>11.390000000000001</v>
+        <v>12.359999999999999</v>
       </c>
       <c r="L12" s="0">
-        <v>59.18</v>
+        <v>58.490000000000002</v>
       </c>
       <c r="M12" s="0">
-        <v>6.4100000000000001</v>
+        <v>6.4199999999999999</v>
       </c>
       <c r="N12" s="0">
-        <v>6.0899999999999999</v>
+        <v>5.8300000000000001</v>
       </c>
       <c r="O12" s="0">
-        <v>3.6499999999999999</v>
+        <v>3.54</v>
       </c>
       <c r="P12" s="0">
+        <v>0.97999999999999998</v>
+      </c>
+      <c r="Q12" s="0">
+        <v>4.7800000000000002</v>
+      </c>
+      <c r="R12" s="0">
         <v>0.31</v>
       </c>
-      <c r="Q12" s="0">
-        <v>4.5499999999999998</v>
-      </c>
-      <c r="R12" s="0">
-        <v>0.14999999999999999</v>
-      </c>
       <c r="S12" s="0">
-        <v>3.1200000000000001</v>
+        <v>2.9900000000000002</v>
       </c>
       <c r="T12" s="0">
-        <v>4.5499999999999998</v>
+        <v>4.8399999999999999</v>
       </c>
       <c r="U12" s="0">
-        <v>7.0199999999999996</v>
+        <v>6.6799999999999997</v>
       </c>
       <c r="V12" s="0">
-        <v>-2.3599999999999999</v>
+        <v>-1.4299999999999999</v>
       </c>
       <c r="W12" s="0">
-        <v>12.720000000000001</v>
+        <v>12.35</v>
       </c>
       <c r="X12" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -1226,73 +1226,73 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>28.949999999999999</v>
+        <v>28.07</v>
       </c>
       <c r="C13" s="0">
-        <v>28.030000000000001</v>
+        <v>26.350000000000001</v>
       </c>
       <c r="D13" s="0">
-        <v>11.41</v>
+        <v>9.9399999999999995</v>
       </c>
       <c r="E13" s="0">
-        <v>20.879999999999999</v>
+        <v>20.02</v>
       </c>
       <c r="F13" s="0">
-        <v>49.68</v>
+        <v>46.840000000000003</v>
       </c>
       <c r="G13" s="0">
-        <v>20.48</v>
+        <v>20.969999999999999</v>
       </c>
       <c r="H13" s="0">
-        <v>45.270000000000003</v>
+        <v>42.270000000000003</v>
       </c>
       <c r="I13" s="0">
-        <v>35.369999999999997</v>
+        <v>34.289999999999999</v>
       </c>
       <c r="J13" s="0">
-        <v>4.54</v>
+        <v>5.4000000000000004</v>
       </c>
       <c r="K13" s="0">
-        <v>4.4900000000000002</v>
+        <v>4.9100000000000001</v>
       </c>
       <c r="L13" s="0">
-        <v>13.94</v>
+        <v>14.08</v>
       </c>
       <c r="M13" s="0">
-        <v>7.3399999999999999</v>
+        <v>6.9400000000000004</v>
       </c>
       <c r="N13" s="0">
-        <v>60.009999999999998</v>
+        <v>58.009999999999998</v>
       </c>
       <c r="O13" s="0">
-        <v>11.880000000000001</v>
+        <v>12.859999999999999</v>
       </c>
       <c r="P13" s="0">
-        <v>35.310000000000002</v>
+        <v>35.399999999999999</v>
       </c>
       <c r="Q13" s="0">
-        <v>9.2799999999999994</v>
+        <v>8.7599999999999998</v>
       </c>
       <c r="R13" s="0">
-        <v>7.9299999999999997</v>
+        <v>7.2999999999999998</v>
       </c>
       <c r="S13" s="0">
-        <v>4.8799999999999999</v>
+        <v>5.0099999999999998</v>
       </c>
       <c r="T13" s="0">
-        <v>-2.2200000000000002</v>
+        <v>-1.48</v>
       </c>
       <c r="U13" s="0">
-        <v>3.96</v>
+        <v>4.4100000000000001</v>
       </c>
       <c r="V13" s="0">
-        <v>2.0299999999999998</v>
+        <v>2.75</v>
       </c>
       <c r="W13" s="0">
-        <v>6.2000000000000002</v>
+        <v>6.2699999999999996</v>
       </c>
       <c r="X13" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -1366,7 +1366,7 @@
         <v>0</v>
       </c>
       <c r="X14" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1435,37 +1435,37 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>21.300000000000001</v>
+        <v>21.829999999999998</v>
       </c>
       <c r="C2" s="0">
-        <v>4.1100000000000003</v>
+        <v>4.2199999999999998</v>
       </c>
       <c r="D2" s="0">
-        <v>18.899999999999999</v>
+        <v>19.16</v>
       </c>
       <c r="E2" s="0">
-        <v>4.0700000000000003</v>
+        <v>3.9300000000000002</v>
       </c>
       <c r="F2" s="0">
-        <v>17.5</v>
+        <v>17.809999999999999</v>
       </c>
       <c r="G2" s="0">
-        <v>4.2800000000000002</v>
+        <v>4.1600000000000001</v>
       </c>
       <c r="H2" s="0">
-        <v>90.480000000000004</v>
+        <v>90.209999999999994</v>
       </c>
       <c r="I2" s="0">
-        <v>18.23</v>
+        <v>17.210000000000001</v>
       </c>
       <c r="J2" s="0">
-        <v>31.5</v>
+        <v>30.620000000000001</v>
       </c>
       <c r="K2" s="0">
-        <v>8.9900000000000002</v>
+        <v>8.9299999999999997</v>
       </c>
       <c r="L2" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -1473,37 +1473,37 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>18.469999999999999</v>
+        <v>17.82</v>
       </c>
       <c r="C3" s="0">
-        <v>8.8800000000000008</v>
+        <v>8.6199999999999992</v>
       </c>
       <c r="D3" s="0">
-        <v>40.840000000000003</v>
+        <v>39.450000000000003</v>
       </c>
       <c r="E3" s="0">
-        <v>9.2100000000000009</v>
+        <v>9.7300000000000004</v>
       </c>
       <c r="F3" s="0">
-        <v>17.91</v>
+        <v>17.289999999999999</v>
       </c>
       <c r="G3" s="0">
-        <v>8.8599999999999994</v>
+        <v>8.5800000000000001</v>
       </c>
       <c r="H3" s="0">
-        <v>21.57</v>
+        <v>21.109999999999999</v>
       </c>
       <c r="I3" s="0">
-        <v>6.0700000000000003</v>
+        <v>5.9000000000000004</v>
       </c>
       <c r="J3" s="0">
-        <v>97.980000000000004</v>
+        <v>97.319999999999993</v>
       </c>
       <c r="K3" s="0">
-        <v>13.220000000000001</v>
+        <v>12.640000000000001</v>
       </c>
       <c r="L3" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -1511,37 +1511,37 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>21.629999999999999</v>
+        <v>21.670000000000002</v>
       </c>
       <c r="C4" s="0">
-        <v>5.3300000000000001</v>
+        <v>5.0300000000000002</v>
       </c>
       <c r="D4" s="0">
-        <v>18.550000000000001</v>
+        <v>18.309999999999999</v>
       </c>
       <c r="E4" s="0">
-        <v>5.4800000000000004</v>
+        <v>5.2199999999999998</v>
       </c>
       <c r="F4" s="0">
-        <v>17.16</v>
+        <v>16.949999999999999</v>
       </c>
       <c r="G4" s="0">
-        <v>4.9199999999999999</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="H4" s="0">
-        <v>89.299999999999997</v>
+        <v>90.030000000000001</v>
       </c>
       <c r="I4" s="0">
-        <v>18.07</v>
+        <v>17.190000000000001</v>
       </c>
       <c r="J4" s="0">
-        <v>25.550000000000001</v>
+        <v>27.640000000000001</v>
       </c>
       <c r="K4" s="0">
-        <v>6.9500000000000002</v>
+        <v>9.3100000000000005</v>
       </c>
       <c r="L4" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -1549,37 +1549,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>18.829999999999998</v>
+        <v>17.75</v>
       </c>
       <c r="C5" s="0">
-        <v>9.8200000000000003</v>
+        <v>9.8699999999999992</v>
       </c>
       <c r="D5" s="0">
-        <v>40.060000000000002</v>
+        <v>38.399999999999999</v>
       </c>
       <c r="E5" s="0">
-        <v>9.8599999999999994</v>
+        <v>10.68</v>
       </c>
       <c r="F5" s="0">
-        <v>17.449999999999999</v>
+        <v>16.449999999999999</v>
       </c>
       <c r="G5" s="0">
-        <v>10.050000000000001</v>
+        <v>9.9900000000000002</v>
       </c>
       <c r="H5" s="0">
-        <v>24.510000000000002</v>
+        <v>27.300000000000001</v>
       </c>
       <c r="I5" s="0">
-        <v>9.75</v>
+        <v>12.73</v>
       </c>
       <c r="J5" s="0">
-        <v>96.579999999999998</v>
+        <v>96.090000000000003</v>
       </c>
       <c r="K5" s="0">
-        <v>18.050000000000001</v>
+        <v>17.09</v>
       </c>
       <c r="L5" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -1587,37 +1587,37 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>18.5</v>
+        <v>18.390000000000001</v>
       </c>
       <c r="C6" s="0">
-        <v>8.3900000000000006</v>
+        <v>7.9199999999999999</v>
       </c>
       <c r="D6" s="0">
-        <v>17.32</v>
+        <v>16.98</v>
       </c>
       <c r="E6" s="0">
-        <v>6.0800000000000001</v>
+        <v>5.8399999999999999</v>
       </c>
       <c r="F6" s="0">
-        <v>15.289999999999999</v>
+        <v>15.109999999999999</v>
       </c>
       <c r="G6" s="0">
-        <v>7.0199999999999996</v>
+        <v>6.6500000000000004</v>
       </c>
       <c r="H6" s="0">
-        <v>86.670000000000002</v>
+        <v>87.900000000000006</v>
       </c>
       <c r="I6" s="0">
-        <v>21.52</v>
+        <v>20.66</v>
       </c>
       <c r="J6" s="0">
-        <v>26.390000000000001</v>
+        <v>25.850000000000001</v>
       </c>
       <c r="K6" s="0">
-        <v>8.6699999999999999</v>
+        <v>8.3599999999999994</v>
       </c>
       <c r="L6" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -1625,37 +1625,37 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>14.51</v>
+        <v>13.529999999999999</v>
       </c>
       <c r="C7" s="0">
-        <v>6.79</v>
+        <v>7.1100000000000003</v>
       </c>
       <c r="D7" s="0">
-        <v>34.829999999999998</v>
+        <v>34.079999999999998</v>
       </c>
       <c r="E7" s="0">
-        <v>5.7300000000000004</v>
+        <v>5.9000000000000004</v>
       </c>
       <c r="F7" s="0">
-        <v>13.56</v>
+        <v>12.630000000000001</v>
       </c>
       <c r="G7" s="0">
-        <v>6.7599999999999998</v>
+        <v>7.0199999999999996</v>
       </c>
       <c r="H7" s="0">
-        <v>19.050000000000001</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="I7" s="0">
-        <v>5.9000000000000004</v>
+        <v>5.8300000000000001</v>
       </c>
       <c r="J7" s="0">
-        <v>95.569999999999993</v>
+        <v>94.810000000000002</v>
       </c>
       <c r="K7" s="0">
-        <v>23.719999999999999</v>
+        <v>22.5</v>
       </c>
       <c r="L7" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1663,37 +1663,37 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
+        <v>25.170000000000002</v>
+      </c>
+      <c r="C8" s="0">
+        <v>6.6299999999999999</v>
+      </c>
+      <c r="D8" s="0">
+        <v>19.870000000000001</v>
+      </c>
+      <c r="E8" s="0">
+        <v>4.8300000000000001</v>
+      </c>
+      <c r="F8" s="0">
+        <v>16.539999999999999</v>
+      </c>
+      <c r="G8" s="0">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="H8" s="0">
+        <v>90.599999999999994</v>
+      </c>
+      <c r="I8" s="0">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="J8" s="0">
         <v>24.550000000000001</v>
       </c>
-      <c r="C8" s="0">
-        <v>6.7300000000000004</v>
-      </c>
-      <c r="D8" s="0">
-        <v>20.059999999999999</v>
-      </c>
-      <c r="E8" s="0">
-        <v>5.0800000000000001</v>
-      </c>
-      <c r="F8" s="0">
-        <v>16.93</v>
-      </c>
-      <c r="G8" s="0">
-        <v>4.5700000000000003</v>
-      </c>
-      <c r="H8" s="0">
-        <v>89.060000000000002</v>
-      </c>
-      <c r="I8" s="0">
-        <v>19.370000000000001</v>
-      </c>
-      <c r="J8" s="0">
-        <v>25.579999999999998</v>
-      </c>
       <c r="K8" s="0">
-        <v>14.25</v>
+        <v>13.82</v>
       </c>
       <c r="L8" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -1701,37 +1701,37 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>21.050000000000001</v>
+        <v>21.09</v>
       </c>
       <c r="C9" s="0">
-        <v>7.0899999999999999</v>
+        <v>6.6799999999999997</v>
       </c>
       <c r="D9" s="0">
-        <v>41.270000000000003</v>
+        <v>40.560000000000002</v>
       </c>
       <c r="E9" s="0">
-        <v>8.3000000000000007</v>
+        <v>8.1400000000000006</v>
       </c>
       <c r="F9" s="0">
-        <v>17.309999999999999</v>
+        <v>17.559999999999999</v>
       </c>
       <c r="G9" s="0">
-        <v>6.0300000000000002</v>
+        <v>5.7400000000000002</v>
       </c>
       <c r="H9" s="0">
-        <v>19.59</v>
+        <v>23.77</v>
       </c>
       <c r="I9" s="0">
-        <v>7.2599999999999998</v>
+        <v>14.890000000000001</v>
       </c>
       <c r="J9" s="0">
-        <v>92.900000000000006</v>
+        <v>92.290000000000006</v>
       </c>
       <c r="K9" s="0">
-        <v>16.670000000000002</v>
+        <v>15.83</v>
       </c>
       <c r="L9" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -1739,37 +1739,37 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>24.989999999999998</v>
+        <v>24.57</v>
       </c>
       <c r="C10" s="0">
-        <v>8.7300000000000004</v>
+        <v>8.3399999999999999</v>
       </c>
       <c r="D10" s="0">
-        <v>22.670000000000002</v>
+        <v>22.370000000000001</v>
       </c>
       <c r="E10" s="0">
-        <v>5.0800000000000001</v>
+        <v>4.8799999999999999</v>
       </c>
       <c r="F10" s="0">
-        <v>18.530000000000001</v>
+        <v>18.420000000000002</v>
       </c>
       <c r="G10" s="0">
-        <v>5.4699999999999998</v>
+        <v>5.1699999999999999</v>
       </c>
       <c r="H10" s="0">
-        <v>86.409999999999997</v>
+        <v>86.060000000000002</v>
       </c>
       <c r="I10" s="0">
-        <v>20.190000000000001</v>
+        <v>19.059999999999999</v>
       </c>
       <c r="J10" s="0">
-        <v>21.100000000000001</v>
+        <v>20.969999999999999</v>
       </c>
       <c r="K10" s="0">
-        <v>6.7699999999999996</v>
+        <v>6.4000000000000004</v>
       </c>
       <c r="L10" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -1777,37 +1777,37 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>19.170000000000002</v>
+        <v>18.940000000000001</v>
       </c>
       <c r="C11" s="0">
-        <v>9.3200000000000003</v>
+        <v>8.8100000000000005</v>
       </c>
       <c r="D11" s="0">
-        <v>40.469999999999999</v>
+        <v>40.340000000000003</v>
       </c>
       <c r="E11" s="0">
-        <v>6.96</v>
+        <v>6.5800000000000001</v>
       </c>
       <c r="F11" s="0">
-        <v>15.91</v>
+        <v>15.56</v>
       </c>
       <c r="G11" s="0">
-        <v>9.4900000000000002</v>
+        <v>9.0099999999999998</v>
       </c>
       <c r="H11" s="0">
-        <v>18.190000000000001</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="I11" s="0">
-        <v>5.6399999999999997</v>
+        <v>5.3799999999999999</v>
       </c>
       <c r="J11" s="0">
-        <v>87.099999999999994</v>
+        <v>87.549999999999997</v>
       </c>
       <c r="K11" s="0">
-        <v>23.449999999999999</v>
+        <v>22.149999999999999</v>
       </c>
       <c r="L11" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -1815,37 +1815,37 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>23.050000000000001</v>
+        <v>22.41</v>
       </c>
       <c r="C12" s="0">
-        <v>7.1600000000000001</v>
+        <v>7.04</v>
       </c>
       <c r="D12" s="0">
-        <v>20.989999999999998</v>
+        <v>20.379999999999999</v>
       </c>
       <c r="E12" s="0">
-        <v>4.0999999999999996</v>
+        <v>4.3200000000000003</v>
       </c>
       <c r="F12" s="0">
-        <v>17.309999999999999</v>
+        <v>16.870000000000001</v>
       </c>
       <c r="G12" s="0">
-        <v>4.2800000000000002</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="H12" s="0">
-        <v>86.760000000000005</v>
+        <v>87.560000000000002</v>
       </c>
       <c r="I12" s="0">
-        <v>18.23</v>
+        <v>17.379999999999999</v>
       </c>
       <c r="J12" s="0">
-        <v>22.760000000000002</v>
+        <v>22.489999999999998</v>
       </c>
       <c r="K12" s="0">
-        <v>12.800000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="L12" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -1853,37 +1853,37 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>19.77</v>
+        <v>18.449999999999999</v>
       </c>
       <c r="C13" s="0">
-        <v>10.300000000000001</v>
+        <v>10.57</v>
       </c>
       <c r="D13" s="0">
-        <v>41.259999999999998</v>
+        <v>40.210000000000001</v>
       </c>
       <c r="E13" s="0">
-        <v>8.7100000000000009</v>
+        <v>8.8699999999999992</v>
       </c>
       <c r="F13" s="0">
-        <v>16.140000000000001</v>
+        <v>15.109999999999999</v>
       </c>
       <c r="G13" s="0">
-        <v>9.4399999999999995</v>
+        <v>9.4800000000000004</v>
       </c>
       <c r="H13" s="0">
-        <v>17.93</v>
+        <v>17.98</v>
       </c>
       <c r="I13" s="0">
-        <v>5.9000000000000004</v>
+        <v>5.5599999999999996</v>
       </c>
       <c r="J13" s="0">
-        <v>92.780000000000001</v>
+        <v>92.799999999999997</v>
       </c>
       <c r="K13" s="0">
-        <v>17.300000000000001</v>
+        <v>16.309999999999999</v>
       </c>
       <c r="L13" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1936,25 +1936,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>58.299999999999997</v>
+        <v>59.799999999999997</v>
       </c>
       <c r="C2" s="0">
         <v>23</v>
       </c>
       <c r="D2" s="0">
-        <v>76.299999999999997</v>
+        <v>74</v>
       </c>
       <c r="E2" s="0">
         <v>32</v>
       </c>
       <c r="F2" s="0">
-        <v>68.099999999999994</v>
+        <v>68.400000000000006</v>
       </c>
       <c r="G2" s="0">
         <v>28</v>
       </c>
       <c r="H2" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -1962,25 +1962,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>43.5</v>
+        <v>42</v>
       </c>
       <c r="C3" s="0">
         <v>16</v>
       </c>
       <c r="D3" s="0">
-        <v>57.700000000000003</v>
+        <v>62.200000000000003</v>
       </c>
       <c r="E3" s="0">
-        <v>31.399999999999999</v>
+        <v>32.899999999999999</v>
       </c>
       <c r="F3" s="0">
-        <v>93.700000000000003</v>
+        <v>98</v>
       </c>
       <c r="G3" s="0">
         <v>31</v>
       </c>
       <c r="H3" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -1988,25 +1988,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>78.099999999999994</v>
+        <v>75.400000000000006</v>
       </c>
       <c r="C4" s="0">
         <v>28</v>
       </c>
       <c r="D4" s="0">
-        <v>85.799999999999997</v>
+        <v>85</v>
       </c>
       <c r="E4" s="0">
         <v>37</v>
       </c>
       <c r="F4" s="0">
-        <v>56.200000000000003</v>
+        <v>60.299999999999997</v>
       </c>
       <c r="G4" s="0">
-        <v>29.699999999999999</v>
+        <v>30.899999999999999</v>
       </c>
       <c r="H4" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -2014,25 +2014,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>49.899999999999999</v>
+        <v>48.799999999999997</v>
       </c>
       <c r="C5" s="0">
-        <v>11.5</v>
+        <v>11.300000000000001</v>
       </c>
       <c r="D5" s="0">
-        <v>71.599999999999994</v>
+        <v>73.5</v>
       </c>
       <c r="E5" s="0">
-        <v>29.699999999999999</v>
+        <v>28.600000000000001</v>
       </c>
       <c r="F5" s="0">
-        <v>95.200000000000003</v>
+        <v>98.700000000000003</v>
       </c>
       <c r="G5" s="0">
         <v>29</v>
       </c>
       <c r="H5" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -2040,25 +2040,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>82.799999999999997</v>
+        <v>82.099999999999994</v>
       </c>
       <c r="C6" s="0">
         <v>30</v>
       </c>
       <c r="D6" s="0">
-        <v>91.5</v>
+        <v>95.5</v>
       </c>
       <c r="E6" s="0">
         <v>28</v>
       </c>
       <c r="F6" s="0">
-        <v>60.100000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="G6" s="0">
-        <v>24.600000000000001</v>
+        <v>24.300000000000001</v>
       </c>
       <c r="H6" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -2066,25 +2066,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>61.299999999999997</v>
+        <v>60.100000000000001</v>
       </c>
       <c r="C7" s="0">
-        <v>15.6</v>
+        <v>15.199999999999999</v>
       </c>
       <c r="D7" s="0">
-        <v>83.200000000000003</v>
+        <v>83.599999999999994</v>
       </c>
       <c r="E7" s="0">
-        <v>25</v>
+        <v>23.600000000000001</v>
       </c>
       <c r="F7" s="0">
-        <v>120.2</v>
+        <v>115</v>
       </c>
       <c r="G7" s="0">
         <v>28</v>
       </c>
       <c r="H7" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -2092,25 +2092,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>64.700000000000003</v>
+        <v>63.299999999999997</v>
       </c>
       <c r="C8" s="0">
         <v>21</v>
       </c>
       <c r="D8" s="0">
-        <v>78.599999999999994</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="E8" s="0">
         <v>27</v>
       </c>
       <c r="F8" s="0">
-        <v>60.700000000000003</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="G8" s="0">
-        <v>33.799999999999997</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="H8" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -2118,25 +2118,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>44.299999999999997</v>
+        <v>44.200000000000003</v>
       </c>
       <c r="C9" s="0">
-        <v>8.9000000000000004</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="D9" s="0">
-        <v>78.299999999999997</v>
+        <v>79.200000000000003</v>
       </c>
       <c r="E9" s="0">
-        <v>21.899999999999999</v>
+        <v>20.600000000000001</v>
       </c>
       <c r="F9" s="0">
-        <v>92.299999999999997</v>
+        <v>94.200000000000003</v>
       </c>
       <c r="G9" s="0">
         <v>27</v>
       </c>
       <c r="H9" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -2144,25 +2144,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>81.900000000000006</v>
+        <v>80</v>
       </c>
       <c r="C10" s="0">
         <v>14</v>
       </c>
       <c r="D10" s="0">
-        <v>89.799999999999997</v>
+        <v>88.400000000000006</v>
       </c>
       <c r="E10" s="0">
         <v>26</v>
       </c>
       <c r="F10" s="0">
-        <v>56.5</v>
+        <v>55.5</v>
       </c>
       <c r="G10" s="0">
-        <v>31</v>
+        <v>29.5</v>
       </c>
       <c r="H10" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -2170,25 +2170,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>53.200000000000003</v>
+        <v>51</v>
       </c>
       <c r="C11" s="0">
-        <v>13.4</v>
+        <v>14.4</v>
       </c>
       <c r="D11" s="0">
-        <v>78.700000000000003</v>
+        <v>80.099999999999994</v>
       </c>
       <c r="E11" s="0">
-        <v>27</v>
+        <v>25.800000000000001</v>
       </c>
       <c r="F11" s="0">
-        <v>108.59999999999999</v>
+        <v>104</v>
       </c>
       <c r="G11" s="0">
         <v>25</v>
       </c>
       <c r="H11" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -2196,25 +2196,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>78.900000000000006</v>
+        <v>79.700000000000003</v>
       </c>
       <c r="C12" s="0">
         <v>23</v>
       </c>
       <c r="D12" s="0">
-        <v>93.099999999999994</v>
+        <v>96.299999999999997</v>
       </c>
       <c r="E12" s="0">
         <v>31</v>
       </c>
       <c r="F12" s="0">
-        <v>63.799999999999997</v>
+        <v>64.5</v>
       </c>
       <c r="G12" s="0">
-        <v>27.800000000000001</v>
+        <v>26.100000000000001</v>
       </c>
       <c r="H12" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -2222,25 +2222,25 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>65.599999999999994</v>
+        <v>63</v>
       </c>
       <c r="C13" s="0">
-        <v>17.199999999999999</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="D13" s="0">
-        <v>92.400000000000006</v>
+        <v>92.299999999999997</v>
       </c>
       <c r="E13" s="0">
-        <v>24</v>
+        <v>22.5</v>
       </c>
       <c r="F13" s="0">
-        <v>103.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="G13" s="0">
         <v>29</v>
       </c>
       <c r="H13" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -2248,25 +2248,25 @@
         <v>24</v>
       </c>
       <c r="B14" s="0">
-        <v>24.600000000000001</v>
+        <v>24.399999999999999</v>
       </c>
       <c r="C14" s="0">
-        <v>5.2999999999999998</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="D14" s="0">
-        <v>36.200000000000003</v>
+        <v>38.700000000000003</v>
       </c>
       <c r="E14" s="0">
-        <v>10.6</v>
+        <v>12.9</v>
       </c>
       <c r="F14" s="0">
-        <v>54.100000000000001</v>
+        <v>52.600000000000001</v>
       </c>
       <c r="G14" s="0">
-        <v>21.899999999999999</v>
+        <v>21.300000000000001</v>
       </c>
       <c r="H14" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2319,25 +2319,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>96.299999999999997</v>
+        <v>97</v>
       </c>
       <c r="C2" s="0">
-        <v>11.800000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="D2" s="0">
-        <v>81.799999999999997</v>
+        <v>81.099999999999994</v>
       </c>
       <c r="E2" s="0">
         <v>6.9000000000000004</v>
       </c>
       <c r="F2" s="0">
-        <v>79.299999999999997</v>
+        <v>79</v>
       </c>
       <c r="G2" s="0">
-        <v>11.5</v>
+        <v>10.9</v>
       </c>
       <c r="H2" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2345,25 +2345,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>112.40000000000001</v>
+        <v>111.59999999999999</v>
       </c>
       <c r="C3" s="0">
-        <v>17.100000000000001</v>
+        <v>16.300000000000001</v>
       </c>
       <c r="D3" s="0">
-        <v>106.5</v>
+        <v>104.7</v>
       </c>
       <c r="E3" s="0">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="F3" s="0">
-        <v>59.700000000000003</v>
+        <v>58.899999999999999</v>
       </c>
       <c r="G3" s="0">
-        <v>6</v>
+        <v>6.2000000000000002</v>
       </c>
       <c r="H3" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -2371,25 +2371,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>91.400000000000006</v>
+        <v>93.200000000000003</v>
       </c>
       <c r="C4" s="0">
         <v>17.300000000000001</v>
       </c>
       <c r="D4" s="0">
-        <v>83.099999999999994</v>
+        <v>82.5</v>
       </c>
       <c r="E4" s="0">
-        <v>7</v>
+        <v>6.7999999999999998</v>
       </c>
       <c r="F4" s="0">
-        <v>94</v>
+        <v>92.900000000000006</v>
       </c>
       <c r="G4" s="0">
-        <v>8.5999999999999996</v>
+        <v>8.9000000000000004</v>
       </c>
       <c r="H4" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -2400,22 +2400,22 @@
         <v>121.5</v>
       </c>
       <c r="C5" s="0">
-        <v>14.9</v>
+        <v>14</v>
       </c>
       <c r="D5" s="0">
-        <v>119.90000000000001</v>
+        <v>117.90000000000001</v>
       </c>
       <c r="E5" s="0">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="F5" s="0">
-        <v>62.200000000000003</v>
+        <v>62</v>
       </c>
       <c r="G5" s="0">
-        <v>4.7000000000000002</v>
+        <v>4.5</v>
       </c>
       <c r="H5" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -2423,25 +2423,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>86.799999999999997</v>
+        <v>89.200000000000003</v>
       </c>
       <c r="C6" s="0">
-        <v>15.699999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="D6" s="0">
-        <v>84</v>
+        <v>83.5</v>
       </c>
       <c r="E6" s="0">
-        <v>5.7000000000000002</v>
+        <v>5.5999999999999996</v>
       </c>
       <c r="F6" s="0">
-        <v>101</v>
+        <v>100.40000000000001</v>
       </c>
       <c r="G6" s="0">
-        <v>10.1</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="H6" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -2449,25 +2449,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>124</v>
+        <v>124.8</v>
       </c>
       <c r="C7" s="0">
-        <v>18.300000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="D7" s="0">
-        <v>125.40000000000001</v>
+        <v>123.5</v>
       </c>
       <c r="E7" s="0">
-        <v>7.5999999999999996</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="F7" s="0">
-        <v>64.900000000000006</v>
+        <v>64.799999999999997</v>
       </c>
       <c r="G7" s="0">
-        <v>5.7000000000000002</v>
+        <v>5.4000000000000004</v>
       </c>
       <c r="H7" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -2475,25 +2475,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>98.5</v>
+        <v>100.59999999999999</v>
       </c>
       <c r="C8" s="0">
-        <v>16.800000000000001</v>
+        <v>17.199999999999999</v>
       </c>
       <c r="D8" s="0">
-        <v>83.700000000000003</v>
+        <v>83.799999999999997</v>
       </c>
       <c r="E8" s="0">
-        <v>6.2000000000000002</v>
+        <v>5.9000000000000004</v>
       </c>
       <c r="F8" s="0">
-        <v>82.900000000000006</v>
+        <v>82.5</v>
       </c>
       <c r="G8" s="0">
-        <v>9</v>
+        <v>8.5999999999999996</v>
       </c>
       <c r="H8" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -2501,25 +2501,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>118.7</v>
+        <v>119.09999999999999</v>
       </c>
       <c r="C9" s="0">
-        <v>16.300000000000001</v>
+        <v>15.4</v>
       </c>
       <c r="D9" s="0">
-        <v>108.90000000000001</v>
+        <v>107.59999999999999</v>
       </c>
       <c r="E9" s="0">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="F9" s="0">
-        <v>62.200000000000003</v>
+        <v>61.799999999999997</v>
       </c>
       <c r="G9" s="0">
-        <v>6</v>
+        <v>5.7999999999999998</v>
       </c>
       <c r="H9" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -2527,25 +2527,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>91.799999999999997</v>
+        <v>93.099999999999994</v>
       </c>
       <c r="C10" s="0">
-        <v>18.300000000000001</v>
+        <v>17.699999999999999</v>
       </c>
       <c r="D10" s="0">
-        <v>86</v>
+        <v>85.299999999999997</v>
       </c>
       <c r="E10" s="0">
-        <v>6.2999999999999998</v>
+        <v>6.4000000000000004</v>
       </c>
       <c r="F10" s="0">
-        <v>95.799999999999997</v>
+        <v>95</v>
       </c>
       <c r="G10" s="0">
         <v>8.0999999999999996</v>
       </c>
       <c r="H10" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -2553,25 +2553,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>121.8</v>
+        <v>123.59999999999999</v>
       </c>
       <c r="C11" s="0">
-        <v>16.5</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="D11" s="0">
-        <v>118.40000000000001</v>
+        <v>117.40000000000001</v>
       </c>
       <c r="E11" s="0">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="F11" s="0">
-        <v>63.799999999999997</v>
+        <v>63.100000000000001</v>
       </c>
       <c r="G11" s="0">
-        <v>6</v>
+        <v>6.0999999999999996</v>
       </c>
       <c r="H11" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -2579,25 +2579,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>89.200000000000003</v>
+        <v>91.200000000000003</v>
       </c>
       <c r="C12" s="0">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="D12" s="0">
-        <v>85.200000000000003</v>
+        <v>84.900000000000006</v>
       </c>
       <c r="E12" s="0">
-        <v>6.7999999999999998</v>
+        <v>6.5</v>
       </c>
       <c r="F12" s="0">
-        <v>103.8</v>
+        <v>103.2</v>
       </c>
       <c r="G12" s="0">
-        <v>8.9000000000000004</v>
+        <v>8.5999999999999996</v>
       </c>
       <c r="H12" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -2605,25 +2605,25 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>128.59999999999999</v>
+        <v>129.90000000000001</v>
       </c>
       <c r="C13" s="0">
-        <v>15.699999999999999</v>
+        <v>15.4</v>
       </c>
       <c r="D13" s="0">
-        <v>132.40000000000001</v>
+        <v>130.80000000000001</v>
       </c>
       <c r="E13" s="0">
-        <v>10.199999999999999</v>
+        <v>10.800000000000001</v>
       </c>
       <c r="F13" s="0">
-        <v>66.5</v>
+        <v>66</v>
       </c>
       <c r="G13" s="0">
-        <v>9.1999999999999993</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="H13" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -2631,25 +2631,25 @@
         <v>24</v>
       </c>
       <c r="B14" s="0">
-        <v>91.200000000000003</v>
+        <v>91.700000000000003</v>
       </c>
       <c r="C14" s="0">
-        <v>8.3000000000000007</v>
+        <v>8</v>
       </c>
       <c r="D14" s="0">
-        <v>74.599999999999994</v>
+        <v>74.200000000000003</v>
       </c>
       <c r="E14" s="0">
-        <v>5.7000000000000002</v>
+        <v>5.5</v>
       </c>
       <c r="F14" s="0">
         <v>44.700000000000003</v>
       </c>
       <c r="G14" s="0">
-        <v>4</v>
+        <v>3.7999999999999998</v>
       </c>
       <c r="H14" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2702,25 +2702,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>162.38</v>
+        <v>160.11000000000001</v>
       </c>
       <c r="C2" s="0">
-        <v>15.890000000000001</v>
+        <v>16.609999999999999</v>
       </c>
       <c r="D2" s="0">
-        <v>87.980000000000004</v>
+        <v>88.219999999999999</v>
       </c>
       <c r="E2" s="0">
-        <v>10.83</v>
+        <v>10.24</v>
       </c>
       <c r="F2" s="0">
-        <v>1.1499999999999999</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="G2" s="0">
-        <v>0.20000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="H2" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2728,25 +2728,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>164.19</v>
+        <v>164.02000000000001</v>
       </c>
       <c r="C3" s="0">
-        <v>27.469999999999999</v>
+        <v>25.91</v>
       </c>
       <c r="D3" s="0">
-        <v>81.680000000000007</v>
+        <v>81.640000000000001</v>
       </c>
       <c r="E3" s="0">
-        <v>5.0099999999999998</v>
+        <v>4.7199999999999998</v>
       </c>
       <c r="F3" s="0">
-        <v>1.1000000000000001</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="G3" s="0">
-        <v>0.19</v>
+        <v>0.17999999999999999</v>
       </c>
       <c r="H3" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -2754,25 +2754,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>162.69</v>
+        <v>163.84999999999999</v>
       </c>
       <c r="C4" s="0">
-        <v>34.68</v>
+        <v>32.899999999999999</v>
       </c>
       <c r="D4" s="0">
-        <v>81.739999999999995</v>
+        <v>81.069999999999993</v>
       </c>
       <c r="E4" s="0">
-        <v>6.5499999999999998</v>
+        <v>6.5300000000000002</v>
       </c>
       <c r="F4" s="0">
         <v>1.0700000000000001</v>
       </c>
       <c r="G4" s="0">
-        <v>0.20999999999999999</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="H4" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -2780,25 +2780,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>160.63999999999999</v>
+        <v>162.33000000000001</v>
       </c>
       <c r="C5" s="0">
-        <v>26.109999999999999</v>
+        <v>25.190000000000001</v>
       </c>
       <c r="D5" s="0">
-        <v>76.760000000000005</v>
+        <v>76.519999999999996</v>
       </c>
       <c r="E5" s="0">
-        <v>6.0499999999999998</v>
+        <v>5.75</v>
       </c>
       <c r="F5" s="0">
         <v>1.02</v>
       </c>
       <c r="G5" s="0">
-        <v>0.22</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="H5" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -2806,25 +2806,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>154.43000000000001</v>
+        <v>157.27000000000001</v>
       </c>
       <c r="C6" s="0">
-        <v>27.27</v>
+        <v>27.23</v>
       </c>
       <c r="D6" s="0">
-        <v>79.040000000000006</v>
+        <v>77.599999999999994</v>
       </c>
       <c r="E6" s="0">
-        <v>8.6799999999999997</v>
+        <v>9.3599999999999994</v>
       </c>
       <c r="F6" s="0">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="G6" s="0">
-        <v>0.23000000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="H6" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -2832,25 +2832,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>160.44</v>
+        <v>158.53</v>
       </c>
       <c r="C7" s="0">
-        <v>35.189999999999998</v>
+        <v>33.719999999999999</v>
       </c>
       <c r="D7" s="0">
-        <v>74.060000000000002</v>
+        <v>74.209999999999994</v>
       </c>
       <c r="E7" s="0">
-        <v>6.3200000000000003</v>
+        <v>5.9699999999999998</v>
       </c>
       <c r="F7" s="0">
-        <v>0.97999999999999998</v>
+        <v>0.96999999999999997</v>
       </c>
       <c r="G7" s="0">
-        <v>0.25</v>
+        <v>0.23999999999999999</v>
       </c>
       <c r="H7" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -2858,25 +2858,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>160.80000000000001</v>
+        <v>160.75</v>
       </c>
       <c r="C8" s="0">
-        <v>24.280000000000001</v>
+        <v>22.890000000000001</v>
       </c>
       <c r="D8" s="0">
-        <v>87.549999999999997</v>
+        <v>87.209999999999994</v>
       </c>
       <c r="E8" s="0">
-        <v>9.6899999999999995</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="F8" s="0">
         <v>1.1499999999999999</v>
       </c>
       <c r="G8" s="0">
-        <v>0.23999999999999999</v>
+        <v>0.22</v>
       </c>
       <c r="H8" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -2884,25 +2884,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>160.41999999999999</v>
+        <v>165.81999999999999</v>
       </c>
       <c r="C9" s="0">
-        <v>21.890000000000001</v>
+        <v>26.809999999999999</v>
       </c>
       <c r="D9" s="0">
-        <v>84.950000000000003</v>
+        <v>82.629999999999995</v>
       </c>
       <c r="E9" s="0">
-        <v>7.8200000000000003</v>
+        <v>10.42</v>
       </c>
       <c r="F9" s="0">
-        <v>1.1399999999999999</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="G9" s="0">
-        <v>0.23000000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="H9" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -2910,25 +2910,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>151.90000000000001</v>
+        <v>151.13999999999999</v>
       </c>
       <c r="C10" s="0">
-        <v>25.91</v>
+        <v>24.550000000000001</v>
       </c>
       <c r="D10" s="0">
-        <v>82.019999999999996</v>
+        <v>82</v>
       </c>
       <c r="E10" s="0">
-        <v>10.130000000000001</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="F10" s="0">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="G10" s="0">
-        <v>0.27000000000000002</v>
+        <v>0.25</v>
       </c>
       <c r="H10" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -2936,25 +2936,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>152.28</v>
+        <v>152.43000000000001</v>
       </c>
       <c r="C11" s="0">
-        <v>30.350000000000001</v>
+        <v>28.609999999999999</v>
       </c>
       <c r="D11" s="0">
-        <v>80.390000000000001</v>
+        <v>80.760000000000005</v>
       </c>
       <c r="E11" s="0">
-        <v>10.6</v>
+        <v>10.06</v>
       </c>
       <c r="F11" s="0">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="G11" s="0">
-        <v>0.25</v>
+        <v>0.23999999999999999</v>
       </c>
       <c r="H11" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -2962,25 +2962,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>151.34999999999999</v>
+        <v>151.97</v>
       </c>
       <c r="C12" s="0">
-        <v>32.640000000000001</v>
+        <v>30.84</v>
       </c>
       <c r="D12" s="0">
-        <v>83.260000000000005</v>
+        <v>82.590000000000003</v>
       </c>
       <c r="E12" s="0">
-        <v>15.82</v>
+        <v>15.07</v>
       </c>
       <c r="F12" s="0">
         <v>0.98999999999999999</v>
       </c>
       <c r="G12" s="0">
-        <v>0.20999999999999999</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="H12" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -2988,25 +2988,25 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>160.52000000000001</v>
+        <v>160.27000000000001</v>
       </c>
       <c r="C13" s="0">
-        <v>24.100000000000001</v>
+        <v>22.739999999999998</v>
       </c>
       <c r="D13" s="0">
-        <v>72.310000000000002</v>
+        <v>73.430000000000007</v>
       </c>
       <c r="E13" s="0">
-        <v>8.1699999999999999</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="F13" s="0">
-        <v>0.95999999999999996</v>
+        <v>0.97999999999999998</v>
       </c>
       <c r="G13" s="0">
-        <v>0.20999999999999999</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="H13" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -3014,25 +3014,25 @@
         <v>24</v>
       </c>
       <c r="B14" s="0">
-        <v>130.44999999999999</v>
+        <v>129.55000000000001</v>
       </c>
       <c r="C14" s="0">
-        <v>17.649999999999999</v>
+        <v>16.879999999999999</v>
       </c>
       <c r="D14" s="0">
-        <v>97.060000000000002</v>
+        <v>96.840000000000003</v>
       </c>
       <c r="E14" s="0">
-        <v>3.6800000000000002</v>
+        <v>3.5299999999999998</v>
       </c>
       <c r="F14" s="0">
-        <v>1.0600000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="G14" s="0">
-        <v>0.17000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="H14" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3085,25 +3085,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>16.210000000000001</v>
+        <v>21.039999999999999</v>
       </c>
       <c r="C2" s="0">
-        <v>13.59</v>
+        <v>19.93</v>
       </c>
       <c r="D2" s="0">
-        <v>37.399999999999999</v>
+        <v>38.689999999999998</v>
       </c>
       <c r="E2" s="0">
-        <v>23.649999999999999</v>
+        <v>22.670000000000002</v>
       </c>
       <c r="F2" s="0">
-        <v>38.729999999999997</v>
+        <v>37.039999999999999</v>
       </c>
       <c r="G2" s="0">
-        <v>27.68</v>
+        <v>26.640000000000001</v>
       </c>
       <c r="H2" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -3111,25 +3111,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>24.43</v>
+        <v>23.609999999999999</v>
       </c>
       <c r="C3" s="0">
-        <v>14.69</v>
+        <v>14.09</v>
       </c>
       <c r="D3" s="0">
-        <v>26.780000000000001</v>
+        <v>27.039999999999999</v>
       </c>
       <c r="E3" s="0">
-        <v>25.039999999999999</v>
+        <v>23.629999999999999</v>
       </c>
       <c r="F3" s="0">
-        <v>36.159999999999997</v>
+        <v>33.490000000000002</v>
       </c>
       <c r="G3" s="0">
-        <v>20.879999999999999</v>
+        <v>21.420000000000002</v>
       </c>
       <c r="H3" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -3137,25 +3137,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>28.5</v>
+        <v>29.609999999999999</v>
       </c>
       <c r="C4" s="0">
-        <v>21.789999999999999</v>
+        <v>20.84</v>
       </c>
       <c r="D4" s="0">
-        <v>41.450000000000003</v>
+        <v>40.630000000000003</v>
       </c>
       <c r="E4" s="0">
-        <v>30.59</v>
+        <v>28.960000000000001</v>
       </c>
       <c r="F4" s="0">
-        <v>28.670000000000002</v>
+        <v>26.969999999999999</v>
       </c>
       <c r="G4" s="0">
-        <v>24.030000000000001</v>
+        <v>23.289999999999999</v>
       </c>
       <c r="H4" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -3163,25 +3163,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>29.800000000000001</v>
+        <v>29.899999999999999</v>
       </c>
       <c r="C5" s="0">
-        <v>19.550000000000001</v>
+        <v>18.440000000000001</v>
       </c>
       <c r="D5" s="0">
-        <v>33.159999999999997</v>
+        <v>35.490000000000002</v>
       </c>
       <c r="E5" s="0">
-        <v>25.91</v>
+        <v>25.52</v>
       </c>
       <c r="F5" s="0">
-        <v>38.409999999999997</v>
+        <v>38.780000000000001</v>
       </c>
       <c r="G5" s="0">
-        <v>31.039999999999999</v>
+        <v>29.289999999999999</v>
       </c>
       <c r="H5" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -3189,25 +3189,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>29.699999999999999</v>
+        <v>29.359999999999999</v>
       </c>
       <c r="C6" s="0">
-        <v>16.43</v>
+        <v>15.529999999999999</v>
       </c>
       <c r="D6" s="0">
-        <v>47.280000000000001</v>
+        <v>47.619999999999997</v>
       </c>
       <c r="E6" s="0">
-        <v>37.119999999999997</v>
+        <v>35.009999999999998</v>
       </c>
       <c r="F6" s="0">
-        <v>31.920000000000002</v>
+        <v>31.23</v>
       </c>
       <c r="G6" s="0">
-        <v>20.670000000000002</v>
+        <v>19.609999999999999</v>
       </c>
       <c r="H6" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -3215,25 +3215,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>38.009999999999998</v>
+        <v>38.030000000000001</v>
       </c>
       <c r="C7" s="0">
-        <v>17.75</v>
+        <v>16.739999999999998</v>
       </c>
       <c r="D7" s="0">
-        <v>38.920000000000002</v>
+        <v>43.130000000000003</v>
       </c>
       <c r="E7" s="0">
-        <v>26.84</v>
+        <v>28.59</v>
       </c>
       <c r="F7" s="0">
-        <v>54.259999999999998</v>
+        <v>50.030000000000001</v>
       </c>
       <c r="G7" s="0">
-        <v>42.32</v>
+        <v>42.079999999999998</v>
       </c>
       <c r="H7" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -3241,25 +3241,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>19.829999999999998</v>
+        <v>21.870000000000001</v>
       </c>
       <c r="C8" s="0">
-        <v>14.18</v>
+        <v>14.6</v>
       </c>
       <c r="D8" s="0">
-        <v>33.439999999999998</v>
+        <v>33.979999999999997</v>
       </c>
       <c r="E8" s="0">
-        <v>24.260000000000002</v>
+        <v>22.75</v>
       </c>
       <c r="F8" s="0">
-        <v>31.949999999999999</v>
+        <v>29.960000000000001</v>
       </c>
       <c r="G8" s="0">
-        <v>27.73</v>
+        <v>26.620000000000001</v>
       </c>
       <c r="H8" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -3267,25 +3267,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>26.280000000000001</v>
+        <v>26.870000000000001</v>
       </c>
       <c r="C9" s="0">
-        <v>12.779999999999999</v>
+        <v>12.09</v>
       </c>
       <c r="D9" s="0">
-        <v>41.590000000000003</v>
+        <v>43.109999999999999</v>
       </c>
       <c r="E9" s="0">
-        <v>32.990000000000002</v>
+        <v>31.190000000000001</v>
       </c>
       <c r="F9" s="0">
-        <v>46.270000000000003</v>
+        <v>43.710000000000001</v>
       </c>
       <c r="G9" s="0">
-        <v>30.75</v>
+        <v>29.760000000000002</v>
       </c>
       <c r="H9" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -3293,25 +3293,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>28.300000000000001</v>
+        <v>30.34</v>
       </c>
       <c r="C10" s="0">
-        <v>15.529999999999999</v>
+        <v>16</v>
       </c>
       <c r="D10" s="0">
-        <v>42.340000000000003</v>
+        <v>44.299999999999997</v>
       </c>
       <c r="E10" s="0">
-        <v>32.920000000000002</v>
+        <v>31.649999999999999</v>
       </c>
       <c r="F10" s="0">
-        <v>28.02</v>
+        <v>26.41</v>
       </c>
       <c r="G10" s="0">
-        <v>21.809999999999999</v>
+        <v>21.18</v>
       </c>
       <c r="H10" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -3319,25 +3319,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>33.329999999999998</v>
+        <v>32.409999999999997</v>
       </c>
       <c r="C11" s="0">
-        <v>16.41</v>
+        <v>15.74</v>
       </c>
       <c r="D11" s="0">
-        <v>38.390000000000001</v>
+        <v>42.649999999999999</v>
       </c>
       <c r="E11" s="0">
-        <v>27.309999999999999</v>
+        <v>29.059999999999999</v>
       </c>
       <c r="F11" s="0">
-        <v>48.039999999999999</v>
+        <v>45.869999999999997</v>
       </c>
       <c r="G11" s="0">
-        <v>40.960000000000001</v>
+        <v>39.229999999999997</v>
       </c>
       <c r="H11" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -3345,25 +3345,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>29.059999999999999</v>
+        <v>30.48</v>
       </c>
       <c r="C12" s="0">
-        <v>17.949999999999999</v>
+        <v>17.32</v>
       </c>
       <c r="D12" s="0">
-        <v>38.57</v>
+        <v>40.890000000000001</v>
       </c>
       <c r="E12" s="0">
-        <v>32.350000000000001</v>
+        <v>31.050000000000001</v>
       </c>
       <c r="F12" s="0">
-        <v>34.399999999999999</v>
+        <v>32.259999999999998</v>
       </c>
       <c r="G12" s="0">
-        <v>22.879999999999999</v>
+        <v>22.34</v>
       </c>
       <c r="H12" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -3371,25 +3371,25 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>41.079999999999998</v>
+        <v>40.18</v>
       </c>
       <c r="C13" s="0">
-        <v>19.969999999999999</v>
+        <v>18.870000000000001</v>
       </c>
       <c r="D13" s="0">
-        <v>54.920000000000002</v>
+        <v>57.840000000000003</v>
       </c>
       <c r="E13" s="0">
-        <v>36.18</v>
+        <v>34.960000000000001</v>
       </c>
       <c r="F13" s="0">
-        <v>53.460000000000001</v>
+        <v>49.590000000000003</v>
       </c>
       <c r="G13" s="0">
-        <v>38.43</v>
+        <v>37.780000000000001</v>
       </c>
       <c r="H13" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -3397,25 +3397,25 @@
         <v>24</v>
       </c>
       <c r="B14" s="0">
-        <v>12.130000000000001</v>
+        <v>13</v>
       </c>
       <c r="C14" s="0">
-        <v>7.8899999999999997</v>
+        <v>7.9299999999999997</v>
       </c>
       <c r="D14" s="0">
-        <v>24.300000000000001</v>
+        <v>27.149999999999999</v>
       </c>
       <c r="E14" s="0">
-        <v>17.469999999999999</v>
+        <v>18.789999999999999</v>
       </c>
       <c r="F14" s="0">
-        <v>26.579999999999998</v>
+        <v>25.350000000000001</v>
       </c>
       <c r="G14" s="0">
-        <v>17.850000000000001</v>
+        <v>17.27</v>
       </c>
       <c r="H14" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3468,25 +3468,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>-42.049999999999997</v>
+        <v>-38.740000000000002</v>
       </c>
       <c r="C2" s="0">
-        <v>43.579999999999998</v>
+        <v>42.399999999999999</v>
       </c>
       <c r="D2" s="0">
-        <v>-38.890000000000001</v>
+        <v>-35.350000000000001</v>
       </c>
       <c r="E2" s="0">
-        <v>70.840000000000003</v>
+        <v>67.719999999999999</v>
       </c>
       <c r="F2" s="0">
-        <v>-29.329999999999998</v>
+        <v>-31.379999999999999</v>
       </c>
       <c r="G2" s="0">
-        <v>17.030000000000001</v>
+        <v>17.32</v>
       </c>
       <c r="H2" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -3494,25 +3494,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>-19.050000000000001</v>
+        <v>-18.34</v>
       </c>
       <c r="C3" s="0">
-        <v>12.81</v>
+        <v>12.279999999999999</v>
       </c>
       <c r="D3" s="0">
-        <v>-30.940000000000001</v>
+        <v>-35.189999999999998</v>
       </c>
       <c r="E3" s="0">
-        <v>39.490000000000002</v>
+        <v>39.579999999999998</v>
       </c>
       <c r="F3" s="0">
-        <v>-57.590000000000003</v>
+        <v>-64.510000000000005</v>
       </c>
       <c r="G3" s="0">
-        <v>58.359999999999999</v>
+        <v>59.219999999999999</v>
       </c>
       <c r="H3" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -3520,25 +3520,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>-49.609999999999999</v>
+        <v>-45.840000000000003</v>
       </c>
       <c r="C4" s="0">
-        <v>42.590000000000003</v>
+        <v>41.880000000000003</v>
       </c>
       <c r="D4" s="0">
         <v>-44.369999999999997</v>
       </c>
       <c r="E4" s="0">
-        <v>73.989999999999995</v>
+        <v>69.760000000000005</v>
       </c>
       <c r="F4" s="0">
-        <v>-27.510000000000002</v>
+        <v>-33.329999999999998</v>
       </c>
       <c r="G4" s="0">
-        <v>14.130000000000001</v>
+        <v>22.699999999999999</v>
       </c>
       <c r="H4" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -3546,25 +3546,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>-20.109999999999999</v>
+        <v>-18.93</v>
       </c>
       <c r="C5" s="0">
-        <v>11.630000000000001</v>
+        <v>11.59</v>
       </c>
       <c r="D5" s="0">
-        <v>-38.460000000000001</v>
+        <v>-37.979999999999997</v>
       </c>
       <c r="E5" s="0">
-        <v>44.310000000000002</v>
+        <v>41.799999999999997</v>
       </c>
       <c r="F5" s="0">
-        <v>-56.759999999999998</v>
+        <v>-59.950000000000003</v>
       </c>
       <c r="G5" s="0">
-        <v>60.770000000000003</v>
+        <v>58.170000000000002</v>
       </c>
       <c r="H5" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -3572,25 +3572,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>-53.079999999999998</v>
+        <v>-52.770000000000003</v>
       </c>
       <c r="C6" s="0">
-        <v>45.380000000000003</v>
+        <v>42.799999999999997</v>
       </c>
       <c r="D6" s="0">
-        <v>-44.25</v>
+        <v>-47.869999999999997</v>
       </c>
       <c r="E6" s="0">
-        <v>70.459999999999994</v>
+        <v>67.409999999999997</v>
       </c>
       <c r="F6" s="0">
-        <v>-28.219999999999999</v>
+        <v>-31.219999999999999</v>
       </c>
       <c r="G6" s="0">
-        <v>14.01</v>
+        <v>16.27</v>
       </c>
       <c r="H6" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -3598,25 +3598,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>-23.300000000000001</v>
+        <v>-22.09</v>
       </c>
       <c r="C7" s="0">
-        <v>15.58</v>
+        <v>15.17</v>
       </c>
       <c r="D7" s="0">
-        <v>-44.280000000000001</v>
+        <v>-40.460000000000001</v>
       </c>
       <c r="E7" s="0">
-        <v>41.170000000000002</v>
+        <v>40.649999999999999</v>
       </c>
       <c r="F7" s="0">
-        <v>-65.950000000000003</v>
+        <v>-65.010000000000005</v>
       </c>
       <c r="G7" s="0">
-        <v>54.229999999999997</v>
+        <v>51.210000000000001</v>
       </c>
       <c r="H7" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -3624,25 +3624,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>-44.840000000000003</v>
+        <v>-41.409999999999997</v>
       </c>
       <c r="C8" s="0">
-        <v>47.380000000000003</v>
+        <v>45.5</v>
       </c>
       <c r="D8" s="0">
-        <v>-45.119999999999997</v>
+        <v>-44.100000000000001</v>
       </c>
       <c r="E8" s="0">
-        <v>73.180000000000007</v>
+        <v>68.519999999999996</v>
       </c>
       <c r="F8" s="0">
-        <v>-28.789999999999999</v>
+        <v>-35.130000000000003</v>
       </c>
       <c r="G8" s="0">
-        <v>15.44</v>
+        <v>23.879999999999999</v>
       </c>
       <c r="H8" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -3650,25 +3650,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>-18.010000000000002</v>
+        <v>-17.370000000000001</v>
       </c>
       <c r="C9" s="0">
-        <v>11.4</v>
+        <v>10.83</v>
       </c>
       <c r="D9" s="0">
-        <v>-36.68</v>
+        <v>-36.049999999999997</v>
       </c>
       <c r="E9" s="0">
-        <v>42.07</v>
+        <v>39.399999999999999</v>
       </c>
       <c r="F9" s="0">
-        <v>-46.079999999999998</v>
+        <v>-50.509999999999998</v>
       </c>
       <c r="G9" s="0">
-        <v>53.140000000000001</v>
+        <v>51.460000000000001</v>
       </c>
       <c r="H9" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -3676,25 +3676,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>-53.579999999999998</v>
+        <v>-49.700000000000003</v>
       </c>
       <c r="C10" s="0">
-        <v>41.840000000000003</v>
+        <v>41.310000000000002</v>
       </c>
       <c r="D10" s="0">
-        <v>-47.5</v>
+        <v>-44.100000000000001</v>
       </c>
       <c r="E10" s="0">
-        <v>67.459999999999994</v>
+        <v>64.5</v>
       </c>
       <c r="F10" s="0">
-        <v>-28.510000000000002</v>
+        <v>-29.079999999999998</v>
       </c>
       <c r="G10" s="0">
-        <v>15</v>
+        <v>14.25</v>
       </c>
       <c r="H10" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -3702,25 +3702,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>-19.829999999999998</v>
+        <v>-18.59</v>
       </c>
       <c r="C11" s="0">
-        <v>8.3499999999999996</v>
+        <v>8.7899999999999991</v>
       </c>
       <c r="D11" s="0">
-        <v>-40.310000000000002</v>
+        <v>-37.469999999999999</v>
       </c>
       <c r="E11" s="0">
-        <v>43.219999999999999</v>
+        <v>41.729999999999997</v>
       </c>
       <c r="F11" s="0">
-        <v>-60.549999999999997</v>
+        <v>-58.140000000000001</v>
       </c>
       <c r="G11" s="0">
-        <v>58.359999999999999</v>
+        <v>55.539999999999999</v>
       </c>
       <c r="H11" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -3728,25 +3728,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>-49.869999999999997</v>
+        <v>-49.229999999999997</v>
       </c>
       <c r="C12" s="0">
-        <v>49.869999999999997</v>
+        <v>46.689999999999998</v>
       </c>
       <c r="D12" s="0">
-        <v>-54.5</v>
+        <v>-55.359999999999999</v>
       </c>
       <c r="E12" s="0">
-        <v>72.140000000000001</v>
+        <v>67.530000000000001</v>
       </c>
       <c r="F12" s="0">
-        <v>-29.390000000000001</v>
+        <v>-32.189999999999998</v>
       </c>
       <c r="G12" s="0">
-        <v>12.58</v>
+        <v>14.460000000000001</v>
       </c>
       <c r="H12" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -3754,25 +3754,25 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>-24.48</v>
+        <v>-22.780000000000001</v>
       </c>
       <c r="C13" s="0">
-        <v>10.5</v>
+        <v>11.07</v>
       </c>
       <c r="D13" s="0">
-        <v>-37.490000000000002</v>
+        <v>-34.509999999999998</v>
       </c>
       <c r="E13" s="0">
-        <v>41.469999999999999</v>
+        <v>39.810000000000002</v>
       </c>
       <c r="F13" s="0">
-        <v>-49.890000000000001</v>
+        <v>-49.939999999999998</v>
       </c>
       <c r="G13" s="0">
-        <v>54.869999999999997</v>
+        <v>51.329999999999998</v>
       </c>
       <c r="H13" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -3780,25 +3780,25 @@
         <v>24</v>
       </c>
       <c r="B14" s="0">
-        <v>-12.449999999999999</v>
+        <v>-11.41</v>
       </c>
       <c r="C14" s="0">
-        <v>8.7899999999999991</v>
+        <v>8.9199999999999999</v>
       </c>
       <c r="D14" s="0">
-        <v>-11.869999999999999</v>
+        <v>-11.57</v>
       </c>
       <c r="E14" s="0">
-        <v>10.720000000000001</v>
+        <v>10.15</v>
       </c>
       <c r="F14" s="0">
-        <v>-27.530000000000001</v>
+        <v>-27.199999999999999</v>
       </c>
       <c r="G14" s="0">
-        <v>13.69</v>
+        <v>12.949999999999999</v>
       </c>
       <c r="H14" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3883,49 +3883,49 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>-3.1899999999999999</v>
+        <v>-2.8500000000000001</v>
       </c>
       <c r="C2" s="0">
-        <v>10.4</v>
+        <v>9.8599999999999994</v>
       </c>
       <c r="D2" s="0">
-        <v>7.79</v>
+        <v>9.6899999999999995</v>
       </c>
       <c r="E2" s="0">
-        <v>18.030000000000001</v>
+        <v>18.02</v>
       </c>
       <c r="F2" s="0">
-        <v>12.57</v>
+        <v>11.140000000000001</v>
       </c>
       <c r="G2" s="0">
-        <v>14.69</v>
+        <v>14.57</v>
       </c>
       <c r="H2" s="0">
-        <v>50.340000000000003</v>
+        <v>50.909999999999997</v>
       </c>
       <c r="I2" s="0">
-        <v>4.1100000000000003</v>
+        <v>4.2800000000000002</v>
       </c>
       <c r="J2" s="0">
-        <v>-16.149999999999999</v>
+        <v>-16.539999999999999</v>
       </c>
       <c r="K2" s="0">
-        <v>7.9100000000000001</v>
+        <v>7.5599999999999996</v>
       </c>
       <c r="L2" s="0">
-        <v>-14.73</v>
+        <v>-15.23</v>
       </c>
       <c r="M2" s="0">
-        <v>6.1600000000000001</v>
+        <v>6.0199999999999996</v>
       </c>
       <c r="N2" s="0">
-        <v>2.3300000000000001</v>
+        <v>2.25</v>
       </c>
       <c r="O2" s="0">
-        <v>4.1100000000000003</v>
+        <v>3.8799999999999999</v>
       </c>
       <c r="P2" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -3933,49 +3933,49 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>-2.2000000000000002</v>
+        <v>-0.14999999999999999</v>
       </c>
       <c r="C3" s="0">
-        <v>18.75</v>
+        <v>18.829999999999998</v>
       </c>
       <c r="D3" s="0">
-        <v>1.96</v>
+        <v>0.78000000000000003</v>
       </c>
       <c r="E3" s="0">
-        <v>6.3399999999999999</v>
+        <v>7.04</v>
       </c>
       <c r="F3" s="0">
-        <v>16.280000000000001</v>
+        <v>14.57</v>
       </c>
       <c r="G3" s="0">
-        <v>20.52</v>
+        <v>20.079999999999998</v>
       </c>
       <c r="H3" s="0">
-        <v>51.43</v>
+        <v>50.420000000000002</v>
       </c>
       <c r="I3" s="0">
-        <v>6.5300000000000002</v>
+        <v>6.9199999999999999</v>
       </c>
       <c r="J3" s="0">
-        <v>-4.9199999999999999</v>
+        <v>-5.1500000000000004</v>
       </c>
       <c r="K3" s="0">
-        <v>1.8300000000000001</v>
+        <v>1.8799999999999999</v>
       </c>
       <c r="L3" s="0">
-        <v>-3.4399999999999999</v>
+        <v>-3.5499999999999998</v>
       </c>
       <c r="M3" s="0">
-        <v>0.76000000000000001</v>
+        <v>0.80000000000000004</v>
       </c>
       <c r="N3" s="0">
-        <v>10.93</v>
+        <v>10.56</v>
       </c>
       <c r="O3" s="0">
-        <v>4.5800000000000001</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="P3" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -3983,49 +3983,49 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>3.5600000000000001</v>
+        <v>4.6299999999999999</v>
       </c>
       <c r="C4" s="0">
-        <v>9.4100000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="D4" s="0">
-        <v>0.20999999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="E4" s="0">
-        <v>21.899999999999999</v>
+        <v>20.809999999999999</v>
       </c>
       <c r="F4" s="0">
-        <v>13.6</v>
+        <v>11.710000000000001</v>
       </c>
       <c r="G4" s="0">
         <v>18</v>
       </c>
       <c r="H4" s="0">
-        <v>49.920000000000002</v>
+        <v>50.079999999999998</v>
       </c>
       <c r="I4" s="0">
-        <v>6.6799999999999997</v>
+        <v>6.3200000000000003</v>
       </c>
       <c r="J4" s="0">
-        <v>-17.43</v>
+        <v>-17.75</v>
       </c>
       <c r="K4" s="0">
-        <v>7.9400000000000004</v>
+        <v>7.5499999999999998</v>
       </c>
       <c r="L4" s="0">
-        <v>-14.800000000000001</v>
+        <v>-15.42</v>
       </c>
       <c r="M4" s="0">
-        <v>8.3800000000000008</v>
+        <v>8.1400000000000006</v>
       </c>
       <c r="N4" s="0">
-        <v>1.3300000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="O4" s="0">
-        <v>1.02</v>
+        <v>1.3100000000000001</v>
       </c>
       <c r="P4" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -4033,49 +4033,49 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>2.3199999999999998</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="C5" s="0">
-        <v>8.3100000000000005</v>
+        <v>7.8899999999999997</v>
       </c>
       <c r="D5" s="0">
-        <v>3.1600000000000001</v>
+        <v>2.8199999999999998</v>
       </c>
       <c r="E5" s="0">
-        <v>6.0300000000000002</v>
+        <v>5.7800000000000002</v>
       </c>
       <c r="F5" s="0">
-        <v>11.18</v>
+        <v>9.8399999999999999</v>
       </c>
       <c r="G5" s="0">
-        <v>20.079999999999998</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="H5" s="0">
-        <v>54.479999999999997</v>
+        <v>54.530000000000001</v>
       </c>
       <c r="I5" s="0">
-        <v>3.4300000000000002</v>
+        <v>3.23</v>
       </c>
       <c r="J5" s="0">
-        <v>-4.0999999999999996</v>
+        <v>-4.3099999999999996</v>
       </c>
       <c r="K5" s="0">
-        <v>1.3400000000000001</v>
+        <v>1.4299999999999999</v>
       </c>
       <c r="L5" s="0">
-        <v>-2.77</v>
+        <v>-2.7400000000000002</v>
       </c>
       <c r="M5" s="0">
-        <v>0.92000000000000004</v>
+        <v>0.87</v>
       </c>
       <c r="N5" s="0">
-        <v>9.4800000000000004</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="O5" s="0">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="P5" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -4083,49 +4083,49 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>-2.6099999999999999</v>
+        <v>-0.25</v>
       </c>
       <c r="C6" s="0">
-        <v>7.9900000000000002</v>
+        <v>10.6</v>
       </c>
       <c r="D6" s="0">
-        <v>6.8300000000000001</v>
+        <v>6.96</v>
       </c>
       <c r="E6" s="0">
-        <v>19.859999999999999</v>
+        <v>18.73</v>
       </c>
       <c r="F6" s="0">
-        <v>3.4199999999999999</v>
+        <v>3.2400000000000002</v>
       </c>
       <c r="G6" s="0">
-        <v>18.93</v>
+        <v>17.859999999999999</v>
       </c>
       <c r="H6" s="0">
-        <v>47.079999999999998</v>
+        <v>47.060000000000002</v>
       </c>
       <c r="I6" s="0">
-        <v>4.79</v>
+        <v>4.5099999999999998</v>
       </c>
       <c r="J6" s="0">
-        <v>-18.41</v>
+        <v>-18.43</v>
       </c>
       <c r="K6" s="0">
-        <v>3.9500000000000002</v>
+        <v>3.73</v>
       </c>
       <c r="L6" s="0">
-        <v>-15.130000000000001</v>
+        <v>-15.6</v>
       </c>
       <c r="M6" s="0">
-        <v>6.1100000000000003</v>
+        <v>5.96</v>
       </c>
       <c r="N6" s="0">
-        <v>1.1899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="O6" s="0">
-        <v>1.6399999999999999</v>
+        <v>1.8300000000000001</v>
       </c>
       <c r="P6" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -4133,49 +4133,49 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>1.53</v>
+        <v>1.03</v>
       </c>
       <c r="C7" s="0">
-        <v>16.399999999999999</v>
+        <v>15.539999999999999</v>
       </c>
       <c r="D7" s="0">
-        <v>4.46</v>
+        <v>6.2400000000000002</v>
       </c>
       <c r="E7" s="0">
-        <v>6.8099999999999996</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="F7" s="0">
-        <v>11.84</v>
+        <v>10.539999999999999</v>
       </c>
       <c r="G7" s="0">
-        <v>15.41</v>
+        <v>15.1</v>
       </c>
       <c r="H7" s="0">
-        <v>54.229999999999997</v>
+        <v>54.609999999999999</v>
       </c>
       <c r="I7" s="0">
-        <v>3.1800000000000002</v>
+        <v>3.2400000000000002</v>
       </c>
       <c r="J7" s="0">
-        <v>-3.2400000000000002</v>
+        <v>-3.3900000000000001</v>
       </c>
       <c r="K7" s="0">
+        <v>0.79000000000000004</v>
+      </c>
+      <c r="L7" s="0">
+        <v>-2.5099999999999998</v>
+      </c>
+      <c r="M7" s="0">
         <v>0.68000000000000005</v>
       </c>
-      <c r="L7" s="0">
-        <v>-2.5499999999999998</v>
-      </c>
-      <c r="M7" s="0">
-        <v>0.69999999999999996</v>
-      </c>
       <c r="N7" s="0">
-        <v>9.8800000000000008</v>
+        <v>9.8100000000000005</v>
       </c>
       <c r="O7" s="0">
-        <v>1.48</v>
+        <v>1.4099999999999999</v>
       </c>
       <c r="P7" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -4183,49 +4183,49 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>2.7599999999999998</v>
+        <v>4.29</v>
       </c>
       <c r="C8" s="0">
-        <v>9.3300000000000001</v>
+        <v>9.8499999999999996</v>
       </c>
       <c r="D8" s="0">
-        <v>0.92000000000000004</v>
+        <v>0.34999999999999998</v>
       </c>
       <c r="E8" s="0">
-        <v>10.83</v>
+        <v>10.279999999999999</v>
       </c>
       <c r="F8" s="0">
-        <v>11.92</v>
+        <v>8.6199999999999992</v>
       </c>
       <c r="G8" s="0">
-        <v>14.83</v>
+        <v>17.039999999999999</v>
       </c>
       <c r="H8" s="0">
-        <v>48.450000000000003</v>
+        <v>49.68</v>
       </c>
       <c r="I8" s="0">
-        <v>5.3600000000000003</v>
+        <v>6.3700000000000001</v>
       </c>
       <c r="J8" s="0">
-        <v>-15.279999999999999</v>
+        <v>-16.399999999999999</v>
       </c>
       <c r="K8" s="0">
-        <v>7.9199999999999999</v>
+        <v>8.2699999999999996</v>
       </c>
       <c r="L8" s="0">
-        <v>-12.85</v>
+        <v>-14.199999999999999</v>
       </c>
       <c r="M8" s="0">
-        <v>8.1199999999999992</v>
+        <v>8.7599999999999998</v>
       </c>
       <c r="N8" s="0">
-        <v>2.0800000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="O8" s="0">
-        <v>6.5300000000000002</v>
+        <v>6.46</v>
       </c>
       <c r="P8" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -4233,49 +4233,49 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>4.7599999999999998</v>
+        <v>6</v>
       </c>
       <c r="C9" s="0">
-        <v>8.5099999999999998</v>
+        <v>8.7799999999999994</v>
       </c>
       <c r="D9" s="0">
-        <v>4.4199999999999999</v>
+        <v>2.29</v>
       </c>
       <c r="E9" s="0">
-        <v>9.4100000000000001</v>
+        <v>10.880000000000001</v>
       </c>
       <c r="F9" s="0">
-        <v>11.43</v>
+        <v>10.34</v>
       </c>
       <c r="G9" s="0">
-        <v>14.84</v>
+        <v>14.27</v>
       </c>
       <c r="H9" s="0">
-        <v>53.609999999999999</v>
+        <v>54.439999999999998</v>
       </c>
       <c r="I9" s="0">
-        <v>2.23</v>
+        <v>3.3700000000000001</v>
       </c>
       <c r="J9" s="0">
-        <v>-5.3499999999999996</v>
+        <v>-5.4199999999999999</v>
       </c>
       <c r="K9" s="0">
-        <v>1.6399999999999999</v>
+        <v>1.5600000000000001</v>
       </c>
       <c r="L9" s="0">
-        <v>-3.25</v>
+        <v>-3.1400000000000001</v>
       </c>
       <c r="M9" s="0">
-        <v>1.1299999999999999</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="N9" s="0">
-        <v>9.7899999999999991</v>
+        <v>9.4299999999999997</v>
       </c>
       <c r="O9" s="0">
-        <v>1.52</v>
+        <v>1.8400000000000001</v>
       </c>
       <c r="P9" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -4283,49 +4283,49 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>-2.2999999999999998</v>
+        <v>-0.73999999999999999</v>
       </c>
       <c r="C10" s="0">
-        <v>12.449999999999999</v>
+        <v>12.73</v>
       </c>
       <c r="D10" s="0">
-        <v>-0.97999999999999998</v>
+        <v>0.69999999999999996</v>
       </c>
       <c r="E10" s="0">
-        <v>19.460000000000001</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="F10" s="0">
-        <v>11.74</v>
+        <v>10.33</v>
       </c>
       <c r="G10" s="0">
-        <v>13.539999999999999</v>
+        <v>13.52</v>
       </c>
       <c r="H10" s="0">
-        <v>50.710000000000001</v>
+        <v>50.859999999999999</v>
       </c>
       <c r="I10" s="0">
-        <v>5.6100000000000003</v>
+        <v>5.3200000000000003</v>
       </c>
       <c r="J10" s="0">
-        <v>-21.07</v>
+        <v>-20.890000000000001</v>
       </c>
       <c r="K10" s="0">
-        <v>2.4399999999999999</v>
+        <v>2.3599999999999999</v>
       </c>
       <c r="L10" s="0">
-        <v>-17.800000000000001</v>
+        <v>-17.98</v>
       </c>
       <c r="M10" s="0">
-        <v>2.1200000000000001</v>
+        <v>2.0800000000000001</v>
       </c>
       <c r="N10" s="0">
-        <v>0.68999999999999995</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="O10" s="0">
-        <v>1.3100000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="P10" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -4333,49 +4333,49 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>2.77</v>
+        <v>3.3300000000000001</v>
       </c>
       <c r="C11" s="0">
-        <v>14.140000000000001</v>
+        <v>13.449999999999999</v>
       </c>
       <c r="D11" s="0">
-        <v>-3.8500000000000001</v>
+        <v>-1.6699999999999999</v>
       </c>
       <c r="E11" s="0">
-        <v>10.699999999999999</v>
+        <v>12.220000000000001</v>
       </c>
       <c r="F11" s="0">
-        <v>13.08</v>
+        <v>12.07</v>
       </c>
       <c r="G11" s="0">
-        <v>13.4</v>
+        <v>13.029999999999999</v>
       </c>
       <c r="H11" s="0">
-        <v>55.210000000000001</v>
+        <v>54.460000000000001</v>
       </c>
       <c r="I11" s="0">
-        <v>2.1299999999999999</v>
+        <v>3.1000000000000001</v>
       </c>
       <c r="J11" s="0">
-        <v>-2.8100000000000001</v>
+        <v>-3.1400000000000001</v>
       </c>
       <c r="K11" s="0">
-        <v>4.7000000000000002</v>
+        <v>4.5499999999999998</v>
       </c>
       <c r="L11" s="0">
-        <v>-1.3100000000000001</v>
+        <v>-1.48</v>
       </c>
       <c r="M11" s="0">
-        <v>4.8700000000000001</v>
+        <v>4.6200000000000001</v>
       </c>
       <c r="N11" s="0">
-        <v>10.65</v>
+        <v>10.59</v>
       </c>
       <c r="O11" s="0">
-        <v>4.7599999999999998</v>
+        <v>4.4900000000000002</v>
       </c>
       <c r="P11" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -4383,49 +4383,49 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>4.5899999999999999</v>
+        <v>6.0499999999999998</v>
       </c>
       <c r="C12" s="0">
-        <v>10.98</v>
+        <v>11.16</v>
       </c>
       <c r="D12" s="0">
-        <v>-9.6300000000000008</v>
+        <v>-7.7300000000000004</v>
       </c>
       <c r="E12" s="0">
-        <v>26.75</v>
+        <v>25.66</v>
       </c>
       <c r="F12" s="0">
-        <v>-0.23999999999999999</v>
+        <v>-2.02</v>
       </c>
       <c r="G12" s="0">
-        <v>13.06</v>
+        <v>13.33</v>
       </c>
       <c r="H12" s="0">
-        <v>50.579999999999998</v>
+        <v>50.609999999999999</v>
       </c>
       <c r="I12" s="0">
-        <v>7.0999999999999996</v>
+        <v>6.7000000000000002</v>
       </c>
       <c r="J12" s="0">
-        <v>-18.23</v>
+        <v>-18.5</v>
       </c>
       <c r="K12" s="0">
-        <v>8.1500000000000004</v>
+        <v>7.7300000000000004</v>
       </c>
       <c r="L12" s="0">
-        <v>-14.800000000000001</v>
+        <v>-15.550000000000001</v>
       </c>
       <c r="M12" s="0">
-        <v>7.9100000000000001</v>
+        <v>7.8300000000000001</v>
       </c>
       <c r="N12" s="0">
-        <v>2.6899999999999999</v>
+        <v>2.27</v>
       </c>
       <c r="O12" s="0">
-        <v>6.3499999999999996</v>
+        <v>6.1299999999999999</v>
       </c>
       <c r="P12" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -4433,49 +4433,49 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>-1.26</v>
+        <v>-0.029999999999999999</v>
       </c>
       <c r="C13" s="0">
-        <v>12.52</v>
+        <v>12.279999999999999</v>
       </c>
       <c r="D13" s="0">
-        <v>9.6199999999999992</v>
+        <v>10.949999999999999</v>
       </c>
       <c r="E13" s="0">
-        <v>9.6300000000000008</v>
+        <v>9.8499999999999996</v>
       </c>
       <c r="F13" s="0">
-        <v>15.08</v>
+        <v>13.289999999999999</v>
       </c>
       <c r="G13" s="0">
-        <v>20.129999999999999</v>
+        <v>19.579999999999998</v>
       </c>
       <c r="H13" s="0">
-        <v>54.920000000000002</v>
+        <v>54.200000000000003</v>
       </c>
       <c r="I13" s="0">
-        <v>3.0099999999999998</v>
+        <v>3.6299999999999999</v>
       </c>
       <c r="J13" s="0">
-        <v>-3.3500000000000001</v>
+        <v>-3.4700000000000002</v>
       </c>
       <c r="K13" s="0">
         <v>1.1100000000000001</v>
       </c>
       <c r="L13" s="0">
-        <v>-2.5</v>
+        <v>-2.4900000000000002</v>
       </c>
       <c r="M13" s="0">
-        <v>0.56000000000000005</v>
+        <v>0.53000000000000003</v>
       </c>
       <c r="N13" s="0">
-        <v>10.52</v>
+        <v>10.6</v>
       </c>
       <c r="O13" s="0">
-        <v>2.2200000000000002</v>
+        <v>2.1099999999999999</v>
       </c>
       <c r="P13" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -4483,49 +4483,49 @@
         <v>24</v>
       </c>
       <c r="B14" s="0">
-        <v>2.7599999999999998</v>
+        <v>1.6000000000000001</v>
       </c>
       <c r="C14" s="0">
-        <v>7.1200000000000001</v>
+        <v>7.6500000000000004</v>
       </c>
       <c r="D14" s="0">
-        <v>-5.25</v>
+        <v>-5.0099999999999998</v>
       </c>
       <c r="E14" s="0">
-        <v>15.58</v>
+        <v>14.710000000000001</v>
       </c>
       <c r="F14" s="0">
-        <v>-0.10000000000000001</v>
+        <v>-0.13</v>
       </c>
       <c r="G14" s="0">
-        <v>16.190000000000001</v>
+        <v>15.27</v>
       </c>
       <c r="H14" s="0">
-        <v>58.100000000000001</v>
+        <v>58.960000000000001</v>
       </c>
       <c r="I14" s="0">
-        <v>9.4399999999999995</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="J14" s="0">
-        <v>-19.510000000000002</v>
+        <v>-20.440000000000001</v>
       </c>
       <c r="K14" s="0">
-        <v>9.0899999999999999</v>
+        <v>9.0600000000000005</v>
       </c>
       <c r="L14" s="0">
-        <v>-18.52</v>
+        <v>-19.68</v>
       </c>
       <c r="M14" s="0">
-        <v>8.8800000000000008</v>
+        <v>9.1500000000000004</v>
       </c>
       <c r="N14" s="0">
-        <v>7.75</v>
+        <v>6.3899999999999997</v>
       </c>
       <c r="O14" s="0">
-        <v>13.92</v>
+        <v>13.81</v>
       </c>
       <c r="P14" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -4642,73 +4642,73 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>51.399999999999999</v>
+        <v>53</v>
       </c>
       <c r="C2" s="0">
-        <v>38.18</v>
+        <v>36.340000000000003</v>
       </c>
       <c r="D2" s="0">
-        <v>14.529999999999999</v>
+        <v>13.69</v>
       </c>
       <c r="E2" s="0">
-        <v>9.3599999999999994</v>
+        <v>9.2100000000000009</v>
       </c>
       <c r="F2" s="0">
-        <v>65.090000000000003</v>
+        <v>63.43</v>
       </c>
       <c r="G2" s="0">
-        <v>60.770000000000003</v>
+        <v>57.539999999999999</v>
       </c>
       <c r="H2" s="0">
-        <v>47.450000000000003</v>
+        <v>47.640000000000001</v>
       </c>
       <c r="I2" s="0">
-        <v>21.48</v>
+        <v>20.260000000000002</v>
       </c>
       <c r="J2" s="0">
-        <v>20.609999999999999</v>
+        <v>20.780000000000001</v>
       </c>
       <c r="K2" s="0">
-        <v>19.149999999999999</v>
+        <v>18.059999999999999</v>
       </c>
       <c r="L2" s="0">
-        <v>59.32</v>
+        <v>59.399999999999999</v>
       </c>
       <c r="M2" s="0">
-        <v>11.73</v>
+        <v>11.07</v>
       </c>
       <c r="N2" s="0">
-        <v>52.450000000000003</v>
+        <v>51.890000000000001</v>
       </c>
       <c r="O2" s="0">
-        <v>5.9299999999999997</v>
+        <v>5.8700000000000001</v>
       </c>
       <c r="P2" s="0">
-        <v>68.390000000000001</v>
+        <v>69.140000000000001</v>
       </c>
       <c r="Q2" s="0">
-        <v>6.79</v>
+        <v>6.8399999999999999</v>
       </c>
       <c r="R2" s="0">
-        <v>20.09</v>
+        <v>19.690000000000001</v>
       </c>
       <c r="S2" s="0">
-        <v>3.04</v>
+        <v>3.1200000000000001</v>
       </c>
       <c r="T2" s="0">
-        <v>29.350000000000001</v>
+        <v>29.210000000000001</v>
       </c>
       <c r="U2" s="0">
-        <v>4.1600000000000001</v>
+        <v>3.9399999999999999</v>
       </c>
       <c r="V2" s="0">
-        <v>27.93</v>
+        <v>27.890000000000001</v>
       </c>
       <c r="W2" s="0">
-        <v>9.1199999999999992</v>
+        <v>8.5999999999999996</v>
       </c>
       <c r="X2" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -4716,73 +4716,73 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>33.109999999999999</v>
+        <v>30.690000000000001</v>
       </c>
       <c r="C3" s="0">
-        <v>14.550000000000001</v>
+        <v>15.710000000000001</v>
       </c>
       <c r="D3" s="0">
-        <v>15.029999999999999</v>
+        <v>15.460000000000001</v>
       </c>
       <c r="E3" s="0">
-        <v>17.34</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="F3" s="0">
-        <v>55.049999999999997</v>
+        <v>58.210000000000001</v>
       </c>
       <c r="G3" s="0">
-        <v>30.609999999999999</v>
+        <v>30.539999999999999</v>
       </c>
       <c r="H3" s="0">
-        <v>77.590000000000003</v>
+        <v>71.319999999999993</v>
       </c>
       <c r="I3" s="0">
-        <v>49.399999999999999</v>
+        <v>50.619999999999997</v>
       </c>
       <c r="J3" s="0">
-        <v>19.489999999999998</v>
+        <v>29.68</v>
       </c>
       <c r="K3" s="0">
-        <v>12.18</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="L3" s="0">
-        <v>34.920000000000002</v>
+        <v>35.130000000000003</v>
       </c>
       <c r="M3" s="0">
-        <v>5.9199999999999999</v>
+        <v>5.6200000000000001</v>
       </c>
       <c r="N3" s="0">
-        <v>82.030000000000001</v>
+        <v>79.010000000000005</v>
       </c>
       <c r="O3" s="0">
-        <v>14.609999999999999</v>
+        <v>16.760000000000002</v>
       </c>
       <c r="P3" s="0">
-        <v>86.890000000000001</v>
+        <v>85.180000000000007</v>
       </c>
       <c r="Q3" s="0">
-        <v>13.31</v>
+        <v>13.66</v>
       </c>
       <c r="R3" s="0">
-        <v>24.780000000000001</v>
+        <v>23.780000000000001</v>
       </c>
       <c r="S3" s="0">
-        <v>4.5300000000000002</v>
+        <v>5.3300000000000001</v>
       </c>
       <c r="T3" s="0">
-        <v>24.48</v>
+        <v>25.73</v>
       </c>
       <c r="U3" s="0">
-        <v>3.6600000000000001</v>
+        <v>5.25</v>
       </c>
       <c r="V3" s="0">
-        <v>25.550000000000001</v>
+        <v>26.41</v>
       </c>
       <c r="W3" s="0">
-        <v>5.5</v>
+        <v>5.8600000000000003</v>
       </c>
       <c r="X3" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -4790,73 +4790,73 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>60.369999999999997</v>
+        <v>58.049999999999997</v>
       </c>
       <c r="C4" s="0">
-        <v>40.719999999999999</v>
+        <v>39.079999999999998</v>
       </c>
       <c r="D4" s="0">
-        <v>18.52</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="E4" s="0">
-        <v>6.4199999999999999</v>
+        <v>6.2000000000000002</v>
       </c>
       <c r="F4" s="0">
-        <v>75.319999999999993</v>
+        <v>74.939999999999998</v>
       </c>
       <c r="G4" s="0">
-        <v>61.740000000000002</v>
+        <v>58.219999999999999</v>
       </c>
       <c r="H4" s="0">
-        <v>41.369999999999997</v>
+        <v>39.899999999999999</v>
       </c>
       <c r="I4" s="0">
-        <v>20.920000000000002</v>
+        <v>20.260000000000002</v>
       </c>
       <c r="J4" s="0">
-        <v>14.81</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="K4" s="0">
-        <v>10.49</v>
+        <v>20.25</v>
       </c>
       <c r="L4" s="0">
-        <v>76.620000000000005</v>
+        <v>75.510000000000005</v>
       </c>
       <c r="M4" s="0">
-        <v>9.3499999999999996</v>
+        <v>9.4800000000000004</v>
       </c>
       <c r="N4" s="0">
-        <v>53.390000000000001</v>
+        <v>52.68</v>
       </c>
       <c r="O4" s="0">
-        <v>6.0300000000000002</v>
+        <v>6.1100000000000003</v>
       </c>
       <c r="P4" s="0">
-        <v>67.590000000000003</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="Q4" s="0">
-        <v>7.4500000000000002</v>
+        <v>7.71</v>
       </c>
       <c r="R4" s="0">
-        <v>17.579999999999998</v>
+        <v>17.550000000000001</v>
       </c>
       <c r="S4" s="0">
-        <v>5.0300000000000002</v>
+        <v>4.75</v>
       </c>
       <c r="T4" s="0">
-        <v>29.670000000000002</v>
+        <v>29.82</v>
       </c>
       <c r="U4" s="0">
-        <v>3.71</v>
+        <v>3.5299999999999998</v>
       </c>
       <c r="V4" s="0">
-        <v>23.77</v>
+        <v>24.629999999999999</v>
       </c>
       <c r="W4" s="0">
-        <v>14.199999999999999</v>
+        <v>13.66</v>
       </c>
       <c r="X4" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -4864,73 +4864,73 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>37.299999999999997</v>
+        <v>36.329999999999998</v>
       </c>
       <c r="C5" s="0">
-        <v>18</v>
+        <v>17.25</v>
       </c>
       <c r="D5" s="0">
-        <v>12.91</v>
+        <v>12.77</v>
       </c>
       <c r="E5" s="0">
-        <v>11.970000000000001</v>
+        <v>11.300000000000001</v>
       </c>
       <c r="F5" s="0">
-        <v>66.390000000000001</v>
+        <v>66.340000000000003</v>
       </c>
       <c r="G5" s="0">
-        <v>28.079999999999998</v>
+        <v>26.48</v>
       </c>
       <c r="H5" s="0">
-        <v>90.939999999999998</v>
+        <v>87.269999999999996</v>
       </c>
       <c r="I5" s="0">
-        <v>50.509999999999998</v>
+        <v>49.009999999999998</v>
       </c>
       <c r="J5" s="0">
-        <v>10.82</v>
+        <v>17.390000000000001</v>
       </c>
       <c r="K5" s="0">
-        <v>4.21</v>
+        <v>21.129999999999999</v>
       </c>
       <c r="L5" s="0">
-        <v>37.710000000000001</v>
+        <v>38.140000000000001</v>
       </c>
       <c r="M5" s="0">
-        <v>4.1500000000000004</v>
+        <v>4.1299999999999999</v>
       </c>
       <c r="N5" s="0">
-        <v>95.739999999999995</v>
+        <v>93.359999999999999</v>
       </c>
       <c r="O5" s="0">
-        <v>13.44</v>
+        <v>14.73</v>
       </c>
       <c r="P5" s="0">
-        <v>95.329999999999998</v>
+        <v>94.939999999999998</v>
       </c>
       <c r="Q5" s="0">
-        <v>11.039999999999999</v>
+        <v>10.48</v>
       </c>
       <c r="R5" s="0">
-        <v>24.719999999999999</v>
+        <v>24.059999999999999</v>
       </c>
       <c r="S5" s="0">
-        <v>3.8999999999999999</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="T5" s="0">
-        <v>24.16</v>
+        <v>24.550000000000001</v>
       </c>
       <c r="U5" s="0">
-        <v>4.8899999999999997</v>
+        <v>4.7800000000000002</v>
       </c>
       <c r="V5" s="0">
-        <v>26.219999999999999</v>
+        <v>26.600000000000001</v>
       </c>
       <c r="W5" s="0">
-        <v>6.6500000000000004</v>
+        <v>6.3799999999999999</v>
       </c>
       <c r="X5" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -4938,73 +4938,73 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>60.869999999999997</v>
+        <v>56.93</v>
       </c>
       <c r="C6" s="0">
-        <v>33.149999999999999</v>
+        <v>33.640000000000001</v>
       </c>
       <c r="D6" s="0">
-        <v>25.309999999999999</v>
+        <v>28.260000000000002</v>
       </c>
       <c r="E6" s="0">
-        <v>18.66</v>
+        <v>19.91</v>
       </c>
       <c r="F6" s="0">
-        <v>81.560000000000002</v>
+        <v>82.900000000000006</v>
       </c>
       <c r="G6" s="0">
-        <v>55.119999999999997</v>
+        <v>52.140000000000001</v>
       </c>
       <c r="H6" s="0">
-        <v>44.57</v>
+        <v>43.880000000000003</v>
       </c>
       <c r="I6" s="0">
-        <v>17.100000000000001</v>
+        <v>16.27</v>
       </c>
       <c r="J6" s="0">
-        <v>15.57</v>
+        <v>18.57</v>
       </c>
       <c r="K6" s="0">
-        <v>9.7799999999999994</v>
+        <v>13.23</v>
       </c>
       <c r="L6" s="0">
-        <v>82.379999999999995</v>
+        <v>81.640000000000001</v>
       </c>
       <c r="M6" s="0">
-        <v>8.9299999999999997</v>
+        <v>8.7400000000000002</v>
       </c>
       <c r="N6" s="0">
-        <v>53.509999999999998</v>
+        <v>53.100000000000001</v>
       </c>
       <c r="O6" s="0">
-        <v>6.0700000000000003</v>
+        <v>5.8700000000000001</v>
       </c>
       <c r="P6" s="0">
-        <v>64.810000000000002</v>
+        <v>66.069999999999993</v>
       </c>
       <c r="Q6" s="0">
-        <v>8.1699999999999999</v>
+        <v>8.6799999999999997</v>
       </c>
       <c r="R6" s="0">
-        <v>18.59</v>
+        <v>18.690000000000001</v>
       </c>
       <c r="S6" s="0">
-        <v>4.5700000000000003</v>
+        <v>4.3200000000000003</v>
       </c>
       <c r="T6" s="0">
-        <v>30.510000000000002</v>
+        <v>30.43</v>
       </c>
       <c r="U6" s="0">
-        <v>4.1399999999999997</v>
+        <v>3.9100000000000001</v>
       </c>
       <c r="V6" s="0">
-        <v>22.039999999999999</v>
+        <v>23.109999999999999</v>
       </c>
       <c r="W6" s="0">
-        <v>11.699999999999999</v>
+        <v>11.539999999999999</v>
       </c>
       <c r="X6" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -5012,73 +5012,73 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>44.780000000000001</v>
+        <v>43.789999999999999</v>
       </c>
       <c r="C7" s="0">
-        <v>21.190000000000001</v>
+        <v>20.219999999999999</v>
       </c>
       <c r="D7" s="0">
-        <v>17.129999999999999</v>
+        <v>16.879999999999999</v>
       </c>
       <c r="E7" s="0">
-        <v>15.25</v>
+        <v>14.4</v>
       </c>
       <c r="F7" s="0">
-        <v>73.230000000000004</v>
+        <v>73.849999999999994</v>
       </c>
       <c r="G7" s="0">
-        <v>22.640000000000001</v>
+        <v>21.43</v>
       </c>
       <c r="H7" s="0">
-        <v>103.11</v>
+        <v>98.730000000000004</v>
       </c>
       <c r="I7" s="0">
-        <v>49.890000000000001</v>
+        <v>49.020000000000003</v>
       </c>
       <c r="J7" s="0">
-        <v>17.100000000000001</v>
+        <v>16.309999999999999</v>
       </c>
       <c r="K7" s="0">
-        <v>12.550000000000001</v>
+        <v>12.09</v>
       </c>
       <c r="L7" s="0">
-        <v>40.899999999999999</v>
+        <v>40.369999999999997</v>
       </c>
       <c r="M7" s="0">
-        <v>7.25</v>
+        <v>7.04</v>
       </c>
       <c r="N7" s="0">
-        <v>102.63</v>
+        <v>101.36</v>
       </c>
       <c r="O7" s="0">
-        <v>10.029999999999999</v>
+        <v>10.27</v>
       </c>
       <c r="P7" s="0">
-        <v>98.980000000000004</v>
+        <v>99.920000000000002</v>
       </c>
       <c r="Q7" s="0">
-        <v>12.18</v>
+        <v>11.859999999999999</v>
       </c>
       <c r="R7" s="0">
-        <v>23.969999999999999</v>
+        <v>24.359999999999999</v>
       </c>
       <c r="S7" s="0">
-        <v>5.2699999999999996</v>
+        <v>5.1200000000000001</v>
       </c>
       <c r="T7" s="0">
-        <v>22.780000000000001</v>
+        <v>22.170000000000002</v>
       </c>
       <c r="U7" s="0">
-        <v>6.0599999999999996</v>
+        <v>6.0300000000000002</v>
       </c>
       <c r="V7" s="0">
-        <v>25</v>
+        <v>24.870000000000001</v>
       </c>
       <c r="W7" s="0">
-        <v>8.9100000000000001</v>
+        <v>8.4100000000000001</v>
       </c>
       <c r="X7" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -5086,73 +5086,73 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>53.859999999999999</v>
+        <v>51.859999999999999</v>
       </c>
       <c r="C8" s="0">
-        <v>40.68</v>
+        <v>38.520000000000003</v>
       </c>
       <c r="D8" s="0">
-        <v>10.390000000000001</v>
+        <v>11.050000000000001</v>
       </c>
       <c r="E8" s="0">
-        <v>6.8499999999999996</v>
+        <v>6.7000000000000002</v>
       </c>
       <c r="F8" s="0">
-        <v>68.359999999999999</v>
+        <v>67.790000000000006</v>
       </c>
       <c r="G8" s="0">
-        <v>61.990000000000002</v>
+        <v>58.009999999999998</v>
       </c>
       <c r="H8" s="0">
-        <v>47.289999999999999</v>
+        <v>45.490000000000002</v>
       </c>
       <c r="I8" s="0">
-        <v>20.23</v>
+        <v>19.68</v>
       </c>
       <c r="J8" s="0">
-        <v>13.449999999999999</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="K8" s="0">
-        <v>14.67</v>
+        <v>22.98</v>
       </c>
       <c r="L8" s="0">
-        <v>65.540000000000006</v>
+        <v>65.230000000000004</v>
       </c>
       <c r="M8" s="0">
-        <v>8.7599999999999998</v>
+        <v>8.3200000000000003</v>
       </c>
       <c r="N8" s="0">
-        <v>52.32</v>
+        <v>51.780000000000001</v>
       </c>
       <c r="O8" s="0">
         <v>5.0700000000000003</v>
       </c>
       <c r="P8" s="0">
-        <v>69.599999999999994</v>
+        <v>70.650000000000006</v>
       </c>
       <c r="Q8" s="0">
-        <v>7.5800000000000001</v>
+        <v>7.8799999999999999</v>
       </c>
       <c r="R8" s="0">
-        <v>17.469999999999999</v>
+        <v>17.34</v>
       </c>
       <c r="S8" s="0">
-        <v>3.1400000000000001</v>
+        <v>2.98</v>
       </c>
       <c r="T8" s="0">
-        <v>31.34</v>
+        <v>32.020000000000003</v>
       </c>
       <c r="U8" s="0">
-        <v>3.3500000000000001</v>
+        <v>3.8199999999999998</v>
       </c>
       <c r="V8" s="0">
-        <v>28.899999999999999</v>
+        <v>29.920000000000002</v>
       </c>
       <c r="W8" s="0">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="X8" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -5160,73 +5160,73 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>30.300000000000001</v>
+        <v>30.219999999999999</v>
       </c>
       <c r="C9" s="0">
-        <v>9.2200000000000006</v>
+        <v>8.6300000000000008</v>
       </c>
       <c r="D9" s="0">
-        <v>13.93</v>
+        <v>13.960000000000001</v>
       </c>
       <c r="E9" s="0">
-        <v>11.94</v>
+        <v>11.17</v>
       </c>
       <c r="F9" s="0">
-        <v>69.719999999999999</v>
+        <v>69.150000000000006</v>
       </c>
       <c r="G9" s="0">
-        <v>22.82</v>
+        <v>21.41</v>
       </c>
       <c r="H9" s="0">
-        <v>77.569999999999993</v>
+        <v>74.700000000000003</v>
       </c>
       <c r="I9" s="0">
-        <v>50.369999999999997</v>
+        <v>47.890000000000001</v>
       </c>
       <c r="J9" s="0">
-        <v>14.779999999999999</v>
+        <v>19.530000000000001</v>
       </c>
       <c r="K9" s="0">
-        <v>9.4100000000000001</v>
+        <v>16.75</v>
       </c>
       <c r="L9" s="0">
-        <v>37.32</v>
+        <v>37.310000000000002</v>
       </c>
       <c r="M9" s="0">
-        <v>5.0499999999999998</v>
+        <v>4.7599999999999998</v>
       </c>
       <c r="N9" s="0">
-        <v>83.700000000000003</v>
+        <v>82.280000000000001</v>
       </c>
       <c r="O9" s="0">
-        <v>12.06</v>
+        <v>12.220000000000001</v>
       </c>
       <c r="P9" s="0">
-        <v>92.129999999999995</v>
+        <v>92.170000000000002</v>
       </c>
       <c r="Q9" s="0">
-        <v>13.24</v>
+        <v>12.48</v>
       </c>
       <c r="R9" s="0">
-        <v>24.829999999999998</v>
+        <v>24.510000000000002</v>
       </c>
       <c r="S9" s="0">
-        <v>3.71</v>
+        <v>3.6499999999999999</v>
       </c>
       <c r="T9" s="0">
-        <v>25.170000000000002</v>
+        <v>25.350000000000001</v>
       </c>
       <c r="U9" s="0">
-        <v>3.2000000000000002</v>
+        <v>3.0699999999999998</v>
       </c>
       <c r="V9" s="0">
-        <v>26.550000000000001</v>
+        <v>26.879999999999999</v>
       </c>
       <c r="W9" s="0">
-        <v>6.71</v>
+        <v>6.4100000000000001</v>
       </c>
       <c r="X9" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -5234,73 +5234,73 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>62.810000000000002</v>
+        <v>61.340000000000003</v>
       </c>
       <c r="C10" s="0">
-        <v>37.920000000000002</v>
+        <v>36.049999999999997</v>
       </c>
       <c r="D10" s="0">
-        <v>18.899999999999999</v>
+        <v>18.539999999999999</v>
       </c>
       <c r="E10" s="0">
-        <v>12.640000000000001</v>
+        <v>11.970000000000001</v>
       </c>
       <c r="F10" s="0">
-        <v>79.329999999999998</v>
+        <v>77.370000000000005</v>
       </c>
       <c r="G10" s="0">
-        <v>51.039999999999999</v>
+        <v>48.520000000000003</v>
       </c>
       <c r="H10" s="0">
-        <v>40.649999999999999</v>
+        <v>40.240000000000002</v>
       </c>
       <c r="I10" s="0">
-        <v>21.620000000000001</v>
+        <v>20.43</v>
       </c>
       <c r="J10" s="0">
-        <v>15.880000000000001</v>
+        <v>15.25</v>
       </c>
       <c r="K10" s="0">
-        <v>10.630000000000001</v>
+        <v>10.220000000000001</v>
       </c>
       <c r="L10" s="0">
-        <v>79.010000000000005</v>
+        <v>78.290000000000006</v>
       </c>
       <c r="M10" s="0">
-        <v>8.6400000000000006</v>
+        <v>8.4600000000000009</v>
       </c>
       <c r="N10" s="0">
-        <v>54.060000000000002</v>
+        <v>53.390000000000001</v>
       </c>
       <c r="O10" s="0">
-        <v>5.9400000000000004</v>
+        <v>5.9900000000000002</v>
       </c>
       <c r="P10" s="0">
-        <v>67.560000000000002</v>
+        <v>68.150000000000006</v>
       </c>
       <c r="Q10" s="0">
-        <v>6.9900000000000002</v>
+        <v>6.8499999999999996</v>
       </c>
       <c r="R10" s="0">
-        <v>16.879999999999999</v>
+        <v>16.739999999999998</v>
       </c>
       <c r="S10" s="0">
-        <v>5.2199999999999998</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="T10" s="0">
-        <v>31.93</v>
+        <v>31.879999999999999</v>
       </c>
       <c r="U10" s="0">
-        <v>3.8799999999999999</v>
+        <v>3.6600000000000001</v>
       </c>
       <c r="V10" s="0">
-        <v>24.210000000000001</v>
+        <v>24.969999999999999</v>
       </c>
       <c r="W10" s="0">
-        <v>14.390000000000001</v>
+        <v>13.77</v>
       </c>
       <c r="X10" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -5308,73 +5308,73 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>35.960000000000001</v>
+        <v>34.32</v>
       </c>
       <c r="C11" s="0">
-        <v>19.219999999999999</v>
+        <v>18.84</v>
       </c>
       <c r="D11" s="0">
-        <v>17.370000000000001</v>
+        <v>16.84</v>
       </c>
       <c r="E11" s="0">
-        <v>14.949999999999999</v>
+        <v>14.19</v>
       </c>
       <c r="F11" s="0">
-        <v>70</v>
+        <v>69.719999999999999</v>
       </c>
       <c r="G11" s="0">
-        <v>26.210000000000001</v>
+        <v>24.719999999999999</v>
       </c>
       <c r="H11" s="0">
-        <v>95.879999999999995</v>
+        <v>90.939999999999998</v>
       </c>
       <c r="I11" s="0">
-        <v>50.350000000000001</v>
+        <v>49.969999999999999</v>
       </c>
       <c r="J11" s="0">
-        <v>12.720000000000001</v>
+        <v>13.07</v>
       </c>
       <c r="K11" s="0">
-        <v>8.1799999999999997</v>
+        <v>7.79</v>
       </c>
       <c r="L11" s="0">
-        <v>38.280000000000001</v>
+        <v>38.32</v>
       </c>
       <c r="M11" s="0">
-        <v>6.0999999999999996</v>
+        <v>5.75</v>
       </c>
       <c r="N11" s="0">
-        <v>96.329999999999998</v>
+        <v>93.939999999999998</v>
       </c>
       <c r="O11" s="0">
-        <v>10.83</v>
+        <v>12.69</v>
       </c>
       <c r="P11" s="0">
-        <v>97.620000000000005</v>
+        <v>98.420000000000002</v>
       </c>
       <c r="Q11" s="0">
-        <v>12.369999999999999</v>
+        <v>11.93</v>
       </c>
       <c r="R11" s="0">
-        <v>25.530000000000001</v>
+        <v>24.760000000000002</v>
       </c>
       <c r="S11" s="0">
-        <v>5.2599999999999998</v>
+        <v>5.5099999999999998</v>
       </c>
       <c r="T11" s="0">
-        <v>22.050000000000001</v>
+        <v>23.440000000000001</v>
       </c>
       <c r="U11" s="0">
-        <v>6.3200000000000003</v>
+        <v>7.4100000000000001</v>
       </c>
       <c r="V11" s="0">
-        <v>24.149999999999999</v>
+        <v>25.16</v>
       </c>
       <c r="W11" s="0">
-        <v>6.4699999999999998</v>
+        <v>6.8899999999999997</v>
       </c>
       <c r="X11" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -5382,73 +5382,73 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>56.439999999999998</v>
+        <v>54.490000000000002</v>
       </c>
       <c r="C12" s="0">
-        <v>43.009999999999998</v>
+        <v>40.659999999999997</v>
       </c>
       <c r="D12" s="0">
-        <v>22.530000000000001</v>
+        <v>25.280000000000001</v>
       </c>
       <c r="E12" s="0">
-        <v>15.5</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="F12" s="0">
-        <v>81.150000000000006</v>
+        <v>82.5</v>
       </c>
       <c r="G12" s="0">
-        <v>58.399999999999999</v>
+        <v>54.780000000000001</v>
       </c>
       <c r="H12" s="0">
-        <v>47.149999999999999</v>
+        <v>45.859999999999999</v>
       </c>
       <c r="I12" s="0">
-        <v>18.969999999999999</v>
+        <v>18.16</v>
       </c>
       <c r="J12" s="0">
-        <v>16.640000000000001</v>
+        <v>18.59</v>
       </c>
       <c r="K12" s="0">
-        <v>13.24</v>
+        <v>13.699999999999999</v>
       </c>
       <c r="L12" s="0">
-        <v>85.780000000000001</v>
+        <v>85.439999999999998</v>
       </c>
       <c r="M12" s="0">
-        <v>7.4699999999999998</v>
+        <v>7.1299999999999999</v>
       </c>
       <c r="N12" s="0">
-        <v>54.219999999999999</v>
+        <v>53.450000000000003</v>
       </c>
       <c r="O12" s="0">
-        <v>6.2300000000000004</v>
+        <v>6.3499999999999996</v>
       </c>
       <c r="P12" s="0">
-        <v>67.700000000000003</v>
+        <v>68.680000000000007</v>
       </c>
       <c r="Q12" s="0">
-        <v>7.3300000000000001</v>
+        <v>7.5800000000000001</v>
       </c>
       <c r="R12" s="0">
-        <v>18.18</v>
+        <v>17.969999999999999</v>
       </c>
       <c r="S12" s="0">
-        <v>3.71</v>
+        <v>3.5600000000000001</v>
       </c>
       <c r="T12" s="0">
-        <v>31.010000000000002</v>
+        <v>31.469999999999999</v>
       </c>
       <c r="U12" s="0">
-        <v>5.8300000000000001</v>
+        <v>5.6799999999999997</v>
       </c>
       <c r="V12" s="0">
-        <v>21.460000000000001</v>
+        <v>22.57</v>
       </c>
       <c r="W12" s="0">
-        <v>13.41</v>
+        <v>13.119999999999999</v>
       </c>
       <c r="X12" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -5456,73 +5456,73 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>44.409999999999997</v>
+        <v>43.049999999999997</v>
       </c>
       <c r="C13" s="0">
-        <v>28</v>
+        <v>26.510000000000002</v>
       </c>
       <c r="D13" s="0">
-        <v>21.079999999999998</v>
+        <v>19.84</v>
       </c>
       <c r="E13" s="0">
-        <v>20.600000000000001</v>
+        <v>19.629999999999999</v>
       </c>
       <c r="F13" s="0">
-        <v>79.700000000000003</v>
+        <v>78.760000000000005</v>
       </c>
       <c r="G13" s="0">
-        <v>22.870000000000001</v>
+        <v>21.579999999999998</v>
       </c>
       <c r="H13" s="0">
-        <v>91.239999999999995</v>
+        <v>86.700000000000003</v>
       </c>
       <c r="I13" s="0">
-        <v>50.659999999999997</v>
+        <v>49.310000000000002</v>
       </c>
       <c r="J13" s="0">
-        <v>12.109999999999999</v>
+        <v>12.84</v>
       </c>
       <c r="K13" s="0">
-        <v>6.2300000000000004</v>
+        <v>6.2199999999999998</v>
       </c>
       <c r="L13" s="0">
-        <v>40.539999999999999</v>
+        <v>41.030000000000001</v>
       </c>
       <c r="M13" s="0">
-        <v>8.2300000000000004</v>
+        <v>7.9100000000000001</v>
       </c>
       <c r="N13" s="0">
-        <v>108.14</v>
+        <v>105.63</v>
       </c>
       <c r="O13" s="0">
-        <v>11.779999999999999</v>
+        <v>13.65</v>
       </c>
       <c r="P13" s="0">
-        <v>102.7</v>
+        <v>103.11</v>
       </c>
       <c r="Q13" s="0">
-        <v>10.1</v>
+        <v>9.6099999999999994</v>
       </c>
       <c r="R13" s="0">
-        <v>25.960000000000001</v>
+        <v>24.949999999999999</v>
       </c>
       <c r="S13" s="0">
-        <v>3.2400000000000002</v>
+        <v>4.4100000000000001</v>
       </c>
       <c r="T13" s="0">
-        <v>24.239999999999998</v>
+        <v>25.149999999999999</v>
       </c>
       <c r="U13" s="0">
-        <v>3.4900000000000002</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="V13" s="0">
-        <v>25.850000000000001</v>
+        <v>26.75</v>
       </c>
       <c r="W13" s="0">
-        <v>8.1899999999999995</v>
+        <v>8.2200000000000006</v>
       </c>
       <c r="X13" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -5530,73 +5530,73 @@
         <v>24</v>
       </c>
       <c r="B14" s="0">
-        <v>15.76</v>
+        <v>15.300000000000001</v>
       </c>
       <c r="C14" s="0">
+        <v>3.73</v>
+      </c>
+      <c r="D14" s="0">
+        <v>9.3300000000000001</v>
+      </c>
+      <c r="E14" s="0">
+        <v>4.2599999999999998</v>
+      </c>
+      <c r="F14" s="0">
+        <v>31.370000000000001</v>
+      </c>
+      <c r="G14" s="0">
+        <v>11.92</v>
+      </c>
+      <c r="H14" s="0">
+        <v>44.710000000000001</v>
+      </c>
+      <c r="I14" s="0">
+        <v>20.600000000000001</v>
+      </c>
+      <c r="J14" s="0">
+        <v>7.8399999999999999</v>
+      </c>
+      <c r="K14" s="0">
+        <v>3.0099999999999998</v>
+      </c>
+      <c r="L14" s="0">
+        <v>26.949999999999999</v>
+      </c>
+      <c r="M14" s="0">
+        <v>2.9500000000000002</v>
+      </c>
+      <c r="N14" s="0">
+        <v>47.619999999999997</v>
+      </c>
+      <c r="O14" s="0">
+        <v>4.75</v>
+      </c>
+      <c r="P14" s="0">
+        <v>67.709999999999994</v>
+      </c>
+      <c r="Q14" s="0">
+        <v>5.2800000000000002</v>
+      </c>
+      <c r="R14" s="0">
+        <v>17.649999999999999</v>
+      </c>
+      <c r="S14" s="0">
         <v>3.6400000000000001</v>
       </c>
-      <c r="D14" s="0">
-        <v>9.0700000000000003</v>
-      </c>
-      <c r="E14" s="0">
-        <v>4.4299999999999997</v>
-      </c>
-      <c r="F14" s="0">
-        <v>29.620000000000001</v>
-      </c>
-      <c r="G14" s="0">
-        <v>11.18</v>
-      </c>
-      <c r="H14" s="0">
-        <v>46.109999999999999</v>
-      </c>
-      <c r="I14" s="0">
-        <v>21.329999999999998</v>
-      </c>
-      <c r="J14" s="0">
-        <v>8</v>
-      </c>
-      <c r="K14" s="0">
-        <v>3.1499999999999999</v>
-      </c>
-      <c r="L14" s="0">
-        <v>26.600000000000001</v>
-      </c>
-      <c r="M14" s="0">
-        <v>2.9100000000000001</v>
-      </c>
-      <c r="N14" s="0">
-        <v>48.130000000000003</v>
-      </c>
-      <c r="O14" s="0">
-        <v>4.7400000000000002</v>
-      </c>
-      <c r="P14" s="0">
-        <v>67.390000000000001</v>
-      </c>
-      <c r="Q14" s="0">
-        <v>5.4900000000000002</v>
-      </c>
-      <c r="R14" s="0">
-        <v>18.030000000000001</v>
-      </c>
-      <c r="S14" s="0">
-        <v>3.6499999999999999</v>
-      </c>
       <c r="T14" s="0">
-        <v>26.460000000000001</v>
+        <v>26.629999999999999</v>
       </c>
       <c r="U14" s="0">
-        <v>2.4700000000000002</v>
+        <v>2.3900000000000001</v>
       </c>
       <c r="V14" s="0">
-        <v>23.82</v>
+        <v>24</v>
       </c>
       <c r="W14" s="0">
-        <v>4.2999999999999998</v>
+        <v>4.0899999999999999</v>
       </c>
       <c r="X14" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
